--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208D29E3-E64D-4EF2-9FBE-72A33287BA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF28F3D-F9BF-4A23-89E3-DA26E2C6B297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="172">
   <si>
     <t>Fecha</t>
   </si>
@@ -267,9 +267,6 @@
     <t>Effetá</t>
   </si>
   <si>
-    <t>Pachuca Brilla</t>
-  </si>
-  <si>
     <t>Plaza Juárez</t>
   </si>
   <si>
@@ -297,21 +294,12 @@
     <t>Temas varios</t>
   </si>
   <si>
-    <t>Incidencia Delictiva</t>
-  </si>
-  <si>
-    <t>SICT</t>
-  </si>
-  <si>
     <t>Afectaciones Por Lluvias</t>
   </si>
   <si>
     <t>Fotonota</t>
   </si>
   <si>
-    <t>Migración</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -321,295 +309,250 @@
     <t>Cintillo</t>
   </si>
   <si>
-    <t>Huracán Priscilla</t>
-  </si>
-  <si>
-    <t>Inseguridad</t>
-  </si>
-  <si>
-    <t>Publicidad gubernamental</t>
-  </si>
-  <si>
-    <t>Editorial</t>
-  </si>
-  <si>
-    <t>Plantean obras millonarias para reconstrucción, tren, hospitales...</t>
-  </si>
-  <si>
-    <t>Presupuesto De Egresos</t>
-  </si>
-  <si>
-    <t>Improvisan puente en Tianguistengo</t>
-  </si>
-  <si>
-    <t>Va renovación a Museo del Ferrocarril</t>
-  </si>
-  <si>
-    <t>Rehabilitación de museo</t>
-  </si>
-  <si>
-    <t>Logra adopción luego de 3 años de lucha</t>
-  </si>
-  <si>
-    <t>Adopción De Menores</t>
-  </si>
-  <si>
-    <t>Se abre socavón en el bulevar Colosio</t>
-  </si>
-  <si>
     <t>Sipdus</t>
   </si>
   <si>
-    <t>Socavón</t>
-  </si>
-  <si>
-    <t>Tira TEPJF demanda contra contralor de Tribunal estatal</t>
-  </si>
-  <si>
-    <t>Órgano Interno de Control</t>
-  </si>
-  <si>
-    <t>Exhortan a fijar y verificar tarifa de taxis</t>
-  </si>
-  <si>
-    <t>GLPVEM</t>
-  </si>
-  <si>
-    <t>Tarifario de taxis</t>
-  </si>
-  <si>
-    <t>Desecha TEPJF demanda del magistrado Leodegario Hernández</t>
-  </si>
-  <si>
-    <t>Simplemente no corresponde lo que cobran los taxistas en Pachuca con lo poco que se gana… y encima preparan incrementar el banderazo a 55 pesos, ahí sí no…</t>
-  </si>
-  <si>
-    <t>Presentan competencias y exhibiciones deportivas</t>
-  </si>
-  <si>
-    <t>OEEH</t>
-  </si>
-  <si>
-    <t>Feria Pachuca</t>
-  </si>
-  <si>
-    <t>Familias reciben con brazos abiertos a siete bebés mediante “Adopción un Puente de Amor”</t>
-  </si>
-  <si>
-    <t>Realizarán estudio técnico para acabar con congestionamientos viales en Pachuca</t>
-  </si>
-  <si>
-    <t>GLPAN</t>
-  </si>
-  <si>
-    <t>Carril confinado</t>
-  </si>
-  <si>
-    <t>Avanzan investigaciones contra exalcalde Sergio Baños “Aquí no se protege a nadie”: PGJEH</t>
-  </si>
-  <si>
-    <t>Denuncia Exalcalde</t>
-  </si>
-  <si>
-    <t>Cierran juicio relacionado con contralor interno y presidencia del Tribunal Estatal Electoral</t>
-  </si>
-  <si>
-    <t>Propone PEF bolsa de $3.7 mil millones para proyectos locales</t>
-  </si>
-  <si>
-    <t>Feria San Francisco Pachuca tendrá amplia cartelera deportiva</t>
-  </si>
-  <si>
-    <t>TEEH, sin facultad para designar a contralor interno</t>
-  </si>
-  <si>
-    <t>Señala presidenta conducta “extraña” de Pedro Haces</t>
-  </si>
-  <si>
-    <t>Cuarta Transformación</t>
-  </si>
-  <si>
-    <t>"A una parte de esta generación de morenistas todavía les escurre el pasado priista: creen que la política social es repartir migajas frente a cámara (…) La izquierda que transforma no es la que da limosna y la exhibe, es la que hace innecesaria la limosna”.</t>
-  </si>
-  <si>
-    <t>Disminuyen delitos que afectan a empresarios</t>
-  </si>
-  <si>
-    <t>Caso Mirna N no ha prescrito, afirma PGJEH</t>
-  </si>
-  <si>
-    <t>Carpeta De Investigación</t>
-  </si>
-  <si>
-    <t>Panteones podrían ser patrimonio cultural</t>
-  </si>
-  <si>
-    <t>INAH</t>
-  </si>
-  <si>
-    <t>Patrimonio cultural</t>
-  </si>
-  <si>
-    <t>Piden revisar legislación en área familiar y penal</t>
-  </si>
-  <si>
-    <t>Exigen legislación</t>
-  </si>
-  <si>
-    <t>Reduce el número de migrantes en Atitalaquia</t>
-  </si>
-  <si>
-    <t>Recortan gasto para combatir Ia corrupción</t>
-  </si>
-  <si>
-    <t>Hidalgo dejará el rezago... "hoy es un estado protagonista": JMS</t>
-  </si>
-  <si>
-    <t>Resuelven problema matemático</t>
-  </si>
-  <si>
-    <t>NFL. Comienza temporada a ritmo de grunge</t>
-  </si>
-  <si>
-    <t>Crimen y austeridad son los retos clave del proceso electoral que está en curso</t>
-  </si>
-  <si>
-    <t>Criterio humano. Piden Femsa y Bimbo privilegiarlo frente a la IA</t>
-  </si>
-  <si>
-    <t>Inteligencia Artificial</t>
-  </si>
-  <si>
-    <t>Desecha TEPJF impugnación de Leodegario por nombramiento</t>
-  </si>
-  <si>
-    <t>Actividad industrial. En mayo, según el Inegi, creció 19.3%</t>
-  </si>
-  <si>
-    <t>Índice De Actividad Industrial</t>
-  </si>
-  <si>
-    <t>Expansión de negocios. Casi 7 de cada 10 empresas están interesadas en crecer.</t>
-  </si>
-  <si>
-    <t>Crecimiento Económico</t>
-  </si>
-  <si>
-    <t>Inspección laboral. Chiapas adopta modelo desarrollado en el estado.</t>
-  </si>
-  <si>
-    <t>Inspección laboral</t>
-  </si>
-  <si>
-    <t>Golean en su debut en la Champions</t>
-  </si>
-  <si>
-    <t>Cambia de piel</t>
-  </si>
-  <si>
-    <t>Avanza un 75% la transición de la Procu a Fiscalía: Hasbun</t>
-  </si>
-  <si>
-    <t>Transición a Fiscalía</t>
-  </si>
-  <si>
-    <t>Tras obras, fue reabierta para la circulación Avenida Madero</t>
-  </si>
-  <si>
     <t>Rehabilitación Vial</t>
   </si>
   <si>
-    <t>Inicia Congreso sesiones con un par de protestas</t>
-  </si>
-  <si>
-    <t>Siete niñas y niños con nueva familia</t>
-  </si>
-  <si>
-    <t>La Semot ha iniciado 67 procedimientos contra el transporte público</t>
-  </si>
-  <si>
-    <t>STCH</t>
-  </si>
-  <si>
-    <t>Supervisión de Transporte</t>
-  </si>
-  <si>
-    <t>Cierran temporalmente carretera Real del Monte-Huasca por daños</t>
-  </si>
-  <si>
-    <t>Con inversión de 37 MDP, Yocelyn Tovar arranca rehabilitación del Libramiento previo a su 2º informe de gobierno</t>
-  </si>
-  <si>
-    <t>El día que la espera terminó: seis niñas y niños comienzan una nueva historia junto a sus familias</t>
-  </si>
-  <si>
-    <t>Con cámaras y drones, policías de Pachuca detienen a presunto integrante de banda dedicada al robo de vehículos</t>
-  </si>
-  <si>
-    <t>Policía municipal</t>
-  </si>
-  <si>
-    <t>Combate a la delincuencia</t>
-  </si>
-  <si>
-    <t>A dos años de gobierno de Jorge Reyes, Pachuca fortalece el control y la transparencia en sus pagos</t>
-  </si>
-  <si>
-    <t>Tlahuelilpan conoce resultados de la administración de Lety Reyes en su 2° informe</t>
-  </si>
-  <si>
-    <t>Socavón en bulevar Colosio provoca cierre parcial y caos vial</t>
-  </si>
-  <si>
-    <t>Said Vargas se reunió con integrantes del CT 48 de Atotonilco el Grande</t>
-  </si>
-  <si>
-    <t>Aún puedes ser un ganador $500 mil. Sorteo San Judas</t>
-  </si>
-  <si>
-    <t>Presentan las actividades deportivas que tendrá la Feria Pachuca 2026</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón encabeza jornada educativa en Ixmiquilpan</t>
-  </si>
-  <si>
-    <t>Semot da seguimiento a acciones para fortalecer la movilidad metropolitana</t>
-  </si>
-  <si>
-    <t>Adopción, un Puente de Amor lleva a seis niños a sus familias</t>
-  </si>
-  <si>
     <t>34,279 luminarias modernizadas</t>
   </si>
   <si>
-    <t>Hidalgo es potencia en marcha. El Polo de Desarrollo Económico Reserva Zapotlán.</t>
-  </si>
-  <si>
-    <t>Jorge Reyes. Dos años al frente de Pachuca</t>
-  </si>
-  <si>
-    <t>¿Adiós al carril confinado? Congreso pide revisar esquema del Tuzobús en Pachuca</t>
-  </si>
-  <si>
-    <t>“En Hidalgo no se protege a nadie”</t>
-  </si>
-  <si>
-    <t>Sabemos que no le harán nada, pero queda exhibido de pies a cabeza: ¡corrupto!</t>
-  </si>
-  <si>
-    <t>Exalcalde</t>
-  </si>
-  <si>
-    <t>Irregularidades exalcalde</t>
-  </si>
-  <si>
-    <t>Empresarios blancos del delito</t>
-  </si>
-  <si>
-    <t>La pesada herencia de muchos alcaldes</t>
-  </si>
-  <si>
-    <t>Mal desempeño de alcaldes</t>
+    <t>Pirotécnicos señalan pérdidas en ventas</t>
+  </si>
+  <si>
+    <t>Pirotecnia</t>
+  </si>
+  <si>
+    <t>Concluye FUL, Estados Unidos próximo invitado</t>
+  </si>
+  <si>
+    <t>Feria Del Libro</t>
+  </si>
+  <si>
+    <t>Sheinbaum anuncia 13 nuevas escuelas</t>
+  </si>
+  <si>
+    <t>Visita Sheinbaum</t>
+  </si>
+  <si>
+    <t>El PRI está vivo y listo para las elecciones 2027</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>Elecciones</t>
+  </si>
+  <si>
+    <t>Serán 5 mil elementos en operativo patrio</t>
+  </si>
+  <si>
+    <t>Fiestas Patrias</t>
+  </si>
+  <si>
+    <t>Reconoce Sheinbaum labor de Menchaca por los hidalguenses</t>
+  </si>
+  <si>
+    <t>Despliegan a 5 mil policías para El Grito</t>
+  </si>
+  <si>
+    <t>Congreso discute hoy la reforma electoral</t>
+  </si>
+  <si>
+    <t>Reforma Electoral</t>
+  </si>
+  <si>
+    <t>Lluivas arrasan puestos den dos tianguis de Tizayuca</t>
+  </si>
+  <si>
+    <t>Rondón aún tiene cuerda</t>
+  </si>
+  <si>
+    <t>Guadalajara, nuevo líder</t>
+  </si>
+  <si>
+    <t>Incrementan intentos de suicidio y depresión</t>
+  </si>
+  <si>
+    <t>Suicidio</t>
+  </si>
+  <si>
+    <t>Alito asegura que en Hidalgo Morena se está hundiendo: es el Morenatanic</t>
+  </si>
+  <si>
+    <t>Evento partidista</t>
+  </si>
+  <si>
+    <t>Sheinbaum rinde informe sobre los avances en varios proyectos</t>
+  </si>
+  <si>
+    <t>Planea Cenhies ampliar oferta académica</t>
+  </si>
+  <si>
+    <t>Oferta académica</t>
+  </si>
+  <si>
+    <t>Vigilarán las fiestas patrias 5 mil policías</t>
+  </si>
+  <si>
+    <t>Destaca Sheinbaum para Hidalgo apoyos, trenes, inversión</t>
+  </si>
+  <si>
+    <t>Reitera el gobernador su apoyo a proyectos federales</t>
+  </si>
+  <si>
+    <t>La IP ve alta incidencia en el robo al transporte</t>
+  </si>
+  <si>
+    <t>Inseguridad Carretera</t>
+  </si>
+  <si>
+    <t>Prevén adelanto de fechas para el registro de candidaturas</t>
+  </si>
+  <si>
+    <t>Pendientes por resolver 50 carpetas por delitos electorales</t>
+  </si>
+  <si>
+    <t>Delitos Electorales</t>
+  </si>
+  <si>
+    <t>Con asistencia histórica cierra feria del libro</t>
+  </si>
+  <si>
+    <t>CJNG y Chapiza extienden lavado a diez sectores de la economía</t>
+  </si>
+  <si>
+    <t>Crimen Organizado</t>
+  </si>
+  <si>
+    <t>Stellantis busca armara 500 mil autos el próximo año</t>
+  </si>
+  <si>
+    <t>Disminuye la práctica de la charrería en la entidad</t>
+  </si>
+  <si>
+    <t>Sheinbaum subraya inversiones para la entidad en Informe</t>
+  </si>
+  <si>
+    <t>Como parte de su gira por los 32 estados del país para presentar su segundo Informe de Gobierno, la presidenta de la República,  Claudia Sheinbaum Pardo, se presentó en las instalaciones de la Feria de Pachuca. La mandataria informó que, hasta el momento, más  de 330 mil personas en todo el país fueron impactadas con la rendición de cuentas regionales.</t>
+  </si>
+  <si>
+    <t>Hallan dos cuerpos junto al Tren Maya</t>
+  </si>
+  <si>
+    <t>FGR</t>
+  </si>
+  <si>
+    <t>Ejecuciones</t>
+  </si>
+  <si>
+    <t>La movilidad se ha vuelto insostenible en Pachuca. La ciudadanía está  colapsada en diversas avenidas y colonias, situación que se complica  aún más con las lluvias. Es una queja constante que, al parecer, solo a las  autoridades no les importa”.</t>
+  </si>
+  <si>
+    <t>Movilidad urbana</t>
+  </si>
+  <si>
+    <t>Sheinbaum entrega a hidalguenses balance de obras, apoyos y megaproyectos</t>
+  </si>
+  <si>
+    <t>Conmemoran el 179 aniversario de la Gesta Heroica de Chapultepec</t>
+  </si>
+  <si>
+    <t>Desplegarán más de 5 mil elementos de seguridad por fiestas patrias en Hidalgo</t>
+  </si>
+  <si>
+    <t>Llegarán 2 mil libros de la Fundación Elena Poniatowska a escuelas de la entidad</t>
+  </si>
+  <si>
+    <t>Donación de libros</t>
+  </si>
+  <si>
+    <t>Reciben programas del Bienestar 1.1 millones de hidalguenses</t>
+  </si>
+  <si>
+    <t>El PRI es inmortal""</t>
+  </si>
+  <si>
+    <t>Alianzas Electorales</t>
+  </si>
+  <si>
+    <t>Cerrarán lateral del bulevar Felipe Ángeles durante 45 días</t>
+  </si>
+  <si>
+    <t>Jorge Reyes anuncia rehabilitación de cuatro parques emblemáticos</t>
+  </si>
+  <si>
+    <t>alcalde</t>
+  </si>
+  <si>
+    <t>Rehabilitación de espacios públicos</t>
+  </si>
+  <si>
+    <t>Congreso prevé aprobar reforma electoral a un día del plazo límite</t>
+  </si>
+  <si>
+    <t>"En Hidalgo tienen un ejército de mujeres y hombres con gran disposición", afirma Menchaca a Sheinbaum</t>
+  </si>
+  <si>
+    <t>Anuncia Semot plan operativo para las fiestas patrias 2026</t>
+  </si>
+  <si>
+    <t>Refuerzan seguridad y llaman a revisar balcones para el Grito en Hidalgo</t>
+  </si>
+  <si>
+    <t>En 2° informe, Tere Olivares destaca saneamiento financiero, obra pública y atención social</t>
+  </si>
+  <si>
+    <t>Parques, Protección Civil, bienestar animal y atención social, entre los nuevos proyectos anunciados por Jorge Reyes para Pachuca</t>
+  </si>
+  <si>
+    <t>Con manifestación y sin evento público, Tania Valdez presenta 2° informe</t>
+  </si>
+  <si>
+    <t>El arte de soiñar llega a Atitalaquia con la exposición ""Sueno""</t>
+  </si>
+  <si>
+    <t>Exposición Artística</t>
+  </si>
+  <si>
+    <t>José José Sinfónico</t>
+  </si>
+  <si>
+    <t>Cecultah</t>
+  </si>
+  <si>
+    <t>Concierto Sinfónico</t>
+  </si>
+  <si>
+    <t>Sheinbaum destaca Tren CDMX-Pachuca para próximo año; Menchaca refrenda apoyo de Hidalgo</t>
+  </si>
+  <si>
+    <t>Jorge Reyes anunció nuevos proyectos para Pachuca</t>
+  </si>
+  <si>
+    <t>Recibe SEPH donación de 2 mil libros de la Fundación Elena Poniatowska</t>
+  </si>
+  <si>
+    <t>Estudiantes de El Mexe se manifiestan; Segob los atiende</t>
+  </si>
+  <si>
+    <t>Gobernación</t>
+  </si>
+  <si>
+    <t>El Mexe</t>
+  </si>
+  <si>
+    <t>Continúan obras en lateral de bulevar Felipe Ángeles</t>
+  </si>
+  <si>
+    <t>Al grito de Hidalgo</t>
+  </si>
+  <si>
+    <t>Grito De Independencia</t>
+  </si>
+  <si>
+    <t>Programas sociales  benefician a más de un millón de hidalguenses: Sheinbaum</t>
   </si>
 </sst>
 </file>
@@ -742,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -757,7 +700,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -857,8 +799,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J63" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J63" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J55" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J55" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1227,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1274,34 +1216,34 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1309,33 +1251,33 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
-        <v>46275</v>
+      <c r="A3" s="11">
+        <v>46279</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>100</v>
+        <v>67</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="G3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1343,626 +1285,626 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
-        <v>46275</v>
+      <c r="A4" s="11">
+        <v>46279</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>101</v>
+        <v>67</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
-        <v>46275</v>
+      <c r="A5" s="11">
+        <v>46279</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" t="s">
-        <v>103</v>
+        <v>67</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J5" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J5" t="str">
+      <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G6" t="s">
-        <v>107</v>
-      </c>
-      <c r="H6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J6" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
-        <v>46275</v>
+    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>46279</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
-      <c r="C7" t="s">
-        <v>108</v>
+      <c r="C7" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J7" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="E7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J7" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
-        <v>46275</v>
+      <c r="A9" s="11">
+        <v>46279</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" t="s">
-        <v>113</v>
+        <v>71</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J9" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J10" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J9" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J11" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J12" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
         <v>112</v>
       </c>
-      <c r="H10" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" t="str">
+      <c r="H13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J10" t="str">
+      <c r="J13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" t="s">
-        <v>116</v>
-      </c>
-      <c r="G11" t="s">
-        <v>117</v>
-      </c>
-      <c r="H11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J11" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" t="s">
-        <v>104</v>
-      </c>
-      <c r="H12" t="s">
-        <v>74</v>
-      </c>
-      <c r="I12" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J12" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" t="s">
-        <v>120</v>
-      </c>
-      <c r="G13" t="s">
-        <v>121</v>
-      </c>
-      <c r="H13" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J13" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
-        <v>46275</v>
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
+        <v>46279</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" t="s">
-        <v>122</v>
+        <v>73</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="F14" t="s">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="G14" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
       </c>
       <c r="I14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J14" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J15" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
+        <v>117</v>
+      </c>
+      <c r="H16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J16" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J14" t="str">
+      <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" t="s">
-        <v>109</v>
-      </c>
-      <c r="H15" t="s">
-        <v>11</v>
-      </c>
-      <c r="I15" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J15" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" t="s">
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" t="s">
         <v>13</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E18" t="s">
         <v>14</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F18" t="s">
         <v>14</v>
       </c>
-      <c r="G16" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" t="s">
-        <v>11</v>
-      </c>
-      <c r="I16" t="str">
+      <c r="G18" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Presidencia de la República</v>
       </c>
-      <c r="J16" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" t="s">
-        <v>126</v>
-      </c>
-      <c r="D17" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" t="s">
-        <v>116</v>
-      </c>
-      <c r="G17" t="s">
-        <v>117</v>
-      </c>
-      <c r="H17" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J17" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>127</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18" t="s">
-        <v>109</v>
-      </c>
-      <c r="H18" t="s">
-        <v>70</v>
-      </c>
-      <c r="I18" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="12">
-        <v>46275</v>
+      <c r="A19" s="11">
+        <v>46279</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>128</v>
+        <v>79</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G19" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="12">
-        <v>46275</v>
+      <c r="A20" s="11">
+        <v>46279</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" t="s">
-        <v>130</v>
+        <v>79</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="D20" t="s">
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="H20" t="s">
         <v>70</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
-        <v>46275</v>
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
+        <v>46279</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" t="s">
-        <v>131</v>
+        <v>79</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G21" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="H21" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
-        <v>46275</v>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="11">
+        <v>46279</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" t="s">
-        <v>132</v>
+        <v>79</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
@@ -1971,13 +1913,13 @@
         <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="H22" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1989,63 +1931,63 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
-        <v>46275</v>
+      <c r="A23" s="11">
+        <v>46279</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>134</v>
+        <v>79</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="F23" t="s">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="G23" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="12">
-        <v>46275</v>
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="11">
+        <v>46279</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" t="s">
-        <v>137</v>
+        <v>79</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="H24" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2057,14 +1999,14 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
-        <v>46275</v>
+      <c r="A25" s="11">
+        <v>46279</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" t="s">
-        <v>139</v>
+        <v>79</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
@@ -2076,7 +2018,7 @@
         <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
@@ -2091,267 +2033,267 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
-        <v>46275</v>
+      <c r="A26" s="11">
+        <v>46279</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" t="s">
-        <v>140</v>
+        <v>68</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="H26" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
-        <v>46275</v>
+    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
+        <v>46279</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" t="s">
-        <v>141</v>
+        <v>68</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
       </c>
       <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J27" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A28" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" t="s">
         <v>24</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F28" t="s">
         <v>24</v>
       </c>
-      <c r="G27" t="s">
-        <v>82</v>
-      </c>
-      <c r="H27" t="s">
-        <v>74</v>
-      </c>
-      <c r="I27" t="str">
+      <c r="G28" t="s">
+        <v>98</v>
+      </c>
+      <c r="H28" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J27" t="str">
+      <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gobernador</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B28" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" t="s">
-        <v>142</v>
-      </c>
-      <c r="D28" t="s">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" t="s">
         <v>12</v>
       </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" t="s">
-        <v>85</v>
-      </c>
-      <c r="H28" t="s">
-        <v>11</v>
-      </c>
-      <c r="I28" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J28" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B29" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" t="s">
-        <v>143</v>
-      </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="G29" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="H29" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="12">
-        <v>46275</v>
+    <row r="30" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
+        <v>46279</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" t="s">
-        <v>144</v>
+        <v>68</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>136</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G30" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="H30" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="12">
-        <v>46275</v>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="11">
+        <v>46279</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" t="s">
-        <v>145</v>
+        <v>77</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="D31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="H31" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="12">
-        <v>46275</v>
+    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="11">
+        <v>46279</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>147</v>
+        <v>77</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="D32" t="s">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="12">
-        <v>46275</v>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="11">
+        <v>46279</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>148</v>
+        <v>77</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="F33" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="G33" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="H33" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2362,30 +2304,30 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="12">
-        <v>46275</v>
+    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
+        <v>46279</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" t="s">
-        <v>150</v>
+        <v>77</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="D34" t="s">
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="G34" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="H34" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2396,321 +2338,321 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="12">
-        <v>46275</v>
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="11">
+        <v>46279</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
-      </c>
-      <c r="C35" t="s">
-        <v>152</v>
+        <v>75</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="D35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F35" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="12">
-        <v>46275</v>
+      <c r="A36" s="11">
+        <v>46279</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" t="s">
-        <v>154</v>
+        <v>75</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G36" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
       </c>
       <c r="I36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="12">
-        <v>46275</v>
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="11">
+        <v>46279</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" t="s">
-        <v>155</v>
+        <v>75</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="12">
-        <v>46275</v>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="11">
+        <v>46279</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" t="s">
-        <v>156</v>
+        <v>75</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>2</v>
+        <v>148</v>
       </c>
       <c r="G38" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="12">
-        <v>46275</v>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="11">
+        <v>46279</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" t="s">
-        <v>158</v>
+        <v>75</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="F39" t="s">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="G39" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="H39" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J39" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" t="s">
+        <v>98</v>
+      </c>
+      <c r="H40" t="s">
+        <v>74</v>
+      </c>
+      <c r="I40" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J39" t="str">
+      <c r="J40" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" t="s">
+        <v>89</v>
+      </c>
+      <c r="E41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" t="s">
+        <v>27</v>
+      </c>
+      <c r="G41" t="s">
+        <v>103</v>
+      </c>
+      <c r="H41" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B40" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40" t="s">
-        <v>160</v>
-      </c>
-      <c r="D40" t="s">
+    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B42" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D42" t="s">
         <v>12</v>
       </c>
-      <c r="E40" t="s">
-        <v>33</v>
-      </c>
-      <c r="F40" t="s">
-        <v>33</v>
-      </c>
-      <c r="G40" t="s">
-        <v>138</v>
-      </c>
-      <c r="H40" t="s">
-        <v>11</v>
-      </c>
-      <c r="I40" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J40" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B41" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" t="s">
-        <v>161</v>
-      </c>
-      <c r="D41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41" t="s">
-        <v>2</v>
-      </c>
-      <c r="G41" t="s">
-        <v>104</v>
-      </c>
-      <c r="H41" t="s">
-        <v>11</v>
-      </c>
-      <c r="I41" t="str">
+      <c r="E42" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" t="s">
+        <v>103</v>
+      </c>
+      <c r="H42" t="s">
+        <v>11</v>
+      </c>
+      <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J41" t="str">
+      <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" t="s">
-        <v>162</v>
-      </c>
-      <c r="D42" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" t="s">
-        <v>27</v>
-      </c>
-      <c r="F42" t="s">
-        <v>163</v>
-      </c>
-      <c r="G42" t="s">
-        <v>164</v>
-      </c>
-      <c r="H42" t="s">
-        <v>11</v>
-      </c>
-      <c r="I42" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J42" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="12">
-        <v>46275</v>
+    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="11">
+        <v>46279</v>
       </c>
       <c r="B43" t="s">
-        <v>79</v>
-      </c>
-      <c r="C43" t="s">
-        <v>165</v>
+        <v>78</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>154</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F43" t="s">
-        <v>87</v>
+        <v>2</v>
       </c>
       <c r="G43" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="12">
-        <v>46275</v>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A44" s="11">
+        <v>46279</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" t="s">
-        <v>166</v>
+        <v>78</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
@@ -2719,10 +2661,10 @@
         <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s">
-        <v>159</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
@@ -2736,49 +2678,49 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="12">
-        <v>46275</v>
+    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="11">
+        <v>46279</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
-      </c>
-      <c r="C45" t="s">
-        <v>167</v>
+        <v>78</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="D45" t="s">
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="12">
-        <v>46275</v>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="11">
+        <v>46279</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" t="s">
-        <v>168</v>
+        <v>78</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="D46" t="s">
         <v>12</v>
@@ -2787,10 +2729,10 @@
         <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>169</v>
+        <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
@@ -2805,169 +2747,169 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="12">
-        <v>46275</v>
+      <c r="A47" s="11">
+        <v>46279</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
-      </c>
-      <c r="C47" t="s">
-        <v>171</v>
+        <v>78</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>159</v>
       </c>
       <c r="D47" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F47" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="G47" t="s">
-        <v>84</v>
+        <v>161</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="12">
-        <v>46275</v>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="11">
+        <v>46279</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
-      </c>
-      <c r="C48" t="s">
-        <v>172</v>
+        <v>78</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>162</v>
       </c>
       <c r="D48" t="s">
         <v>13</v>
       </c>
       <c r="E48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" t="s">
+        <v>98</v>
+      </c>
+      <c r="H48" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J48" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B49" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" t="s">
         <v>16</v>
       </c>
-      <c r="F48" t="s">
-        <v>81</v>
-      </c>
-      <c r="G48" t="s">
-        <v>84</v>
-      </c>
-      <c r="H48" t="s">
-        <v>74</v>
-      </c>
-      <c r="I48" t="str">
+      <c r="F49" t="s">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s">
+        <v>83</v>
+      </c>
+      <c r="H49" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Alcaldías</v>
       </c>
-      <c r="J48" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B49" t="s">
-        <v>79</v>
-      </c>
-      <c r="C49" t="s">
-        <v>173</v>
-      </c>
-      <c r="D49" t="s">
-        <v>93</v>
-      </c>
-      <c r="E49" t="s">
-        <v>106</v>
-      </c>
-      <c r="F49" t="s">
-        <v>106</v>
-      </c>
-      <c r="G49" t="s">
-        <v>107</v>
-      </c>
-      <c r="H49" t="s">
-        <v>11</v>
-      </c>
-      <c r="I49" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
       <c r="J49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="12">
-        <v>46275</v>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="11">
+        <v>46279</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
-      </c>
-      <c r="C50" t="s">
-        <v>174</v>
+        <v>78</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F50" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G50" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="12">
-        <v>46275</v>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="11">
+        <v>46279</v>
       </c>
       <c r="B51" t="s">
-        <v>79</v>
-      </c>
-      <c r="C51" t="s">
-        <v>175</v>
+        <v>78</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>165</v>
       </c>
       <c r="D51" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F51" t="s">
-        <v>10</v>
+        <v>166</v>
       </c>
       <c r="G51" t="s">
-        <v>85</v>
+        <v>167</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2975,26 +2917,26 @@
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="12">
-        <v>46275</v>
+      <c r="A52" s="11">
+        <v>46279</v>
       </c>
       <c r="B52" t="s">
-        <v>76</v>
-      </c>
-      <c r="C52" t="s">
-        <v>176</v>
+        <v>78</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="F52" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
@@ -3009,375 +2951,103 @@
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="12">
-        <v>46275</v>
+      <c r="A53" s="11">
+        <v>46279</v>
       </c>
       <c r="B53" t="s">
-        <v>76</v>
-      </c>
-      <c r="C53" t="s">
-        <v>177</v>
+        <v>78</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>169</v>
       </c>
       <c r="D53" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="E53" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F53" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G53" t="s">
+        <v>170</v>
+      </c>
+      <c r="H53" t="s">
+        <v>11</v>
+      </c>
+      <c r="I53" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J53" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="11">
+        <v>46279</v>
+      </c>
+      <c r="B54" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="H53" t="s">
-        <v>11</v>
-      </c>
-      <c r="I53" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J53" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B54" t="s">
-        <v>76</v>
-      </c>
-      <c r="C54" t="s">
-        <v>178</v>
-      </c>
       <c r="D54" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="E54" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F54" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s">
         <v>11</v>
       </c>
       <c r="I54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="12">
-        <v>46275</v>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="11">
+        <v>46279</v>
       </c>
       <c r="B55" t="s">
         <v>76</v>
       </c>
-      <c r="C55" t="s">
-        <v>179</v>
+      <c r="C55" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="D55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E55" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F55" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H55" t="s">
         <v>11</v>
       </c>
       <c r="I55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J55" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B56" t="s">
-        <v>76</v>
-      </c>
-      <c r="C56" t="s">
-        <v>180</v>
-      </c>
-      <c r="D56" t="s">
-        <v>83</v>
-      </c>
-      <c r="E56" t="s">
-        <v>16</v>
-      </c>
-      <c r="F56" t="s">
-        <v>16</v>
-      </c>
-      <c r="G56" t="s">
-        <v>96</v>
-      </c>
-      <c r="H56" t="s">
-        <v>11</v>
-      </c>
-      <c r="I56" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J56" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B57" t="s">
-        <v>76</v>
-      </c>
-      <c r="C57" t="s">
-        <v>181</v>
-      </c>
-      <c r="D57" t="s">
-        <v>83</v>
-      </c>
-      <c r="E57" t="s">
-        <v>38</v>
-      </c>
-      <c r="F57" t="s">
-        <v>38</v>
-      </c>
-      <c r="G57" t="s">
-        <v>82</v>
-      </c>
-      <c r="H57" t="s">
-        <v>11</v>
-      </c>
-      <c r="I57" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J57" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B58" t="s">
-        <v>75</v>
-      </c>
-      <c r="C58" t="s">
-        <v>182</v>
-      </c>
-      <c r="D58" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" t="s">
-        <v>16</v>
-      </c>
-      <c r="F58" t="s">
-        <v>81</v>
-      </c>
-      <c r="G58" t="s">
-        <v>84</v>
-      </c>
-      <c r="H58" t="s">
-        <v>74</v>
-      </c>
-      <c r="I58" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J58" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B59" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" t="s">
-        <v>183</v>
-      </c>
-      <c r="D59" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" t="s">
-        <v>33</v>
-      </c>
-      <c r="F59" t="s">
-        <v>120</v>
-      </c>
-      <c r="G59" t="s">
-        <v>121</v>
-      </c>
-      <c r="H59" t="s">
-        <v>11</v>
-      </c>
-      <c r="I59" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J59" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B60" t="s">
-        <v>75</v>
-      </c>
-      <c r="C60" t="s">
-        <v>184</v>
-      </c>
-      <c r="D60" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" t="s">
-        <v>17</v>
-      </c>
-      <c r="F60" t="s">
-        <v>2</v>
-      </c>
-      <c r="G60" t="s">
-        <v>123</v>
-      </c>
-      <c r="H60" t="s">
-        <v>74</v>
-      </c>
-      <c r="I60" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J60" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B61" t="s">
-        <v>75</v>
-      </c>
-      <c r="C61" t="s">
-        <v>185</v>
-      </c>
-      <c r="D61" t="s">
-        <v>97</v>
-      </c>
-      <c r="E61" t="s">
-        <v>16</v>
-      </c>
-      <c r="F61" t="s">
-        <v>186</v>
-      </c>
-      <c r="G61" t="s">
-        <v>187</v>
-      </c>
-      <c r="H61" t="s">
-        <v>70</v>
-      </c>
-      <c r="I61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B62" t="s">
-        <v>75</v>
-      </c>
-      <c r="C62" t="s">
-        <v>188</v>
-      </c>
-      <c r="D62" t="s">
-        <v>12</v>
-      </c>
-      <c r="E62" t="s">
-        <v>22</v>
-      </c>
-      <c r="F62" t="s">
-        <v>22</v>
-      </c>
-      <c r="G62" t="s">
-        <v>95</v>
-      </c>
-      <c r="H62" t="s">
-        <v>70</v>
-      </c>
-      <c r="I62" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J62" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="12">
-        <v>46275</v>
-      </c>
-      <c r="B63" t="s">
-        <v>75</v>
-      </c>
-      <c r="C63" t="s">
-        <v>189</v>
-      </c>
-      <c r="D63" t="s">
-        <v>12</v>
-      </c>
-      <c r="E63" t="s">
-        <v>18</v>
-      </c>
-      <c r="F63" t="s">
-        <v>18</v>
-      </c>
-      <c r="G63" t="s">
-        <v>190</v>
-      </c>
-      <c r="H63" t="s">
-        <v>70</v>
-      </c>
-      <c r="I63" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
-      </c>
-      <c r="J63" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
@@ -3949,7 +3619,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B49" t="s">
         <v>44</v>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF28F3D-F9BF-4A23-89E3-DA26E2C6B297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FAB1A0-7E99-4414-97BE-1BE76E5251AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="180">
   <si>
     <t>Fecha</t>
   </si>
@@ -282,277 +282,301 @@
     <t>Alcalde</t>
   </si>
   <si>
-    <t>Informe De Gobierno</t>
-  </si>
-  <si>
     <t>Publicidad</t>
   </si>
   <si>
-    <t>Informe Alcalde</t>
-  </si>
-  <si>
     <t>Temas varios</t>
   </si>
   <si>
     <t>Afectaciones Por Lluvias</t>
   </si>
   <si>
-    <t>Fotonota</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>Conmemoración Aniversario</t>
-  </si>
-  <si>
     <t>Cintillo</t>
   </si>
   <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
     <t>Rehabilitación Vial</t>
   </si>
   <si>
-    <t>34,279 luminarias modernizadas</t>
-  </si>
-  <si>
-    <t>Pirotécnicos señalan pérdidas en ventas</t>
-  </si>
-  <si>
-    <t>Pirotecnia</t>
-  </si>
-  <si>
-    <t>Concluye FUL, Estados Unidos próximo invitado</t>
-  </si>
-  <si>
-    <t>Feria Del Libro</t>
-  </si>
-  <si>
-    <t>Sheinbaum anuncia 13 nuevas escuelas</t>
-  </si>
-  <si>
-    <t>Visita Sheinbaum</t>
-  </si>
-  <si>
-    <t>El PRI está vivo y listo para las elecciones 2027</t>
-  </si>
-  <si>
-    <t>PRI</t>
-  </si>
-  <si>
-    <t>Elecciones</t>
-  </si>
-  <si>
-    <t>Serán 5 mil elementos en operativo patrio</t>
-  </si>
-  <si>
     <t>Fiestas Patrias</t>
   </si>
   <si>
-    <t>Reconoce Sheinbaum labor de Menchaca por los hidalguenses</t>
-  </si>
-  <si>
-    <t>Despliegan a 5 mil policías para El Grito</t>
-  </si>
-  <si>
-    <t>Congreso discute hoy la reforma electoral</t>
-  </si>
-  <si>
     <t>Reforma Electoral</t>
   </si>
   <si>
-    <t>Lluivas arrasan puestos den dos tianguis de Tizayuca</t>
-  </si>
-  <si>
-    <t>Rondón aún tiene cuerda</t>
-  </si>
-  <si>
-    <t>Guadalajara, nuevo líder</t>
-  </si>
-  <si>
-    <t>Incrementan intentos de suicidio y depresión</t>
-  </si>
-  <si>
     <t>Suicidio</t>
   </si>
   <si>
-    <t>Alito asegura que en Hidalgo Morena se está hundiendo: es el Morenatanic</t>
-  </si>
-  <si>
-    <t>Evento partidista</t>
-  </si>
-  <si>
-    <t>Sheinbaum rinde informe sobre los avances en varios proyectos</t>
-  </si>
-  <si>
-    <t>Planea Cenhies ampliar oferta académica</t>
-  </si>
-  <si>
-    <t>Oferta académica</t>
-  </si>
-  <si>
-    <t>Vigilarán las fiestas patrias 5 mil policías</t>
-  </si>
-  <si>
-    <t>Destaca Sheinbaum para Hidalgo apoyos, trenes, inversión</t>
-  </si>
-  <si>
-    <t>Reitera el gobernador su apoyo a proyectos federales</t>
-  </si>
-  <si>
-    <t>La IP ve alta incidencia en el robo al transporte</t>
-  </si>
-  <si>
-    <t>Inseguridad Carretera</t>
-  </si>
-  <si>
-    <t>Prevén adelanto de fechas para el registro de candidaturas</t>
-  </si>
-  <si>
-    <t>Pendientes por resolver 50 carpetas por delitos electorales</t>
-  </si>
-  <si>
-    <t>Delitos Electorales</t>
-  </si>
-  <si>
-    <t>Con asistencia histórica cierra feria del libro</t>
-  </si>
-  <si>
-    <t>CJNG y Chapiza extienden lavado a diez sectores de la economía</t>
-  </si>
-  <si>
-    <t>Crimen Organizado</t>
-  </si>
-  <si>
-    <t>Stellantis busca armara 500 mil autos el próximo año</t>
-  </si>
-  <si>
-    <t>Disminuye la práctica de la charrería en la entidad</t>
-  </si>
-  <si>
-    <t>Sheinbaum subraya inversiones para la entidad en Informe</t>
-  </si>
-  <si>
-    <t>Como parte de su gira por los 32 estados del país para presentar su segundo Informe de Gobierno, la presidenta de la República,  Claudia Sheinbaum Pardo, se presentó en las instalaciones de la Feria de Pachuca. La mandataria informó que, hasta el momento, más  de 330 mil personas en todo el país fueron impactadas con la rendición de cuentas regionales.</t>
-  </si>
-  <si>
-    <t>Hallan dos cuerpos junto al Tren Maya</t>
-  </si>
-  <si>
-    <t>FGR</t>
-  </si>
-  <si>
-    <t>Ejecuciones</t>
-  </si>
-  <si>
-    <t>La movilidad se ha vuelto insostenible en Pachuca. La ciudadanía está  colapsada en diversas avenidas y colonias, situación que se complica  aún más con las lluvias. Es una queja constante que, al parecer, solo a las  autoridades no les importa”.</t>
-  </si>
-  <si>
-    <t>Movilidad urbana</t>
-  </si>
-  <si>
-    <t>Sheinbaum entrega a hidalguenses balance de obras, apoyos y megaproyectos</t>
-  </si>
-  <si>
-    <t>Conmemoran el 179 aniversario de la Gesta Heroica de Chapultepec</t>
-  </si>
-  <si>
-    <t>Desplegarán más de 5 mil elementos de seguridad por fiestas patrias en Hidalgo</t>
-  </si>
-  <si>
-    <t>Llegarán 2 mil libros de la Fundación Elena Poniatowska a escuelas de la entidad</t>
-  </si>
-  <si>
-    <t>Donación de libros</t>
-  </si>
-  <si>
-    <t>Reciben programas del Bienestar 1.1 millones de hidalguenses</t>
-  </si>
-  <si>
-    <t>El PRI es inmortal""</t>
-  </si>
-  <si>
-    <t>Alianzas Electorales</t>
-  </si>
-  <si>
-    <t>Cerrarán lateral del bulevar Felipe Ángeles durante 45 días</t>
-  </si>
-  <si>
-    <t>Jorge Reyes anuncia rehabilitación de cuatro parques emblemáticos</t>
-  </si>
-  <si>
-    <t>alcalde</t>
-  </si>
-  <si>
-    <t>Rehabilitación de espacios públicos</t>
-  </si>
-  <si>
-    <t>Congreso prevé aprobar reforma electoral a un día del plazo límite</t>
-  </si>
-  <si>
-    <t>"En Hidalgo tienen un ejército de mujeres y hombres con gran disposición", afirma Menchaca a Sheinbaum</t>
-  </si>
-  <si>
-    <t>Anuncia Semot plan operativo para las fiestas patrias 2026</t>
-  </si>
-  <si>
-    <t>Refuerzan seguridad y llaman a revisar balcones para el Grito en Hidalgo</t>
-  </si>
-  <si>
-    <t>En 2° informe, Tere Olivares destaca saneamiento financiero, obra pública y atención social</t>
-  </si>
-  <si>
-    <t>Parques, Protección Civil, bienestar animal y atención social, entre los nuevos proyectos anunciados por Jorge Reyes para Pachuca</t>
-  </si>
-  <si>
-    <t>Con manifestación y sin evento público, Tania Valdez presenta 2° informe</t>
-  </si>
-  <si>
-    <t>El arte de soiñar llega a Atitalaquia con la exposición ""Sueno""</t>
-  </si>
-  <si>
-    <t>Exposición Artística</t>
-  </si>
-  <si>
-    <t>José José Sinfónico</t>
-  </si>
-  <si>
-    <t>Cecultah</t>
-  </si>
-  <si>
-    <t>Concierto Sinfónico</t>
-  </si>
-  <si>
-    <t>Sheinbaum destaca Tren CDMX-Pachuca para próximo año; Menchaca refrenda apoyo de Hidalgo</t>
-  </si>
-  <si>
-    <t>Jorge Reyes anunció nuevos proyectos para Pachuca</t>
-  </si>
-  <si>
-    <t>Recibe SEPH donación de 2 mil libros de la Fundación Elena Poniatowska</t>
-  </si>
-  <si>
-    <t>Estudiantes de El Mexe se manifiestan; Segob los atiende</t>
-  </si>
-  <si>
-    <t>Gobernación</t>
-  </si>
-  <si>
     <t>El Mexe</t>
   </si>
   <si>
-    <t>Continúan obras en lateral de bulevar Felipe Ángeles</t>
-  </si>
-  <si>
-    <t>Al grito de Hidalgo</t>
-  </si>
-  <si>
     <t>Grito De Independencia</t>
   </si>
   <si>
-    <t>Programas sociales  benefician a más de un millón de hidalguenses: Sheinbaum</t>
+    <t>Alcoholímetro operará durante toda la semana</t>
+  </si>
+  <si>
+    <t>Alcoholímetro</t>
+  </si>
+  <si>
+    <t>Charros y escaramuzas recorren calles céntricas</t>
+  </si>
+  <si>
+    <t>Piden ampliar estudio para cuidar especies</t>
+  </si>
+  <si>
+    <t>Tren AIFA</t>
+  </si>
+  <si>
+    <t>Rechazó el Congreso división de municipios</t>
+  </si>
+  <si>
+    <t>Colapsa puente por tercera vez en Huautla</t>
+  </si>
+  <si>
+    <t>Aprueban reforma sin paridad de género</t>
+  </si>
+  <si>
+    <t>Charros y escaramuzas toman calles</t>
+  </si>
+  <si>
+    <t>Todo listo para el festejo del Gritoi</t>
+  </si>
+  <si>
+    <t>Hidalguense presenta corto en Nueva York</t>
+  </si>
+  <si>
+    <t>Producción audiovisual</t>
+  </si>
+  <si>
+    <t>Incomunicadas 18 localidades en Huautla por precipitaciones</t>
+  </si>
+  <si>
+    <t>Preparan diagnóstico con IA por tráfico en Pachuca</t>
+  </si>
+  <si>
+    <t>Ordenamiento vial</t>
+  </si>
+  <si>
+    <t>Retiran la concesión a la combi que se accidentó</t>
+  </si>
+  <si>
+    <t>Concesiones transporte público</t>
+  </si>
+  <si>
+    <t>Busca SNTE Hidalgo blindar autonomía</t>
+  </si>
+  <si>
+    <t>Autonomía</t>
+  </si>
+  <si>
+    <t>Aprueba el Congreso la reforma electoral</t>
+  </si>
+  <si>
+    <t>Tradición charra se apoderó de la ciudad</t>
+  </si>
+  <si>
+    <t>El Reloj de Pachuca: 116 años contando la historia</t>
+  </si>
+  <si>
+    <t>Reloj De Pachuca</t>
+  </si>
+  <si>
+    <t>¡Se hunden las Tuzas!</t>
+  </si>
+  <si>
+    <t>Reforma achica cabildos; ahorro será destinado a obras públicas</t>
+  </si>
+  <si>
+    <t>Transparencia útil: Julio Menchaca envía iniciativa al Legislativo</t>
+  </si>
+  <si>
+    <t>Iniciativa</t>
+  </si>
+  <si>
+    <t>Anuncian cierres viales y emiten recomendaciones</t>
+  </si>
+  <si>
+    <t>Defienden exclusividad de carril para el Tuzobús</t>
+  </si>
+  <si>
+    <t>Carril confinado</t>
+  </si>
+  <si>
+    <t>Festejan charros su día con recorrido por Pachuca</t>
+  </si>
+  <si>
+    <t>Pasa de 75 a 99% la eficiencia del servicio de transporte</t>
+  </si>
+  <si>
+    <t>Eficiencia de transporte público</t>
+  </si>
+  <si>
+    <t>Aseguran vivienda ligada al grupo criminal La Barredora</t>
+  </si>
+  <si>
+    <t>Sedena</t>
+  </si>
+  <si>
+    <t>Combate a la delincuencia</t>
+  </si>
+  <si>
+    <t>Influencers: cuando la vida vale unos clics</t>
+  </si>
+  <si>
+    <t>Empresarios ven al T-Mec ""en el limbo"" y temen por las cadenas productivas</t>
+  </si>
+  <si>
+    <t>T-Mec</t>
+  </si>
+  <si>
+    <t>Canadá convoca a Europa a estrechar los lazos económicos</t>
+  </si>
+  <si>
+    <t>Falsificación cae 24% y el crimen privilegia los de 500</t>
+  </si>
+  <si>
+    <t>Charros desfilan en conmemoración de su día</t>
+  </si>
+  <si>
+    <t>Medirán flujo vehicular para solucionar embotellamientos</t>
+  </si>
+  <si>
+    <t>Congreso local aprueba desaparecer regidores y síndicos de minoría</t>
+  </si>
+  <si>
+    <t>Suspende Grito Esuinapa tras asesinato de maestra de kínder</t>
+  </si>
+  <si>
+    <t>No hay manera de defender la patria de intervencionismos extranjeros si el municipio de al lado no tiene  agua, si la gente sigue esperando lo más básico para vivir con dignidad”.</t>
+  </si>
+  <si>
+    <t>Intervención extranjera</t>
+  </si>
+  <si>
+    <t>Todo listo para celebrar el Grito de Independencia en Plaza Juárez</t>
+  </si>
+  <si>
+    <t>Aprueba Congreso reforma electoral con menos cargos municipales y cambio en registros</t>
+  </si>
+  <si>
+    <t>Pierde concesión ruta Tilcuautla-Pachuca involucrada en accidente en Bulevar Minero</t>
+  </si>
+  <si>
+    <t>Impulsa Menchaca la creación de nueva estructura de transparencia en Hidalgo</t>
+  </si>
+  <si>
+    <t>Extinción ITAIH</t>
+  </si>
+  <si>
+    <t>Tizayuca, entre las zonas con mayor riesgo suicida en Hidalgo</t>
+  </si>
+  <si>
+    <t>Congreso de hidalgo aprueba reforma electoral para 2027</t>
+  </si>
+  <si>
+    <t>Pachuca ampliará operativo alcoholímetro durante festejos patrios</t>
+  </si>
+  <si>
+    <t>Con cámaras e Inteligencia Artificial analizarán el tráfico de Pachuca</t>
+  </si>
+  <si>
+    <t>Normalistas del El Mexe reconocen avances de la Procuraduría en investigación por homicidio de estudiante</t>
+  </si>
+  <si>
+    <t>Carril confinado del Tuzobús seguirá cerrado a autos particulares</t>
+  </si>
+  <si>
+    <t>Hidalgo reorganizará transparencia y protección de datos</t>
+  </si>
+  <si>
+    <t>Congreso de Hidalgo aprueba reforma electoral: reduce regidurías para 2027</t>
+  </si>
+  <si>
+    <t>Continúan las jornadas de faena para mejorar caminos y vialidades de Ajacuba</t>
+  </si>
+  <si>
+    <t>Envía Menchaca iniciativas para fortalecer la transparencia, protección de datos y simplificación administrativa</t>
+  </si>
+  <si>
+    <t>Esperan más de 1000 corredores en Trail Expo Feria San Francisco Tlahuelilpan 2026</t>
+  </si>
+  <si>
+    <t>Carrera atlética</t>
+  </si>
+  <si>
+    <t>Claudia Sandoval refuerza identidad de Atitalaquia con nuevo mural</t>
+  </si>
+  <si>
+    <t>Muralismo</t>
+  </si>
+  <si>
+    <t>Mujeres emprendedoras llevan su arte a la sala Quetzalcóatl de Tula</t>
+  </si>
+  <si>
+    <t>Más de 5 mil policías resguardarán a familias hidalguenses durante festejos patrios</t>
+  </si>
+  <si>
+    <t>Reunión Gabinete De Seguridad</t>
+  </si>
+  <si>
+    <t>Capacitación gratuita de conducción responsable</t>
+  </si>
+  <si>
+    <t>Educación vial</t>
+  </si>
+  <si>
+    <t>Pachuca Brilla</t>
+  </si>
+  <si>
+    <t>Incrementa demanda del Transporte Metropolitano; aumentan más de 23 mil usuarios</t>
+  </si>
+  <si>
+    <t>Afluencia Tuzobús</t>
+  </si>
+  <si>
+    <t>Habrpa operativo alcoholímetro en estas fiestas patrias en Pachuca</t>
+  </si>
+  <si>
+    <t>SSPH desmantela taller de regrabado y clonación de identificaciones vehiculares en Pachuca</t>
+  </si>
+  <si>
+    <t>Envía Julio Menchaca iniciativas para fortalecer la transparencia, protección de datos y simplificación administrativa</t>
+  </si>
+  <si>
+    <t>Celebraron Día del Charro</t>
+  </si>
+  <si>
+    <t>116 aniversario del Reloj de Pachuca</t>
+  </si>
+  <si>
+    <t>Al grito de Hidalgo: Carlos Rivera</t>
+  </si>
+  <si>
+    <t>Aprueban reforma al Código Electoral</t>
+  </si>
+  <si>
+    <t>Prometen dar con responsable del asesinato de estudiante</t>
+  </si>
+  <si>
+    <t>Feminicidio</t>
+  </si>
+  <si>
+    <t>Urgen a reformar impuestos a bebidas alcohólicas</t>
+  </si>
+  <si>
+    <t>Consumo de alcohol</t>
+  </si>
+  <si>
+    <t>Es un hecho que uno de los principales problemas en Pachuca es la falta de transporte público eficiente y digno, por lo que la remodelación del Tuzobús es un buen principio para mejorar el servicio.</t>
+  </si>
+  <si>
+    <t>Editorial</t>
+  </si>
+  <si>
+    <t>Modernización Tuzobús</t>
   </si>
 </sst>
 </file>
@@ -799,8 +823,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J55" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J55" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J64" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J64" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1169,7 +1193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1218,32 +1242,32 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
         <v>93</v>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>94</v>
-      </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1252,25 +1276,25 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -1286,28 +1310,28 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1315,37 +1339,37 @@
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1354,149 +1378,149 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G7" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B9" t="s">
         <v>71</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1508,7 +1532,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
@@ -1522,15 +1546,15 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
@@ -1542,7 +1566,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
@@ -1558,59 +1582,59 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B13" t="s">
         <v>73</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
@@ -1624,68 +1648,68 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B14" t="s">
         <v>73</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
       </c>
       <c r="I14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G15" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1694,13 +1718,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B16" t="s">
         <v>73</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
@@ -1712,7 +1736,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
@@ -1728,198 +1752,198 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B17" t="s">
         <v>73</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G17" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B19" t="s">
         <v>79</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G19" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B20" t="s">
         <v>79</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G20" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H20" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B21" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G21" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s">
         <v>11</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B22" t="s">
         <v>79</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H22" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1932,25 +1956,25 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B23" t="s">
         <v>79</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
@@ -1964,68 +1988,68 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B24" t="s">
         <v>79</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H24" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B25" t="s">
         <v>79</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="G25" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="H25" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2034,13 +2058,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
@@ -2052,7 +2076,7 @@
         <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
@@ -2068,192 +2092,192 @@
     </row>
     <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" t="s">
+        <v>130</v>
+      </c>
+      <c r="H27" t="s">
+        <v>70</v>
+      </c>
+      <c r="I27" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J27" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D27" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" t="s">
-        <v>98</v>
-      </c>
-      <c r="H27" t="s">
-        <v>11</v>
-      </c>
-      <c r="I27" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J27" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="120" x14ac:dyDescent="0.25">
-      <c r="A28" s="11">
-        <v>46279</v>
-      </c>
-      <c r="B28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>132</v>
-      </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B30" t="s">
         <v>68</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H31" t="s">
         <v>74</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="G32" t="s">
         <v>88</v>
@@ -2263,71 +2287,71 @@
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F33" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G33" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F34" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G34" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H34" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2340,66 +2364,66 @@
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D35" t="s">
         <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="G35" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D36" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="G36" t="s">
-        <v>145</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
       </c>
       <c r="I36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2408,25 +2432,25 @@
     </row>
     <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="F37" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="G37" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
@@ -2442,161 +2466,161 @@
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F38" t="s">
-        <v>148</v>
+        <v>24</v>
       </c>
       <c r="G38" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="H38" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F39" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G40" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F41" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D42" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G42" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H42" t="s">
         <v>11</v>
@@ -2610,30 +2634,30 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G43" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2644,185 +2668,185 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="G44" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D45" t="s">
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F45" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="G45" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B46" t="s">
         <v>78</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D46" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="E46" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G46" t="s">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B47" t="s">
         <v>78</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D47" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B48" t="s">
         <v>78</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D48" t="s">
         <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F48" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G48" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
       <c r="H48" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B49" t="s">
         <v>78</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
@@ -2831,10 +2855,10 @@
         <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -2850,93 +2874,93 @@
     </row>
     <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B50" t="s">
         <v>78</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B51" t="s">
         <v>78</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B52" t="s">
         <v>78</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D52" t="s">
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="F52" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="G52" t="s">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
@@ -2947,109 +2971,415 @@
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B53" t="s">
         <v>78</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E53" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J53" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B54" t="s">
+        <v>163</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>27</v>
+      </c>
+      <c r="F54" t="s">
+        <v>27</v>
+      </c>
+      <c r="G54" t="s">
+        <v>165</v>
+      </c>
+      <c r="H54" t="s">
+        <v>74</v>
+      </c>
+      <c r="I54" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J53" t="str">
+      <c r="J54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="11">
-        <v>46279</v>
-      </c>
-      <c r="B54" t="s">
-        <v>78</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D54" t="s">
-        <v>82</v>
-      </c>
-      <c r="E54" t="s">
-        <v>16</v>
-      </c>
-      <c r="F54" t="s">
-        <v>16</v>
-      </c>
-      <c r="G54" t="s">
-        <v>81</v>
-      </c>
-      <c r="H54" t="s">
-        <v>11</v>
-      </c>
-      <c r="I54" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J54" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B55" t="s">
+        <v>163</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" t="s">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s">
+        <v>93</v>
+      </c>
+      <c r="H55" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J55" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B56" t="s">
+        <v>163</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" t="s">
+        <v>22</v>
+      </c>
+      <c r="F56" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" t="s">
+        <v>127</v>
+      </c>
+      <c r="H56" t="s">
+        <v>11</v>
+      </c>
+      <c r="I56" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J56" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A57" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B57" t="s">
+        <v>163</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" t="s">
+        <v>24</v>
+      </c>
+      <c r="F57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" t="s">
+        <v>143</v>
+      </c>
+      <c r="H57" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J57" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B58" t="s">
+        <v>163</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" t="s">
+        <v>87</v>
+      </c>
+      <c r="H58" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J58" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B59" t="s">
+        <v>163</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" t="s">
+        <v>114</v>
+      </c>
+      <c r="H59" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J59" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B60" t="s">
+        <v>163</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D60" t="s">
+        <v>81</v>
+      </c>
+      <c r="E60" t="s">
+        <v>21</v>
+      </c>
+      <c r="F60" t="s">
+        <v>21</v>
+      </c>
+      <c r="G60" t="s">
+        <v>91</v>
+      </c>
+      <c r="H60" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B61" t="s">
         <v>76</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C61" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D61" t="s">
         <v>13</v>
       </c>
-      <c r="E55" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55" t="s">
-        <v>14</v>
-      </c>
-      <c r="G55" t="s">
-        <v>98</v>
-      </c>
-      <c r="H55" t="s">
-        <v>11</v>
-      </c>
-      <c r="I55" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J55" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+      <c r="E61" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" t="s">
+        <v>88</v>
+      </c>
+      <c r="H61" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B62" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" t="s">
+        <v>174</v>
+      </c>
+      <c r="H62" t="s">
+        <v>11</v>
+      </c>
+      <c r="I62" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J62" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B63" t="s">
+        <v>76</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" t="s">
+        <v>176</v>
+      </c>
+      <c r="H63" t="s">
+        <v>11</v>
+      </c>
+      <c r="I63" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J63" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A64" s="11">
+        <v>46280</v>
+      </c>
+      <c r="B64" t="s">
+        <v>76</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D64" t="s">
+        <v>178</v>
+      </c>
+      <c r="E64" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64" t="s">
+        <v>179</v>
+      </c>
+      <c r="H64" t="s">
+        <v>74</v>
+      </c>
+      <c r="I64" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J64" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
       </c>
     </row>
   </sheetData>
@@ -3619,7 +3949,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B49" t="s">
         <v>44</v>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FAB1A0-7E99-4414-97BE-1BE76E5251AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010FAEEE-0502-4068-8AFC-D0E28A8E9CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="186">
   <si>
     <t>Fecha</t>
   </si>
@@ -285,9 +285,6 @@
     <t>Publicidad</t>
   </si>
   <si>
-    <t>Temas varios</t>
-  </si>
-  <si>
     <t>Afectaciones Por Lluvias</t>
   </si>
   <si>
@@ -297,286 +294,307 @@
     <t>Cintillo</t>
   </si>
   <si>
-    <t>Rehabilitación Vial</t>
-  </si>
-  <si>
     <t>Fiestas Patrias</t>
   </si>
   <si>
     <t>Reforma Electoral</t>
   </si>
   <si>
-    <t>Suicidio</t>
-  </si>
-  <si>
     <t>El Mexe</t>
   </si>
   <si>
     <t>Grito De Independencia</t>
   </si>
   <si>
-    <t>Alcoholímetro operará durante toda la semana</t>
-  </si>
-  <si>
     <t>Alcoholímetro</t>
   </si>
   <si>
-    <t>Charros y escaramuzas recorren calles céntricas</t>
-  </si>
-  <si>
-    <t>Piden ampliar estudio para cuidar especies</t>
-  </si>
-  <si>
-    <t>Tren AIFA</t>
-  </si>
-  <si>
-    <t>Rechazó el Congreso división de municipios</t>
-  </si>
-  <si>
-    <t>Colapsa puente por tercera vez en Huautla</t>
-  </si>
-  <si>
-    <t>Aprueban reforma sin paridad de género</t>
-  </si>
-  <si>
-    <t>Charros y escaramuzas toman calles</t>
-  </si>
-  <si>
-    <t>Todo listo para el festejo del Gritoi</t>
-  </si>
-  <si>
-    <t>Hidalguense presenta corto en Nueva York</t>
-  </si>
-  <si>
-    <t>Producción audiovisual</t>
-  </si>
-  <si>
-    <t>Incomunicadas 18 localidades en Huautla por precipitaciones</t>
-  </si>
-  <si>
-    <t>Preparan diagnóstico con IA por tráfico en Pachuca</t>
-  </si>
-  <si>
-    <t>Ordenamiento vial</t>
-  </si>
-  <si>
-    <t>Retiran la concesión a la combi que se accidentó</t>
-  </si>
-  <si>
-    <t>Concesiones transporte público</t>
-  </si>
-  <si>
-    <t>Busca SNTE Hidalgo blindar autonomía</t>
-  </si>
-  <si>
-    <t>Autonomía</t>
-  </si>
-  <si>
-    <t>Aprueba el Congreso la reforma electoral</t>
-  </si>
-  <si>
-    <t>Tradición charra se apoderó de la ciudad</t>
-  </si>
-  <si>
-    <t>El Reloj de Pachuca: 116 años contando la historia</t>
-  </si>
-  <si>
-    <t>Reloj De Pachuca</t>
-  </si>
-  <si>
-    <t>¡Se hunden las Tuzas!</t>
-  </si>
-  <si>
-    <t>Reforma achica cabildos; ahorro será destinado a obras públicas</t>
-  </si>
-  <si>
-    <t>Transparencia útil: Julio Menchaca envía iniciativa al Legislativo</t>
-  </si>
-  <si>
     <t>Iniciativa</t>
   </si>
   <si>
-    <t>Anuncian cierres viales y emiten recomendaciones</t>
-  </si>
-  <si>
-    <t>Defienden exclusividad de carril para el Tuzobús</t>
-  </si>
-  <si>
-    <t>Carril confinado</t>
-  </si>
-  <si>
-    <t>Festejan charros su día con recorrido por Pachuca</t>
-  </si>
-  <si>
-    <t>Pasa de 75 a 99% la eficiencia del servicio de transporte</t>
-  </si>
-  <si>
-    <t>Eficiencia de transporte público</t>
-  </si>
-  <si>
-    <t>Aseguran vivienda ligada al grupo criminal La Barredora</t>
-  </si>
-  <si>
     <t>Sedena</t>
   </si>
   <si>
-    <t>Combate a la delincuencia</t>
-  </si>
-  <si>
-    <t>Influencers: cuando la vida vale unos clics</t>
-  </si>
-  <si>
-    <t>Empresarios ven al T-Mec ""en el limbo"" y temen por las cadenas productivas</t>
-  </si>
-  <si>
-    <t>T-Mec</t>
-  </si>
-  <si>
-    <t>Canadá convoca a Europa a estrechar los lazos económicos</t>
-  </si>
-  <si>
-    <t>Falsificación cae 24% y el crimen privilegia los de 500</t>
-  </si>
-  <si>
-    <t>Charros desfilan en conmemoración de su día</t>
-  </si>
-  <si>
-    <t>Medirán flujo vehicular para solucionar embotellamientos</t>
-  </si>
-  <si>
-    <t>Congreso local aprueba desaparecer regidores y síndicos de minoría</t>
-  </si>
-  <si>
-    <t>Suspende Grito Esuinapa tras asesinato de maestra de kínder</t>
-  </si>
-  <si>
-    <t>No hay manera de defender la patria de intervencionismos extranjeros si el municipio de al lado no tiene  agua, si la gente sigue esperando lo más básico para vivir con dignidad”.</t>
-  </si>
-  <si>
     <t>Intervención extranjera</t>
   </si>
   <si>
-    <t>Todo listo para celebrar el Grito de Independencia en Plaza Juárez</t>
-  </si>
-  <si>
-    <t>Aprueba Congreso reforma electoral con menos cargos municipales y cambio en registros</t>
-  </si>
-  <si>
-    <t>Pierde concesión ruta Tilcuautla-Pachuca involucrada en accidente en Bulevar Minero</t>
-  </si>
-  <si>
-    <t>Impulsa Menchaca la creación de nueva estructura de transparencia en Hidalgo</t>
-  </si>
-  <si>
-    <t>Extinción ITAIH</t>
-  </si>
-  <si>
-    <t>Tizayuca, entre las zonas con mayor riesgo suicida en Hidalgo</t>
-  </si>
-  <si>
-    <t>Congreso de hidalgo aprueba reforma electoral para 2027</t>
-  </si>
-  <si>
-    <t>Pachuca ampliará operativo alcoholímetro durante festejos patrios</t>
-  </si>
-  <si>
-    <t>Con cámaras e Inteligencia Artificial analizarán el tráfico de Pachuca</t>
-  </si>
-  <si>
-    <t>Normalistas del El Mexe reconocen avances de la Procuraduría en investigación por homicidio de estudiante</t>
-  </si>
-  <si>
-    <t>Carril confinado del Tuzobús seguirá cerrado a autos particulares</t>
-  </si>
-  <si>
-    <t>Hidalgo reorganizará transparencia y protección de datos</t>
-  </si>
-  <si>
-    <t>Congreso de Hidalgo aprueba reforma electoral: reduce regidurías para 2027</t>
-  </si>
-  <si>
-    <t>Continúan las jornadas de faena para mejorar caminos y vialidades de Ajacuba</t>
-  </si>
-  <si>
-    <t>Envía Menchaca iniciativas para fortalecer la transparencia, protección de datos y simplificación administrativa</t>
-  </si>
-  <si>
-    <t>Esperan más de 1000 corredores en Trail Expo Feria San Francisco Tlahuelilpan 2026</t>
-  </si>
-  <si>
-    <t>Carrera atlética</t>
-  </si>
-  <si>
-    <t>Claudia Sandoval refuerza identidad de Atitalaquia con nuevo mural</t>
-  </si>
-  <si>
-    <t>Muralismo</t>
-  </si>
-  <si>
-    <t>Mujeres emprendedoras llevan su arte a la sala Quetzalcóatl de Tula</t>
-  </si>
-  <si>
-    <t>Más de 5 mil policías resguardarán a familias hidalguenses durante festejos patrios</t>
-  </si>
-  <si>
-    <t>Reunión Gabinete De Seguridad</t>
-  </si>
-  <si>
-    <t>Capacitación gratuita de conducción responsable</t>
-  </si>
-  <si>
-    <t>Educación vial</t>
-  </si>
-  <si>
     <t>Pachuca Brilla</t>
   </si>
   <si>
-    <t>Incrementa demanda del Transporte Metropolitano; aumentan más de 23 mil usuarios</t>
-  </si>
-  <si>
-    <t>Afluencia Tuzobús</t>
-  </si>
-  <si>
-    <t>Habrpa operativo alcoholímetro en estas fiestas patrias en Pachuca</t>
-  </si>
-  <si>
-    <t>SSPH desmantela taller de regrabado y clonación de identificaciones vehiculares en Pachuca</t>
-  </si>
-  <si>
-    <t>Envía Julio Menchaca iniciativas para fortalecer la transparencia, protección de datos y simplificación administrativa</t>
-  </si>
-  <si>
-    <t>Celebraron Día del Charro</t>
-  </si>
-  <si>
-    <t>116 aniversario del Reloj de Pachuca</t>
-  </si>
-  <si>
-    <t>Al grito de Hidalgo: Carlos Rivera</t>
-  </si>
-  <si>
-    <t>Aprueban reforma al Código Electoral</t>
-  </si>
-  <si>
-    <t>Prometen dar con responsable del asesinato de estudiante</t>
-  </si>
-  <si>
-    <t>Feminicidio</t>
-  </si>
-  <si>
-    <t>Urgen a reformar impuestos a bebidas alcohólicas</t>
-  </si>
-  <si>
-    <t>Consumo de alcohol</t>
-  </si>
-  <si>
-    <t>Es un hecho que uno de los principales problemas en Pachuca es la falta de transporte público eficiente y digno, por lo que la remodelación del Tuzobús es un buen principio para mejorar el servicio.</t>
-  </si>
-  <si>
-    <t>Editorial</t>
-  </si>
-  <si>
-    <t>Modernización Tuzobús</t>
+    <t>Conmemoran 216 años de la Independencia</t>
+  </si>
+  <si>
+    <t>Desfile cívico</t>
+  </si>
+  <si>
+    <t>Seis dieron positivo en el alcoholímetro</t>
+  </si>
+  <si>
+    <t>Policía municipal</t>
+  </si>
+  <si>
+    <t>Escuelas enfrentan reducción de alumnos</t>
+  </si>
+  <si>
+    <t>Reducción de alumnos</t>
+  </si>
+  <si>
+    <t>Sin rechazo empresarial la jornada de 40 horas</t>
+  </si>
+  <si>
+    <t>Ley 40 horas</t>
+  </si>
+  <si>
+    <t>Llama obispo a aclarar la muerte de párroco</t>
+  </si>
+  <si>
+    <t>Homicidio de párroco</t>
+  </si>
+  <si>
+    <t>Saldo blanco durante los festejos de Independencia</t>
+  </si>
+  <si>
+    <t>Ciudadanos disfrutaron noche del Grito</t>
+  </si>
+  <si>
+    <t>Asesinan a párroco de Huejutla</t>
+  </si>
+  <si>
+    <t>México no será colonia ni protectorado de nadie, dice Sheinbaum</t>
+  </si>
+  <si>
+    <t>Llevan fiestas patrias a La Habana, Cuba</t>
+  </si>
+  <si>
+    <t>Preparan una intervención al pisal</t>
+  </si>
+  <si>
+    <t>Pisal Ben Gurión</t>
+  </si>
+  <si>
+    <t>El Checho abre puerta mexicana</t>
+  </si>
+  <si>
+    <t>Barsa sigue imparable</t>
+  </si>
+  <si>
+    <t>"¡Que viva la transformación!", fue la arenga de Julio Menchaca</t>
+  </si>
+  <si>
+    <t>Los daños en las vialidades, por las lluvias, dice titular de Sipdus</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Indaga PGJEH muerte en la Normal Mexe</t>
+  </si>
+  <si>
+    <t>Desfilaron más de 4 mil durante la parada cívica: 16 de septiembre</t>
+  </si>
+  <si>
+    <t>Celebra el PRI cambios en La Reforma para elección 2027</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>Buscan blindar la elección mediante pacto de civilidad</t>
+  </si>
+  <si>
+    <t>Reunión con partidos</t>
+  </si>
+  <si>
+    <t>Dictan sentencia a 168 secuestradores en 4 años</t>
+  </si>
+  <si>
+    <t>Combate Al Secuestro</t>
+  </si>
+  <si>
+    <t>Lanza Tránsito de Pachuca curso de manejo gratuito</t>
+  </si>
+  <si>
+    <t>Curso de manejo</t>
+  </si>
+  <si>
+    <t>Van 12 mmdp en apooyos sociales para Hidalgo</t>
+  </si>
+  <si>
+    <t>Programas Del Bienestar</t>
+  </si>
+  <si>
+    <t>Desfile. Reportan saldo blanco en celebraciones de Independencia</t>
+  </si>
+  <si>
+    <t>Arrancan obras en pisal del parque</t>
+  </si>
+  <si>
+    <t>Europa y su obsesión con la migración</t>
+  </si>
+  <si>
+    <t>Migración</t>
+  </si>
+  <si>
+    <t>Doblete a Donald Trump: la Reserva sube las tasas y Canadá se une a la UE</t>
+  </si>
+  <si>
+    <t>Temas internacionales</t>
+  </si>
+  <si>
+    <t>Trevilla: fuerzas armadas están listas para todo reto</t>
+  </si>
+  <si>
+    <t>Decisión de FED y crudo caro pegan a boom de IA</t>
+  </si>
+  <si>
+    <t>Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>Carecen de Atlas de Riesgos 15 municipios afectados por vaguada</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Atlas de Riesgos</t>
+  </si>
+  <si>
+    <t>En su mensaje previo al Desfile Cívico Militar por el 216 aniversario de la Independencia, Sheinbaum afirmó que la lucha nació de una causa  popular, lo que distingue a México de otros procesos de América Latina.</t>
+  </si>
+  <si>
+    <t>Fotonota</t>
+  </si>
+  <si>
+    <t>Ni colonia ni protectorado, proclama Sheinbaum al celebrar la Independencia</t>
+  </si>
+  <si>
+    <t>Trump pide castigo para narcopolíticos</t>
+  </si>
+  <si>
+    <t>El forcejeo por la candidatura a la presidencia municipal de Pachuca no es tan terso como parece,  genera dudas y deja la puerta entreabierta a una sorpresa en las urnas electorales de 2027”.</t>
+  </si>
+  <si>
+    <t>Candidaturas</t>
+  </si>
+  <si>
+    <t>Más de 4 mil  personas participaron en desfile cívico-militar en Pachuca</t>
+  </si>
+  <si>
+    <t>Rehabilitación del Pisal Monumental podría concluir en marzo de 2027</t>
+  </si>
+  <si>
+    <t>Alcoholímetro de Pachuca retiene seis vehículos durante operativo por fiestas patrias</t>
+  </si>
+  <si>
+    <t>Fallece Juana Olivia Alarcón Rivera, diputada de Nueva Alianza Hidalgo</t>
+  </si>
+  <si>
+    <t>GLPANALH</t>
+  </si>
+  <si>
+    <t>Deceso diputada</t>
+  </si>
+  <si>
+    <t>Asesinan a sacerdote en Lolotla; Procuraduría investiga</t>
+  </si>
+  <si>
+    <t>PRI celebra que se descartara resparto alfabético de candidaturas</t>
+  </si>
+  <si>
+    <t>SEPH asegura que hay diálogo con El Mexe</t>
+  </si>
+  <si>
+    <t>¿Qué cambió con la reforma electoral en Hidalgo?</t>
+  </si>
+  <si>
+    <t>SSPH descarta hackeo al C5i de Hidalgo</t>
+  </si>
+  <si>
+    <t>C5i</t>
+  </si>
+  <si>
+    <t>Hackeo</t>
+  </si>
+  <si>
+    <t>Espacio Hidalgo pelea por conservar su registro</t>
+  </si>
+  <si>
+    <t>pérdida de registro</t>
+  </si>
+  <si>
+    <t>Usarán inteligencia artificial para analizar tráfico en Pachuca</t>
+  </si>
+  <si>
+    <t>Docente de la UTSH participa en seminario internacional en China</t>
+  </si>
+  <si>
+    <t>Encuentro internacional</t>
+  </si>
+  <si>
+    <t>Cercanía y unión caracterizaron los festejos patrios en Hidalgo</t>
+  </si>
+  <si>
+    <t>Pachuca conmemora el 216 aniversario del inicio de la Independencia de México</t>
+  </si>
+  <si>
+    <t>En Tula realizan evento cívico y desfile con motivo del 216 aniversario de la Independencia de México</t>
+  </si>
+  <si>
+    <t>Pachuca concluye operativo de Fiestas Patrias con saldo blanco</t>
+  </si>
+  <si>
+    <t>Repuve acerca registro vehicular gratuito a todas las regiones</t>
+  </si>
+  <si>
+    <t>Repuve</t>
+  </si>
+  <si>
+    <t>Unidad móvil</t>
+  </si>
+  <si>
+    <t>Hidalgo concluye festejos patrios con desfile cívico-militar</t>
+  </si>
+  <si>
+    <t>Participaron 158 elementos de Seguridad de Pachuca en eventos</t>
+  </si>
+  <si>
+    <t>Repuve acerca registro vehicular gratuito en todas las regiones</t>
+  </si>
+  <si>
+    <t>Registraron saldo blanco durante las celebraciones</t>
+  </si>
+  <si>
+    <t>Capacita SEPH a coordinadores de los Centros de Maestros</t>
+  </si>
+  <si>
+    <t>Capacitación docente</t>
+  </si>
+  <si>
+    <t>José José Sinfónico</t>
+  </si>
+  <si>
+    <t>Cecultah</t>
+  </si>
+  <si>
+    <t>Concierto Sinfónico</t>
+  </si>
+  <si>
+    <t>Con la pirotecnia no se juega</t>
+  </si>
+  <si>
+    <t>Pirotecnia</t>
+  </si>
+  <si>
+    <t>Saldo blanco en Hidalgo tras festejos patrios</t>
+  </si>
+  <si>
+    <t>Ejecutan a sacerdote católico</t>
+  </si>
+  <si>
+    <t>Proponen crear la medalla ""Leona Vicario""</t>
+  </si>
+  <si>
+    <t>"México no se doblega, no se arrodilla y nunca se vende"</t>
   </si>
 </sst>
 </file>
@@ -823,8 +841,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J64" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J64" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J62" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J62" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1193,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1242,66 +1260,66 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="G3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1310,28 +1328,28 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1344,164 +1362,164 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G5" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B9" t="s">
         <v>71</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1512,49 +1530,49 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J10" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
-      <c r="J10" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B11" t="s">
         <v>71</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
@@ -1566,7 +1584,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
@@ -1582,13 +1600,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B12" t="s">
         <v>71</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
@@ -1600,7 +1618,7 @@
         <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
@@ -1616,47 +1634,47 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B13" t="s">
         <v>73</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
       </c>
       <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B14" t="s">
         <v>73</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
@@ -1668,7 +1686,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
@@ -1682,200 +1700,200 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
         <v>88</v>
       </c>
       <c r="H15" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B16" t="s">
         <v>73</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B17" t="s">
         <v>73</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B18" t="s">
         <v>73</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="F19" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J19" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
-      <c r="J19" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B20" t="s">
         <v>79</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H20" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1883,98 +1901,98 @@
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B21" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G21" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="H21" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B22" t="s">
         <v>79</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="G22" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
       </c>
       <c r="I22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B23" t="s">
         <v>79</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G23" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
@@ -1988,27 +2006,27 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B24" t="s">
         <v>79</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G24" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="H24" t="s">
         <v>74</v>
@@ -2019,52 +2037,52 @@
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B25" t="s">
         <v>79</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F25" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="H25" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B26" t="s">
         <v>79</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
@@ -2076,7 +2094,7 @@
         <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
@@ -2092,13 +2110,13 @@
     </row>
     <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B27" t="s">
         <v>79</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
@@ -2110,10 +2128,10 @@
         <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H27" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2124,34 +2142,34 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B28" t="s">
         <v>79</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2160,13 +2178,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B29" t="s">
         <v>79</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
@@ -2178,7 +2196,7 @@
         <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
@@ -2192,92 +2210,92 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B30" t="s">
         <v>68</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="G30" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B31" t="s">
         <v>68</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D31" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F31" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="H31" t="s">
         <v>74</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B32" t="s">
         <v>68</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G32" t="s">
         <v>88</v>
@@ -2287,41 +2305,41 @@
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J32" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
-      <c r="J32" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B33" t="s">
         <v>68</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2330,59 +2348,59 @@
     </row>
     <row r="34" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B34" t="s">
         <v>68</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D34" t="s">
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G34" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H34" t="s">
         <v>70</v>
       </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B35" t="s">
         <v>77</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D35" t="s">
         <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F35" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G35" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -2398,130 +2416,130 @@
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B36" t="s">
         <v>77</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D36" t="s">
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
       </c>
       <c r="I36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B37" t="s">
         <v>77</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="G37" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B38" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="G38" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H38" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G39" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="H39" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2534,130 +2552,130 @@
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B40" t="s">
         <v>75</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="F40" t="s">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="G40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J40" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
-      <c r="J40" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B41" t="s">
         <v>75</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D41" t="s">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B42" t="s">
         <v>75</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D42" t="s">
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G42" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s">
         <v>11</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B43" t="s">
         <v>75</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F43" t="s">
-        <v>17</v>
+        <v>157</v>
       </c>
       <c r="G43" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="H43" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2668,61 +2686,61 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B44" t="s">
         <v>75</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="F44" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G44" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="E45" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G45" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
@@ -2733,101 +2751,101 @@
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B46" t="s">
         <v>78</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D46" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F46" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G46" t="s">
-        <v>88</v>
+        <v>163</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B47" t="s">
         <v>78</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G47" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B48" t="s">
         <v>78</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F48" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G48" t="s">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2835,18 +2853,18 @@
       </c>
       <c r="J48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B49" t="s">
         <v>78</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
@@ -2855,10 +2873,10 @@
         <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -2874,13 +2892,13 @@
     </row>
     <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B50" t="s">
         <v>78</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
@@ -2889,10 +2907,10 @@
         <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
@@ -2908,50 +2926,50 @@
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B51" t="s">
         <v>78</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
       <c r="G51" t="s">
-        <v>82</v>
+        <v>170</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="D52" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E52" t="s">
         <v>24</v>
@@ -2960,7 +2978,7 @@
         <v>24</v>
       </c>
       <c r="G52" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
@@ -2974,27 +2992,27 @@
         <v>Gobernador</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="D53" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="E53" t="s">
         <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="G53" t="s">
-        <v>162</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
@@ -3010,28 +3028,28 @@
     </row>
     <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B54" t="s">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F54" t="s">
-        <v>27</v>
+        <v>169</v>
       </c>
       <c r="G54" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H54" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3042,61 +3060,61 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B55" t="s">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D55" t="s">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F55" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="G55" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H55" t="s">
         <v>11</v>
       </c>
       <c r="I55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B56" t="s">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="D56" t="s">
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F56" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
@@ -3110,27 +3128,27 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B57" t="s">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="D57" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="E57" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
+        <v>178</v>
       </c>
       <c r="G57" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
@@ -3141,37 +3159,37 @@
       </c>
       <c r="J57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B58" t="s">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="D58" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F58" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="H58" t="s">
         <v>11</v>
       </c>
       <c r="I58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -3180,62 +3198,62 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B59" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D59" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E59" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F59" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G59" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="H59" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B60" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="D60" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G60" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H60" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I60" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3248,16 +3266,16 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B61" t="s">
         <v>76</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="D61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E61" t="s">
         <v>33</v>
@@ -3266,7 +3284,7 @@
         <v>33</v>
       </c>
       <c r="G61" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s">
         <v>11</v>
@@ -3282,104 +3300,36 @@
     </row>
     <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="B62" t="s">
         <v>76</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D62" t="s">
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F62" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G62" t="s">
-        <v>174</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I62" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J62" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
-      </c>
-      <c r="J62" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="11">
-        <v>46280</v>
-      </c>
-      <c r="B63" t="s">
-        <v>76</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D63" t="s">
-        <v>12</v>
-      </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" t="s">
-        <v>10</v>
-      </c>
-      <c r="G63" t="s">
-        <v>176</v>
-      </c>
-      <c r="H63" t="s">
-        <v>11</v>
-      </c>
-      <c r="I63" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J63" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A64" s="11">
-        <v>46280</v>
-      </c>
-      <c r="B64" t="s">
-        <v>76</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D64" t="s">
-        <v>178</v>
-      </c>
-      <c r="E64" t="s">
-        <v>27</v>
-      </c>
-      <c r="F64" t="s">
-        <v>27</v>
-      </c>
-      <c r="G64" t="s">
-        <v>179</v>
-      </c>
-      <c r="H64" t="s">
-        <v>74</v>
-      </c>
-      <c r="I64" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J64" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
       </c>
     </row>
   </sheetData>
@@ -3949,7 +3899,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B49" t="s">
         <v>44</v>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010FAEEE-0502-4068-8AFC-D0E28A8E9CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A3C5BB-15CD-433C-9DE1-128FC474DFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="179">
   <si>
     <t>Fecha</t>
   </si>
@@ -267,9 +267,6 @@
     <t>Effetá</t>
   </si>
   <si>
-    <t>Plaza Juárez</t>
-  </si>
-  <si>
     <t>Síntesis</t>
   </si>
   <si>
@@ -285,316 +282,298 @@
     <t>Publicidad</t>
   </si>
   <si>
-    <t>Afectaciones Por Lluvias</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>Cintillo</t>
-  </si>
-  <si>
-    <t>Fiestas Patrias</t>
-  </si>
-  <si>
-    <t>Reforma Electoral</t>
-  </si>
-  <si>
     <t>El Mexe</t>
   </si>
   <si>
     <t>Grito De Independencia</t>
   </si>
   <si>
-    <t>Alcoholímetro</t>
-  </si>
-  <si>
-    <t>Iniciativa</t>
-  </si>
-  <si>
-    <t>Sedena</t>
-  </si>
-  <si>
-    <t>Intervención extranjera</t>
-  </si>
-  <si>
     <t>Pachuca Brilla</t>
   </si>
   <si>
-    <t>Conmemoran 216 años de la Independencia</t>
-  </si>
-  <si>
-    <t>Desfile cívico</t>
-  </si>
-  <si>
-    <t>Seis dieron positivo en el alcoholímetro</t>
-  </si>
-  <si>
-    <t>Policía municipal</t>
-  </si>
-  <si>
-    <t>Escuelas enfrentan reducción de alumnos</t>
-  </si>
-  <si>
-    <t>Reducción de alumnos</t>
-  </si>
-  <si>
-    <t>Sin rechazo empresarial la jornada de 40 horas</t>
-  </si>
-  <si>
-    <t>Ley 40 horas</t>
-  </si>
-  <si>
-    <t>Llama obispo a aclarar la muerte de párroco</t>
-  </si>
-  <si>
-    <t>Homicidio de párroco</t>
-  </si>
-  <si>
-    <t>Saldo blanco durante los festejos de Independencia</t>
-  </si>
-  <si>
-    <t>Ciudadanos disfrutaron noche del Grito</t>
-  </si>
-  <si>
-    <t>Asesinan a párroco de Huejutla</t>
-  </si>
-  <si>
-    <t>México no será colonia ni protectorado de nadie, dice Sheinbaum</t>
-  </si>
-  <si>
-    <t>Llevan fiestas patrias a La Habana, Cuba</t>
-  </si>
-  <si>
-    <t>Preparan una intervención al pisal</t>
-  </si>
-  <si>
-    <t>Pisal Ben Gurión</t>
-  </si>
-  <si>
-    <t>El Checho abre puerta mexicana</t>
-  </si>
-  <si>
-    <t>Barsa sigue imparable</t>
-  </si>
-  <si>
-    <t>"¡Que viva la transformación!", fue la arenga de Julio Menchaca</t>
-  </si>
-  <si>
-    <t>Los daños en las vialidades, por las lluvias, dice titular de Sipdus</t>
-  </si>
-  <si>
     <t>Sipdus</t>
   </si>
   <si>
-    <t>Indaga PGJEH muerte en la Normal Mexe</t>
-  </si>
-  <si>
-    <t>Desfilaron más de 4 mil durante la parada cívica: 16 de septiembre</t>
-  </si>
-  <si>
-    <t>Celebra el PRI cambios en La Reforma para elección 2027</t>
-  </si>
-  <si>
-    <t>PRI</t>
-  </si>
-  <si>
-    <t>Buscan blindar la elección mediante pacto de civilidad</t>
-  </si>
-  <si>
-    <t>Reunión con partidos</t>
-  </si>
-  <si>
-    <t>Dictan sentencia a 168 secuestradores en 4 años</t>
-  </si>
-  <si>
-    <t>Combate Al Secuestro</t>
-  </si>
-  <si>
-    <t>Lanza Tránsito de Pachuca curso de manejo gratuito</t>
-  </si>
-  <si>
-    <t>Curso de manejo</t>
-  </si>
-  <si>
-    <t>Van 12 mmdp en apooyos sociales para Hidalgo</t>
-  </si>
-  <si>
-    <t>Programas Del Bienestar</t>
-  </si>
-  <si>
-    <t>Desfile. Reportan saldo blanco en celebraciones de Independencia</t>
-  </si>
-  <si>
-    <t>Arrancan obras en pisal del parque</t>
-  </si>
-  <si>
-    <t>Europa y su obsesión con la migración</t>
-  </si>
-  <si>
-    <t>Migración</t>
-  </si>
-  <si>
-    <t>Doblete a Donald Trump: la Reserva sube las tasas y Canadá se une a la UE</t>
-  </si>
-  <si>
-    <t>Temas internacionales</t>
-  </si>
-  <si>
-    <t>Trevilla: fuerzas armadas están listas para todo reto</t>
-  </si>
-  <si>
-    <t>Decisión de FED y crudo caro pegan a boom de IA</t>
-  </si>
-  <si>
-    <t>Inteligencia Artificial</t>
-  </si>
-  <si>
-    <t>Carecen de Atlas de Riesgos 15 municipios afectados por vaguada</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>Atlas de Riesgos</t>
-  </si>
-  <si>
-    <t>En su mensaje previo al Desfile Cívico Militar por el 216 aniversario de la Independencia, Sheinbaum afirmó que la lucha nació de una causa  popular, lo que distingue a México de otros procesos de América Latina.</t>
-  </si>
-  <si>
-    <t>Fotonota</t>
-  </si>
-  <si>
-    <t>Ni colonia ni protectorado, proclama Sheinbaum al celebrar la Independencia</t>
-  </si>
-  <si>
-    <t>Trump pide castigo para narcopolíticos</t>
-  </si>
-  <si>
-    <t>El forcejeo por la candidatura a la presidencia municipal de Pachuca no es tan terso como parece,  genera dudas y deja la puerta entreabierta a una sorpresa en las urnas electorales de 2027”.</t>
-  </si>
-  <si>
-    <t>Candidaturas</t>
-  </si>
-  <si>
-    <t>Más de 4 mil  personas participaron en desfile cívico-militar en Pachuca</t>
-  </si>
-  <si>
-    <t>Rehabilitación del Pisal Monumental podría concluir en marzo de 2027</t>
-  </si>
-  <si>
-    <t>Alcoholímetro de Pachuca retiene seis vehículos durante operativo por fiestas patrias</t>
-  </si>
-  <si>
-    <t>Fallece Juana Olivia Alarcón Rivera, diputada de Nueva Alianza Hidalgo</t>
-  </si>
-  <si>
-    <t>GLPANALH</t>
-  </si>
-  <si>
-    <t>Deceso diputada</t>
-  </si>
-  <si>
-    <t>Asesinan a sacerdote en Lolotla; Procuraduría investiga</t>
-  </si>
-  <si>
-    <t>PRI celebra que se descartara resparto alfabético de candidaturas</t>
-  </si>
-  <si>
-    <t>SEPH asegura que hay diálogo con El Mexe</t>
-  </si>
-  <si>
-    <t>¿Qué cambió con la reforma electoral en Hidalgo?</t>
-  </si>
-  <si>
-    <t>SSPH descarta hackeo al C5i de Hidalgo</t>
-  </si>
-  <si>
-    <t>C5i</t>
-  </si>
-  <si>
-    <t>Hackeo</t>
-  </si>
-  <si>
-    <t>Espacio Hidalgo pelea por conservar su registro</t>
-  </si>
-  <si>
-    <t>pérdida de registro</t>
-  </si>
-  <si>
-    <t>Usarán inteligencia artificial para analizar tráfico en Pachuca</t>
-  </si>
-  <si>
-    <t>Docente de la UTSH participa en seminario internacional en China</t>
-  </si>
-  <si>
-    <t>Encuentro internacional</t>
-  </si>
-  <si>
-    <t>Cercanía y unión caracterizaron los festejos patrios en Hidalgo</t>
-  </si>
-  <si>
-    <t>Pachuca conmemora el 216 aniversario del inicio de la Independencia de México</t>
-  </si>
-  <si>
-    <t>En Tula realizan evento cívico y desfile con motivo del 216 aniversario de la Independencia de México</t>
-  </si>
-  <si>
-    <t>Pachuca concluye operativo de Fiestas Patrias con saldo blanco</t>
-  </si>
-  <si>
-    <t>Repuve acerca registro vehicular gratuito a todas las regiones</t>
-  </si>
-  <si>
-    <t>Repuve</t>
-  </si>
-  <si>
-    <t>Unidad móvil</t>
-  </si>
-  <si>
-    <t>Hidalgo concluye festejos patrios con desfile cívico-militar</t>
-  </si>
-  <si>
-    <t>Participaron 158 elementos de Seguridad de Pachuca en eventos</t>
-  </si>
-  <si>
-    <t>Repuve acerca registro vehicular gratuito en todas las regiones</t>
-  </si>
-  <si>
-    <t>Registraron saldo blanco durante las celebraciones</t>
-  </si>
-  <si>
-    <t>Capacita SEPH a coordinadores de los Centros de Maestros</t>
-  </si>
-  <si>
-    <t>Capacitación docente</t>
-  </si>
-  <si>
-    <t>José José Sinfónico</t>
-  </si>
-  <si>
-    <t>Cecultah</t>
-  </si>
-  <si>
-    <t>Concierto Sinfónico</t>
-  </si>
-  <si>
-    <t>Con la pirotecnia no se juega</t>
-  </si>
-  <si>
     <t>Pirotecnia</t>
   </si>
   <si>
-    <t>Saldo blanco en Hidalgo tras festejos patrios</t>
-  </si>
-  <si>
-    <t>Ejecutan a sacerdote católico</t>
-  </si>
-  <si>
-    <t>Proponen crear la medalla ""Leona Vicario""</t>
-  </si>
-  <si>
-    <t>"México no se doblega, no se arrodilla y nunca se vende"</t>
+    <t>Denuncian falta de respuesta del Congreso</t>
+  </si>
+  <si>
+    <t>Municipio 85</t>
+  </si>
+  <si>
+    <t>Cierran dos calles por obras de rehabilitación</t>
+  </si>
+  <si>
+    <t>Rehabilitación Vial</t>
+  </si>
+  <si>
+    <t>Pide Julio Menchaca prudencia en Jaltocán</t>
+  </si>
+  <si>
+    <t>Homicidio de sacerdote</t>
+  </si>
+  <si>
+    <t>Retiran lote de medicamento para diabetes</t>
+  </si>
+  <si>
+    <t>Salud</t>
+  </si>
+  <si>
+    <t>Farmacovigilancia</t>
+  </si>
+  <si>
+    <t>Exigen restituir a profesora en Jardín de Niños, en Tula</t>
+  </si>
+  <si>
+    <t>Básica</t>
+  </si>
+  <si>
+    <t>Exigen Restitución De Docente</t>
+  </si>
+  <si>
+    <t>Destinan 26 mil mdp para pista alterna Hidalgo-Querétaro</t>
+  </si>
+  <si>
+    <t>Ampliación carretera</t>
+  </si>
+  <si>
+    <t>Aumenta huachicoleo 17 por ciento en la entidad</t>
+  </si>
+  <si>
+    <t>Pemex</t>
+  </si>
+  <si>
+    <t>Huachicol</t>
+  </si>
+  <si>
+    <t>Menchaca, cuarto en aprobación nacional</t>
+  </si>
+  <si>
+    <t>Aprobación Gobernador</t>
+  </si>
+  <si>
+    <t>Buscan revivir parquímetros en Pachuca</t>
+  </si>
+  <si>
+    <t>Parquímetros</t>
+  </si>
+  <si>
+    <t>Desmontan el escenario en la Plaza Juárez</t>
+  </si>
+  <si>
+    <t>Reportan cuatro muertes violentas en solo 15 días</t>
+  </si>
+  <si>
+    <t>Homicidios</t>
+  </si>
+  <si>
+    <t>Pachuca esperará foros antes de fijar su postura sobre el carril confinado</t>
+  </si>
+  <si>
+    <t>Carril confinado</t>
+  </si>
+  <si>
+    <t>Dictan 142 sentencias penales a adolescentes</t>
+  </si>
+  <si>
+    <t>Sentencia a adolescentes</t>
+  </si>
+  <si>
+    <t>Ladran, pero no muerden</t>
+  </si>
+  <si>
+    <t>Anuncian histórica justa internacional</t>
+  </si>
+  <si>
+    <t>Paranacionales Conade</t>
+  </si>
+  <si>
+    <t>Congreso acumula tres diputados fallecidos estando en funciones</t>
+  </si>
+  <si>
+    <t>Deceso diputado</t>
+  </si>
+  <si>
+    <t>Clásico nacional de cuentas pendientes</t>
+  </si>
+  <si>
+    <t>El gobierno federal apuesta por reforzar la conexión terrestre</t>
+  </si>
+  <si>
+    <t>SICT</t>
+  </si>
+  <si>
+    <t>Es la segunda fase de la vía Tamazunchale-Huejutla</t>
+  </si>
+  <si>
+    <t>Carretera Huejutla</t>
+  </si>
+  <si>
+    <t>Endhó: una zona tóxica y cancerígena</t>
+  </si>
+  <si>
+    <t>Conagua</t>
+  </si>
+  <si>
+    <t>Presa Endhó</t>
+  </si>
+  <si>
+    <t>investiga la PGJEH crimen de sacerdsote en la sierra; piden evitar especulación</t>
+  </si>
+  <si>
+    <t>Inicia la intervención de 34 estaciones del Tuzobús en octubre</t>
+  </si>
+  <si>
+    <t>Sitmah</t>
+  </si>
+  <si>
+    <t>Rehabilitación estaciones Tuzobús</t>
+  </si>
+  <si>
+    <t>Van 72 paratletas a competencia nacional</t>
+  </si>
+  <si>
+    <t>En Guanajuato decomisan 59 millones de litros de huachicol</t>
+  </si>
+  <si>
+    <t>Combate Al Huachicol</t>
+  </si>
+  <si>
+    <t>No detectar a tiempo la diabetes agrava su impacto</t>
+  </si>
+  <si>
+    <t>Control de enfermedades</t>
+  </si>
+  <si>
+    <t>Invertirán 3 mdp para transformar Centro Veterinario en hospital</t>
+  </si>
+  <si>
+    <t>Hospital veterinario</t>
+  </si>
+  <si>
+    <t>Menchaca abandera a delegación paralímpica para nacional de Conade</t>
+  </si>
+  <si>
+    <t>Sin certeza, el cobro de 800 mdp de Accendo  pendientes: Hacienda</t>
+  </si>
+  <si>
+    <t>Accendo</t>
+  </si>
+  <si>
+    <t>Megaalmacén de Guanajuato: 59 millones de litros de huachicol</t>
+  </si>
+  <si>
+    <t>Todavía no arranca el proceso electoral local, pero los tiempos apremian y ya varios andan en  campaña. Algunos lo hacen de manera discreta y otros aprovechan los resquicios que deja la ley  para promover su imagen de manera anticipada”.</t>
+  </si>
+  <si>
+    <t>Investiga Procuraduría homicidio de párroco de Huejutla</t>
+  </si>
+  <si>
+    <t>Pachuca, único municipio mexicano presente en congreso internacional de bomberos</t>
+  </si>
+  <si>
+    <t>Congreso internacional de bomberos</t>
+  </si>
+  <si>
+    <t>Representarán 72 paradeportistas a Hidalgo en la justa Conade 2026</t>
+  </si>
+  <si>
+    <t>Inhide</t>
+  </si>
+  <si>
+    <t>Tendrá representación  indígena participación  limitada en cabildo de  Cardonal</t>
+  </si>
+  <si>
+    <t>Temas varios</t>
+  </si>
+  <si>
+    <t>Prevén rehabilitación de 20 fuentes en Pachuca</t>
+  </si>
+  <si>
+    <t>Rehabilitación de espacios públicos</t>
+  </si>
+  <si>
+    <t>Medécigo reporta avances en seguridad</t>
+  </si>
+  <si>
+    <t>Equipamiento policiaco</t>
+  </si>
+  <si>
+    <t>Menchaca, el cuarto gobernador con mayor aprobación del país: Mitofsky</t>
+  </si>
+  <si>
+    <t>Revés al TEEH</t>
+  </si>
+  <si>
+    <t>Resolución de juicio</t>
+  </si>
+  <si>
+    <t>Es todo un tema las normales rurales""</t>
+  </si>
+  <si>
+    <t>Menchaca confirma diálogo con Segob e Iglesia por crimen de sacerdote</t>
+  </si>
+  <si>
+    <t>Retienen 64 vehículos por dar transporte sin autorización</t>
+  </si>
+  <si>
+    <t>Concesiones transporte público</t>
+  </si>
+  <si>
+    <t>Menchaca pide prudencia tras dichos de alcalde contra sacerdote</t>
+  </si>
+  <si>
+    <t>Menchaca abandera a paratletas rumbo a la Conade 2026</t>
+  </si>
+  <si>
+    <t>Pachuca destaca como único municipio mexicano en congreso internacional de bomberos</t>
+  </si>
+  <si>
+    <t>Congreso Internacional</t>
+  </si>
+  <si>
+    <t>Impulsa Saderh al campo hidalguense con entrega de apoyos productivos en La Misión y Zimapán</t>
+  </si>
+  <si>
+    <t>Entrega De Apoyos</t>
+  </si>
+  <si>
+    <t>Revocan concesión y revisan paraderos tras accidente en Pachuca</t>
+  </si>
+  <si>
+    <t>Alistan definición de tarifas para taxis en Hidalgo</t>
+  </si>
+  <si>
+    <t>Tarifario de taxis</t>
+  </si>
+  <si>
+    <t>La pirotecnia no es un juego</t>
+  </si>
+  <si>
+    <t>Julio Menchaca abandera a paratletas rumbo a la Paralimpiada Nacional 2026</t>
+  </si>
+  <si>
+    <t>DIFH fortalece accesibilidad para personas con discapacidad</t>
+  </si>
+  <si>
+    <t>Apoyo a personas con discapacidad</t>
+  </si>
+  <si>
+    <t>Docente de la UTVM realiza estancia académica en Estados Unidos</t>
+  </si>
+  <si>
+    <t>Universidades</t>
+  </si>
+  <si>
+    <t>Movilidad Académica</t>
+  </si>
+  <si>
+    <t>Menchaca, cuarto gobernador con mayor aprobación ciudadana: Mitofsky</t>
   </si>
 </sst>
 </file>
@@ -841,8 +820,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J62" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J62" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J53" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J53" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1211,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1260,93 +1239,93 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="G3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -1357,67 +1336,67 @@
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="G5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="H5" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="G6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H6" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1428,98 +1407,98 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H7" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="G8" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="H8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B9" t="s">
         <v>71</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1527,37 +1506,37 @@
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1566,7 +1545,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B11" t="s">
         <v>71</v>
@@ -1575,35 +1554,35 @@
         <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>109</v>
@@ -1612,16 +1591,16 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
         <v>110</v>
       </c>
       <c r="H12" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1632,9 +1611,9 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B13" t="s">
         <v>73</v>
@@ -1646,20 +1625,20 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
       </c>
       <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1668,25 +1647,25 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B14" t="s">
         <v>73</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
@@ -1700,61 +1679,61 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="H15" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B16" t="s">
         <v>73</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
@@ -1765,105 +1744,105 @@
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B17" t="s">
         <v>73</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G17" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B18" t="s">
         <v>73</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>2</v>
+        <v>122</v>
       </c>
       <c r="G19" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1872,149 +1851,149 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="G20" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="G21" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H21" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J21" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
-      <c r="J21" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
       </c>
       <c r="I22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" t="s">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="G23" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H23" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D24" t="s">
         <v>9</v>
@@ -2026,10 +2005,10 @@
         <v>24</v>
       </c>
       <c r="G24" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="H24" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2040,49 +2019,49 @@
         <v>Gobernador</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
@@ -2094,7 +2073,7 @@
         <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
@@ -2110,168 +2089,168 @@
     </row>
     <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J27" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
-      <c r="J27" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="G28" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="H28" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B30" t="s">
         <v>68</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F30" t="s">
-        <v>138</v>
+        <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B31" t="s">
         <v>68</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="H31" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2280,195 +2259,195 @@
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D32" t="s">
         <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G33" t="s">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="H33" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D34" t="s">
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
-        <v>18</v>
+        <v>148</v>
       </c>
       <c r="G34" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="H34" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F35" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D36" t="s">
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
       </c>
       <c r="I36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D37" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E37" t="s">
         <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
@@ -2484,127 +2463,127 @@
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F38" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="G38" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="H38" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B39" t="s">
         <v>75</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="F39" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G39" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="H39" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B40" t="s">
         <v>75</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="F40" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B41" t="s">
         <v>75</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D41" t="s">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F41" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G41" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
@@ -2615,64 +2594,64 @@
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="11">
+        <v>46283</v>
+      </c>
+      <c r="B42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" t="s">
+        <v>27</v>
+      </c>
+      <c r="G42" t="s">
+        <v>161</v>
+      </c>
+      <c r="H42" t="s">
+        <v>11</v>
+      </c>
+      <c r="I42" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J42" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="11">
-        <v>46282</v>
-      </c>
-      <c r="B42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" t="s">
-        <v>33</v>
-      </c>
-      <c r="F42" t="s">
-        <v>33</v>
-      </c>
-      <c r="G42" t="s">
-        <v>86</v>
-      </c>
-      <c r="H42" t="s">
-        <v>11</v>
-      </c>
-      <c r="I42" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J42" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F43" t="s">
-        <v>157</v>
+        <v>24</v>
       </c>
       <c r="G43" t="s">
-        <v>158</v>
+        <v>92</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
@@ -2683,98 +2662,98 @@
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B44" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="F44" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="G44" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D45" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D46" t="s">
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="F46" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G46" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
@@ -2790,28 +2769,28 @@
     </row>
     <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F47" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G47" t="s">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="H47" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2819,30 +2798,30 @@
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D48" t="s">
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F48" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G48" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
@@ -2856,27 +2835,27 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D49" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="E49" t="s">
         <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -2892,59 +2871,59 @@
     </row>
     <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D50" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G50" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F51" t="s">
-        <v>169</v>
+        <v>36</v>
       </c>
       <c r="G51" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
@@ -2960,25 +2939,25 @@
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F52" t="s">
-        <v>24</v>
+        <v>176</v>
       </c>
       <c r="G52" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
@@ -2989,347 +2968,41 @@
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D53" t="s">
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F53" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="G53" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="H53" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="11">
-        <v>46282</v>
-      </c>
-      <c r="B54" t="s">
-        <v>93</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D54" t="s">
-        <v>12</v>
-      </c>
-      <c r="E54" t="s">
-        <v>23</v>
-      </c>
-      <c r="F54" t="s">
-        <v>169</v>
-      </c>
-      <c r="G54" t="s">
-        <v>170</v>
-      </c>
-      <c r="H54" t="s">
-        <v>11</v>
-      </c>
-      <c r="I54" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J54" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="11">
-        <v>46282</v>
-      </c>
-      <c r="B55" t="s">
-        <v>93</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D55" t="s">
-        <v>12</v>
-      </c>
-      <c r="E55" t="s">
-        <v>22</v>
-      </c>
-      <c r="F55" t="s">
-        <v>22</v>
-      </c>
-      <c r="G55" t="s">
-        <v>85</v>
-      </c>
-      <c r="H55" t="s">
-        <v>11</v>
-      </c>
-      <c r="I55" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J55" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="11">
-        <v>46282</v>
-      </c>
-      <c r="B56" t="s">
-        <v>93</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D56" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" t="s">
-        <v>26</v>
-      </c>
-      <c r="F56" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" t="s">
-        <v>176</v>
-      </c>
-      <c r="H56" t="s">
-        <v>11</v>
-      </c>
-      <c r="I56" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J56" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="11">
-        <v>46282</v>
-      </c>
-      <c r="B57" t="s">
-        <v>93</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D57" t="s">
-        <v>81</v>
-      </c>
-      <c r="E57" t="s">
-        <v>28</v>
-      </c>
-      <c r="F57" t="s">
-        <v>178</v>
-      </c>
-      <c r="G57" t="s">
-        <v>179</v>
-      </c>
-      <c r="H57" t="s">
-        <v>11</v>
-      </c>
-      <c r="I57" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J57" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="11">
-        <v>46282</v>
-      </c>
-      <c r="B58" t="s">
-        <v>93</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D58" t="s">
-        <v>81</v>
-      </c>
-      <c r="E58" t="s">
-        <v>16</v>
-      </c>
-      <c r="F58" t="s">
-        <v>16</v>
-      </c>
-      <c r="G58" t="s">
-        <v>181</v>
-      </c>
-      <c r="H58" t="s">
-        <v>11</v>
-      </c>
-      <c r="I58" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J58" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="11">
-        <v>46282</v>
-      </c>
-      <c r="B59" t="s">
-        <v>76</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D59" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" t="s">
-        <v>38</v>
-      </c>
-      <c r="F59" t="s">
-        <v>38</v>
-      </c>
-      <c r="G59" t="s">
-        <v>85</v>
-      </c>
-      <c r="H59" t="s">
-        <v>74</v>
-      </c>
-      <c r="I59" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J59" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="11">
-        <v>46282</v>
-      </c>
-      <c r="B60" t="s">
-        <v>76</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D60" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" t="s">
-        <v>17</v>
-      </c>
-      <c r="F60" t="s">
-        <v>17</v>
-      </c>
-      <c r="G60" t="s">
-        <v>103</v>
-      </c>
-      <c r="H60" t="s">
-        <v>70</v>
-      </c>
-      <c r="I60" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J60" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="11">
-        <v>46282</v>
-      </c>
-      <c r="B61" t="s">
-        <v>76</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D61" t="s">
-        <v>12</v>
-      </c>
-      <c r="E61" t="s">
-        <v>33</v>
-      </c>
-      <c r="F61" t="s">
-        <v>33</v>
-      </c>
-      <c r="G61" t="s">
-        <v>90</v>
-      </c>
-      <c r="H61" t="s">
-        <v>11</v>
-      </c>
-      <c r="I61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="11">
-        <v>46282</v>
-      </c>
-      <c r="B62" t="s">
-        <v>76</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D62" t="s">
-        <v>12</v>
-      </c>
-      <c r="E62" t="s">
-        <v>14</v>
-      </c>
-      <c r="F62" t="s">
-        <v>14</v>
-      </c>
-      <c r="G62" t="s">
-        <v>88</v>
-      </c>
-      <c r="H62" t="s">
-        <v>74</v>
-      </c>
-      <c r="I62" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J62" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
   </sheetData>
@@ -3899,7 +3572,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B49" t="s">
         <v>44</v>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A3C5BB-15CD-433C-9DE1-128FC474DFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DD9D3E-1ADB-40A9-A424-3904DD8286FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="190">
   <si>
     <t>Fecha</t>
   </si>
@@ -285,295 +285,328 @@
     <t>PAZ</t>
   </si>
   <si>
-    <t>El Mexe</t>
-  </si>
-  <si>
-    <t>Grito De Independencia</t>
-  </si>
-  <si>
     <t>Pachuca Brilla</t>
   </si>
   <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
-    <t>Pirotecnia</t>
-  </si>
-  <si>
-    <t>Denuncian falta de respuesta del Congreso</t>
-  </si>
-  <si>
-    <t>Municipio 85</t>
-  </si>
-  <si>
-    <t>Cierran dos calles por obras de rehabilitación</t>
-  </si>
-  <si>
-    <t>Rehabilitación Vial</t>
-  </si>
-  <si>
-    <t>Pide Julio Menchaca prudencia en Jaltocán</t>
-  </si>
-  <si>
     <t>Homicidio de sacerdote</t>
   </si>
   <si>
-    <t>Retiran lote de medicamento para diabetes</t>
-  </si>
-  <si>
-    <t>Salud</t>
-  </si>
-  <si>
-    <t>Farmacovigilancia</t>
-  </si>
-  <si>
-    <t>Exigen restituir a profesora en Jardín de Niños, en Tula</t>
-  </si>
-  <si>
-    <t>Básica</t>
-  </si>
-  <si>
-    <t>Exigen Restitución De Docente</t>
-  </si>
-  <si>
-    <t>Destinan 26 mil mdp para pista alterna Hidalgo-Querétaro</t>
-  </si>
-  <si>
-    <t>Ampliación carretera</t>
-  </si>
-  <si>
-    <t>Aumenta huachicoleo 17 por ciento en la entidad</t>
-  </si>
-  <si>
-    <t>Pemex</t>
-  </si>
-  <si>
     <t>Huachicol</t>
   </si>
   <si>
-    <t>Menchaca, cuarto en aprobación nacional</t>
-  </si>
-  <si>
-    <t>Aprobación Gobernador</t>
-  </si>
-  <si>
-    <t>Buscan revivir parquímetros en Pachuca</t>
-  </si>
-  <si>
-    <t>Parquímetros</t>
-  </si>
-  <si>
-    <t>Desmontan el escenario en la Plaza Juárez</t>
-  </si>
-  <si>
-    <t>Reportan cuatro muertes violentas en solo 15 días</t>
-  </si>
-  <si>
     <t>Homicidios</t>
   </si>
   <si>
-    <t>Pachuca esperará foros antes de fijar su postura sobre el carril confinado</t>
-  </si>
-  <si>
-    <t>Carril confinado</t>
-  </si>
-  <si>
-    <t>Dictan 142 sentencias penales a adolescentes</t>
-  </si>
-  <si>
-    <t>Sentencia a adolescentes</t>
-  </si>
-  <si>
-    <t>Ladran, pero no muerden</t>
-  </si>
-  <si>
-    <t>Anuncian histórica justa internacional</t>
-  </si>
-  <si>
-    <t>Paranacionales Conade</t>
-  </si>
-  <si>
-    <t>Congreso acumula tres diputados fallecidos estando en funciones</t>
-  </si>
-  <si>
-    <t>Deceso diputado</t>
-  </si>
-  <si>
-    <t>Clásico nacional de cuentas pendientes</t>
-  </si>
-  <si>
-    <t>El gobierno federal apuesta por reforzar la conexión terrestre</t>
-  </si>
-  <si>
-    <t>SICT</t>
-  </si>
-  <si>
-    <t>Es la segunda fase de la vía Tamazunchale-Huejutla</t>
-  </si>
-  <si>
-    <t>Carretera Huejutla</t>
-  </si>
-  <si>
-    <t>Endhó: una zona tóxica y cancerígena</t>
-  </si>
-  <si>
-    <t>Conagua</t>
-  </si>
-  <si>
-    <t>Presa Endhó</t>
-  </si>
-  <si>
-    <t>investiga la PGJEH crimen de sacerdsote en la sierra; piden evitar especulación</t>
-  </si>
-  <si>
-    <t>Inicia la intervención de 34 estaciones del Tuzobús en octubre</t>
-  </si>
-  <si>
-    <t>Sitmah</t>
-  </si>
-  <si>
-    <t>Rehabilitación estaciones Tuzobús</t>
-  </si>
-  <si>
-    <t>Van 72 paratletas a competencia nacional</t>
-  </si>
-  <si>
-    <t>En Guanajuato decomisan 59 millones de litros de huachicol</t>
-  </si>
-  <si>
-    <t>Combate Al Huachicol</t>
-  </si>
-  <si>
-    <t>No detectar a tiempo la diabetes agrava su impacto</t>
-  </si>
-  <si>
-    <t>Control de enfermedades</t>
-  </si>
-  <si>
-    <t>Invertirán 3 mdp para transformar Centro Veterinario en hospital</t>
-  </si>
-  <si>
-    <t>Hospital veterinario</t>
-  </si>
-  <si>
-    <t>Menchaca abandera a delegación paralímpica para nacional de Conade</t>
-  </si>
-  <si>
-    <t>Sin certeza, el cobro de 800 mdp de Accendo  pendientes: Hacienda</t>
-  </si>
-  <si>
-    <t>Accendo</t>
-  </si>
-  <si>
-    <t>Megaalmacén de Guanajuato: 59 millones de litros de huachicol</t>
-  </si>
-  <si>
-    <t>Todavía no arranca el proceso electoral local, pero los tiempos apremian y ya varios andan en  campaña. Algunos lo hacen de manera discreta y otros aprovechan los resquicios que deja la ley  para promover su imagen de manera anticipada”.</t>
-  </si>
-  <si>
-    <t>Investiga Procuraduría homicidio de párroco de Huejutla</t>
-  </si>
-  <si>
-    <t>Pachuca, único municipio mexicano presente en congreso internacional de bomberos</t>
-  </si>
-  <si>
-    <t>Congreso internacional de bomberos</t>
-  </si>
-  <si>
-    <t>Representarán 72 paradeportistas a Hidalgo en la justa Conade 2026</t>
-  </si>
-  <si>
-    <t>Inhide</t>
-  </si>
-  <si>
-    <t>Tendrá representación  indígena participación  limitada en cabildo de  Cardonal</t>
-  </si>
-  <si>
     <t>Temas varios</t>
   </si>
   <si>
-    <t>Prevén rehabilitación de 20 fuentes en Pachuca</t>
-  </si>
-  <si>
-    <t>Rehabilitación de espacios públicos</t>
-  </si>
-  <si>
-    <t>Medécigo reporta avances en seguridad</t>
-  </si>
-  <si>
-    <t>Equipamiento policiaco</t>
-  </si>
-  <si>
-    <t>Menchaca, el cuarto gobernador con mayor aprobación del país: Mitofsky</t>
-  </si>
-  <si>
-    <t>Revés al TEEH</t>
-  </si>
-  <si>
-    <t>Resolución de juicio</t>
-  </si>
-  <si>
-    <t>Es todo un tema las normales rurales""</t>
-  </si>
-  <si>
-    <t>Menchaca confirma diálogo con Segob e Iglesia por crimen de sacerdote</t>
-  </si>
-  <si>
-    <t>Retienen 64 vehículos por dar transporte sin autorización</t>
-  </si>
-  <si>
-    <t>Concesiones transporte público</t>
-  </si>
-  <si>
-    <t>Menchaca pide prudencia tras dichos de alcalde contra sacerdote</t>
-  </si>
-  <si>
-    <t>Menchaca abandera a paratletas rumbo a la Conade 2026</t>
-  </si>
-  <si>
-    <t>Pachuca destaca como único municipio mexicano en congreso internacional de bomberos</t>
-  </si>
-  <si>
-    <t>Congreso Internacional</t>
-  </si>
-  <si>
-    <t>Impulsa Saderh al campo hidalguense con entrega de apoyos productivos en La Misión y Zimapán</t>
-  </si>
-  <si>
-    <t>Entrega De Apoyos</t>
-  </si>
-  <si>
-    <t>Revocan concesión y revisan paraderos tras accidente en Pachuca</t>
-  </si>
-  <si>
-    <t>Alistan definición de tarifas para taxis en Hidalgo</t>
-  </si>
-  <si>
     <t>Tarifario de taxis</t>
   </si>
   <si>
-    <t>La pirotecnia no es un juego</t>
-  </si>
-  <si>
-    <t>Julio Menchaca abandera a paratletas rumbo a la Paralimpiada Nacional 2026</t>
-  </si>
-  <si>
-    <t>DIFH fortalece accesibilidad para personas con discapacidad</t>
-  </si>
-  <si>
-    <t>Apoyo a personas con discapacidad</t>
-  </si>
-  <si>
-    <t>Docente de la UTVM realiza estancia académica en Estados Unidos</t>
-  </si>
-  <si>
     <t>Universidades</t>
   </si>
   <si>
-    <t>Movilidad Académica</t>
-  </si>
-  <si>
-    <t>Menchaca, cuarto gobernador con mayor aprobación ciudadana: Mitofsky</t>
+    <t>Temen menor pasaje con nuevas tarifas</t>
+  </si>
+  <si>
+    <t>Fortalecen acciones contra enfermedades diarreicas</t>
+  </si>
+  <si>
+    <t>EDAs</t>
+  </si>
+  <si>
+    <t>Llevan vacunas antirrábicas a cinco colonias de Pachuca</t>
+  </si>
+  <si>
+    <t>Vacunación Antirrábica</t>
+  </si>
+  <si>
+    <t>Morena Hidalgo define coordinadores este mes</t>
+  </si>
+  <si>
+    <t>Candidaturas</t>
+  </si>
+  <si>
+    <t>Sube el precio de jitomate y cebolla</t>
+  </si>
+  <si>
+    <t>Canasta básica</t>
+  </si>
+  <si>
+    <t>Vecinos votan por delegada y hacen peticiones</t>
+  </si>
+  <si>
+    <t>Elección de delegados</t>
+  </si>
+  <si>
+    <t>Hacen marcha y homenaje por párroco asesinado</t>
+  </si>
+  <si>
+    <t>Perfila Cruz Azul 1-5 mdd contra contaminación</t>
+  </si>
+  <si>
+    <t>Cruz Azul</t>
+  </si>
+  <si>
+    <t>Ejecutaron obras en Platah sin permiso</t>
+  </si>
+  <si>
+    <t>Platah</t>
+  </si>
+  <si>
+    <t>Sin tregua, huachicoleo en Cuautepec</t>
+  </si>
+  <si>
+    <t>Inicia caída de Morena, afirma MC</t>
+  </si>
+  <si>
+    <t>Crecen diabetes e hipertensión en la entidad</t>
+  </si>
+  <si>
+    <t>Vigilancia Epidemiológica</t>
+  </si>
+  <si>
+    <t>Hilda Miranda prepara más de 20 iniciativas en el Congreso</t>
+  </si>
+  <si>
+    <t>GLMorena</t>
+  </si>
+  <si>
+    <t>Trabajo legislativo</t>
+  </si>
+  <si>
+    <t>Cae incidencia delictiva casi 7 por ciento en mes de agosto</t>
+  </si>
+  <si>
+    <t>Incidencia Delictiva</t>
+  </si>
+  <si>
+    <t>Familiares y exparejas asesoran a legisladores</t>
+  </si>
+  <si>
+    <t>Nepotismo</t>
+  </si>
+  <si>
+    <t>Tuzas no dan una</t>
+  </si>
+  <si>
+    <t>Remontada con sello de Rondón</t>
+  </si>
+  <si>
+    <t>Concentran 2 municipios la mitad de homicidios</t>
+  </si>
+  <si>
+    <t>Con alcaldías de Hidalgo amplían influencia electoral de la ZMVM</t>
+  </si>
+  <si>
+    <t>ZMVM</t>
+  </si>
+  <si>
+    <t>INE actuará con adelantados de Morena y AN... si hay denuncia</t>
+  </si>
+  <si>
+    <t>Actos anticipados de campaña</t>
+  </si>
+  <si>
+    <t>Mochaorejas que pudo ser escritor, optó por el crimen</t>
+  </si>
+  <si>
+    <t>Pachuca rescata empate ante Tijuana</t>
+  </si>
+  <si>
+    <t>Padecimientos gastrointestinales 90% por agua y alimentos: SSH</t>
+  </si>
+  <si>
+    <t>EDAS</t>
+  </si>
+  <si>
+    <t>Estudio busca preservar una especie endémica de agave</t>
+  </si>
+  <si>
+    <t>Conservación Biodiversidad</t>
+  </si>
+  <si>
+    <t>SSPH detiene a expolicía de Tula con armas y droga</t>
+  </si>
+  <si>
+    <t>Detención de policía</t>
+  </si>
+  <si>
+    <t>Cae natalidad mientras avanza envejecimiento en la entidad: informe</t>
+  </si>
+  <si>
+    <t>Dinámica demográfica</t>
+  </si>
+  <si>
+    <t>Quince millones de personas expuestas por filtración de datos de Aeroméxico</t>
+  </si>
+  <si>
+    <t>Corrupción</t>
+  </si>
+  <si>
+    <t>Corren a ritmo de música regional</t>
+  </si>
+  <si>
+    <t>Carrera atlética</t>
+  </si>
+  <si>
+    <t>El avance de las mujeres se encuentra nuevamente en disputa en el panorama  mundial, con intentos de restringir nuestros derechos, que son los primeros en  perderse. Por ello debemos redoblar esfuerzos en nuestro país y en Hidalgo para  que la izquierda logre que estas desigualdades no se reproduzcan”.</t>
+  </si>
+  <si>
+    <t>Acuerdan CFE y gobierno de Hidalgo acciones para prevenir fallas eléctricas</t>
+  </si>
+  <si>
+    <t>Suministro eléctrico</t>
+  </si>
+  <si>
+    <t>Exhiben conflictos en cabildos durante informes de alcaldes</t>
+  </si>
+  <si>
+    <t>Enfrentamiento Político</t>
+  </si>
+  <si>
+    <t>Impulsa ITESHU conservación del agave con apoyo del Fondo Hidalgo</t>
+  </si>
+  <si>
+    <t>Pachuca Atentan a mano armada contra hombre en el centro de la capital hidalguense</t>
+  </si>
+  <si>
+    <t>Ataque Armado</t>
+  </si>
+  <si>
+    <t>Protestas marcan segundos informes de alcaldes en seis municipios de Hidalgo</t>
+  </si>
+  <si>
+    <t>Informe Alcalde</t>
+  </si>
+  <si>
+    <t>Cae líder criminal en Tula</t>
+  </si>
+  <si>
+    <t>Alcaldesa de Ajacuba acude al Tribunal por demora del IEEH</t>
+  </si>
+  <si>
+    <t>Juicio Político</t>
+  </si>
+  <si>
+    <t>Las buscaban por secuestro exprés</t>
+  </si>
+  <si>
+    <t>Aprehensión</t>
+  </si>
+  <si>
+    <t>Feria San Francisco tendrá límite de 35 mil visitantes</t>
+  </si>
+  <si>
+    <t>OEEH</t>
+  </si>
+  <si>
+    <t>Feria Pachuca</t>
+  </si>
+  <si>
+    <t>Hidalgo concentra tres de cada 10 delitos huachicoleros del país</t>
+  </si>
+  <si>
+    <t>Realizará Cobaeh Segunda Jornada Juvenil, Cultural y Académica</t>
+  </si>
+  <si>
+    <t>Cintillo</t>
+  </si>
+  <si>
+    <t>Media superior</t>
+  </si>
+  <si>
+    <t>Festival Cultural</t>
+  </si>
+  <si>
+    <t>Inspira César Costa a la FUL con un mensaje de vida y anhelos</t>
+  </si>
+  <si>
+    <t>Feria Del Libro</t>
+  </si>
+  <si>
+    <t>Ana María Rivera encabeza inicio de obra de drenaje sanitario en La Palma</t>
+  </si>
+  <si>
+    <t>Drenaje</t>
+  </si>
+  <si>
+    <t>Hidalgo, sede de la tercera Gimnasiada Nacional</t>
+  </si>
+  <si>
+    <t>Gimnasiada Nacional</t>
+  </si>
+  <si>
+    <t>Tula participa en simulacro nacional</t>
+  </si>
+  <si>
+    <t>Simulacro Sismo</t>
+  </si>
+  <si>
+    <t>El 18° Festival Nacional de Guitarra Ramón Noble reunirá en Hidalgo a intérpretes de México y Texas</t>
+  </si>
+  <si>
+    <t>Instituciones de Salud y municipios acuerdan acciones para prevenir enfermedades diarreicas y fortalecer vigilancia en la calidad del agua</t>
+  </si>
+  <si>
+    <t>Festival Cultural San Francisco</t>
+  </si>
+  <si>
+    <t>Orquesta Filarmónica de Pachuca se presentará en el Festival Cultural San Francisco 2026</t>
+  </si>
+  <si>
+    <t>Tuzos rescatan empate ante Xolos con doblete de Rondón</t>
+  </si>
+  <si>
+    <t>SSPH asegura generador de violencia en la región de Tula</t>
+  </si>
+  <si>
+    <t>Investigación del ITESHU impulsa conservación del agave en Hidalgo</t>
+  </si>
+  <si>
+    <t>¡Ya viene el Festival Internacional del Paste en Real del Monte!</t>
+  </si>
+  <si>
+    <t>Festival Del Paste</t>
+  </si>
+  <si>
+    <t>Hidalgo te acompaña, estés donde estés</t>
+  </si>
+  <si>
+    <t>Atención A Migrantes</t>
+  </si>
+  <si>
+    <t>Plaza Juárez</t>
+  </si>
+  <si>
+    <t>Auto impacta colectiva en Pachuca; reportan seis heridos</t>
+  </si>
+  <si>
+    <t>Accidente transporte público</t>
+  </si>
+  <si>
+    <t>Acusan a Aeroméxico de posible filtración de datos personales</t>
+  </si>
+  <si>
+    <t>corrupción</t>
+  </si>
+  <si>
+    <t>Pachuca se ha convertido en una ciudad receptora de migrantes, provenientes sobre todo del Estado de México, y no ha dado tiempo para un crecimiento con planeación, por lo que la falta de servicios es notoria en muchos puntos de la capital.</t>
+  </si>
+  <si>
+    <t>Editorial</t>
+  </si>
+  <si>
+    <t>Falta de servicios públicos</t>
+  </si>
+  <si>
+    <t>Alcaldesa deja fuera a asambleístas de su informe</t>
+  </si>
+  <si>
+    <t>¿Cuándo debo volar por los aires a Irán?""</t>
+  </si>
+  <si>
+    <t>Temas internacionales</t>
   </si>
 </sst>
 </file>
@@ -820,8 +853,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J53" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J53" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J59" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J59" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1190,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1239,59 +1272,59 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H2" t="s">
         <v>70</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -1305,58 +1338,58 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
         <v>95</v>
@@ -1366,7 +1399,7 @@
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Partidos</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1375,7 +1408,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
@@ -1384,57 +1417,57 @@
         <v>96</v>
       </c>
       <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H6" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J6" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>46286</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
         <v>9</v>
       </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J6" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
-        <v>46283</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
         <v>99</v>
       </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>100</v>
-      </c>
       <c r="H7" t="s">
         <v>11</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1443,229 +1476,229 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s">
         <v>70</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B9" t="s">
         <v>71</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H9" t="s">
         <v>74</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B11" t="s">
         <v>71</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="G12" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
       </c>
       <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B14" t="s">
         <v>73</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="G14" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
@@ -1679,95 +1712,95 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="H15" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B16" t="s">
         <v>73</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H16" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B17" t="s">
         <v>73</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G17" t="s">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
@@ -1783,13 +1816,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B18" t="s">
         <v>73</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
@@ -1815,197 +1848,197 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B20" t="s">
         <v>78</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="G20" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B21" t="s">
         <v>78</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>126</v>
+        <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H21" t="s">
         <v>70</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B22" t="s">
         <v>78</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
       </c>
       <c r="I22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B23" t="s">
         <v>78</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="H23" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B24" t="s">
         <v>78</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F24" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
@@ -2016,105 +2049,105 @@
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B25" t="s">
         <v>78</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G26" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B27" t="s">
         <v>68</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2123,232 +2156,232 @@
     </row>
     <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B28" t="s">
         <v>68</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F28" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="H28" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B29" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B30" t="s">
         <v>68</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G31" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="H31" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B32" t="s">
         <v>76</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="H32" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B33" t="s">
         <v>76</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B34" t="s">
         <v>76</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D34" t="s">
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F34" t="s">
-        <v>148</v>
+        <v>22</v>
       </c>
       <c r="G34" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="H34" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2361,28 +2394,28 @@
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E35" t="s">
         <v>16</v>
       </c>
       <c r="F35" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H35" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2395,50 +2428,50 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G36" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
       </c>
       <c r="I36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B37" t="s">
         <v>75</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D37" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E37" t="s">
         <v>16</v>
@@ -2447,7 +2480,7 @@
         <v>79</v>
       </c>
       <c r="G37" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
@@ -2461,30 +2494,30 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B38" t="s">
         <v>75</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="H38" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2492,99 +2525,99 @@
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B39" t="s">
         <v>75</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="F39" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="G39" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B40" t="s">
         <v>75</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="G40" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C41" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D41" t="s">
+        <v>157</v>
+      </c>
+      <c r="E41" t="s">
+        <v>26</v>
+      </c>
+      <c r="F41" t="s">
+        <v>158</v>
+      </c>
+      <c r="G41" t="s">
         <v>159</v>
       </c>
-      <c r="D41" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" t="s">
-        <v>24</v>
-      </c>
-      <c r="F41" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" t="s">
-        <v>92</v>
-      </c>
       <c r="H41" t="s">
         <v>11</v>
       </c>
@@ -2594,12 +2627,12 @@
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B42" t="s">
         <v>77</v>
@@ -2611,10 +2644,10 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="F42" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="G42" t="s">
         <v>161</v>
@@ -2624,16 +2657,16 @@
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B43" t="s">
         <v>77</v>
@@ -2642,50 +2675,50 @@
         <v>162</v>
       </c>
       <c r="D43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F43" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B44" t="s">
         <v>77</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G44" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
@@ -2696,18 +2729,18 @@
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B45" t="s">
         <v>77</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D45" t="s">
         <v>12</v>
@@ -2719,7 +2752,7 @@
         <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
@@ -2735,25 +2768,25 @@
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B46" t="s">
         <v>77</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D46" t="s">
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="F46" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G46" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
@@ -2767,27 +2800,27 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B47" t="s">
         <v>77</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
@@ -2803,25 +2836,25 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B48" t="s">
         <v>77</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D48" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="E48" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F48" t="s">
-        <v>27</v>
+        <v>153</v>
       </c>
       <c r="G48" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
@@ -2835,80 +2868,80 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>171</v>
       </c>
       <c r="D49" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G49" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
       </c>
       <c r="I49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>172</v>
       </c>
       <c r="D50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G50" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>173</v>
@@ -2917,13 +2950,13 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F51" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G51" t="s">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
@@ -2939,13 +2972,13 @@
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D52" t="s">
         <v>12</v>
@@ -2954,10 +2987,10 @@
         <v>26</v>
       </c>
       <c r="F52" t="s">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="G52" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
@@ -2973,36 +3006,240 @@
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D53" t="s">
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="H53" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J53" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="11">
+        <v>46286</v>
+      </c>
+      <c r="B54" t="s">
+        <v>82</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D54" t="s">
+        <v>80</v>
+      </c>
+      <c r="E54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" t="s">
+        <v>178</v>
+      </c>
+      <c r="H54" t="s">
+        <v>11</v>
+      </c>
+      <c r="I54" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J53" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+      <c r="J54" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="11">
+        <v>46286</v>
+      </c>
+      <c r="B55" t="s">
+        <v>179</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" t="s">
+        <v>27</v>
+      </c>
+      <c r="G55" t="s">
+        <v>181</v>
+      </c>
+      <c r="H55" t="s">
+        <v>70</v>
+      </c>
+      <c r="I55" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J55" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56" s="11">
+        <v>46286</v>
+      </c>
+      <c r="B56" t="s">
+        <v>179</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" t="s">
+        <v>183</v>
+      </c>
+      <c r="H56" t="s">
+        <v>70</v>
+      </c>
+      <c r="I56" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J56" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A57" s="11">
+        <v>46286</v>
+      </c>
+      <c r="B57" t="s">
+        <v>179</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D57" t="s">
+        <v>185</v>
+      </c>
+      <c r="E57" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" t="s">
+        <v>186</v>
+      </c>
+      <c r="H57" t="s">
+        <v>70</v>
+      </c>
+      <c r="I57" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J57" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="11">
+        <v>46286</v>
+      </c>
+      <c r="B58" t="s">
+        <v>179</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>16</v>
+      </c>
+      <c r="F58" t="s">
+        <v>79</v>
+      </c>
+      <c r="G58" t="s">
+        <v>146</v>
+      </c>
+      <c r="H58" t="s">
+        <v>70</v>
+      </c>
+      <c r="I58" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J58" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="11">
+        <v>46286</v>
+      </c>
+      <c r="B59" t="s">
+        <v>179</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" t="s">
+        <v>189</v>
+      </c>
+      <c r="H59" t="s">
+        <v>70</v>
+      </c>
+      <c r="I59" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J59" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
       </c>
     </row>
   </sheetData>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DD9D3E-1ADB-40A9-A424-3904DD8286FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DEBEC3-352C-41C2-BEFC-2CA867FA63E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="185">
   <si>
     <t>Fecha</t>
   </si>
@@ -291,322 +291,307 @@
     <t>Homicidio de sacerdote</t>
   </si>
   <si>
-    <t>Huachicol</t>
-  </si>
-  <si>
-    <t>Homicidios</t>
-  </si>
-  <si>
-    <t>Temas varios</t>
-  </si>
-  <si>
     <t>Tarifario de taxis</t>
   </si>
   <si>
-    <t>Universidades</t>
-  </si>
-  <si>
-    <t>Temen menor pasaje con nuevas tarifas</t>
-  </si>
-  <si>
-    <t>Fortalecen acciones contra enfermedades diarreicas</t>
-  </si>
-  <si>
-    <t>EDAs</t>
-  </si>
-  <si>
-    <t>Llevan vacunas antirrábicas a cinco colonias de Pachuca</t>
-  </si>
-  <si>
-    <t>Vacunación Antirrábica</t>
-  </si>
-  <si>
-    <t>Morena Hidalgo define coordinadores este mes</t>
-  </si>
-  <si>
-    <t>Candidaturas</t>
-  </si>
-  <si>
-    <t>Sube el precio de jitomate y cebolla</t>
-  </si>
-  <si>
-    <t>Canasta básica</t>
-  </si>
-  <si>
-    <t>Vecinos votan por delegada y hacen peticiones</t>
-  </si>
-  <si>
-    <t>Elección de delegados</t>
-  </si>
-  <si>
-    <t>Hacen marcha y homenaje por párroco asesinado</t>
-  </si>
-  <si>
-    <t>Perfila Cruz Azul 1-5 mdd contra contaminación</t>
-  </si>
-  <si>
-    <t>Cruz Azul</t>
-  </si>
-  <si>
-    <t>Ejecutaron obras en Platah sin permiso</t>
-  </si>
-  <si>
-    <t>Platah</t>
-  </si>
-  <si>
-    <t>Sin tregua, huachicoleo en Cuautepec</t>
-  </si>
-  <si>
-    <t>Inicia caída de Morena, afirma MC</t>
-  </si>
-  <si>
-    <t>Crecen diabetes e hipertensión en la entidad</t>
-  </si>
-  <si>
-    <t>Vigilancia Epidemiológica</t>
-  </si>
-  <si>
-    <t>Hilda Miranda prepara más de 20 iniciativas en el Congreso</t>
-  </si>
-  <si>
-    <t>GLMorena</t>
-  </si>
-  <si>
-    <t>Trabajo legislativo</t>
-  </si>
-  <si>
-    <t>Cae incidencia delictiva casi 7 por ciento en mes de agosto</t>
-  </si>
-  <si>
-    <t>Incidencia Delictiva</t>
-  </si>
-  <si>
-    <t>Familiares y exparejas asesoran a legisladores</t>
-  </si>
-  <si>
-    <t>Nepotismo</t>
-  </si>
-  <si>
-    <t>Tuzas no dan una</t>
-  </si>
-  <si>
-    <t>Remontada con sello de Rondón</t>
-  </si>
-  <si>
-    <t>Concentran 2 municipios la mitad de homicidios</t>
-  </si>
-  <si>
-    <t>Con alcaldías de Hidalgo amplían influencia electoral de la ZMVM</t>
-  </si>
-  <si>
-    <t>ZMVM</t>
-  </si>
-  <si>
-    <t>INE actuará con adelantados de Morena y AN... si hay denuncia</t>
-  </si>
-  <si>
-    <t>Actos anticipados de campaña</t>
-  </si>
-  <si>
-    <t>Mochaorejas que pudo ser escritor, optó por el crimen</t>
-  </si>
-  <si>
-    <t>Pachuca rescata empate ante Tijuana</t>
-  </si>
-  <si>
-    <t>Padecimientos gastrointestinales 90% por agua y alimentos: SSH</t>
-  </si>
-  <si>
-    <t>EDAS</t>
-  </si>
-  <si>
-    <t>Estudio busca preservar una especie endémica de agave</t>
-  </si>
-  <si>
-    <t>Conservación Biodiversidad</t>
-  </si>
-  <si>
-    <t>SSPH detiene a expolicía de Tula con armas y droga</t>
-  </si>
-  <si>
-    <t>Detención de policía</t>
-  </si>
-  <si>
-    <t>Cae natalidad mientras avanza envejecimiento en la entidad: informe</t>
-  </si>
-  <si>
-    <t>Dinámica demográfica</t>
-  </si>
-  <si>
-    <t>Quince millones de personas expuestas por filtración de datos de Aeroméxico</t>
-  </si>
-  <si>
-    <t>Corrupción</t>
-  </si>
-  <si>
-    <t>Corren a ritmo de música regional</t>
-  </si>
-  <si>
-    <t>Carrera atlética</t>
-  </si>
-  <si>
-    <t>El avance de las mujeres se encuentra nuevamente en disputa en el panorama  mundial, con intentos de restringir nuestros derechos, que son los primeros en  perderse. Por ello debemos redoblar esfuerzos en nuestro país y en Hidalgo para  que la izquierda logre que estas desigualdades no se reproduzcan”.</t>
-  </si>
-  <si>
-    <t>Acuerdan CFE y gobierno de Hidalgo acciones para prevenir fallas eléctricas</t>
-  </si>
-  <si>
-    <t>Suministro eléctrico</t>
-  </si>
-  <si>
-    <t>Exhiben conflictos en cabildos durante informes de alcaldes</t>
-  </si>
-  <si>
-    <t>Enfrentamiento Político</t>
-  </si>
-  <si>
-    <t>Impulsa ITESHU conservación del agave con apoyo del Fondo Hidalgo</t>
-  </si>
-  <si>
-    <t>Pachuca Atentan a mano armada contra hombre en el centro de la capital hidalguense</t>
-  </si>
-  <si>
     <t>Ataque Armado</t>
   </si>
   <si>
-    <t>Protestas marcan segundos informes de alcaldes en seis municipios de Hidalgo</t>
-  </si>
-  <si>
-    <t>Informe Alcalde</t>
-  </si>
-  <si>
-    <t>Cae líder criminal en Tula</t>
-  </si>
-  <si>
-    <t>Alcaldesa de Ajacuba acude al Tribunal por demora del IEEH</t>
-  </si>
-  <si>
-    <t>Juicio Político</t>
-  </si>
-  <si>
-    <t>Las buscaban por secuestro exprés</t>
-  </si>
-  <si>
-    <t>Aprehensión</t>
-  </si>
-  <si>
-    <t>Feria San Francisco tendrá límite de 35 mil visitantes</t>
-  </si>
-  <si>
     <t>OEEH</t>
   </si>
   <si>
     <t>Feria Pachuca</t>
   </si>
   <si>
-    <t>Hidalgo concentra tres de cada 10 delitos huachicoleros del país</t>
-  </si>
-  <si>
-    <t>Realizará Cobaeh Segunda Jornada Juvenil, Cultural y Académica</t>
-  </si>
-  <si>
     <t>Cintillo</t>
   </si>
   <si>
-    <t>Media superior</t>
-  </si>
-  <si>
-    <t>Festival Cultural</t>
-  </si>
-  <si>
-    <t>Inspira César Costa a la FUL con un mensaje de vida y anhelos</t>
-  </si>
-  <si>
-    <t>Feria Del Libro</t>
-  </si>
-  <si>
-    <t>Ana María Rivera encabeza inicio de obra de drenaje sanitario en La Palma</t>
-  </si>
-  <si>
-    <t>Drenaje</t>
-  </si>
-  <si>
-    <t>Hidalgo, sede de la tercera Gimnasiada Nacional</t>
-  </si>
-  <si>
     <t>Gimnasiada Nacional</t>
   </si>
   <si>
-    <t>Tula participa en simulacro nacional</t>
-  </si>
-  <si>
-    <t>Simulacro Sismo</t>
-  </si>
-  <si>
-    <t>El 18° Festival Nacional de Guitarra Ramón Noble reunirá en Hidalgo a intérpretes de México y Texas</t>
-  </si>
-  <si>
-    <t>Instituciones de Salud y municipios acuerdan acciones para prevenir enfermedades diarreicas y fortalecer vigilancia en la calidad del agua</t>
-  </si>
-  <si>
-    <t>Festival Cultural San Francisco</t>
-  </si>
-  <si>
-    <t>Orquesta Filarmónica de Pachuca se presentará en el Festival Cultural San Francisco 2026</t>
-  </si>
-  <si>
-    <t>Tuzos rescatan empate ante Xolos con doblete de Rondón</t>
-  </si>
-  <si>
-    <t>SSPH asegura generador de violencia en la región de Tula</t>
-  </si>
-  <si>
-    <t>Investigación del ITESHU impulsa conservación del agave en Hidalgo</t>
-  </si>
-  <si>
-    <t>¡Ya viene el Festival Internacional del Paste en Real del Monte!</t>
-  </si>
-  <si>
-    <t>Festival Del Paste</t>
-  </si>
-  <si>
-    <t>Hidalgo te acompaña, estés donde estés</t>
-  </si>
-  <si>
-    <t>Atención A Migrantes</t>
-  </si>
-  <si>
     <t>Plaza Juárez</t>
   </si>
   <si>
-    <t>Auto impacta colectiva en Pachuca; reportan seis heridos</t>
-  </si>
-  <si>
     <t>Accidente transporte público</t>
   </si>
   <si>
-    <t>Acusan a Aeroméxico de posible filtración de datos personales</t>
-  </si>
-  <si>
-    <t>corrupción</t>
-  </si>
-  <si>
-    <t>Pachuca se ha convertido en una ciudad receptora de migrantes, provenientes sobre todo del Estado de México, y no ha dado tiempo para un crecimiento con planeación, por lo que la falta de servicios es notoria en muchos puntos de la capital.</t>
-  </si>
-  <si>
-    <t>Editorial</t>
-  </si>
-  <si>
-    <t>Falta de servicios públicos</t>
-  </si>
-  <si>
-    <t>Alcaldesa deja fuera a asambleístas de su informe</t>
-  </si>
-  <si>
-    <t>¿Cuándo debo volar por los aires a Irán?""</t>
-  </si>
-  <si>
     <t>Temas internacionales</t>
+  </si>
+  <si>
+    <t>Bloquean para exigir obras... serán escuchados</t>
+  </si>
+  <si>
+    <t>Bloqueo Carretero</t>
+  </si>
+  <si>
+    <t>Incrementan 20.4 % fraudes en la entidad</t>
+  </si>
+  <si>
+    <t>Fraude</t>
+  </si>
+  <si>
+    <t>Teléfonos celulares, ni en clases ni en el recreo</t>
+  </si>
+  <si>
+    <t>Regulación de dispositivos digitales</t>
+  </si>
+  <si>
+    <t>Subirán 20% tarifas del servicio de taxi: usuarios consideran elevado el nuevo costo y piden que entre el serviio de plataformas</t>
+  </si>
+  <si>
+    <t>Proveedores quedaron a deber medicamento</t>
+  </si>
+  <si>
+    <t>Salud</t>
+  </si>
+  <si>
+    <t>Abasto De Medicamentos</t>
+  </si>
+  <si>
+    <t>Celulares en escuelas, solo para emergencias</t>
+  </si>
+  <si>
+    <t>Prevén más de 10 mil candidaturas en 2027</t>
+  </si>
+  <si>
+    <t>Elecciones</t>
+  </si>
+  <si>
+    <t>Aumenta tarifa de taxis en Pachuca y La Reforma</t>
+  </si>
+  <si>
+    <t>Bloquean 6 horas la Pachuca-Sahagún</t>
+  </si>
+  <si>
+    <t>Cierre Carretero</t>
+  </si>
+  <si>
+    <t>Siguen 3 pistas en caso párroco</t>
+  </si>
+  <si>
+    <t>Xotec: fusiona lucha libre y teatro en el cuadrilátero</t>
+  </si>
+  <si>
+    <t>Evento Cultural</t>
+  </si>
+  <si>
+    <t>Tocan fondo</t>
+  </si>
+  <si>
+    <t>Clasifican a gimnasiada</t>
+  </si>
+  <si>
+    <t>Inhide</t>
+  </si>
+  <si>
+    <t>Acumulan más accidentes las Rutas 47 y 108</t>
+  </si>
+  <si>
+    <t>STCH</t>
+  </si>
+  <si>
+    <t>Van 2 carpetas de investigación por tentativa de feminicidio</t>
+  </si>
+  <si>
+    <t>Feminicidio</t>
+  </si>
+  <si>
+    <t>Presentan nueva tarifa de taxis</t>
+  </si>
+  <si>
+    <t>Asael llama a sus homólogos a cerrar filas por el presupuesto</t>
+  </si>
+  <si>
+    <t>Modificación Presupuestal</t>
+  </si>
+  <si>
+    <t>Pachuca plantea ley de ingresos por 1,603 mdp</t>
+  </si>
+  <si>
+    <t>Ley De Ingresos</t>
+  </si>
+  <si>
+    <t>Servicio de taxis aumenta tarifa, pondrán límite con dispositivos</t>
+  </si>
+  <si>
+    <t>Inteligencia artificial: hora de actuar</t>
+  </si>
+  <si>
+    <t>Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>Debate sobre IA y celulares en los 475 años de la Universidad</t>
+  </si>
+  <si>
+    <t>La Diócesis de Huejutla colabora en investigación</t>
+  </si>
+  <si>
+    <t>Ataques de Estados Unidos a lanchas son ""Ejecuciones extrajudiciales"": ONU</t>
+  </si>
+  <si>
+    <t>El retiro de celulares debe ser con acuerdos, pide Natividad Castrejón</t>
+  </si>
+  <si>
+    <t>Caen tres tras balacera</t>
+  </si>
+  <si>
+    <t>Tarifa de taxis incrementará 20%: Semot</t>
+  </si>
+  <si>
+    <t>Acuerdan prohibir uso de celulares en primaria y secundaria</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH, Natividad Castrejón Valdez, precisó que no se trata de una prohibición, sino de una restricción. Explicó que en nivel  básico no podrán utilizarse celulares o tabletas, salvo en actividades académicas; en secundaria podrán emplearse en casos de emergencia,  pero deberán permanecer apagados durante toda la jornada escolar.</t>
+  </si>
+  <si>
+    <t>Fotonota</t>
+  </si>
+  <si>
+    <t>Violencia deja 9 muertos en Morelos y Guanajuato</t>
+  </si>
+  <si>
+    <t>Ola De Violencia</t>
+  </si>
+  <si>
+    <t>Una cosa es perder terreno en infraestructura o mercado laboral, temas que se corrigen con obra pública y política de empleo, y otra muy distinta es retroceder en derecho o en sistema político y gobiernos, donde el deterioro habla de percepción de seguridad, corrupción o manejo de finanzas públicas”.</t>
+  </si>
+  <si>
+    <t>Informe De Gobierno</t>
+  </si>
+  <si>
+    <t>Anuncian aumento del 20% en la tarifa de taxis; ajuste iniciará en Pachuca y La Reforma</t>
+  </si>
+  <si>
+    <t>Uso de celulares en escuelas  solo para emergencias o  actividades planeadas: SEPH</t>
+  </si>
+  <si>
+    <t>Exigen reparación integral tras muerte de  Karla y lesiones de Estrella</t>
+  </si>
+  <si>
+    <t>Atropellamiento estudiante</t>
+  </si>
+  <si>
+    <t>Siguen tres líneas de investigación por muerte de párroco de Huejutla</t>
+  </si>
+  <si>
+    <t>Participarán 139 artesanos en la Feria San Francisco Hidalgo 2026</t>
+  </si>
+  <si>
+    <t>Taxis en Hidalgo aumentarán 20% su tarifa</t>
+  </si>
+  <si>
+    <t>Hidalgo, entre estados con mayor crecimiento del PIB y avance en empleo: IMCO</t>
+  </si>
+  <si>
+    <t>Crecimiento Económico</t>
+  </si>
+  <si>
+    <t>Interceptan a pareja que transportaba 72 kilos de marihuana</t>
+  </si>
+  <si>
+    <t>Combate Al Narcomenudeo</t>
+  </si>
+  <si>
+    <t>Piden 25 millones de reparación por muerte de Karla</t>
+  </si>
+  <si>
+    <t>¡Adiós celulares!</t>
+  </si>
+  <si>
+    <t>Tuzobús ampliará servicio durante la Feria</t>
+  </si>
+  <si>
+    <t>Sitmah</t>
+  </si>
+  <si>
+    <t>Regularán uso de celulares en escuelas de Hidalgo</t>
+  </si>
+  <si>
+    <t>Sube 20% tarifa de taxis en Pachuca y Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>En operativo coordinado por el Gabinete de Seguridad, detienen a tres personas tras altercado en Pachuca</t>
+  </si>
+  <si>
+    <t>Reunión Gabinete De Seguridad</t>
+  </si>
+  <si>
+    <t>Ana María Rivera inaugura red eléctrica en Tezontepec de Aldama</t>
+  </si>
+  <si>
+    <t>Obras De Infraestructura</t>
+  </si>
+  <si>
+    <t>Entrega Claudia Sandoval mobiliario a Primaria de Tlamaco</t>
+  </si>
+  <si>
+    <t>Entrega De Equipo Escolar</t>
+  </si>
+  <si>
+    <t>Said Vargas continúa con el acercamiento a la base magisterial</t>
+  </si>
+  <si>
+    <t>Reunión con sindicato</t>
+  </si>
+  <si>
+    <t>Trabajo en equipo entre DIFH y DIF Huejutla amplía apoyos para grupos prioritarios</t>
+  </si>
+  <si>
+    <t>Cobertura de apoyos sociales</t>
+  </si>
+  <si>
+    <t>Garza Leal</t>
+  </si>
+  <si>
+    <t>Publicidad comercial</t>
+  </si>
+  <si>
+    <t>Actualizan tarifa de taxis en Hidalgo; buscan fortalecer calidad del servicio</t>
+  </si>
+  <si>
+    <t>Todo listo para la edición 2026 de la Feria de San Francisco</t>
+  </si>
+  <si>
+    <t>Carlos Rivera pone pausa a su carrera tras concierto en el Grito</t>
+  </si>
+  <si>
+    <t>Grito De Independencia</t>
+  </si>
+  <si>
+    <t>Educación integral: el estado evalúa aprendizajes, cuida emociones y promueve tecnología responsable</t>
+  </si>
+  <si>
+    <t>Fortalecimiento educativo</t>
+  </si>
+  <si>
+    <t>Gabinete de Seguridad detiene a tres personas tras altercado en Pachuca</t>
+  </si>
+  <si>
+    <t>Un espacio para encontrarnos</t>
+  </si>
+  <si>
+    <t>Apoyo a artesanos</t>
+  </si>
+  <si>
+    <t>Con la pirotecnia no se juega</t>
+  </si>
+  <si>
+    <t>Pirotecnia</t>
+  </si>
+  <si>
+    <t>Tarifa mínima de taxis aumentará a 45 pesos</t>
+  </si>
+  <si>
+    <t>Capturan a pareja con 72 kilos de presunta marihuana</t>
+  </si>
+  <si>
+    <t>Restringen uso de dispositivos móviles en aulas</t>
+  </si>
+  <si>
+    <t>Audiencia por triple feminicidio, continuará el jueves</t>
+  </si>
+  <si>
+    <t>Proceso Por Feminicidio</t>
   </si>
 </sst>
 </file>
@@ -853,8 +838,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J59" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J59" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J61" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J61" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1223,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1272,28 +1257,28 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1306,28 +1291,28 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1338,102 +1323,102 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="G6" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H6" t="s">
         <v>70</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1442,127 +1427,127 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" t="s">
         <v>98</v>
       </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" t="s">
-        <v>99</v>
-      </c>
       <c r="H7" t="s">
         <v>11</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B9" t="s">
         <v>71</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
@@ -1578,66 +1563,66 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B11" t="s">
         <v>71</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B12" t="s">
         <v>71</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="G12" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1646,96 +1631,96 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
       </c>
       <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B14" t="s">
         <v>73</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G14" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
       </c>
       <c r="I14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="G15" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1746,102 +1731,102 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B16" t="s">
         <v>73</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H16" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B17" t="s">
         <v>73</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B18" t="s">
         <v>73</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1850,59 +1835,59 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B19" t="s">
         <v>73</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B20" t="s">
         <v>78</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
         <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
@@ -1913,18 +1898,18 @@
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B21" t="s">
         <v>78</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
@@ -1936,10 +1921,10 @@
         <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H21" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1950,18 +1935,18 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B22" t="s">
         <v>78</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -1970,7 +1955,7 @@
         <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
@@ -1986,81 +1971,81 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B23" t="s">
         <v>78</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G23" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B24" t="s">
         <v>78</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B25" t="s">
         <v>78</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
@@ -2069,10 +2054,10 @@
         <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="G25" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
@@ -2088,75 +2073,75 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B27" t="s">
         <v>68</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G27" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B28" t="s">
         <v>68</v>
@@ -2165,72 +2150,72 @@
         <v>133</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B29" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" t="s">
         <v>135</v>
       </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B30" t="s">
         <v>68</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
@@ -2242,10 +2227,10 @@
         <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="H30" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2256,43 +2241,43 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>138</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F31" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="G31" t="s">
         <v>139</v>
       </c>
       <c r="H31" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B32" t="s">
         <v>76</v>
@@ -2301,38 +2286,38 @@
         <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F32" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="H32" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B33" t="s">
         <v>76</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
@@ -2341,10 +2326,10 @@
         <v>26</v>
       </c>
       <c r="F33" t="s">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -2360,28 +2345,28 @@
     </row>
     <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B34" t="s">
         <v>76</v>
       </c>
       <c r="C34" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" t="s">
         <v>143</v>
       </c>
-      <c r="D34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" t="s">
-        <v>22</v>
-      </c>
-      <c r="G34" t="s">
-        <v>144</v>
-      </c>
       <c r="H34" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2394,59 +2379,59 @@
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C35" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J35" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B36" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D35" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" t="s">
-        <v>79</v>
-      </c>
-      <c r="G35" t="s">
-        <v>146</v>
-      </c>
-      <c r="H35" t="s">
-        <v>70</v>
-      </c>
-      <c r="I35" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J35" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="11">
-        <v>46286</v>
-      </c>
-      <c r="B36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="D36" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G36" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
@@ -2460,64 +2445,64 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B37" t="s">
         <v>75</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D37" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F37" t="s">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="G37" t="s">
-        <v>149</v>
+        <v>84</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B38" t="s">
         <v>75</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="F38" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="G38" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H38" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2528,27 +2513,27 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B39" t="s">
         <v>75</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F39" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="G39" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
@@ -2562,30 +2547,30 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B40" t="s">
         <v>75</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G40" t="s">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="H40" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2596,27 +2581,27 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D41" t="s">
-        <v>157</v>
+        <v>12</v>
       </c>
       <c r="E41" t="s">
         <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>158</v>
+        <v>2</v>
       </c>
       <c r="G41" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
@@ -2630,98 +2615,98 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B42" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F42" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="G42" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B43" t="s">
         <v>77</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D43" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="E43" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F43" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>163</v>
+        <v>98</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B44" t="s">
         <v>77</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G44" t="s">
-        <v>165</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2732,163 +2717,163 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B45" t="s">
         <v>77</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G45" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B46" t="s">
         <v>77</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D46" t="s">
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B47" t="s">
         <v>77</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B48" t="s">
         <v>77</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D48" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B49" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F49" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G49" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -2902,18 +2887,18 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B50" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D50" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
@@ -2922,7 +2907,7 @@
         <v>10</v>
       </c>
       <c r="G50" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
@@ -2938,25 +2923,25 @@
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B51" t="s">
         <v>82</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D51" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F51" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G51" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
@@ -2972,25 +2957,25 @@
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B52" t="s">
         <v>82</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D52" t="s">
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F52" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G52" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
@@ -3006,59 +2991,59 @@
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B53" t="s">
         <v>82</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D53" t="s">
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G53" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B54" t="s">
         <v>82</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D54" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G54" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H54" t="s">
         <v>11</v>
@@ -3074,28 +3059,28 @@
     </row>
     <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B55" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F55" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G55" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="H55" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3103,55 +3088,55 @@
       </c>
       <c r="J55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D56" t="s">
+        <v>80</v>
+      </c>
+      <c r="E56" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" t="s">
+        <v>177</v>
+      </c>
+      <c r="H56" t="s">
+        <v>11</v>
+      </c>
+      <c r="I56" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J56" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="11">
-        <v>46286</v>
-      </c>
-      <c r="B56" t="s">
-        <v>179</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D56" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" t="s">
-        <v>10</v>
-      </c>
-      <c r="G56" t="s">
-        <v>183</v>
-      </c>
-      <c r="H56" t="s">
-        <v>70</v>
-      </c>
-      <c r="I56" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J56" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B57" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D57" t="s">
-        <v>185</v>
+        <v>80</v>
       </c>
       <c r="E57" t="s">
         <v>16</v>
@@ -3160,10 +3145,10 @@
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="H57" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3176,68 +3161,136 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B58" t="s">
-        <v>179</v>
+        <v>90</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D58" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F58" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="G58" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="H58" t="s">
         <v>70</v>
       </c>
       <c r="I58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B59" t="s">
-        <v>179</v>
+        <v>90</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D59" t="s">
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F59" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G59" t="s">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="H59" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J59" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B60" t="s">
+        <v>90</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>26</v>
+      </c>
+      <c r="F60" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" t="s">
+        <v>98</v>
+      </c>
+      <c r="H60" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B61" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>58</v>
+      </c>
+      <c r="F61" t="s">
+        <v>58</v>
+      </c>
+      <c r="G61" t="s">
+        <v>184</v>
+      </c>
+      <c r="H61" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Otros</v>
       </c>
-      <c r="J59" t="str">
+      <c r="J61" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DEBEC3-352C-41C2-BEFC-2CA867FA63E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FB5703-AA99-4E1D-BFD4-A7571F14A325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="181">
   <si>
     <t>Fecha</t>
   </si>
@@ -243,9 +243,6 @@
     <t>El Sol de Hidalgo</t>
   </si>
   <si>
-    <t>La Jornada Hidalgo</t>
-  </si>
-  <si>
     <t>OCSAD</t>
   </si>
   <si>
@@ -288,15 +285,9 @@
     <t>Pachuca Brilla</t>
   </si>
   <si>
-    <t>Homicidio de sacerdote</t>
-  </si>
-  <si>
     <t>Tarifario de taxis</t>
   </si>
   <si>
-    <t>Ataque Armado</t>
-  </si>
-  <si>
     <t>OEEH</t>
   </si>
   <si>
@@ -306,292 +297,289 @@
     <t>Cintillo</t>
   </si>
   <si>
-    <t>Gimnasiada Nacional</t>
-  </si>
-  <si>
     <t>Plaza Juárez</t>
   </si>
   <si>
-    <t>Accidente transporte público</t>
-  </si>
-  <si>
-    <t>Temas internacionales</t>
-  </si>
-  <si>
-    <t>Bloquean para exigir obras... serán escuchados</t>
-  </si>
-  <si>
-    <t>Bloqueo Carretero</t>
-  </si>
-  <si>
-    <t>Incrementan 20.4 % fraudes en la entidad</t>
-  </si>
-  <si>
-    <t>Fraude</t>
-  </si>
-  <si>
-    <t>Teléfonos celulares, ni en clases ni en el recreo</t>
-  </si>
-  <si>
     <t>Regulación de dispositivos digitales</t>
   </si>
   <si>
-    <t>Subirán 20% tarifas del servicio de taxi: usuarios consideran elevado el nuevo costo y piden que entre el serviio de plataformas</t>
-  </si>
-  <si>
-    <t>Proveedores quedaron a deber medicamento</t>
-  </si>
-  <si>
-    <t>Salud</t>
-  </si>
-  <si>
-    <t>Abasto De Medicamentos</t>
-  </si>
-  <si>
-    <t>Celulares en escuelas, solo para emergencias</t>
-  </si>
-  <si>
-    <t>Prevén más de 10 mil candidaturas en 2027</t>
-  </si>
-  <si>
-    <t>Elecciones</t>
-  </si>
-  <si>
-    <t>Aumenta tarifa de taxis en Pachuca y La Reforma</t>
-  </si>
-  <si>
-    <t>Bloquean 6 horas la Pachuca-Sahagún</t>
-  </si>
-  <si>
-    <t>Cierre Carretero</t>
-  </si>
-  <si>
-    <t>Siguen 3 pistas en caso párroco</t>
-  </si>
-  <si>
-    <t>Xotec: fusiona lucha libre y teatro en el cuadrilátero</t>
-  </si>
-  <si>
-    <t>Evento Cultural</t>
-  </si>
-  <si>
-    <t>Tocan fondo</t>
-  </si>
-  <si>
-    <t>Clasifican a gimnasiada</t>
-  </si>
-  <si>
     <t>Inhide</t>
   </si>
   <si>
-    <t>Acumulan más accidentes las Rutas 47 y 108</t>
-  </si>
-  <si>
-    <t>STCH</t>
-  </si>
-  <si>
-    <t>Van 2 carpetas de investigación por tentativa de feminicidio</t>
-  </si>
-  <si>
-    <t>Feminicidio</t>
-  </si>
-  <si>
-    <t>Presentan nueva tarifa de taxis</t>
-  </si>
-  <si>
-    <t>Asael llama a sus homólogos a cerrar filas por el presupuesto</t>
-  </si>
-  <si>
-    <t>Modificación Presupuestal</t>
-  </si>
-  <si>
-    <t>Pachuca plantea ley de ingresos por 1,603 mdp</t>
-  </si>
-  <si>
-    <t>Ley De Ingresos</t>
-  </si>
-  <si>
-    <t>Servicio de taxis aumenta tarifa, pondrán límite con dispositivos</t>
-  </si>
-  <si>
-    <t>Inteligencia artificial: hora de actuar</t>
-  </si>
-  <si>
-    <t>Inteligencia Artificial</t>
-  </si>
-  <si>
-    <t>Debate sobre IA y celulares en los 475 años de la Universidad</t>
-  </si>
-  <si>
-    <t>La Diócesis de Huejutla colabora en investigación</t>
-  </si>
-  <si>
-    <t>Ataques de Estados Unidos a lanchas son ""Ejecuciones extrajudiciales"": ONU</t>
-  </si>
-  <si>
-    <t>El retiro de celulares debe ser con acuerdos, pide Natividad Castrejón</t>
-  </si>
-  <si>
-    <t>Caen tres tras balacera</t>
-  </si>
-  <si>
-    <t>Tarifa de taxis incrementará 20%: Semot</t>
-  </si>
-  <si>
-    <t>Acuerdan prohibir uso de celulares en primaria y secundaria</t>
-  </si>
-  <si>
-    <t>El titular de la SEPH, Natividad Castrejón Valdez, precisó que no se trata de una prohibición, sino de una restricción. Explicó que en nivel  básico no podrán utilizarse celulares o tabletas, salvo en actividades académicas; en secundaria podrán emplearse en casos de emergencia,  pero deberán permanecer apagados durante toda la jornada escolar.</t>
-  </si>
-  <si>
-    <t>Fotonota</t>
-  </si>
-  <si>
-    <t>Violencia deja 9 muertos en Morelos y Guanajuato</t>
-  </si>
-  <si>
-    <t>Ola De Violencia</t>
-  </si>
-  <si>
-    <t>Una cosa es perder terreno en infraestructura o mercado laboral, temas que se corrigen con obra pública y política de empleo, y otra muy distinta es retroceder en derecho o en sistema político y gobiernos, donde el deterioro habla de percepción de seguridad, corrupción o manejo de finanzas públicas”.</t>
-  </si>
-  <si>
-    <t>Informe De Gobierno</t>
-  </si>
-  <si>
-    <t>Anuncian aumento del 20% en la tarifa de taxis; ajuste iniciará en Pachuca y La Reforma</t>
-  </si>
-  <si>
-    <t>Uso de celulares en escuelas  solo para emergencias o  actividades planeadas: SEPH</t>
-  </si>
-  <si>
-    <t>Exigen reparación integral tras muerte de  Karla y lesiones de Estrella</t>
-  </si>
-  <si>
-    <t>Atropellamiento estudiante</t>
-  </si>
-  <si>
-    <t>Siguen tres líneas de investigación por muerte de párroco de Huejutla</t>
-  </si>
-  <si>
-    <t>Participarán 139 artesanos en la Feria San Francisco Hidalgo 2026</t>
-  </si>
-  <si>
-    <t>Taxis en Hidalgo aumentarán 20% su tarifa</t>
-  </si>
-  <si>
-    <t>Hidalgo, entre estados con mayor crecimiento del PIB y avance en empleo: IMCO</t>
-  </si>
-  <si>
     <t>Crecimiento Económico</t>
   </si>
   <si>
-    <t>Interceptan a pareja que transportaba 72 kilos de marihuana</t>
-  </si>
-  <si>
-    <t>Combate Al Narcomenudeo</t>
-  </si>
-  <si>
-    <t>Piden 25 millones de reparación por muerte de Karla</t>
-  </si>
-  <si>
-    <t>¡Adiós celulares!</t>
-  </si>
-  <si>
-    <t>Tuzobús ampliará servicio durante la Feria</t>
-  </si>
-  <si>
-    <t>Sitmah</t>
-  </si>
-  <si>
-    <t>Regularán uso de celulares en escuelas de Hidalgo</t>
-  </si>
-  <si>
-    <t>Sube 20% tarifa de taxis en Pachuca y Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>En operativo coordinado por el Gabinete de Seguridad, detienen a tres personas tras altercado en Pachuca</t>
-  </si>
-  <si>
-    <t>Reunión Gabinete De Seguridad</t>
-  </si>
-  <si>
-    <t>Ana María Rivera inaugura red eléctrica en Tezontepec de Aldama</t>
-  </si>
-  <si>
-    <t>Obras De Infraestructura</t>
-  </si>
-  <si>
-    <t>Entrega Claudia Sandoval mobiliario a Primaria de Tlamaco</t>
-  </si>
-  <si>
-    <t>Entrega De Equipo Escolar</t>
-  </si>
-  <si>
-    <t>Said Vargas continúa con el acercamiento a la base magisterial</t>
-  </si>
-  <si>
     <t>Reunión con sindicato</t>
   </si>
   <si>
-    <t>Trabajo en equipo entre DIFH y DIF Huejutla amplía apoyos para grupos prioritarios</t>
-  </si>
-  <si>
-    <t>Cobertura de apoyos sociales</t>
-  </si>
-  <si>
-    <t>Garza Leal</t>
-  </si>
-  <si>
-    <t>Publicidad comercial</t>
-  </si>
-  <si>
-    <t>Actualizan tarifa de taxis en Hidalgo; buscan fortalecer calidad del servicio</t>
-  </si>
-  <si>
-    <t>Todo listo para la edición 2026 de la Feria de San Francisco</t>
-  </si>
-  <si>
-    <t>Carlos Rivera pone pausa a su carrera tras concierto en el Grito</t>
-  </si>
-  <si>
-    <t>Grito De Independencia</t>
-  </si>
-  <si>
-    <t>Educación integral: el estado evalúa aprendizajes, cuida emociones y promueve tecnología responsable</t>
-  </si>
-  <si>
-    <t>Fortalecimiento educativo</t>
-  </si>
-  <si>
-    <t>Gabinete de Seguridad detiene a tres personas tras altercado en Pachuca</t>
-  </si>
-  <si>
-    <t>Un espacio para encontrarnos</t>
-  </si>
-  <si>
-    <t>Apoyo a artesanos</t>
-  </si>
-  <si>
     <t>Con la pirotecnia no se juega</t>
   </si>
   <si>
     <t>Pirotecnia</t>
   </si>
   <si>
-    <t>Tarifa mínima de taxis aumentará a 45 pesos</t>
-  </si>
-  <si>
-    <t>Capturan a pareja con 72 kilos de presunta marihuana</t>
-  </si>
-  <si>
-    <t>Restringen uso de dispositivos móviles en aulas</t>
-  </si>
-  <si>
-    <t>Audiencia por triple feminicidio, continuará el jueves</t>
-  </si>
-  <si>
-    <t>Proceso Por Feminicidio</t>
+    <t>Crece vivienda más que población: Inegi</t>
+  </si>
+  <si>
+    <t>Dinámica demográfica</t>
+  </si>
+  <si>
+    <t>Aún sin llegar la maquinaria</t>
+  </si>
+  <si>
+    <t>Conagua</t>
+  </si>
+  <si>
+    <t>Control lirio acuático</t>
+  </si>
+  <si>
+    <t>Piden que maestros tampoco usen celular</t>
+  </si>
+  <si>
+    <t>Mendoza llama a revisar estrategia de seguridad</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>Intervención extranjera</t>
+  </si>
+  <si>
+    <t>Rinden homenaje a Juana Alarcón</t>
+  </si>
+  <si>
+    <t>Deceso de diputada</t>
+  </si>
+  <si>
+    <t>Registra Inegi 19 mil desplazamientos por desastres y violencia</t>
+  </si>
+  <si>
+    <t>Taxis en Pachuca, deteriorados</t>
+  </si>
+  <si>
+    <t>Viajan con sabor huasteco</t>
+  </si>
+  <si>
+    <t>Temas varios</t>
+  </si>
+  <si>
+    <t>En Tizayuca, transporte público provoca accidentes</t>
+  </si>
+  <si>
+    <t>Deficiencias transporte público</t>
+  </si>
+  <si>
+    <t>Pausan llamado de leigisladora suplente</t>
+  </si>
+  <si>
+    <t>Diputado suplente</t>
+  </si>
+  <si>
+    <t>Celebran a universidades tecnológicas y politécnicas</t>
+  </si>
+  <si>
+    <t>Conmemoración Aniversario</t>
+  </si>
+  <si>
+    <t>Pendiente, homologar sueldo a nivel federal en Tecnológicos</t>
+  </si>
+  <si>
+    <t>Universidades</t>
+  </si>
+  <si>
+    <t>Homologación salarial</t>
+  </si>
+  <si>
+    <t>Ve gobernador libertad en las manifestaciones en los informes</t>
+  </si>
+  <si>
+    <t>Manifestación informe</t>
+  </si>
+  <si>
+    <t>Vigilaría Congreso el servicio de transporte</t>
+  </si>
+  <si>
+    <t>Cesaron al Rambo</t>
+  </si>
+  <si>
+    <t>Dan el último adiós a la dip. Juana Alarcón</t>
+  </si>
+  <si>
+    <t>Realiza DIFH entrega de 305 becas pilaress</t>
+  </si>
+  <si>
+    <t>Pilares</t>
+  </si>
+  <si>
+    <t>IMCO: Hidalgo registra avances en economía, salud y seguridad</t>
+  </si>
+  <si>
+    <t>Desplazamientos y dependencia de apoyos revela encuesta del Inegi</t>
+  </si>
+  <si>
+    <t>Celebran a las universidades tecnológicas y politécnicas</t>
+  </si>
+  <si>
+    <t>Brecha laboral: Participación masculina es de 6 por cada 4 mujeres</t>
+  </si>
+  <si>
+    <t>Brecha de género</t>
+  </si>
+  <si>
+    <t>Trump compara a los cárteles de México co el grupo ISIS</t>
+  </si>
+  <si>
+    <t>Traerán debate sobre futuro e innovación</t>
+  </si>
+  <si>
+    <t>Abren la posibilidad para demandar a plataformas digitales en nuestro país</t>
+  </si>
+  <si>
+    <t>Next Energy pide se revise el caso de su propietario preso</t>
+  </si>
+  <si>
+    <t>Viajan en vehículo articular apenas 1.5 personas</t>
+  </si>
+  <si>
+    <t>Movilidad urbana</t>
+  </si>
+  <si>
+    <t>Aumenta 14.9 puntos porcentuales la eficiencia terminal en universidades de la entidad</t>
+  </si>
+  <si>
+    <t>Eficiencia terminal</t>
+  </si>
+  <si>
+    <t>Hidalgo suma 162 mil habitantes y alcanza una población de 3.2 millones</t>
+  </si>
+  <si>
+    <t>Menchaca pide a su gabinete prepararse para comparecencias ante el Congreso</t>
+  </si>
+  <si>
+    <t>Comparecencias</t>
+  </si>
+  <si>
+    <t>Rinden homenaje póstumo a la diputada Juana Olivia Alarcón</t>
+  </si>
+  <si>
+    <t>Pachuca tendrá ingreso de 1.6 mdp por espectáculos de la Feria San Francisco</t>
+  </si>
+  <si>
+    <t>Sin firma, no hay pruebas contra Osorio Chong por desvío en Policía Federal: Secretaría Anticorrupción</t>
+  </si>
+  <si>
+    <t>Corrupción</t>
+  </si>
+  <si>
+    <t>Uber y DIDI siguen prohibidos en Hidalgo</t>
+  </si>
+  <si>
+    <t>Apps de transporte</t>
+  </si>
+  <si>
+    <t>DIFH entrega becas a 305 niños de 17 municipios</t>
+  </si>
+  <si>
+    <t>Hidalgo, sede de la Olimpiada Nacional 2027</t>
+  </si>
+  <si>
+    <t>Olimpiada Nacional</t>
+  </si>
+  <si>
+    <t>Aumentan a 84.5% los estudiantes que logran concluir universidad</t>
+  </si>
+  <si>
+    <t>Hidalgo ya supera los 3.2 millones de habitantes</t>
+  </si>
+  <si>
+    <t>Hidalgo buscará regresar al top 15 en competitividad</t>
+  </si>
+  <si>
+    <t>La tarifa sube, ¿y el servicio?</t>
+  </si>
+  <si>
+    <t>Editorial</t>
+  </si>
+  <si>
+    <t>Invita Semot a fomentar el respeto a la jerarquía de la movilidad</t>
+  </si>
+  <si>
+    <t>Jerarquía de la Movilidad</t>
+  </si>
+  <si>
+    <t>Tula fortalece su capacidad operativa en seguridad con inversión superior a 6 mdp</t>
+  </si>
+  <si>
+    <t>Fortalecimiento Policiaco</t>
+  </si>
+  <si>
+    <t>Obras tienen un año de garantía por vicios ocultos: Sipdus</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Garantía de obra</t>
+  </si>
+  <si>
+    <t>Said Vargas fortalece estructuras sindicales del SNTE en la Otomí-Tepehua</t>
+  </si>
+  <si>
+    <t>Menchaca no descarta comparecencia del Oficial Mayor ante el Congreso</t>
+  </si>
+  <si>
+    <t>Policía de Ajacuba fortalece acciones de prevención del delito con jornadas sobre prevención del suicidio</t>
+  </si>
+  <si>
+    <t>Policía municipal</t>
+  </si>
+  <si>
+    <t>Prevención del suicidio</t>
+  </si>
+  <si>
+    <t>Pachuca recibirá 1.6 mdp por espacios para Feria</t>
+  </si>
+  <si>
+    <t>Hidalgo será sede de la Olimpiada Nacional 2027; lo oficializa Conade</t>
+  </si>
+  <si>
+    <t>Tuzos enfrentarán a la Selección Mexicana sub 23 en Hidalgo</t>
+  </si>
+  <si>
+    <t>llaa</t>
+  </si>
+  <si>
+    <t>Julio Menchaca respalda labor de universidades tecnológicas y politécnicas</t>
+  </si>
+  <si>
+    <t>Brinda DIFH Hidalgo becas para apoyar la economía familiar de usuarios</t>
+  </si>
+  <si>
+    <t>Tuzas se quedan sin DT: cesan a Óscar Torres</t>
+  </si>
+  <si>
+    <t>¡Late con orgullo!</t>
+  </si>
+  <si>
+    <t>Rodolfo, el niño que se convirtió en El Santo</t>
+  </si>
+  <si>
+    <t>Aniversario natalicio</t>
+  </si>
+  <si>
+    <t>El país supera los 130 millones de habitantes</t>
+  </si>
+  <si>
+    <t>Resultados del ICE 2026 muestran áreas de oportunidad: JMS</t>
+  </si>
+  <si>
+    <t>Seis puertos mexicanos están restringidos por el huracán Polo</t>
+  </si>
+  <si>
+    <t>Alerta Meteorológica</t>
+  </si>
+  <si>
+    <t>Honor a quien honor merece. El personaje de El Santo es sin duda uno de los más queridos en México y sin duda dejó escuela en la lucha libre en nuestro país y en el mundo. Este día conmemoramos con orgullo 109 años de su nacimiento en Tulancingo.</t>
   </si>
 </sst>
 </file>
@@ -838,8 +826,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J61" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J61" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J59" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J59" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1208,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1257,7 +1245,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
@@ -1266,32 +1254,32 @@
         <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
         <v>94</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -1303,63 +1291,63 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="G3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -1368,137 +1356,137 @@
         <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="H5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J6" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
         <v>14</v>
       </c>
-      <c r="F6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" t="str">
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Presidencia de la República</v>
       </c>
-      <c r="J6" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" t="s">
-        <v>98</v>
-      </c>
-      <c r="H7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>106</v>
@@ -1507,50 +1495,50 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1563,149 +1551,149 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J13" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" t="s">
+        <v>118</v>
+      </c>
+      <c r="H14" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J13" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" t="s">
-        <v>114</v>
-      </c>
-      <c r="G14" t="s">
-        <v>89</v>
-      </c>
-      <c r="H14" t="s">
-        <v>11</v>
-      </c>
       <c r="I14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -1714,13 +1702,13 @@
         <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>116</v>
+        <v>27</v>
       </c>
       <c r="G15" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1731,287 +1719,287 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G16" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G17" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J17" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" t="s">
+        <v>123</v>
+      </c>
+      <c r="H18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J17" t="str">
+      <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" t="s">
-        <v>121</v>
-      </c>
-      <c r="H18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I18" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
-      </c>
-      <c r="J18" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" t="s">
-        <v>123</v>
-      </c>
-      <c r="H19" t="s">
-        <v>11</v>
-      </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J20" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" t="s">
+        <v>113</v>
+      </c>
+      <c r="H21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J20" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" t="s">
-        <v>126</v>
-      </c>
-      <c r="H21" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J22" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
         <v>10</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F23" t="s">
         <v>10</v>
       </c>
-      <c r="G22" t="s">
-        <v>126</v>
-      </c>
-      <c r="H22" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J22" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" t="s">
-        <v>17</v>
-      </c>
       <c r="G23" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="H23" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
@@ -2023,10 +2011,10 @@
         <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="H24" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2039,66 +2027,66 @@
     </row>
     <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2107,62 +2095,62 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="H27" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="H28" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2170,105 +2158,105 @@
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J29" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B30" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" t="s">
+        <v>139</v>
+      </c>
+      <c r="H30" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J29" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B30" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D30" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" t="s">
-        <v>137</v>
-      </c>
-      <c r="H30" t="s">
-        <v>70</v>
-      </c>
-      <c r="I30" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D31" t="s">
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G31" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="H31" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2277,22 +2265,22 @@
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F32" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="G32" t="s">
         <v>84</v>
@@ -2311,263 +2299,263 @@
     </row>
     <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>143</v>
+      </c>
+      <c r="H33" t="s">
+        <v>69</v>
+      </c>
+      <c r="I33" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J33" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" t="s">
+        <v>24</v>
+      </c>
+      <c r="G34" t="s">
+        <v>145</v>
+      </c>
+      <c r="H34" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J34" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" t="s">
+        <v>36</v>
+      </c>
+      <c r="G35" t="s">
+        <v>123</v>
+      </c>
+      <c r="H35" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J35" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" t="s">
+        <v>148</v>
+      </c>
+      <c r="H36" t="s">
+        <v>73</v>
+      </c>
+      <c r="I36" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J36" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
         <v>26</v>
       </c>
-      <c r="F33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G33" t="s">
-        <v>98</v>
-      </c>
-      <c r="H33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I33" t="str">
+      <c r="F37" t="s">
+        <v>115</v>
+      </c>
+      <c r="G37" t="s">
+        <v>136</v>
+      </c>
+      <c r="H37" t="s">
+        <v>73</v>
+      </c>
+      <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J33" t="str">
+      <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" t="s">
-        <v>143</v>
-      </c>
-      <c r="H34" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" t="str">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" t="s">
+        <v>94</v>
+      </c>
+      <c r="H38" t="s">
+        <v>11</v>
+      </c>
+      <c r="I38" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J38" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" t="s">
+        <v>89</v>
+      </c>
+      <c r="H39" t="s">
+        <v>11</v>
+      </c>
+      <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J34" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B35" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D35" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" t="s">
-        <v>11</v>
-      </c>
-      <c r="I35" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J35" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B36" t="s">
-        <v>76</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D36" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" t="s">
-        <v>87</v>
-      </c>
-      <c r="H36" t="s">
-        <v>11</v>
-      </c>
-      <c r="I36" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J36" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D37" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" t="s">
-        <v>27</v>
-      </c>
-      <c r="F37" t="s">
-        <v>2</v>
-      </c>
-      <c r="G37" t="s">
-        <v>84</v>
-      </c>
-      <c r="H37" t="s">
-        <v>11</v>
-      </c>
-      <c r="I37" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J37" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B38" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" t="s">
-        <v>54</v>
-      </c>
-      <c r="F38" t="s">
-        <v>54</v>
-      </c>
-      <c r="G38" t="s">
-        <v>148</v>
-      </c>
-      <c r="H38" t="s">
-        <v>74</v>
-      </c>
-      <c r="I38" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J38" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B39" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D39" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" t="s">
-        <v>22</v>
-      </c>
-      <c r="G39" t="s">
-        <v>150</v>
-      </c>
-      <c r="H39" t="s">
-        <v>11</v>
-      </c>
-      <c r="I39" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D40" t="s">
-        <v>12</v>
+        <v>153</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F40" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G40" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
@@ -2581,30 +2569,30 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D41" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="E41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G41" t="s">
-        <v>98</v>
+        <v>155</v>
       </c>
       <c r="H41" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2615,64 +2603,64 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="G42" t="s">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="H42" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D43" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="F43" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="G43" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="H43" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2685,50 +2673,50 @@
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B44" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G44" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E45" t="s">
         <v>24</v>
@@ -2737,7 +2725,7 @@
         <v>24</v>
       </c>
       <c r="G45" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
@@ -2753,13 +2741,13 @@
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D46" t="s">
         <v>12</v>
@@ -2768,10 +2756,10 @@
         <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="G46" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
@@ -2785,15 +2773,15 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
@@ -2805,7 +2793,7 @@
         <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
@@ -2821,476 +2809,408 @@
     </row>
     <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B48" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D48" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F48" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="H48" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D49" t="s">
-        <v>12</v>
+        <v>169</v>
       </c>
       <c r="E49" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="G49" t="s">
-        <v>166</v>
+        <v>71</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
       </c>
       <c r="I49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J49" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>24</v>
+      </c>
+      <c r="F50" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" t="s">
+        <v>136</v>
+      </c>
+      <c r="H50" t="s">
+        <v>73</v>
+      </c>
+      <c r="I50" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J49" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B50" t="s">
-        <v>77</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D50" t="s">
-        <v>80</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50" t="s">
-        <v>168</v>
-      </c>
-      <c r="H50" t="s">
-        <v>11</v>
-      </c>
-      <c r="I50" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>36</v>
+      </c>
+      <c r="F51" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51" t="s">
+        <v>123</v>
+      </c>
+      <c r="H51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I51" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J51" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B52" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" t="s">
+        <v>71</v>
+      </c>
+      <c r="H52" t="s">
+        <v>11</v>
+      </c>
+      <c r="I52" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J52" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B53" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D53" t="s">
+        <v>79</v>
+      </c>
+      <c r="E53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53" t="s">
+        <v>83</v>
+      </c>
+      <c r="G53" t="s">
+        <v>84</v>
+      </c>
+      <c r="H53" t="s">
+        <v>11</v>
+      </c>
+      <c r="I53" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J53" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B54" t="s">
+        <v>81</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" t="s">
+        <v>92</v>
+      </c>
+      <c r="H54" t="s">
+        <v>11</v>
+      </c>
+      <c r="I54" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J54" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B55" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D55" t="s">
         <v>13</v>
       </c>
-      <c r="E51" t="s">
-        <v>27</v>
-      </c>
-      <c r="F51" t="s">
-        <v>2</v>
-      </c>
-      <c r="G51" t="s">
-        <v>84</v>
-      </c>
-      <c r="H51" t="s">
-        <v>11</v>
-      </c>
-      <c r="I51" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J51" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B52" t="s">
-        <v>82</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D52" t="s">
-        <v>12</v>
-      </c>
-      <c r="E52" t="s">
-        <v>29</v>
-      </c>
-      <c r="F52" t="s">
-        <v>86</v>
-      </c>
-      <c r="G52" t="s">
-        <v>87</v>
-      </c>
-      <c r="H52" t="s">
-        <v>11</v>
-      </c>
-      <c r="I52" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J52" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B53" t="s">
-        <v>82</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D53" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="E55" t="s">
         <v>10</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F55" t="s">
         <v>10</v>
       </c>
-      <c r="G53" t="s">
-        <v>172</v>
-      </c>
-      <c r="H53" t="s">
-        <v>11</v>
-      </c>
-      <c r="I53" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J53" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B54" t="s">
-        <v>82</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D54" t="s">
-        <v>12</v>
-      </c>
-      <c r="E54" t="s">
-        <v>26</v>
-      </c>
-      <c r="F54" t="s">
-        <v>2</v>
-      </c>
-      <c r="G54" t="s">
-        <v>174</v>
-      </c>
-      <c r="H54" t="s">
-        <v>11</v>
-      </c>
-      <c r="I54" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J54" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B55" t="s">
-        <v>82</v>
-      </c>
-      <c r="C55" s="5" t="s">
+      <c r="G55" t="s">
         <v>175</v>
       </c>
-      <c r="D55" t="s">
-        <v>12</v>
-      </c>
-      <c r="E55" t="s">
-        <v>24</v>
-      </c>
-      <c r="F55" t="s">
-        <v>24</v>
-      </c>
-      <c r="G55" t="s">
-        <v>158</v>
-      </c>
       <c r="H55" t="s">
         <v>11</v>
       </c>
       <c r="I55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>176</v>
       </c>
       <c r="D56" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G56" t="s">
+        <v>94</v>
+      </c>
+      <c r="H56" t="s">
+        <v>11</v>
+      </c>
+      <c r="I56" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J56" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B57" t="s">
+        <v>86</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="H56" t="s">
-        <v>11</v>
-      </c>
-      <c r="I56" t="str">
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" t="s">
+        <v>24</v>
+      </c>
+      <c r="F57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" t="s">
+        <v>89</v>
+      </c>
+      <c r="H57" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J56" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B57" t="s">
-        <v>82</v>
-      </c>
-      <c r="C57" s="5" t="s">
+      <c r="J57" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B58" t="s">
+        <v>86</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D57" t="s">
-        <v>80</v>
-      </c>
-      <c r="E57" t="s">
-        <v>16</v>
-      </c>
-      <c r="F57" t="s">
-        <v>16</v>
-      </c>
-      <c r="G57" t="s">
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" t="s">
         <v>179</v>
       </c>
-      <c r="H57" t="s">
-        <v>11</v>
-      </c>
-      <c r="I57" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J57" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B58" t="s">
-        <v>90</v>
-      </c>
-      <c r="C58" s="5" t="s">
+      <c r="H58" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J58" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A59" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B59" t="s">
+        <v>86</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="D58" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" t="s">
-        <v>27</v>
-      </c>
-      <c r="F58" t="s">
-        <v>27</v>
-      </c>
-      <c r="G58" t="s">
-        <v>84</v>
-      </c>
-      <c r="H58" t="s">
-        <v>70</v>
-      </c>
-      <c r="I58" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J58" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>181</v>
-      </c>
       <c r="D59" t="s">
-        <v>12</v>
+        <v>153</v>
       </c>
       <c r="E59" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F59" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G59" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H59" t="s">
         <v>11</v>
       </c>
       <c r="I59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J59" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B60" t="s">
-        <v>90</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D60" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" t="s">
-        <v>26</v>
-      </c>
-      <c r="F60" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" t="s">
-        <v>98</v>
-      </c>
-      <c r="H60" t="s">
-        <v>11</v>
-      </c>
-      <c r="I60" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J60" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="11">
-        <v>46287</v>
-      </c>
-      <c r="B61" t="s">
-        <v>90</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D61" t="s">
-        <v>12</v>
-      </c>
-      <c r="E61" t="s">
-        <v>58</v>
-      </c>
-      <c r="F61" t="s">
-        <v>58</v>
-      </c>
-      <c r="G61" t="s">
-        <v>184</v>
-      </c>
-      <c r="H61" t="s">
-        <v>11</v>
-      </c>
-      <c r="I61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J61" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
@@ -3350,7 +3270,7 @@
         <v>31</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>66</v>
@@ -3386,7 +3306,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
         <v>32</v>
@@ -3862,7 +3782,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B49" t="s">
         <v>44</v>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FB5703-AA99-4E1D-BFD4-A7571F14A325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A66FA50-E096-4E37-B883-EC72BC71DA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="179">
   <si>
     <t>Fecha</t>
   </si>
@@ -276,9 +276,6 @@
     <t>Alcalde</t>
   </si>
   <si>
-    <t>Publicidad</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -300,286 +297,283 @@
     <t>Plaza Juárez</t>
   </si>
   <si>
-    <t>Regulación de dispositivos digitales</t>
-  </si>
-  <si>
-    <t>Inhide</t>
-  </si>
-  <si>
-    <t>Crecimiento Económico</t>
-  </si>
-  <si>
-    <t>Reunión con sindicato</t>
-  </si>
-  <si>
-    <t>Con la pirotecnia no se juega</t>
-  </si>
-  <si>
-    <t>Pirotecnia</t>
-  </si>
-  <si>
-    <t>Crece vivienda más que población: Inegi</t>
-  </si>
-  <si>
     <t>Dinámica demográfica</t>
   </si>
   <si>
-    <t>Aún sin llegar la maquinaria</t>
-  </si>
-  <si>
-    <t>Conagua</t>
-  </si>
-  <si>
-    <t>Control lirio acuático</t>
-  </si>
-  <si>
-    <t>Piden que maestros tampoco usen celular</t>
-  </si>
-  <si>
-    <t>Mendoza llama a revisar estrategia de seguridad</t>
-  </si>
-  <si>
-    <t>PRI</t>
-  </si>
-  <si>
-    <t>Intervención extranjera</t>
-  </si>
-  <si>
-    <t>Rinden homenaje a Juana Alarcón</t>
-  </si>
-  <si>
-    <t>Deceso de diputada</t>
-  </si>
-  <si>
-    <t>Registra Inegi 19 mil desplazamientos por desastres y violencia</t>
-  </si>
-  <si>
-    <t>Taxis en Pachuca, deteriorados</t>
-  </si>
-  <si>
-    <t>Viajan con sabor huasteco</t>
-  </si>
-  <si>
     <t>Temas varios</t>
   </si>
   <si>
-    <t>En Tizayuca, transporte público provoca accidentes</t>
-  </si>
-  <si>
-    <t>Deficiencias transporte público</t>
-  </si>
-  <si>
-    <t>Pausan llamado de leigisladora suplente</t>
-  </si>
-  <si>
-    <t>Diputado suplente</t>
-  </si>
-  <si>
-    <t>Celebran a universidades tecnológicas y politécnicas</t>
-  </si>
-  <si>
-    <t>Conmemoración Aniversario</t>
-  </si>
-  <si>
-    <t>Pendiente, homologar sueldo a nivel federal en Tecnológicos</t>
-  </si>
-  <si>
-    <t>Universidades</t>
-  </si>
-  <si>
-    <t>Homologación salarial</t>
-  </si>
-  <si>
-    <t>Ve gobernador libertad en las manifestaciones en los informes</t>
-  </si>
-  <si>
-    <t>Manifestación informe</t>
-  </si>
-  <si>
-    <t>Vigilaría Congreso el servicio de transporte</t>
-  </si>
-  <si>
-    <t>Cesaron al Rambo</t>
-  </si>
-  <si>
-    <t>Dan el último adiós a la dip. Juana Alarcón</t>
-  </si>
-  <si>
-    <t>Realiza DIFH entrega de 305 becas pilaress</t>
-  </si>
-  <si>
-    <t>Pilares</t>
-  </si>
-  <si>
-    <t>IMCO: Hidalgo registra avances en economía, salud y seguridad</t>
-  </si>
-  <si>
-    <t>Desplazamientos y dependencia de apoyos revela encuesta del Inegi</t>
-  </si>
-  <si>
-    <t>Celebran a las universidades tecnológicas y politécnicas</t>
-  </si>
-  <si>
-    <t>Brecha laboral: Participación masculina es de 6 por cada 4 mujeres</t>
-  </si>
-  <si>
-    <t>Brecha de género</t>
-  </si>
-  <si>
-    <t>Trump compara a los cárteles de México co el grupo ISIS</t>
-  </si>
-  <si>
-    <t>Traerán debate sobre futuro e innovación</t>
-  </si>
-  <si>
-    <t>Abren la posibilidad para demandar a plataformas digitales en nuestro país</t>
-  </si>
-  <si>
-    <t>Next Energy pide se revise el caso de su propietario preso</t>
-  </si>
-  <si>
-    <t>Viajan en vehículo articular apenas 1.5 personas</t>
-  </si>
-  <si>
-    <t>Movilidad urbana</t>
-  </si>
-  <si>
-    <t>Aumenta 14.9 puntos porcentuales la eficiencia terminal en universidades de la entidad</t>
-  </si>
-  <si>
-    <t>Eficiencia terminal</t>
-  </si>
-  <si>
-    <t>Hidalgo suma 162 mil habitantes y alcanza una población de 3.2 millones</t>
-  </si>
-  <si>
-    <t>Menchaca pide a su gabinete prepararse para comparecencias ante el Congreso</t>
-  </si>
-  <si>
     <t>Comparecencias</t>
   </si>
   <si>
-    <t>Rinden homenaje póstumo a la diputada Juana Olivia Alarcón</t>
-  </si>
-  <si>
-    <t>Pachuca tendrá ingreso de 1.6 mdp por espectáculos de la Feria San Francisco</t>
-  </si>
-  <si>
-    <t>Sin firma, no hay pruebas contra Osorio Chong por desvío en Policía Federal: Secretaría Anticorrupción</t>
-  </si>
-  <si>
-    <t>Corrupción</t>
-  </si>
-  <si>
-    <t>Uber y DIDI siguen prohibidos en Hidalgo</t>
-  </si>
-  <si>
     <t>Apps de transporte</t>
   </si>
   <si>
-    <t>DIFH entrega becas a 305 niños de 17 municipios</t>
-  </si>
-  <si>
-    <t>Hidalgo, sede de la Olimpiada Nacional 2027</t>
-  </si>
-  <si>
     <t>Olimpiada Nacional</t>
   </si>
   <si>
-    <t>Aumentan a 84.5% los estudiantes que logran concluir universidad</t>
-  </si>
-  <si>
-    <t>Hidalgo ya supera los 3.2 millones de habitantes</t>
-  </si>
-  <si>
-    <t>Hidalgo buscará regresar al top 15 en competitividad</t>
-  </si>
-  <si>
-    <t>La tarifa sube, ¿y el servicio?</t>
-  </si>
-  <si>
     <t>Editorial</t>
   </si>
   <si>
-    <t>Invita Semot a fomentar el respeto a la jerarquía de la movilidad</t>
-  </si>
-  <si>
-    <t>Jerarquía de la Movilidad</t>
-  </si>
-  <si>
-    <t>Tula fortalece su capacidad operativa en seguridad con inversión superior a 6 mdp</t>
-  </si>
-  <si>
-    <t>Fortalecimiento Policiaco</t>
-  </si>
-  <si>
-    <t>Obras tienen un año de garantía por vicios ocultos: Sipdus</t>
-  </si>
-  <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
-    <t>Garantía de obra</t>
-  </si>
-  <si>
-    <t>Said Vargas fortalece estructuras sindicales del SNTE en la Otomí-Tepehua</t>
-  </si>
-  <si>
-    <t>Menchaca no descarta comparecencia del Oficial Mayor ante el Congreso</t>
-  </si>
-  <si>
-    <t>Policía de Ajacuba fortalece acciones de prevención del delito con jornadas sobre prevención del suicidio</t>
-  </si>
-  <si>
-    <t>Policía municipal</t>
-  </si>
-  <si>
     <t>Prevención del suicidio</t>
   </si>
   <si>
-    <t>Pachuca recibirá 1.6 mdp por espacios para Feria</t>
-  </si>
-  <si>
-    <t>Hidalgo será sede de la Olimpiada Nacional 2027; lo oficializa Conade</t>
-  </si>
-  <si>
-    <t>Tuzos enfrentarán a la Selección Mexicana sub 23 en Hidalgo</t>
-  </si>
-  <si>
-    <t>llaa</t>
-  </si>
-  <si>
-    <t>Julio Menchaca respalda labor de universidades tecnológicas y politécnicas</t>
-  </si>
-  <si>
-    <t>Brinda DIFH Hidalgo becas para apoyar la economía familiar de usuarios</t>
-  </si>
-  <si>
-    <t>Tuzas se quedan sin DT: cesan a Óscar Torres</t>
-  </si>
-  <si>
-    <t>¡Late con orgullo!</t>
-  </si>
-  <si>
-    <t>Rodolfo, el niño que se convirtió en El Santo</t>
-  </si>
-  <si>
-    <t>Aniversario natalicio</t>
-  </si>
-  <si>
-    <t>El país supera los 130 millones de habitantes</t>
-  </si>
-  <si>
-    <t>Resultados del ICE 2026 muestran áreas de oportunidad: JMS</t>
-  </si>
-  <si>
-    <t>Seis puertos mexicanos están restringidos por el huracán Polo</t>
-  </si>
-  <si>
-    <t>Alerta Meteorológica</t>
-  </si>
-  <si>
-    <t>Honor a quien honor merece. El personaje de El Santo es sin duda uno de los más queridos en México y sin duda dejó escuela en la lucha libre en nuestro país y en el mundo. Este día conmemoramos con orgullo 109 años de su nacimiento en Tulancingo.</t>
+    <t>Avance de 45% en tren México-Pachuca</t>
+  </si>
+  <si>
+    <t>SICT</t>
+  </si>
+  <si>
+    <t>Tren AIFA</t>
+  </si>
+  <si>
+    <t>Nuevas tarifas de taxis ya se aplican</t>
+  </si>
+  <si>
+    <t>Aumenta migración hidalguense 78.15%</t>
+  </si>
+  <si>
+    <t>Migrantes</t>
+  </si>
+  <si>
+    <t>Busca Morena coalición rumbo a las elecciones</t>
+  </si>
+  <si>
+    <t>Alianzas Electorales</t>
+  </si>
+  <si>
+    <t>Desmiente ICE Dremas a la feria de Pachuca</t>
+  </si>
+  <si>
+    <t>Asesoran a jóvenes para prevenir suicidio</t>
+  </si>
+  <si>
+    <t>Destruyen un huachitúnel de 143 metros</t>
+  </si>
+  <si>
+    <t>Huachitúnel</t>
+  </si>
+  <si>
+    <t>Amarra Hidalgo sede de olimpiada</t>
+  </si>
+  <si>
+    <t>Entra en vigor incremento en taxis: $189, la tarifa más cara</t>
+  </si>
+  <si>
+    <t>Honran al Enmascarado de Plata</t>
+  </si>
+  <si>
+    <t>Homenaje póstumo</t>
+  </si>
+  <si>
+    <t>Tren AIFA va al 45 por ciento</t>
+  </si>
+  <si>
+    <t>Registra Hidalgo un menor número de nacimiento en 5 años</t>
+  </si>
+  <si>
+    <t>El Rey va por otra marca</t>
+  </si>
+  <si>
+    <t>Wembley abre la nueva era</t>
+  </si>
+  <si>
+    <t>Comparecencias serán del 12 al 22 de octubre</t>
+  </si>
+  <si>
+    <t>Hidalgo reportó tres secuestros en el octavo mes del presente año</t>
+  </si>
+  <si>
+    <t>Secuestro</t>
+  </si>
+  <si>
+    <t>Buscan obligar emisión de sesiones de cabildos</t>
+  </si>
+  <si>
+    <t>Sesión De Cabildo</t>
+  </si>
+  <si>
+    <t>Proponen multas de hasta 11 mil 731 pesos por maltrato animal</t>
+  </si>
+  <si>
+    <t>Iniciativa</t>
+  </si>
+  <si>
+    <t>Todo listo para el arranque de la Feria de San Francisco 2026</t>
+  </si>
+  <si>
+    <t>Fotonota</t>
+  </si>
+  <si>
+    <t>En 3 meses destruyen 17 huachitúneles; crece tendencia en la entidad</t>
+  </si>
+  <si>
+    <t>Pemex</t>
+  </si>
+  <si>
+    <t>Reubicados por catástrofes: La entidad se ubica en top 10 por hogares afectados</t>
+  </si>
+  <si>
+    <t>Reubicación de viviendas</t>
+  </si>
+  <si>
+    <t>Cae bono demográfico</t>
+  </si>
+  <si>
+    <t>México es el nuevo vecino preferido</t>
+  </si>
+  <si>
+    <t>T-Mec</t>
+  </si>
+  <si>
+    <t>Deportes: el estado será sede de Orgullo Nacional 2027</t>
+  </si>
+  <si>
+    <t>Llega XI a Estados Unidos con la oferta de pena capital por tráfico de fentanilo</t>
+  </si>
+  <si>
+    <t>Temas internacionales</t>
+  </si>
+  <si>
+    <t>Buena relación con Trump</t>
+  </si>
+  <si>
+    <t>Entra en vigor la nueva tarifa; habrá taxímetros en breve</t>
+  </si>
+  <si>
+    <t>Senadora del PRI, de nuevo bajo la lupa por compra de predios en Pachuca</t>
+  </si>
+  <si>
+    <t>Viggiano</t>
+  </si>
+  <si>
+    <t>Enriquecimiento ilícito</t>
+  </si>
+  <si>
+    <t>La Jornada Hidalgo</t>
+  </si>
+  <si>
+    <t>Sin alza en tres años, la Feria de Pachuca apuesta por patrocinios</t>
+  </si>
+  <si>
+    <t>Viggiano compra a Chitiva terreno por debajo de su valor</t>
+  </si>
+  <si>
+    <t>En Tulancingo excluyen a síndico por rechazar contratos exprés</t>
+  </si>
+  <si>
+    <t>Opacidad</t>
+  </si>
+  <si>
+    <t>Tren AIFA-Pachuca lleva avance de 45%; arrancaría en 2027</t>
+  </si>
+  <si>
+    <t>Detienen a edil de Juchitán por homicidio y nexos con el narco</t>
+  </si>
+  <si>
+    <t>FGR</t>
+  </si>
+  <si>
+    <t>Detención Alcalde</t>
+  </si>
+  <si>
+    <t>Falta desmontar la otra red, la que no se destruye con maquinaria pesada. Es la de los políticos,  empresarios, lavadores de dinero y factureros que, desde el poder, desde el dinero o desde el  escritorio, convirtieron a Hidalgo en el estado del robo de combustible”. J</t>
+  </si>
+  <si>
+    <t>Combate Al Huachicol</t>
+  </si>
+  <si>
+    <t>Hidalgo será sede del Campeonato de Boccia 2026 y la Olimpiada Nacional 2027</t>
+  </si>
+  <si>
+    <t>Tren de pasajeros AIFA-Pachuca presenta un avance del 45%</t>
+  </si>
+  <si>
+    <t>Persiste maltrato animal en Hidalgo; judicializan 21 carpetas de investigación</t>
+  </si>
+  <si>
+    <t>Maltrato animal</t>
+  </si>
+  <si>
+    <t>Inician el 12 de octubre comparecencias del gabinete estatal: Andrés Velázquez</t>
+  </si>
+  <si>
+    <t>Junta de Gobierno</t>
+  </si>
+  <si>
+    <t>Dan 120 días a choferes de Pachuca para que instalen taxímetros. ¡Adiós a los cobros excesivos!</t>
+  </si>
+  <si>
+    <t>Piden en el Congreso mayores castigos por maltrato animal</t>
+  </si>
+  <si>
+    <t>¿Anular una elección por injerencia extranjera?</t>
+  </si>
+  <si>
+    <t>Reforma Electoral</t>
+  </si>
+  <si>
+    <t>Prepárense y estudien"": Pide Menchaca a sus secretarios; irán al Congreso por glosa del Cuarto Infome</t>
+  </si>
+  <si>
+    <t>ICE Dreams México se deslinda de show en la Feria de Pachuca</t>
+  </si>
+  <si>
+    <t>Tren AIFA-Pachuca: reubican a 49 familias</t>
+  </si>
+  <si>
+    <t>Uber y Didi continúan prohibidos en Hidalgo: Menchaca</t>
+  </si>
+  <si>
+    <t>Investigación de Xpectro FM exhibe inconsistencias del patrimonio inmobilidario de la senadora Carolina Viggiano</t>
+  </si>
+  <si>
+    <t>Hidalgo, sede de Orgullo Nacional 2027 y Centroamericano de Boccia 2026</t>
+  </si>
+  <si>
+    <t>Autoridades supervisan destrucción de túnel en Teocalco</t>
+  </si>
+  <si>
+    <t>Yocelyn Tovar encabeza entrega de equipamiento a PC y Bomberos</t>
+  </si>
+  <si>
+    <t>Equipamiento policiaco</t>
+  </si>
+  <si>
+    <t>Claudia Sandoval continúa gestiones ante la Secretaría de Economía</t>
+  </si>
+  <si>
+    <t>Entran en vigor nuevas tarifas de taxis en Pachuca y Mineral de la Reforma; mínima de 45 pesos</t>
+  </si>
+  <si>
+    <t>Encabeza Natividad Castrejón estrategia ""El ABC de las emociones"" en el estado</t>
+  </si>
+  <si>
+    <t>Educación socioemocional</t>
+  </si>
+  <si>
+    <t>Investigación cuestiona a Carolina Viggiano compra de terrenos exclusivos a bajo precio en Pachuca</t>
+  </si>
+  <si>
+    <t>Para 2027, banderazo de una parte del tren AIFA-Pachuca: Sheinbaum</t>
+  </si>
+  <si>
+    <t>Taxis cobrarán hasta 133 pesos desde la Feria</t>
+  </si>
+  <si>
+    <t>Sheinbaum evita confrontar a Trump tras sus  nuevos dichos</t>
+  </si>
+  <si>
+    <t>Suman un total de 23 casos de gusano barrenador en Hidalgo</t>
+  </si>
+  <si>
+    <t>Salud</t>
+  </si>
+  <si>
+    <t>Gusano barrenador</t>
+  </si>
+  <si>
+    <t>Hidalgo, sede de Orgullo Nacional 2027</t>
   </si>
 </sst>
 </file>
@@ -826,8 +820,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J59" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J59" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J60" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J60" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1196,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1245,7 +1239,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
@@ -1254,19 +1248,19 @@
         <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="G2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1279,75 +1273,75 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
         <v>98</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>87</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -1359,16 +1353,16 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
         <v>100</v>
       </c>
-      <c r="F5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" t="s">
-        <v>101</v>
-      </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1381,96 +1375,96 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J6" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>46289</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" t="s">
         <v>11</v>
       </c>
-      <c r="I6" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J6" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
-        <v>46288</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H7" t="s">
-        <v>69</v>
-      </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1483,50 +1477,50 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
         <v>27</v>
@@ -1535,7 +1529,7 @@
         <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s">
         <v>69</v>
@@ -1551,32 +1545,32 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B11" t="s">
         <v>70</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1585,406 +1579,406 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B12" t="s">
         <v>70</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="G12" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H12" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>115</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
       </c>
       <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B14" t="s">
         <v>72</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="H14" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B15" t="s">
         <v>72</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B16" t="s">
         <v>72</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B17" t="s">
         <v>72</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="H17" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B18" t="s">
         <v>72</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H18" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="H19" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>121</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B21" t="s">
         <v>77</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="G21" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="H21" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B22" t="s">
         <v>77</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
       </c>
       <c r="I22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B23" t="s">
         <v>77</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1993,100 +1987,100 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B24" t="s">
         <v>77</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B25" t="s">
         <v>77</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G25" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B26" t="s">
         <v>77</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2095,62 +2089,62 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B27" t="s">
         <v>77</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>131</v>
+      </c>
+      <c r="H27" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J27" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="11">
+        <v>46289</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" t="s">
-        <v>134</v>
-      </c>
-      <c r="H27" t="s">
-        <v>69</v>
-      </c>
-      <c r="I27" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J27" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="11">
-        <v>46288</v>
-      </c>
-      <c r="B28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>135</v>
-      </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F28" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G28" t="s">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2158,37 +2152,37 @@
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="G29" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="H29" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Sucesión gubernamental</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2197,28 +2191,28 @@
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>138</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2226,37 +2220,37 @@
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D31" t="s">
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="G31" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="H31" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Sucesión gubernamental</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2265,44 +2259,44 @@
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="C32" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" t="s">
         <v>141</v>
       </c>
-      <c r="D32" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" t="s">
-        <v>29</v>
-      </c>
-      <c r="F32" t="s">
-        <v>83</v>
-      </c>
-      <c r="G32" t="s">
-        <v>84</v>
-      </c>
       <c r="H32" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>142</v>
@@ -2314,41 +2308,41 @@
         <v>14</v>
       </c>
       <c r="F33" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" t="s">
+        <v>95</v>
+      </c>
+      <c r="H33" t="s">
+        <v>73</v>
+      </c>
+      <c r="I33" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J33" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
+        <v>46289</v>
+      </c>
+      <c r="B34" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
         <v>14</v>
       </c>
-      <c r="G33" t="s">
-        <v>143</v>
-      </c>
-      <c r="H33" t="s">
-        <v>69</v>
-      </c>
-      <c r="I33" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J33" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="11">
-        <v>46288</v>
-      </c>
-      <c r="B34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="5" t="s">
+      <c r="F34" t="s">
         <v>144</v>
-      </c>
-      <c r="D34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" t="s">
-        <v>24</v>
       </c>
       <c r="G34" t="s">
         <v>145</v>
@@ -2358,34 +2352,34 @@
       </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>146</v>
       </c>
       <c r="D35" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F35" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G35" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -2399,18 +2393,18 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D36" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
         <v>24</v>
@@ -2419,10 +2413,10 @@
         <v>24</v>
       </c>
       <c r="G36" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2435,10 +2429,10 @@
     </row>
     <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>149</v>
@@ -2447,32 +2441,32 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F37" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="H37" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>150</v>
@@ -2481,72 +2475,72 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F39" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="G39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B40" t="s">
         <v>74</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D40" t="s">
-        <v>153</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
         <v>27</v>
@@ -2555,10 +2549,10 @@
         <v>27</v>
       </c>
       <c r="G40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2571,56 +2565,56 @@
     </row>
     <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B41" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D41" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F41" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G41" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H41" t="s">
         <v>73</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>156</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="E42" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="G42" t="s">
         <v>157</v>
@@ -2630,19 +2624,19 @@
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>158</v>
@@ -2651,13 +2645,13 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>159</v>
+        <v>24</v>
       </c>
       <c r="F43" t="s">
-        <v>159</v>
+        <v>24</v>
       </c>
       <c r="G43" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s">
         <v>73</v>
@@ -2668,139 +2662,139 @@
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G44" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D45" t="s">
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="G45" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B46" t="s">
         <v>76</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D46" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="E46" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F46" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
       <c r="G46" t="s">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B47" t="s">
         <v>76</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="G47" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="H47" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Sucesión gubernamental</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2809,25 +2803,25 @@
     </row>
     <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B48" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F48" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="G48" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s">
         <v>73</v>
@@ -2838,166 +2832,166 @@
       </c>
       <c r="J48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D49" t="s">
-        <v>169</v>
+        <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F49" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
       </c>
       <c r="I49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B50" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="H50" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B51" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B52" t="s">
+        <v>80</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52" t="s">
+        <v>27</v>
+      </c>
+      <c r="G52" t="s">
         <v>81</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D52" t="s">
-        <v>12</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>10</v>
-      </c>
-      <c r="G52" t="s">
-        <v>71</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
       </c>
       <c r="I52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B53" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D53" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F53" t="s">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="G53" t="s">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
@@ -3011,132 +3005,132 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>91</v>
+        <v>171</v>
       </c>
       <c r="D54" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="F54" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="G54" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="H54" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Sucesión gubernamental</v>
       </c>
       <c r="J54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B55" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F55" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G55" t="s">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B56" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D56" t="s">
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F56" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G56" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
       </c>
       <c r="I56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D57" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G57" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3144,18 +3138,18 @@
       </c>
       <c r="J57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B58" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D58" t="s">
         <v>12</v>
@@ -3167,7 +3161,7 @@
         <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="H58" t="s">
         <v>11</v>
@@ -3181,38 +3175,72 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D59" t="s">
-        <v>153</v>
+        <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F59" t="s">
-        <v>10</v>
+        <v>176</v>
       </c>
       <c r="G59" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H59" t="s">
         <v>11</v>
       </c>
       <c r="I59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="11">
+        <v>46289</v>
+      </c>
+      <c r="B60" t="s">
+        <v>85</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" t="s">
+        <v>24</v>
+      </c>
+      <c r="G60" t="s">
+        <v>90</v>
+      </c>
+      <c r="H60" t="s">
+        <v>73</v>
+      </c>
+      <c r="I60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
       </c>
     </row>
   </sheetData>
@@ -3782,7 +3810,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B49" t="s">
         <v>44</v>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A66FA50-E096-4E37-B883-EC72BC71DA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128B5E84-EFF7-410C-A778-DD174B98C97E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="187">
   <si>
     <t>Fecha</t>
   </si>
@@ -303,277 +303,301 @@
     <t>Temas varios</t>
   </si>
   <si>
-    <t>Comparecencias</t>
-  </si>
-  <si>
-    <t>Apps de transporte</t>
-  </si>
-  <si>
-    <t>Olimpiada Nacional</t>
-  </si>
-  <si>
     <t>Editorial</t>
   </si>
   <si>
-    <t>Prevención del suicidio</t>
-  </si>
-  <si>
-    <t>Avance de 45% en tren México-Pachuca</t>
-  </si>
-  <si>
-    <t>SICT</t>
-  </si>
-  <si>
-    <t>Tren AIFA</t>
-  </si>
-  <si>
-    <t>Nuevas tarifas de taxis ya se aplican</t>
-  </si>
-  <si>
-    <t>Aumenta migración hidalguense 78.15%</t>
-  </si>
-  <si>
-    <t>Migrantes</t>
-  </si>
-  <si>
-    <t>Busca Morena coalición rumbo a las elecciones</t>
-  </si>
-  <si>
     <t>Alianzas Electorales</t>
   </si>
   <si>
-    <t>Desmiente ICE Dremas a la feria de Pachuca</t>
-  </si>
-  <si>
-    <t>Asesoran a jóvenes para prevenir suicidio</t>
-  </si>
-  <si>
-    <t>Destruyen un huachitúnel de 143 metros</t>
-  </si>
-  <si>
-    <t>Huachitúnel</t>
-  </si>
-  <si>
-    <t>Amarra Hidalgo sede de olimpiada</t>
-  </si>
-  <si>
-    <t>Entra en vigor incremento en taxis: $189, la tarifa más cara</t>
-  </si>
-  <si>
-    <t>Honran al Enmascarado de Plata</t>
-  </si>
-  <si>
-    <t>Homenaje póstumo</t>
-  </si>
-  <si>
-    <t>Tren AIFA va al 45 por ciento</t>
-  </si>
-  <si>
-    <t>Registra Hidalgo un menor número de nacimiento en 5 años</t>
-  </si>
-  <si>
-    <t>El Rey va por otra marca</t>
-  </si>
-  <si>
-    <t>Wembley abre la nueva era</t>
-  </si>
-  <si>
-    <t>Comparecencias serán del 12 al 22 de octubre</t>
-  </si>
-  <si>
-    <t>Hidalgo reportó tres secuestros en el octavo mes del presente año</t>
-  </si>
-  <si>
-    <t>Secuestro</t>
-  </si>
-  <si>
-    <t>Buscan obligar emisión de sesiones de cabildos</t>
-  </si>
-  <si>
-    <t>Sesión De Cabildo</t>
-  </si>
-  <si>
-    <t>Proponen multas de hasta 11 mil 731 pesos por maltrato animal</t>
-  </si>
-  <si>
-    <t>Iniciativa</t>
-  </si>
-  <si>
-    <t>Todo listo para el arranque de la Feria de San Francisco 2026</t>
-  </si>
-  <si>
-    <t>Fotonota</t>
-  </si>
-  <si>
-    <t>En 3 meses destruyen 17 huachitúneles; crece tendencia en la entidad</t>
-  </si>
-  <si>
-    <t>Pemex</t>
-  </si>
-  <si>
-    <t>Reubicados por catástrofes: La entidad se ubica en top 10 por hogares afectados</t>
-  </si>
-  <si>
-    <t>Reubicación de viviendas</t>
-  </si>
-  <si>
-    <t>Cae bono demográfico</t>
-  </si>
-  <si>
-    <t>México es el nuevo vecino preferido</t>
-  </si>
-  <si>
-    <t>T-Mec</t>
-  </si>
-  <si>
-    <t>Deportes: el estado será sede de Orgullo Nacional 2027</t>
-  </si>
-  <si>
-    <t>Llega XI a Estados Unidos con la oferta de pena capital por tráfico de fentanilo</t>
-  </si>
-  <si>
-    <t>Temas internacionales</t>
-  </si>
-  <si>
-    <t>Buena relación con Trump</t>
-  </si>
-  <si>
-    <t>Entra en vigor la nueva tarifa; habrá taxímetros en breve</t>
-  </si>
-  <si>
-    <t>Senadora del PRI, de nuevo bajo la lupa por compra de predios en Pachuca</t>
-  </si>
-  <si>
-    <t>Viggiano</t>
-  </si>
-  <si>
-    <t>Enriquecimiento ilícito</t>
-  </si>
-  <si>
     <t>La Jornada Hidalgo</t>
   </si>
   <si>
-    <t>Sin alza en tres años, la Feria de Pachuca apuesta por patrocinios</t>
-  </si>
-  <si>
-    <t>Viggiano compra a Chitiva terreno por debajo de su valor</t>
-  </si>
-  <si>
-    <t>En Tulancingo excluyen a síndico por rechazar contratos exprés</t>
-  </si>
-  <si>
-    <t>Opacidad</t>
-  </si>
-  <si>
-    <t>Tren AIFA-Pachuca lleva avance de 45%; arrancaría en 2027</t>
-  </si>
-  <si>
-    <t>Detienen a edil de Juchitán por homicidio y nexos con el narco</t>
-  </si>
-  <si>
-    <t>FGR</t>
-  </si>
-  <si>
-    <t>Detención Alcalde</t>
-  </si>
-  <si>
-    <t>Falta desmontar la otra red, la que no se destruye con maquinaria pesada. Es la de los políticos,  empresarios, lavadores de dinero y factureros que, desde el poder, desde el dinero o desde el  escritorio, convirtieron a Hidalgo en el estado del robo de combustible”. J</t>
-  </si>
-  <si>
-    <t>Combate Al Huachicol</t>
-  </si>
-  <si>
-    <t>Hidalgo será sede del Campeonato de Boccia 2026 y la Olimpiada Nacional 2027</t>
-  </si>
-  <si>
-    <t>Tren de pasajeros AIFA-Pachuca presenta un avance del 45%</t>
-  </si>
-  <si>
-    <t>Persiste maltrato animal en Hidalgo; judicializan 21 carpetas de investigación</t>
-  </si>
-  <si>
-    <t>Maltrato animal</t>
-  </si>
-  <si>
-    <t>Inician el 12 de octubre comparecencias del gabinete estatal: Andrés Velázquez</t>
-  </si>
-  <si>
     <t>Junta de Gobierno</t>
   </si>
   <si>
-    <t>Dan 120 días a choferes de Pachuca para que instalen taxímetros. ¡Adiós a los cobros excesivos!</t>
-  </si>
-  <si>
-    <t>Piden en el Congreso mayores castigos por maltrato animal</t>
-  </si>
-  <si>
-    <t>¿Anular una elección por injerencia extranjera?</t>
-  </si>
-  <si>
     <t>Reforma Electoral</t>
   </si>
   <si>
-    <t>Prepárense y estudien"": Pide Menchaca a sus secretarios; irán al Congreso por glosa del Cuarto Infome</t>
-  </si>
-  <si>
-    <t>ICE Dreams México se deslinda de show en la Feria de Pachuca</t>
-  </si>
-  <si>
-    <t>Tren AIFA-Pachuca: reubican a 49 familias</t>
-  </si>
-  <si>
-    <t>Uber y Didi continúan prohibidos en Hidalgo: Menchaca</t>
-  </si>
-  <si>
-    <t>Investigación de Xpectro FM exhibe inconsistencias del patrimonio inmobilidario de la senadora Carolina Viggiano</t>
-  </si>
-  <si>
-    <t>Hidalgo, sede de Orgullo Nacional 2027 y Centroamericano de Boccia 2026</t>
-  </si>
-  <si>
-    <t>Autoridades supervisan destrucción de túnel en Teocalco</t>
-  </si>
-  <si>
-    <t>Yocelyn Tovar encabeza entrega de equipamiento a PC y Bomberos</t>
-  </si>
-  <si>
-    <t>Equipamiento policiaco</t>
-  </si>
-  <si>
-    <t>Claudia Sandoval continúa gestiones ante la Secretaría de Economía</t>
-  </si>
-  <si>
-    <t>Entran en vigor nuevas tarifas de taxis en Pachuca y Mineral de la Reforma; mínima de 45 pesos</t>
-  </si>
-  <si>
-    <t>Encabeza Natividad Castrejón estrategia ""El ABC de las emociones"" en el estado</t>
-  </si>
-  <si>
-    <t>Educación socioemocional</t>
-  </si>
-  <si>
-    <t>Investigación cuestiona a Carolina Viggiano compra de terrenos exclusivos a bajo precio en Pachuca</t>
-  </si>
-  <si>
-    <t>Para 2027, banderazo de una parte del tren AIFA-Pachuca: Sheinbaum</t>
-  </si>
-  <si>
-    <t>Taxis cobrarán hasta 133 pesos desde la Feria</t>
-  </si>
-  <si>
-    <t>Sheinbaum evita confrontar a Trump tras sus  nuevos dichos</t>
-  </si>
-  <si>
-    <t>Suman un total de 23 casos de gusano barrenador en Hidalgo</t>
-  </si>
-  <si>
-    <t>Salud</t>
-  </si>
-  <si>
-    <t>Gusano barrenador</t>
-  </si>
-  <si>
-    <t>Hidalgo, sede de Orgullo Nacional 2027</t>
+    <t>Acercan lectura a los jóvenes de Pachuca</t>
+  </si>
+  <si>
+    <t>Fomento A La Lectura</t>
+  </si>
+  <si>
+    <t>Reclaman por falta de insumos y personal</t>
+  </si>
+  <si>
+    <t>IMSS</t>
+  </si>
+  <si>
+    <t>Abasto De Insumos Médicos</t>
+  </si>
+  <si>
+    <t>Familias asisten a la apertura de la Feria 2026</t>
+  </si>
+  <si>
+    <t>Hospital aún no pasa al IMSS-Bienestar</t>
+  </si>
+  <si>
+    <t>Nuevo Hospital General</t>
+  </si>
+  <si>
+    <t>Aparición acecha vías en Santiago Tulantepec</t>
+  </si>
+  <si>
+    <t>Entregan 760 apoyos a negocios</t>
+  </si>
+  <si>
+    <t>Apoyo a emprendedores</t>
+  </si>
+  <si>
+    <t>Arranca la Feria San Francisco; hoy la inauguran</t>
+  </si>
+  <si>
+    <t>Dejan ir alcaldes 300 mdp para la reconstrucción</t>
+  </si>
+  <si>
+    <t>Huracán Priscilla</t>
+  </si>
+  <si>
+    <t>Ignoran taxistas el nuevo tarifario de Movilidad</t>
+  </si>
+  <si>
+    <t>Dan apoyos de $25 mil a emprendendores</t>
+  </si>
+  <si>
+    <t>Morena busca alianza con PT, PVEM y NA</t>
+  </si>
+  <si>
+    <t>Alista la federación supercomputadora en Tulancingo</t>
+  </si>
+  <si>
+    <t>Centro de datos</t>
+  </si>
+  <si>
+    <t>Traza ruta para volver al podio</t>
+  </si>
+  <si>
+    <t>Habrá noche de puños en la feria</t>
+  </si>
+  <si>
+    <t>Basura y hasta refris tapan los drenes y rejillas</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Caasim</t>
+  </si>
+  <si>
+    <t>Drenaje tapado</t>
+  </si>
+  <si>
+    <t>Rechazan que reforma vaya a ""achicar"" a la oposición</t>
+  </si>
+  <si>
+    <t>Hidalgo envejece: crece población de 65 años y más, señala el Inegi</t>
+  </si>
+  <si>
+    <t>Se vigilará que taxis respeten nuevas tarifas, dice Menchaca</t>
+  </si>
+  <si>
+    <t>Arranca la Feria San Francisco Pachuca 2026</t>
+  </si>
+  <si>
+    <t>Construcción crece 42% en julio; detonan obra pública y privada</t>
+  </si>
+  <si>
+    <t>Índice De Actividad Industrial</t>
+  </si>
+  <si>
+    <t>Apoyo a empresarios: Reciben 191 emprendedores 19 mdp en 21 municipios</t>
+  </si>
+  <si>
+    <t>Operativo permanecerá durante la Feria de Pachuca</t>
+  </si>
+  <si>
+    <t>C5i</t>
+  </si>
+  <si>
+    <t>Ántel Zárraga en el Mundial</t>
+  </si>
+  <si>
+    <t>Garantizan sanciones más estrictas a taxis que abusen</t>
+  </si>
+  <si>
+    <t>Vivien jornada de innovación en el Tec de Monterrey</t>
+  </si>
+  <si>
+    <t>Crece el impacto del TRI tras el mundial</t>
+  </si>
+  <si>
+    <t>Control humano"" sobre la IA y una relación pacífica: Xi a Trump</t>
+  </si>
+  <si>
+    <t>Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>Entregan 760 apoyos a emprendedores; 191 afectados por lluvias</t>
+  </si>
+  <si>
+    <t>Tras dos años, dan fecha para fallo por triple feminicidio en Tulantepec</t>
+  </si>
+  <si>
+    <t>Sentencia Feminicida</t>
+  </si>
+  <si>
+    <t>Desaprovechan municipios afectados crédito de Banobras</t>
+  </si>
+  <si>
+    <t>Queman a pareja de ""brujos"" en comunidad de Ocosingo</t>
+  </si>
+  <si>
+    <t>Linchamiento</t>
+  </si>
+  <si>
+    <t>El reto como nación es complejo. Mientras la mayoría de los hombres sigamos viendo a las  mujeres como débiles, complementarias del sexo fuerte, subsidiarias del bienestar masculino, la  violencia hacia ellas prevalecerá ”.</t>
+  </si>
+  <si>
+    <t>Violencia De Género</t>
+  </si>
+  <si>
+    <t>Programa estatal beneficia a 760 emprendedores en Hidalgo</t>
+  </si>
+  <si>
+    <t>Reforzarán cumplimiento de tarifas de taxis durante la Feria de San Francisco Pachuca</t>
+  </si>
+  <si>
+    <t>Celebrarán 200 años de relación con Inglaterra a través de un partido de futbol</t>
+  </si>
+  <si>
+    <t>Conmemoración centenario</t>
+  </si>
+  <si>
+    <t>Llama Arturo Garita a fortalecer capacidades ante avance de inteligencia artifical</t>
+  </si>
+  <si>
+    <t>Intercambian señalamientos magistrados del TEEH durante juicio de regidor</t>
+  </si>
+  <si>
+    <t>Enfrentamiento Político</t>
+  </si>
+  <si>
+    <t>¡Arranca la fiesta de Hidalgo!</t>
+  </si>
+  <si>
+    <t>Morena se desmarca de Shadia e Israel</t>
+  </si>
+  <si>
+    <t>Muestre las pruebas""</t>
+  </si>
+  <si>
+    <t>Habrá sanciones para taxistas</t>
+  </si>
+  <si>
+    <t>A casi un año del desastre, cinco personas siguen desaparecidas en Tianguistengo</t>
+  </si>
+  <si>
+    <t>Dan 50 años de prisión a dos por secuestro de vendedor de autos en Hidalgo</t>
+  </si>
+  <si>
+    <t>UECS</t>
+  </si>
+  <si>
+    <t>Combate Al Secuestro</t>
+  </si>
+  <si>
+    <t>Ampliarán Colosio para desahogar tráfico en la glorieta 24 Horas</t>
+  </si>
+  <si>
+    <t>Glorieta 24 Horas</t>
+  </si>
+  <si>
+    <t>La Sección 15 mantiene presencia permanente en el territorio hidalguense</t>
+  </si>
+  <si>
+    <t>Correcto ejercicio del presupuesto genera mejores condiciones de vida para las familias: JMS</t>
+  </si>
+  <si>
+    <t>Taxistas tendrán 120 días para instalar taxímetros en Pachuca y la Reforma</t>
+  </si>
+  <si>
+    <t>Mirna Rubio rinde cuentas: 32 iniciativas presentadas</t>
+  </si>
+  <si>
+    <t>Informe Legislativo</t>
+  </si>
+  <si>
+    <t>Pachuca despliega operativo de seguridad para la Feria de San Francisco</t>
+  </si>
+  <si>
+    <t>Policía municipal</t>
+  </si>
+  <si>
+    <t>PC y Bomberos de Ajacuba fortalecen su preeparación</t>
+  </si>
+  <si>
+    <t>Capacitación PC</t>
+  </si>
+  <si>
+    <t>Seguridad Pública de Pachuca detiene a mujer en mandamiento judicial vigente</t>
+  </si>
+  <si>
+    <t>Detención</t>
+  </si>
+  <si>
+    <t>Esterilización canina y felina</t>
+  </si>
+  <si>
+    <t>Publicidad</t>
+  </si>
+  <si>
+    <t>Campaña de esterilización</t>
+  </si>
+  <si>
+    <t>Bronco abrió la Feria de Pachuca con exitosa presentación</t>
+  </si>
+  <si>
+    <t>Realiza SEPH el encuentro ""Voces que transforman""</t>
+  </si>
+  <si>
+    <t>Foro educativo</t>
+  </si>
+  <si>
+    <t>Habrá función estelar de box este sábado en teatro del pueblo</t>
+  </si>
+  <si>
+    <t>Entrega Julio Menchaca apoyos de programa Emprendiendo paso a paso</t>
+  </si>
+  <si>
+    <t>Convoca DIF Pachuca a participar en la Beca Municipal a la Excelencia Académica</t>
+  </si>
+  <si>
+    <t>Becas</t>
+  </si>
+  <si>
+    <t>¡Late con orgullo!</t>
+  </si>
+  <si>
+    <t>Se retirarán concesiones a transportistas que incumplan la ley</t>
+  </si>
+  <si>
+    <t>Fallo por triple feminicidio se dictará el 8 de octubre</t>
+  </si>
+  <si>
+    <t>Ya era tiempo de poner un alto a los transportistas abusivos. Sin embargo, el servicio sigue siendo insuficiente, se necesitan alternativas como autobuses de ruta con tarifas bajas acorde a los salarios de Pachuca ...</t>
+  </si>
+  <si>
+    <t>Deficiencias transporte público</t>
+  </si>
+  <si>
+    <t>En la Feria, habrá operativo integral de vigilancia</t>
+  </si>
+  <si>
+    <t>Corea del Sur y la empresa Lego invertirán en México</t>
+  </si>
+  <si>
+    <t>Atracción De Inversiones</t>
   </si>
 </sst>
 </file>
@@ -820,8 +844,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J60" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J60" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J64" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J64" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1190,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1239,7 +1263,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
@@ -1248,23 +1272,23 @@
         <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
         <v>94</v>
-      </c>
-      <c r="G2" t="s">
-        <v>95</v>
       </c>
       <c r="H2" t="s">
         <v>73</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1273,75 +1297,75 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
         <v>96</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
       <c r="G3" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="G4" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -1350,32 +1374,32 @@
         <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
         <v>100</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
@@ -1387,29 +1411,29 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -1418,19 +1442,19 @@
         <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1438,30 +1462,30 @@
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B8" t="s">
         <v>70</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
@@ -1477,7 +1501,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
@@ -1486,41 +1510,41 @@
         <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="H9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
         <v>27</v>
@@ -1545,41 +1569,41 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B11" t="s">
         <v>70</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B12" t="s">
         <v>70</v>
@@ -1591,29 +1615,29 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H12" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Partidos</v>
       </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B13" t="s">
         <v>70</v>
@@ -1631,7 +1655,7 @@
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
@@ -1647,13 +1671,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B14" t="s">
         <v>72</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
@@ -1681,59 +1705,59 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B15" t="s">
         <v>72</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B16" t="s">
         <v>72</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="G16" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
@@ -1747,68 +1771,68 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B17" t="s">
         <v>72</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B18" t="s">
         <v>72</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1817,50 +1841,50 @@
     </row>
     <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B19" t="s">
         <v>72</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G19" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B20" t="s">
         <v>72</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="E20" t="s">
         <v>29</v>
@@ -1872,7 +1896,7 @@
         <v>83</v>
       </c>
       <c r="H20" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1885,7 +1909,7 @@
     </row>
     <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B21" t="s">
         <v>77</v>
@@ -1897,20 +1921,20 @@
         <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" t="s">
         <v>123</v>
       </c>
-      <c r="G21" t="s">
-        <v>104</v>
-      </c>
       <c r="H21" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1919,7 +1943,7 @@
     </row>
     <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B22" t="s">
         <v>77</v>
@@ -1931,20 +1955,20 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
       </c>
       <c r="I22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1953,41 +1977,41 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B23" t="s">
         <v>77</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" t="s">
         <v>126</v>
       </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
       <c r="G23" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B24" t="s">
         <v>77</v>
@@ -1999,20 +2023,20 @@
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2021,16 +2045,16 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B25" t="s">
         <v>77</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E25" t="s">
         <v>24</v>
@@ -2039,10 +2063,10 @@
         <v>24</v>
       </c>
       <c r="G25" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2053,18 +2077,18 @@
         <v>Gobernador</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B26" t="s">
         <v>77</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -2073,7 +2097,7 @@
         <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
@@ -2089,168 +2113,168 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B27" t="s">
         <v>77</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B28" t="s">
         <v>77</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G28" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="F29" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="H29" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Sucesión gubernamental</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="F30" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="G30" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="H30" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="H31" t="s">
         <v>69</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Sucesión gubernamental</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2259,66 +2283,66 @@
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>140</v>
-      </c>
       <c r="D32" t="s">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G32" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H32" t="s">
         <v>69</v>
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B33" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G33" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="H33" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2327,59 +2351,59 @@
     </row>
     <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B34" t="s">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F34" t="s">
-        <v>144</v>
+        <v>24</v>
       </c>
       <c r="G34" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="H34" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B35" t="s">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F35" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G35" t="s">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -2395,66 +2419,66 @@
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B36" t="s">
         <v>75</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
       </c>
       <c r="I36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B37" t="s">
         <v>75</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2463,130 +2487,130 @@
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B38" t="s">
         <v>75</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="F38" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G38" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J38" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="11">
+        <v>46290</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" t="s">
+        <v>82</v>
+      </c>
+      <c r="G39" t="s">
+        <v>83</v>
+      </c>
+      <c r="H39" t="s">
+        <v>73</v>
+      </c>
+      <c r="I39" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J38" t="str">
+      <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
-        <v>46289</v>
-      </c>
-      <c r="B39" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D39" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" t="s">
-        <v>33</v>
-      </c>
-      <c r="F39" t="s">
-        <v>153</v>
-      </c>
-      <c r="G39" t="s">
-        <v>88</v>
-      </c>
-      <c r="H39" t="s">
-        <v>11</v>
-      </c>
-      <c r="I39" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J39" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B40" t="s">
         <v>74</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F40" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G40" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B41" t="s">
         <v>74</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D41" t="s">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="F41" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="G41" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H41" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2599,96 +2623,96 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B42" t="s">
         <v>74</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F42" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G42" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B43" t="s">
         <v>74</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F43" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H43" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B44" t="s">
         <v>74</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="G44" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="H44" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2699,132 +2723,132 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B45" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="E45" t="s">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="F45" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="G45" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B46" t="s">
         <v>76</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D46" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G46" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B47" t="s">
         <v>76</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="F47" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="G47" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="H47" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Sucesión gubernamental</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B48" t="s">
         <v>76</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D48" t="s">
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F48" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G48" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2832,52 +2856,52 @@
       </c>
       <c r="J48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B49" t="s">
         <v>76</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F49" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="G49" t="s">
-        <v>104</v>
+        <v>162</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
       </c>
       <c r="I49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B50" t="s">
         <v>76</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
@@ -2886,10 +2910,10 @@
         <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="G50" t="s">
-        <v>166</v>
+        <v>83</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
@@ -2903,15 +2927,15 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B51" t="s">
         <v>76</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
@@ -2920,10 +2944,10 @@
         <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
@@ -2939,130 +2963,130 @@
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B52" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C52" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" t="s">
+        <v>164</v>
+      </c>
+      <c r="G52" t="s">
         <v>168</v>
       </c>
-      <c r="D52" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" t="s">
-        <v>27</v>
-      </c>
-      <c r="F52" t="s">
-        <v>27</v>
-      </c>
-      <c r="G52" t="s">
-        <v>81</v>
-      </c>
       <c r="H52" t="s">
         <v>11</v>
       </c>
       <c r="I52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B53" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>169</v>
       </c>
       <c r="D53" t="s">
-        <v>12</v>
+        <v>170</v>
       </c>
       <c r="E53" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B54" t="s">
         <v>80</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="F54" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="G54" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Sucesión gubernamental</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B55" t="s">
         <v>80</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D55" t="s">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F55" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G55" t="s">
-        <v>90</v>
+        <v>174</v>
       </c>
       <c r="H55" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3070,67 +3094,67 @@
       </c>
       <c r="J55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B56" t="s">
         <v>80</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D56" t="s">
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F56" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G56" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
       </c>
       <c r="I56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B57" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F57" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G57" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="H57" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3138,89 +3162,89 @@
       </c>
       <c r="J57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B58" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D58" t="s">
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F58" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="G58" t="s">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="H58" t="s">
         <v>11</v>
       </c>
       <c r="I58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D59" t="s">
-        <v>12</v>
+        <v>170</v>
       </c>
       <c r="E59" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F59" t="s">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="G59" t="s">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s">
         <v>11</v>
       </c>
       <c r="I59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B60" t="s">
         <v>85</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D60" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E60" t="s">
         <v>24</v>
@@ -3229,7 +3253,7 @@
         <v>24</v>
       </c>
       <c r="G60" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s">
         <v>73</v>
@@ -3241,6 +3265,142 @@
       <c r="J60" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>46290</v>
+      </c>
+      <c r="B61" t="s">
+        <v>85</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>58</v>
+      </c>
+      <c r="F61" t="s">
+        <v>58</v>
+      </c>
+      <c r="G61" t="s">
+        <v>135</v>
+      </c>
+      <c r="H61" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A62" s="11">
+        <v>46290</v>
+      </c>
+      <c r="B62" t="s">
+        <v>85</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D62" t="s">
+        <v>88</v>
+      </c>
+      <c r="E62" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62" t="s">
+        <v>27</v>
+      </c>
+      <c r="G62" t="s">
+        <v>183</v>
+      </c>
+      <c r="H62" t="s">
+        <v>11</v>
+      </c>
+      <c r="I62" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J62" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="11">
+        <v>46290</v>
+      </c>
+      <c r="B63" t="s">
+        <v>85</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s">
+        <v>22</v>
+      </c>
+      <c r="F63" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63" t="s">
+        <v>83</v>
+      </c>
+      <c r="H63" t="s">
+        <v>11</v>
+      </c>
+      <c r="I63" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J63" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="11">
+        <v>46290</v>
+      </c>
+      <c r="B64" t="s">
+        <v>85</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" t="s">
+        <v>186</v>
+      </c>
+      <c r="H64" t="s">
+        <v>11</v>
+      </c>
+      <c r="I64" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J64" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
       </c>
     </row>
   </sheetData>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128B5E84-EFF7-410C-A778-DD174B98C97E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6567D5E1-D687-4A97-A8FC-13CD71B907C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="187">
   <si>
     <t>Fecha</t>
   </si>
@@ -240,9 +240,6 @@
     <t>Gabinete</t>
   </si>
   <si>
-    <t>El Sol de Hidalgo</t>
-  </si>
-  <si>
     <t>OCSAD</t>
   </si>
   <si>
@@ -306,298 +303,301 @@
     <t>Editorial</t>
   </si>
   <si>
-    <t>Alianzas Electorales</t>
-  </si>
-  <si>
     <t>La Jornada Hidalgo</t>
   </si>
   <si>
-    <t>Junta de Gobierno</t>
-  </si>
-  <si>
-    <t>Reforma Electoral</t>
-  </si>
-  <si>
-    <t>Acercan lectura a los jóvenes de Pachuca</t>
-  </si>
-  <si>
-    <t>Fomento A La Lectura</t>
-  </si>
-  <si>
-    <t>Reclaman por falta de insumos y personal</t>
-  </si>
-  <si>
-    <t>IMSS</t>
-  </si>
-  <si>
-    <t>Abasto De Insumos Médicos</t>
-  </si>
-  <si>
-    <t>Familias asisten a la apertura de la Feria 2026</t>
-  </si>
-  <si>
-    <t>Hospital aún no pasa al IMSS-Bienestar</t>
-  </si>
-  <si>
-    <t>Nuevo Hospital General</t>
-  </si>
-  <si>
-    <t>Aparición acecha vías en Santiago Tulantepec</t>
-  </si>
-  <si>
-    <t>Entregan 760 apoyos a negocios</t>
-  </si>
-  <si>
-    <t>Apoyo a emprendedores</t>
-  </si>
-  <si>
-    <t>Arranca la Feria San Francisco; hoy la inauguran</t>
-  </si>
-  <si>
-    <t>Dejan ir alcaldes 300 mdp para la reconstrucción</t>
-  </si>
-  <si>
-    <t>Huracán Priscilla</t>
-  </si>
-  <si>
-    <t>Ignoran taxistas el nuevo tarifario de Movilidad</t>
-  </si>
-  <si>
-    <t>Dan apoyos de $25 mil a emprendendores</t>
-  </si>
-  <si>
-    <t>Morena busca alianza con PT, PVEM y NA</t>
-  </si>
-  <si>
-    <t>Alista la federación supercomputadora en Tulancingo</t>
-  </si>
-  <si>
-    <t>Centro de datos</t>
-  </si>
-  <si>
-    <t>Traza ruta para volver al podio</t>
-  </si>
-  <si>
-    <t>Habrá noche de puños en la feria</t>
-  </si>
-  <si>
-    <t>Basura y hasta refris tapan los drenes y rejillas</t>
-  </si>
-  <si>
     <t>Sipdus</t>
   </si>
   <si>
     <t>Caasim</t>
   </si>
   <si>
-    <t>Drenaje tapado</t>
-  </si>
-  <si>
-    <t>Rechazan que reforma vaya a ""achicar"" a la oposición</t>
-  </si>
-  <si>
-    <t>Hidalgo envejece: crece población de 65 años y más, señala el Inegi</t>
-  </si>
-  <si>
-    <t>Se vigilará que taxis respeten nuevas tarifas, dice Menchaca</t>
-  </si>
-  <si>
-    <t>Arranca la Feria San Francisco Pachuca 2026</t>
-  </si>
-  <si>
-    <t>Construcción crece 42% en julio; detonan obra pública y privada</t>
-  </si>
-  <si>
-    <t>Índice De Actividad Industrial</t>
-  </si>
-  <si>
-    <t>Apoyo a empresarios: Reciben 191 emprendedores 19 mdp en 21 municipios</t>
-  </si>
-  <si>
-    <t>Operativo permanecerá durante la Feria de Pachuca</t>
-  </si>
-  <si>
-    <t>C5i</t>
-  </si>
-  <si>
-    <t>Ántel Zárraga en el Mundial</t>
-  </si>
-  <si>
-    <t>Garantizan sanciones más estrictas a taxis que abusen</t>
-  </si>
-  <si>
-    <t>Vivien jornada de innovación en el Tec de Monterrey</t>
-  </si>
-  <si>
-    <t>Crece el impacto del TRI tras el mundial</t>
-  </si>
-  <si>
-    <t>Control humano"" sobre la IA y una relación pacífica: Xi a Trump</t>
-  </si>
-  <si>
-    <t>Inteligencia Artificial</t>
-  </si>
-  <si>
-    <t>Entregan 760 apoyos a emprendedores; 191 afectados por lluvias</t>
-  </si>
-  <si>
-    <t>Tras dos años, dan fecha para fallo por triple feminicidio en Tulantepec</t>
-  </si>
-  <si>
-    <t>Sentencia Feminicida</t>
-  </si>
-  <si>
-    <t>Desaprovechan municipios afectados crédito de Banobras</t>
-  </si>
-  <si>
-    <t>Queman a pareja de ""brujos"" en comunidad de Ocosingo</t>
-  </si>
-  <si>
-    <t>Linchamiento</t>
-  </si>
-  <si>
-    <t>El reto como nación es complejo. Mientras la mayoría de los hombres sigamos viendo a las  mujeres como débiles, complementarias del sexo fuerte, subsidiarias del bienestar masculino, la  violencia hacia ellas prevalecerá ”.</t>
-  </si>
-  <si>
-    <t>Violencia De Género</t>
-  </si>
-  <si>
-    <t>Programa estatal beneficia a 760 emprendedores en Hidalgo</t>
-  </si>
-  <si>
-    <t>Reforzarán cumplimiento de tarifas de taxis durante la Feria de San Francisco Pachuca</t>
-  </si>
-  <si>
-    <t>Celebrarán 200 años de relación con Inglaterra a través de un partido de futbol</t>
-  </si>
-  <si>
-    <t>Conmemoración centenario</t>
-  </si>
-  <si>
-    <t>Llama Arturo Garita a fortalecer capacidades ante avance de inteligencia artifical</t>
-  </si>
-  <si>
-    <t>Intercambian señalamientos magistrados del TEEH durante juicio de regidor</t>
-  </si>
-  <si>
     <t>Enfrentamiento Político</t>
   </si>
   <si>
-    <t>¡Arranca la fiesta de Hidalgo!</t>
-  </si>
-  <si>
-    <t>Morena se desmarca de Shadia e Israel</t>
-  </si>
-  <si>
-    <t>Muestre las pruebas""</t>
-  </si>
-  <si>
-    <t>Habrá sanciones para taxistas</t>
-  </si>
-  <si>
-    <t>A casi un año del desastre, cinco personas siguen desaparecidas en Tianguistengo</t>
-  </si>
-  <si>
-    <t>Dan 50 años de prisión a dos por secuestro de vendedor de autos en Hidalgo</t>
-  </si>
-  <si>
-    <t>UECS</t>
-  </si>
-  <si>
-    <t>Combate Al Secuestro</t>
-  </si>
-  <si>
-    <t>Ampliarán Colosio para desahogar tráfico en la glorieta 24 Horas</t>
-  </si>
-  <si>
-    <t>Glorieta 24 Horas</t>
-  </si>
-  <si>
-    <t>La Sección 15 mantiene presencia permanente en el territorio hidalguense</t>
-  </si>
-  <si>
-    <t>Correcto ejercicio del presupuesto genera mejores condiciones de vida para las familias: JMS</t>
-  </si>
-  <si>
-    <t>Taxistas tendrán 120 días para instalar taxímetros en Pachuca y la Reforma</t>
-  </si>
-  <si>
-    <t>Mirna Rubio rinde cuentas: 32 iniciativas presentadas</t>
-  </si>
-  <si>
-    <t>Informe Legislativo</t>
-  </si>
-  <si>
-    <t>Pachuca despliega operativo de seguridad para la Feria de San Francisco</t>
-  </si>
-  <si>
     <t>Policía municipal</t>
   </si>
   <si>
-    <t>PC y Bomberos de Ajacuba fortalecen su preeparación</t>
-  </si>
-  <si>
-    <t>Capacitación PC</t>
-  </si>
-  <si>
-    <t>Seguridad Pública de Pachuca detiene a mujer en mandamiento judicial vigente</t>
-  </si>
-  <si>
-    <t>Detención</t>
-  </si>
-  <si>
-    <t>Esterilización canina y felina</t>
-  </si>
-  <si>
     <t>Publicidad</t>
   </si>
   <si>
-    <t>Campaña de esterilización</t>
-  </si>
-  <si>
-    <t>Bronco abrió la Feria de Pachuca con exitosa presentación</t>
-  </si>
-  <si>
-    <t>Realiza SEPH el encuentro ""Voces que transforman""</t>
-  </si>
-  <si>
-    <t>Foro educativo</t>
-  </si>
-  <si>
-    <t>Habrá función estelar de box este sábado en teatro del pueblo</t>
-  </si>
-  <si>
-    <t>Entrega Julio Menchaca apoyos de programa Emprendiendo paso a paso</t>
-  </si>
-  <si>
-    <t>Convoca DIF Pachuca a participar en la Beca Municipal a la Excelencia Académica</t>
-  </si>
-  <si>
-    <t>Becas</t>
-  </si>
-  <si>
-    <t>¡Late con orgullo!</t>
-  </si>
-  <si>
-    <t>Se retirarán concesiones a transportistas que incumplan la ley</t>
-  </si>
-  <si>
-    <t>Fallo por triple feminicidio se dictará el 8 de octubre</t>
-  </si>
-  <si>
-    <t>Ya era tiempo de poner un alto a los transportistas abusivos. Sin embargo, el servicio sigue siendo insuficiente, se necesitan alternativas como autobuses de ruta con tarifas bajas acorde a los salarios de Pachuca ...</t>
-  </si>
-  <si>
-    <t>Deficiencias transporte público</t>
-  </si>
-  <si>
-    <t>En la Feria, habrá operativo integral de vigilancia</t>
-  </si>
-  <si>
-    <t>Corea del Sur y la empresa Lego invertirán en México</t>
-  </si>
-  <si>
     <t>Atracción De Inversiones</t>
+  </si>
+  <si>
+    <t>Podrán votar en Hidalgo 2.4 millones de electores</t>
+  </si>
+  <si>
+    <t>Elecciones</t>
+  </si>
+  <si>
+    <t>Rendición de cuentas es obediencia al pueblo: CSP</t>
+  </si>
+  <si>
+    <t>Informe Sheinbaum</t>
+  </si>
+  <si>
+    <t>Gana Tizayuca en desplazamiento interno forzado</t>
+  </si>
+  <si>
+    <t>Jornadas de Salud, en 9 municipios</t>
+  </si>
+  <si>
+    <t>Jornada de salud</t>
+  </si>
+  <si>
+    <t>Taxistas rechazan tarifa de 45 pesos</t>
+  </si>
+  <si>
+    <t>Preparan nuevos impuestos</t>
+  </si>
+  <si>
+    <t>Aumento de impuestos</t>
+  </si>
+  <si>
+    <t>Duro desplome financiero</t>
+  </si>
+  <si>
+    <t>Forjando un destino en el pancracio</t>
+  </si>
+  <si>
+    <t>Los rectores, entre la academia y la función</t>
+  </si>
+  <si>
+    <t>Universidades</t>
+  </si>
+  <si>
+    <t>Perfil académico</t>
+  </si>
+  <si>
+    <t>Frenan diferencias políticas obtener emprésito para obras en Hidalgo</t>
+  </si>
+  <si>
+    <t>Obras De Infraestructura</t>
+  </si>
+  <si>
+    <t>Taxistas piden un banderazo de 50 pesos, pues "no les sale"</t>
+  </si>
+  <si>
+    <t>Se registran en la capital 461 asaltos entre enero y agosto</t>
+  </si>
+  <si>
+    <t>Incidencia Delictiva</t>
+  </si>
+  <si>
+    <t>Sheinbaum: ""nueva Constitución"" blindó soberanía y política social</t>
+  </si>
+  <si>
+    <t>Alcaldes y legisladoras de CdMX ocuparon zona VIP</t>
+  </si>
+  <si>
+    <t>infom</t>
+  </si>
+  <si>
+    <t>FGR identifica 6 empresas de Texas ligadas al huachicol</t>
+  </si>
+  <si>
+    <t>FGR</t>
+  </si>
+  <si>
+    <t>Huachicol</t>
+  </si>
+  <si>
+    <t>Secretariado Ejecutivo: Por privación ilegal de la libertad 500 carpetas</t>
+  </si>
+  <si>
+    <t>Secuestro</t>
+  </si>
+  <si>
+    <t>Pega a diez de 84 municipios sequía durante el temporal</t>
+  </si>
+  <si>
+    <t>Conagua</t>
+  </si>
+  <si>
+    <t>Sequía</t>
+  </si>
+  <si>
+    <t>La movilidad mejorará con trenes y nuevas vialidades</t>
+  </si>
+  <si>
+    <t>Tren AIFA</t>
+  </si>
+  <si>
+    <t>La Presidenta realizó un ejercicio de rendición de cuentas por dos años al frente del Poder Ejecutivo federal</t>
+  </si>
+  <si>
+    <t>Fotonota</t>
+  </si>
+  <si>
+    <t>"T-MEC, valioso e irremplazable", admite Johnson</t>
+  </si>
+  <si>
+    <t>oto</t>
+  </si>
+  <si>
+    <t>T-Mec</t>
+  </si>
+  <si>
+    <t>UN futuro competitivo y resiliente para la región""</t>
+  </si>
+  <si>
+    <t>Elogios y advertencias en la visita de Xi a Washington</t>
+  </si>
+  <si>
+    <t>Escolaridad logra alcanzar los 10 años en promedio</t>
+  </si>
+  <si>
+    <t>Eficiencia terminal</t>
+  </si>
+  <si>
+    <t>Rendir cuentas, acto de obediencia con el pueblo: CSP</t>
+  </si>
+  <si>
+    <t>Taxistas de Pachuca piden elevar a 50 pesos la tarifa mínima</t>
+  </si>
+  <si>
+    <t>Ante miles de personas congregadas en el Zócalo, Claudia Sheinbaum cerró su mensaje con un llamado a continuar la transformación en unidad y bajo la premisa de que no hay divorcio entre pueblo y gobierno</t>
+  </si>
+  <si>
+    <t>Sin duda, el PRI no fue mejor, ni otros gobernantes hidalguenses han estado  exentos de hacer cosas terribles. Pero sí esperábamos mejores condiciones  para el ejercicio de los derechos con esta transición”.</t>
+  </si>
+  <si>
+    <t>Mal Desempeño</t>
+  </si>
+  <si>
+    <t>Apuesta empresa italiana por Hidalgo con inversión de 200 mdp</t>
+  </si>
+  <si>
+    <t>Amplían formación tecnológica del CECYTEH en Tizayuca</t>
+  </si>
+  <si>
+    <t>Laboratorio STEM</t>
+  </si>
+  <si>
+    <t>Desmantelan en Pachuca almacén de huachicol</t>
+  </si>
+  <si>
+    <t>Combate Al Huachicol</t>
+  </si>
+  <si>
+    <t>Cuestionan taxistas nueva tarifa: proponen una mínima de 50 pesos</t>
+  </si>
+  <si>
+    <t>Hi-Ref construirá en Hidalgo su primera planta fuera de Italia</t>
+  </si>
+  <si>
+    <t>Entre hilos y telar de cintura</t>
+  </si>
+  <si>
+    <t>Caasim enfrenta amparo por dejar sin reparar pavimento</t>
+  </si>
+  <si>
+    <t>Zanjas Caasim</t>
+  </si>
+  <si>
+    <t>Activistas señalan barreras para acceder al aborto</t>
+  </si>
+  <si>
+    <t>ILE</t>
+  </si>
+  <si>
+    <t>Simey niega pelito con Cuauhtémoc</t>
+  </si>
+  <si>
+    <t>Simey</t>
+  </si>
+  <si>
+    <t>Taxistas independientes piden tarifa mínima de 50 pesos</t>
+  </si>
+  <si>
+    <t>Infonavit invita a conocer viviendas del Bienestar en Tepeji</t>
+  </si>
+  <si>
+    <t>Infonavit</t>
+  </si>
+  <si>
+    <t>Plan Nacional De Vivienda</t>
+  </si>
+  <si>
+    <t>Unidad k9 rescata a lomito que corría en el bulevar Fellipe Ángeles</t>
+  </si>
+  <si>
+    <t>Rescate Animal</t>
+  </si>
+  <si>
+    <t>Menchaca prevé que Tren México-Pachuca opere en 2027</t>
+  </si>
+  <si>
+    <t>Tepa F.C. debuta con triunfo en Tlahuelilpan dentro de la Liga TDP</t>
+  </si>
+  <si>
+    <t>Cuidar Pachuca también es tarea de quienes la vivimos todos los días: Jorge Reyes</t>
+  </si>
+  <si>
+    <t>alcalde</t>
+  </si>
+  <si>
+    <t>Zitlaly Zúñiga impulsa trabajo conjunto para mejorar la calle Lucrecia Torres</t>
+  </si>
+  <si>
+    <t>Conservación de vialidades</t>
+  </si>
+  <si>
+    <t>La Sección 15 fortalece sus estructuras con visión de futuro y participación de la juventud</t>
+  </si>
+  <si>
+    <t>Reunión con sindicato</t>
+  </si>
+  <si>
+    <t>Conoce el Pabellón Artesanal</t>
+  </si>
+  <si>
+    <t>Recuperación De Espacios Públicos</t>
+  </si>
+  <si>
+    <t>Los Askis y Grupo Ilusión pusieron a bailar a la feria</t>
+  </si>
+  <si>
+    <t>Remmy Valenzuela estremeció el Palenque con su show</t>
+  </si>
+  <si>
+    <t>Hidalgo fortalece al Cecyteh con nuevas carreras y laboratorio STEM en Tizayuca</t>
+  </si>
+  <si>
+    <t>SSPH asegura hidrocarburo de procedencia ilícita en la capital</t>
+  </si>
+  <si>
+    <t>Tu voz cuenta</t>
+  </si>
+  <si>
+    <t>Ordenamiento Territorial</t>
+  </si>
+  <si>
+    <t>Con la pirotecnia no se juega</t>
+  </si>
+  <si>
+    <t>Pirotecnia</t>
+  </si>
+  <si>
+    <t>Taxistas piden nuevo aumento; usuarios exigen que se respeten las tarifas</t>
+  </si>
+  <si>
+    <t>Huracán Polo deja dos menores muertos y tres desaparecidos</t>
+  </si>
+  <si>
+    <t>Doble asesinato estudiantil vuelve a sacudir Morelos</t>
+  </si>
+  <si>
+    <t>Homicidios</t>
+  </si>
+  <si>
+    <t>En Hidalgo, habrá temperaturas superiores a los 35 grados</t>
+  </si>
+  <si>
+    <t>Alerta Meteorológica</t>
+  </si>
+  <si>
+    <t>Morelos está de luto; otros 2  estudiantes de la Prepa 2, de la  Universidad morelense fueron  asesinados. Son ya 6 los alumnos  ultimados violentamente. Están  matando a nuestros  estudiantes, al futuro  de nuestra sociedad, es  momento de reaccionar  con todo contra los  criminales.</t>
   </si>
 </sst>
 </file>
@@ -844,8 +844,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J64" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J64" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J58" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J58" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1214,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1263,16 +1263,16 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1281,10 +1281,10 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1297,28 +1297,28 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1331,50 +1331,50 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
@@ -1383,10 +1383,10 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1399,134 +1399,134 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
         <v>70</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" t="s">
-        <v>83</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>106</v>
-      </c>
       <c r="H9" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1535,28 +1535,28 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="G10" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1567,136 +1567,136 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J11" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J11" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
-        <v>46290</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" t="s">
-        <v>89</v>
-      </c>
-      <c r="H12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
-      </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
       </c>
       <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J13" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" t="s">
+        <v>72</v>
+      </c>
+      <c r="I14" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Presidencia de la República</v>
-      </c>
-      <c r="J13" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <v>46290</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1705,115 +1705,115 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H15" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>115</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G16" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
@@ -1822,10 +1822,10 @@
         <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="G18" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
@@ -1839,15 +1839,15 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
@@ -1859,10 +1859,10 @@
         <v>24</v>
       </c>
       <c r="G19" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="H19" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1873,61 +1873,61 @@
         <v>Gobernador</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>129</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G21" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H21" t="s">
         <v>11</v>
@@ -1941,15 +1941,15 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
@@ -1961,7 +1961,7 @@
         <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
@@ -1977,232 +1977,232 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>126</v>
+        <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="H24" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F25" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J25" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" t="s">
+        <v>27</v>
+      </c>
+      <c r="G26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" t="s">
+        <v>68</v>
+      </c>
+      <c r="I26" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J25" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
-        <v>46290</v>
-      </c>
-      <c r="B26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="J26" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" t="s">
         <v>129</v>
       </c>
-      <c r="D26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" t="s">
-        <v>87</v>
-      </c>
-      <c r="H26" t="s">
-        <v>11</v>
-      </c>
-      <c r="I26" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J26" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
-        <v>46290</v>
-      </c>
-      <c r="B27" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D27" t="s">
-        <v>12</v>
-      </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="G28" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H28" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D29" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G29" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2210,203 +2210,203 @@
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="G30" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="H30" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F31" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G31" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="H31" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="D32" t="s">
         <v>12</v>
       </c>
       <c r="E32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" t="s">
+        <v>27</v>
+      </c>
+      <c r="G32" t="s">
+        <v>80</v>
+      </c>
+      <c r="H32" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J32" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" t="s">
+        <v>94</v>
+      </c>
+      <c r="H33" t="s">
+        <v>72</v>
+      </c>
+      <c r="I33" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J33" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s">
         <v>10</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F34" t="s">
         <v>10</v>
       </c>
-      <c r="G32" t="s">
-        <v>138</v>
-      </c>
-      <c r="H32" t="s">
-        <v>69</v>
-      </c>
-      <c r="I32" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J32" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
-        <v>46290</v>
-      </c>
-      <c r="B33" t="s">
-        <v>90</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D33" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" t="s">
-        <v>140</v>
-      </c>
-      <c r="H33" t="s">
+      <c r="G34" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34" t="s">
         <v>11</v>
       </c>
-      <c r="I33" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J33" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="11">
-        <v>46290</v>
-      </c>
-      <c r="B34" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D34" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34" t="s">
-        <v>103</v>
-      </c>
-      <c r="H34" t="s">
-        <v>73</v>
-      </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="H35" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2417,68 +2417,68 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D36" t="s">
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="H36" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="G37" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Sucesión gubernamental</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2487,202 +2487,202 @@
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="G38" t="s">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s">
+        <v>68</v>
+      </c>
+      <c r="I38" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J38" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B39" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D39" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" t="s">
+        <v>158</v>
+      </c>
+      <c r="G39" t="s">
+        <v>159</v>
+      </c>
+      <c r="H39" t="s">
         <v>11</v>
       </c>
-      <c r="I38" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J38" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
-        <v>46290</v>
-      </c>
-      <c r="B39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D39" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" t="s">
-        <v>82</v>
-      </c>
-      <c r="G39" t="s">
-        <v>83</v>
-      </c>
-      <c r="H39" t="s">
-        <v>73</v>
-      </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="G40" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="D41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="F41" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="G41" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="H41" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B42" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G42" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H42" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>165</v>
       </c>
       <c r="G43" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2691,164 +2691,164 @@
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B44" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H44" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="D45" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="G45" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D46" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G46" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="G47" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D48" t="s">
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F48" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2859,154 +2859,154 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F49" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
       </c>
       <c r="I49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F50" t="s">
-        <v>164</v>
+        <v>2</v>
       </c>
       <c r="G50" t="s">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B51" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G51" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B52" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="D52" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="E52" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F52" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="G52" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
       </c>
       <c r="I52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B53" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="D53" t="s">
-        <v>170</v>
+        <v>93</v>
       </c>
       <c r="E53" t="s">
         <v>16</v>
@@ -3015,7 +3015,7 @@
         <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
@@ -3031,28 +3031,28 @@
     </row>
     <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B54" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D54" t="s">
         <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F54" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3063,342 +3063,138 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B55" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D55" t="s">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G55" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B56" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D56" t="s">
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F56" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="G56" t="s">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="H56" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B57" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="D57" t="s">
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G57" t="s">
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
       </c>
       <c r="I57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D58" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="E58" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F58" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="G58" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H58" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J58" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="11">
-        <v>46290</v>
-      </c>
-      <c r="B59" t="s">
-        <v>80</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D59" t="s">
-        <v>170</v>
-      </c>
-      <c r="E59" t="s">
-        <v>29</v>
-      </c>
-      <c r="F59" t="s">
-        <v>82</v>
-      </c>
-      <c r="G59" t="s">
-        <v>83</v>
-      </c>
-      <c r="H59" t="s">
-        <v>11</v>
-      </c>
-      <c r="I59" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J59" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="11">
-        <v>46290</v>
-      </c>
-      <c r="B60" t="s">
-        <v>85</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D60" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" t="s">
-        <v>24</v>
-      </c>
-      <c r="F60" t="s">
-        <v>24</v>
-      </c>
-      <c r="G60" t="s">
-        <v>81</v>
-      </c>
-      <c r="H60" t="s">
-        <v>73</v>
-      </c>
-      <c r="I60" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J60" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="11">
-        <v>46290</v>
-      </c>
-      <c r="B61" t="s">
-        <v>85</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D61" t="s">
-        <v>12</v>
-      </c>
-      <c r="E61" t="s">
-        <v>58</v>
-      </c>
-      <c r="F61" t="s">
-        <v>58</v>
-      </c>
-      <c r="G61" t="s">
-        <v>135</v>
-      </c>
-      <c r="H61" t="s">
-        <v>11</v>
-      </c>
-      <c r="I61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A62" s="11">
-        <v>46290</v>
-      </c>
-      <c r="B62" t="s">
-        <v>85</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D62" t="s">
-        <v>88</v>
-      </c>
-      <c r="E62" t="s">
-        <v>27</v>
-      </c>
-      <c r="F62" t="s">
-        <v>27</v>
-      </c>
-      <c r="G62" t="s">
-        <v>183</v>
-      </c>
-      <c r="H62" t="s">
-        <v>11</v>
-      </c>
-      <c r="I62" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J62" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="11">
-        <v>46290</v>
-      </c>
-      <c r="B63" t="s">
-        <v>85</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D63" t="s">
-        <v>12</v>
-      </c>
-      <c r="E63" t="s">
-        <v>22</v>
-      </c>
-      <c r="F63" t="s">
-        <v>22</v>
-      </c>
-      <c r="G63" t="s">
-        <v>83</v>
-      </c>
-      <c r="H63" t="s">
-        <v>11</v>
-      </c>
-      <c r="I63" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J63" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="11">
-        <v>46290</v>
-      </c>
-      <c r="B64" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D64" t="s">
-        <v>12</v>
-      </c>
-      <c r="E64" t="s">
-        <v>14</v>
-      </c>
-      <c r="F64" t="s">
-        <v>14</v>
-      </c>
-      <c r="G64" t="s">
-        <v>186</v>
-      </c>
-      <c r="H64" t="s">
-        <v>11</v>
-      </c>
-      <c r="I64" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J64" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
@@ -3458,7 +3254,7 @@
         <v>31</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
         <v>66</v>
@@ -3494,7 +3290,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
         <v>32</v>
@@ -3970,7 +3766,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B49" t="s">
         <v>44</v>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6567D5E1-D687-4A97-A8FC-13CD71B907C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C418593E-BD0B-4958-8553-6A85E3D0E514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="187">
   <si>
     <t>Fecha</t>
   </si>
@@ -294,310 +294,310 @@
     <t>Plaza Juárez</t>
   </si>
   <si>
-    <t>Dinámica demográfica</t>
-  </si>
-  <si>
     <t>Temas varios</t>
   </si>
   <si>
-    <t>Editorial</t>
-  </si>
-  <si>
     <t>La Jornada Hidalgo</t>
   </si>
   <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
-    <t>Caasim</t>
-  </si>
-  <si>
-    <t>Enfrentamiento Político</t>
-  </si>
-  <si>
     <t>Policía municipal</t>
   </si>
   <si>
     <t>Publicidad</t>
   </si>
   <si>
-    <t>Atracción De Inversiones</t>
-  </si>
-  <si>
-    <t>Podrán votar en Hidalgo 2.4 millones de electores</t>
-  </si>
-  <si>
     <t>Elecciones</t>
   </si>
   <si>
-    <t>Rendición de cuentas es obediencia al pueblo: CSP</t>
-  </si>
-  <si>
-    <t>Informe Sheinbaum</t>
-  </si>
-  <si>
-    <t>Gana Tizayuca en desplazamiento interno forzado</t>
-  </si>
-  <si>
-    <t>Jornadas de Salud, en 9 municipios</t>
-  </si>
-  <si>
-    <t>Jornada de salud</t>
-  </si>
-  <si>
-    <t>Taxistas rechazan tarifa de 45 pesos</t>
-  </si>
-  <si>
-    <t>Preparan nuevos impuestos</t>
-  </si>
-  <si>
-    <t>Aumento de impuestos</t>
-  </si>
-  <si>
-    <t>Duro desplome financiero</t>
-  </si>
-  <si>
-    <t>Forjando un destino en el pancracio</t>
-  </si>
-  <si>
-    <t>Los rectores, entre la academia y la función</t>
-  </si>
-  <si>
-    <t>Universidades</t>
-  </si>
-  <si>
-    <t>Perfil académico</t>
-  </si>
-  <si>
-    <t>Frenan diferencias políticas obtener emprésito para obras en Hidalgo</t>
-  </si>
-  <si>
-    <t>Obras De Infraestructura</t>
-  </si>
-  <si>
-    <t>Taxistas piden un banderazo de 50 pesos, pues "no les sale"</t>
-  </si>
-  <si>
-    <t>Se registran en la capital 461 asaltos entre enero y agosto</t>
-  </si>
-  <si>
-    <t>Incidencia Delictiva</t>
-  </si>
-  <si>
-    <t>Sheinbaum: ""nueva Constitución"" blindó soberanía y política social</t>
-  </si>
-  <si>
-    <t>Alcaldes y legisladoras de CdMX ocuparon zona VIP</t>
-  </si>
-  <si>
-    <t>infom</t>
-  </si>
-  <si>
-    <t>FGR identifica 6 empresas de Texas ligadas al huachicol</t>
-  </si>
-  <si>
     <t>FGR</t>
   </si>
   <si>
-    <t>Huachicol</t>
-  </si>
-  <si>
-    <t>Secretariado Ejecutivo: Por privación ilegal de la libertad 500 carpetas</t>
-  </si>
-  <si>
-    <t>Secuestro</t>
-  </si>
-  <si>
-    <t>Pega a diez de 84 municipios sequía durante el temporal</t>
-  </si>
-  <si>
-    <t>Conagua</t>
-  </si>
-  <si>
-    <t>Sequía</t>
-  </si>
-  <si>
-    <t>La movilidad mejorará con trenes y nuevas vialidades</t>
-  </si>
-  <si>
-    <t>Tren AIFA</t>
-  </si>
-  <si>
-    <t>La Presidenta realizó un ejercicio de rendición de cuentas por dos años al frente del Poder Ejecutivo federal</t>
-  </si>
-  <si>
-    <t>Fotonota</t>
-  </si>
-  <si>
-    <t>"T-MEC, valioso e irremplazable", admite Johnson</t>
-  </si>
-  <si>
-    <t>oto</t>
-  </si>
-  <si>
-    <t>T-Mec</t>
-  </si>
-  <si>
-    <t>UN futuro competitivo y resiliente para la región""</t>
-  </si>
-  <si>
-    <t>Elogios y advertencias en la visita de Xi a Washington</t>
-  </si>
-  <si>
-    <t>Escolaridad logra alcanzar los 10 años en promedio</t>
-  </si>
-  <si>
-    <t>Eficiencia terminal</t>
-  </si>
-  <si>
-    <t>Rendir cuentas, acto de obediencia con el pueblo: CSP</t>
-  </si>
-  <si>
-    <t>Taxistas de Pachuca piden elevar a 50 pesos la tarifa mínima</t>
-  </si>
-  <si>
-    <t>Ante miles de personas congregadas en el Zócalo, Claudia Sheinbaum cerró su mensaje con un llamado a continuar la transformación en unidad y bajo la premisa de que no hay divorcio entre pueblo y gobierno</t>
-  </si>
-  <si>
-    <t>Sin duda, el PRI no fue mejor, ni otros gobernantes hidalguenses han estado  exentos de hacer cosas terribles. Pero sí esperábamos mejores condiciones  para el ejercicio de los derechos con esta transición”.</t>
-  </si>
-  <si>
-    <t>Mal Desempeño</t>
-  </si>
-  <si>
-    <t>Apuesta empresa italiana por Hidalgo con inversión de 200 mdp</t>
-  </si>
-  <si>
-    <t>Amplían formación tecnológica del CECYTEH en Tizayuca</t>
-  </si>
-  <si>
     <t>Laboratorio STEM</t>
   </si>
   <si>
-    <t>Desmantelan en Pachuca almacén de huachicol</t>
-  </si>
-  <si>
     <t>Combate Al Huachicol</t>
   </si>
   <si>
-    <t>Cuestionan taxistas nueva tarifa: proponen una mínima de 50 pesos</t>
-  </si>
-  <si>
-    <t>Hi-Ref construirá en Hidalgo su primera planta fuera de Italia</t>
-  </si>
-  <si>
-    <t>Entre hilos y telar de cintura</t>
-  </si>
-  <si>
-    <t>Caasim enfrenta amparo por dejar sin reparar pavimento</t>
-  </si>
-  <si>
-    <t>Zanjas Caasim</t>
-  </si>
-  <si>
-    <t>Activistas señalan barreras para acceder al aborto</t>
-  </si>
-  <si>
     <t>ILE</t>
   </si>
   <si>
-    <t>Simey niega pelito con Cuauhtémoc</t>
-  </si>
-  <si>
     <t>Simey</t>
   </si>
   <si>
-    <t>Taxistas independientes piden tarifa mínima de 50 pesos</t>
-  </si>
-  <si>
-    <t>Infonavit invita a conocer viviendas del Bienestar en Tepeji</t>
-  </si>
-  <si>
-    <t>Infonavit</t>
-  </si>
-  <si>
-    <t>Plan Nacional De Vivienda</t>
-  </si>
-  <si>
-    <t>Unidad k9 rescata a lomito que corría en el bulevar Fellipe Ángeles</t>
-  </si>
-  <si>
-    <t>Rescate Animal</t>
-  </si>
-  <si>
-    <t>Menchaca prevé que Tren México-Pachuca opere en 2027</t>
-  </si>
-  <si>
-    <t>Tepa F.C. debuta con triunfo en Tlahuelilpan dentro de la Liga TDP</t>
-  </si>
-  <si>
-    <t>Cuidar Pachuca también es tarea de quienes la vivimos todos los días: Jorge Reyes</t>
-  </si>
-  <si>
-    <t>alcalde</t>
-  </si>
-  <si>
-    <t>Zitlaly Zúñiga impulsa trabajo conjunto para mejorar la calle Lucrecia Torres</t>
-  </si>
-  <si>
-    <t>Conservación de vialidades</t>
-  </si>
-  <si>
-    <t>La Sección 15 fortalece sus estructuras con visión de futuro y participación de la juventud</t>
-  </si>
-  <si>
-    <t>Reunión con sindicato</t>
-  </si>
-  <si>
-    <t>Conoce el Pabellón Artesanal</t>
-  </si>
-  <si>
-    <t>Recuperación De Espacios Públicos</t>
-  </si>
-  <si>
-    <t>Los Askis y Grupo Ilusión pusieron a bailar a la feria</t>
-  </si>
-  <si>
-    <t>Remmy Valenzuela estremeció el Palenque con su show</t>
-  </si>
-  <si>
-    <t>Hidalgo fortalece al Cecyteh con nuevas carreras y laboratorio STEM en Tizayuca</t>
-  </si>
-  <si>
     <t>SSPH asegura hidrocarburo de procedencia ilícita en la capital</t>
   </si>
   <si>
     <t>Tu voz cuenta</t>
   </si>
   <si>
-    <t>Ordenamiento Territorial</t>
-  </si>
-  <si>
-    <t>Con la pirotecnia no se juega</t>
-  </si>
-  <si>
-    <t>Pirotecnia</t>
-  </si>
-  <si>
-    <t>Taxistas piden nuevo aumento; usuarios exigen que se respeten las tarifas</t>
-  </si>
-  <si>
-    <t>Huracán Polo deja dos menores muertos y tres desaparecidos</t>
-  </si>
-  <si>
-    <t>Doble asesinato estudiantil vuelve a sacudir Morelos</t>
-  </si>
-  <si>
-    <t>Homicidios</t>
-  </si>
-  <si>
-    <t>En Hidalgo, habrá temperaturas superiores a los 35 grados</t>
-  </si>
-  <si>
-    <t>Alerta Meteorológica</t>
-  </si>
-  <si>
-    <t>Morelos está de luto; otros 2  estudiantes de la Prepa 2, de la  Universidad morelense fueron  asesinados. Son ya 6 los alumnos  ultimados violentamente. Están  matando a nuestros  estudiantes, al futuro  de nuestra sociedad, es  momento de reaccionar  con todo contra los  criminales.</t>
+    <t>El Sol de Hidalgo</t>
+  </si>
+  <si>
+    <t>Reajusta ayuntamiento su prespuesto anual</t>
+  </si>
+  <si>
+    <t>Presupuesto De Egresos</t>
+  </si>
+  <si>
+    <t>Señalan afectaciones en caminos y accesos</t>
+  </si>
+  <si>
+    <t>SICT</t>
+  </si>
+  <si>
+    <t>Tren México Querétaro</t>
+  </si>
+  <si>
+    <t>Hay menos ninis en México, OCDE</t>
+  </si>
+  <si>
+    <t>Tasa de desocupación</t>
+  </si>
+  <si>
+    <t>Apuesta Menchaca por coordinación interestatal</t>
+  </si>
+  <si>
+    <t>Coordinación interestatal</t>
+  </si>
+  <si>
+    <t>Feria San Francisco mantendrá formato</t>
+  </si>
+  <si>
+    <t>Feria tradicional</t>
+  </si>
+  <si>
+    <t>Exponen talento artesanan</t>
+  </si>
+  <si>
+    <t>Acuerdan trabajo coordinado en seguridad</t>
+  </si>
+  <si>
+    <t>Caen 10 al día por alcoholímetro</t>
+  </si>
+  <si>
+    <t>Detienen en Argentina a hija de Gerardo Sosa</t>
+  </si>
+  <si>
+    <t>Grupo Universidad</t>
+  </si>
+  <si>
+    <t>Obligan a aspirantes a transparentar trayectoria</t>
+  </si>
+  <si>
+    <t>Candidaturas</t>
+  </si>
+  <si>
+    <t>Recortan 38 mdp a Pachuca</t>
+  </si>
+  <si>
+    <t>25 años de vestirse de Pueblo Mágico</t>
+  </si>
+  <si>
+    <t>Pueblos Mágicos</t>
+  </si>
+  <si>
+    <t>Hidalgo, de los estados con tarifa fija para taxi</t>
+  </si>
+  <si>
+    <t>Lizbeth Ordaz destaca avances en la paridad de género</t>
+  </si>
+  <si>
+    <t>GLMorena</t>
+  </si>
+  <si>
+    <t>Paridad de género</t>
+  </si>
+  <si>
+    <t>Analiza IEEH distribución de acciones afirmativas</t>
+  </si>
+  <si>
+    <t>Acción afirmativa</t>
+  </si>
+  <si>
+    <t>La ofensiva sin brújula</t>
+  </si>
+  <si>
+    <t>A petición del os usuarios, baja el costo del estacionamiento</t>
+  </si>
+  <si>
+    <t>Regularán en Congreso tema de asesores</t>
+  </si>
+  <si>
+    <t>Junta de Gobierno</t>
+  </si>
+  <si>
+    <t>Asesores</t>
+  </si>
+  <si>
+    <t>Destrucción de túneles; nueva era del combate al huachicol</t>
+  </si>
+  <si>
+    <t>Huachitúnel</t>
+  </si>
+  <si>
+    <t>Reportan la detención de Ana Carmen Sosa</t>
+  </si>
+  <si>
+    <t>El IEEH sin aumento, a dos meses del año electoral</t>
+  </si>
+  <si>
+    <t>Presupuesto IEEH</t>
+  </si>
+  <si>
+    <t>Estiman 55 mil visitantes durante primeros cuatro días de feria</t>
+  </si>
+  <si>
+    <t>Vende terreno 9 veces más caro a empresa sancionada</t>
+  </si>
+  <si>
+    <t>Viggiano</t>
+  </si>
+  <si>
+    <t>Enriquecimiento ilícito</t>
+  </si>
+  <si>
+    <t>Eligen al estado para industria cinematográfica</t>
+  </si>
+  <si>
+    <t>Producción audiovisual</t>
+  </si>
+  <si>
+    <t>Clara Luz repite en Nuevo León y el Verde concreta dos estados... más QR y SLP</t>
+  </si>
+  <si>
+    <t>Cuarenta horas de carretera después, Ruffo llegó a su casa</t>
+  </si>
+  <si>
+    <t>Preparan en La Reforma a nuevos agentes K9</t>
+  </si>
+  <si>
+    <t>Unidad canina</t>
+  </si>
+  <si>
+    <t>Ante recortes, Pachuca cambia su presupuesto para mantener servicios</t>
+  </si>
+  <si>
+    <t>SCJN da marcha atrás a alternancia de género en Durango y S.L. Potosí</t>
+  </si>
+  <si>
+    <t>Morena define operadores rumbo a 2027</t>
+  </si>
+  <si>
+    <t>Todavía persisten expresiones de racismo y clasismo que pretenden reducir a nuestros pueblos a una  fotografía, artesanía o celebración, cuando son comunidades con voz, derechos y capacidad para decidir su  propio futuro”</t>
+  </si>
+  <si>
+    <t>Apoyo a pueblos originarios</t>
+  </si>
+  <si>
+    <t>Feria San Francsico supera 55 mil visitantes; baja costo de estacionamiento</t>
+  </si>
+  <si>
+    <t>Menchaca destaca combate al huachicol en reunión Interestatal de paz y seguridad</t>
+  </si>
+  <si>
+    <t>A más de 5 años de la despenalización, persisten barreras para el aborto seguro en Hidalgo</t>
+  </si>
+  <si>
+    <t>Recorte de 38 mdp obliga a Pachuca a ajustar presupuesto y postergar proyectos</t>
+  </si>
+  <si>
+    <t>Recorte federal de 38 millones a Pachuca</t>
+  </si>
+  <si>
+    <t>Hidalgo refuerza coordinación en seguridad con cuatro estados</t>
+  </si>
+  <si>
+    <t>Alcoholímetro deja 38 detenidos en el primer fin de semana de Feria: Estacionamiento de la Feria San Francisco baja a 120 pesos</t>
+  </si>
+  <si>
+    <t>Candidatos de Hidalgo deberán transparentar su perfil</t>
+  </si>
+  <si>
+    <t>Ningún turista ha dejado de venir"": Turismo minimiza impacto del tráfico en la México-Pachuca</t>
+  </si>
+  <si>
+    <t>Afluencia Turística</t>
+  </si>
+  <si>
+    <t>Bajan a 120 pesos tarifa de estacionamiento en el Feria de Pachuca</t>
+  </si>
+  <si>
+    <t>Clausuran túnel y cinco tomas clandestinas para sustracción de hidrocarburo</t>
+  </si>
+  <si>
+    <t>Reunión Gabinete De Seguridad</t>
+  </si>
+  <si>
+    <t>Coordianción entre estados, respuesta clara y contundente para la paz y seguridad: Julio Menchaca</t>
+  </si>
+  <si>
+    <t>Zitlaly Zúñiga entrega apoyos para mejorar la movilidad y calidad de vida de las familias de Ajacuba</t>
+  </si>
+  <si>
+    <t>Movilidad incluyente</t>
+  </si>
+  <si>
+    <t>Tere Olivares inicia obra de más de 1 mdp en calle Arnulfo Morel de Tlaxcoapan</t>
+  </si>
+  <si>
+    <t>Rehabilitación Vial</t>
+  </si>
+  <si>
+    <t>Taxistas piden tarifa mínima de 50 pesos</t>
+  </si>
+  <si>
+    <t>IEEH aprueba implementación y operación del Sistema "Candidatas y Candidatos, Conóceles"</t>
+  </si>
+  <si>
+    <t>Artesanos Tlaxcoapanenses presentes en la feria Pachuca 2026</t>
+  </si>
+  <si>
+    <t>Escuela de Muralismo para la Transformación abre convocatoria en Pachuca</t>
+  </si>
+  <si>
+    <t>Muralismo</t>
+  </si>
+  <si>
+    <t>Claudia Sandoval conmemora el 205 Aniversario de la Consumación de la Independencia con desfile cívico</t>
+  </si>
+  <si>
+    <t>Desfile cívico</t>
+  </si>
+  <si>
+    <t>Emprendimiento que florece</t>
+  </si>
+  <si>
+    <t>Apoyo a emprendedores</t>
+  </si>
+  <si>
+    <t>Coordinación entre estados, respuesta clara y contundente para la paz y seguridad: Julio Menchaca</t>
+  </si>
+  <si>
+    <t>Trío Aurora Hidalguenses y Calibre 50 llenan de tradición la Feria Pachuca</t>
+  </si>
+  <si>
+    <t>Escuela de Muralismo para la transformación abre convocatoria en Pachuca</t>
+  </si>
+  <si>
+    <t>SEPH inaugura nuevos laboratorios STEM en San Agustín Metzquittitlán Huazalingo</t>
+  </si>
+  <si>
+    <t>Desarrollo Urbano</t>
+  </si>
+  <si>
+    <t>Coordinación de estados para la paz y seguridad</t>
+  </si>
+  <si>
+    <t>Rastrearán funerarias por caso Ayotzinapan</t>
+  </si>
+  <si>
+    <t>Alertan sobre falsificación y adulteración de medicamentos</t>
+  </si>
+  <si>
+    <t>Farmacovigilancia</t>
+  </si>
+  <si>
+    <t>Cayó en Argentina hija de Gerardo Sosa, iba a volar a Chile</t>
   </si>
 </sst>
 </file>
@@ -844,8 +844,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J58" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J58" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J63" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J63" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1214,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1263,32 +1263,32 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1297,28 +1297,28 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="G3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1331,32 +1331,32 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="H4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1365,28 +1365,28 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1394,139 +1394,139 @@
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1535,127 +1535,127 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J10" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" t="s">
         <v>11</v>
       </c>
-      <c r="I10" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J10" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
-        <v>46293</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="I11" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J11" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
         <v>16</v>
       </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" t="s">
-        <v>111</v>
-      </c>
-      <c r="H11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J11" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
-        <v>46293</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>27</v>
-      </c>
       <c r="F12" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="H12" t="s">
         <v>68</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
@@ -1669,265 +1669,265 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G14" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s">
         <v>72</v>
       </c>
       <c r="I14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="G15" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="H15" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F16" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="G16" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G17" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="H18" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="G19" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B20" t="s">
         <v>76</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G20" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="H20" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B21" t="s">
         <v>76</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="G21" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="H21" t="s">
         <v>11</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B22" t="s">
         <v>76</v>
@@ -1955,13 +1955,13 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G22" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
@@ -1975,438 +1975,438 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B23" t="s">
         <v>76</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="F24" t="s">
-        <v>26</v>
+        <v>137</v>
       </c>
       <c r="G24" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Sucesión gubernamental</v>
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G25" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="H25" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G26" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="H26" t="s">
         <v>68</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H28" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H29" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="H30" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D31" t="s">
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G31" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="G32" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="H32" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>148</v>
       </c>
       <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>61</v>
+      </c>
+      <c r="F33" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" t="s">
+        <v>149</v>
+      </c>
+      <c r="H33" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Sucesión gubernamental</v>
+      </c>
+      <c r="J33" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" t="s">
         <v>13</v>
       </c>
-      <c r="E33" t="s">
-        <v>54</v>
-      </c>
-      <c r="F33" t="s">
-        <v>54</v>
-      </c>
-      <c r="G33" t="s">
-        <v>94</v>
-      </c>
-      <c r="H33" t="s">
+      <c r="E34" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" t="s">
+        <v>82</v>
+      </c>
+      <c r="H34" t="s">
         <v>72</v>
       </c>
-      <c r="I33" t="str">
+      <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J33" t="str">
+      <c r="J34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="11">
-        <v>46293</v>
-      </c>
-      <c r="B34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" t="s">
-        <v>86</v>
-      </c>
-      <c r="H34" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J34" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="F35" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="G35" t="s">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="H35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2414,15 +2414,15 @@
       </c>
       <c r="J35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>152</v>
@@ -2431,13 +2431,13 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s">
         <v>68</v>
@@ -2451,358 +2451,358 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>155</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H37" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Sucesión gubernamental</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B38" t="s">
         <v>73</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="H38" t="s">
         <v>68</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C39" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" t="s">
+        <v>106</v>
+      </c>
+      <c r="H39" t="s">
+        <v>72</v>
+      </c>
+      <c r="I39" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J39" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A40" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" t="s">
+        <v>81</v>
+      </c>
+      <c r="G40" t="s">
+        <v>82</v>
+      </c>
+      <c r="H40" t="s">
+        <v>72</v>
+      </c>
+      <c r="I40" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J40" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D39" t="s">
-        <v>83</v>
-      </c>
-      <c r="E39" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" t="s">
-        <v>158</v>
-      </c>
-      <c r="G39" t="s">
-        <v>159</v>
-      </c>
-      <c r="H39" t="s">
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41" t="s">
+        <v>40</v>
+      </c>
+      <c r="G41" t="s">
+        <v>115</v>
+      </c>
+      <c r="H41" t="s">
         <v>11</v>
       </c>
-      <c r="I39" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J39" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="11">
-        <v>46293</v>
-      </c>
-      <c r="B40" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D40" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" t="s">
-        <v>16</v>
-      </c>
-      <c r="F40" t="s">
-        <v>92</v>
-      </c>
-      <c r="G40" t="s">
-        <v>161</v>
-      </c>
-      <c r="H40" t="s">
-        <v>11</v>
-      </c>
-      <c r="I40" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J40" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="11">
-        <v>46293</v>
-      </c>
-      <c r="B41" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D41" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" t="s">
-        <v>24</v>
-      </c>
-      <c r="F41" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" t="s">
-        <v>127</v>
-      </c>
-      <c r="H41" t="s">
-        <v>72</v>
-      </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G42" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="H42" t="s">
         <v>11</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B43" t="s">
         <v>75</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D43" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="E43" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F43" t="s">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B44" t="s">
         <v>75</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F44" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="G44" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B45" t="s">
         <v>75</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G45" t="s">
-        <v>169</v>
+        <v>106</v>
       </c>
       <c r="H45" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B46" t="s">
         <v>75</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D46" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E47" t="s">
         <v>16</v>
@@ -2811,7 +2811,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
@@ -2827,28 +2827,28 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D48" t="s">
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F48" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="G48" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2861,198 +2861,198 @@
     </row>
     <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F49" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="G49" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
       </c>
       <c r="I49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B51" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D52" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F52" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
       </c>
       <c r="I52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D53" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E53" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="G53" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D54" t="s">
         <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F54" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G54" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="H54" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3060,71 +3060,71 @@
       </c>
       <c r="J54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D55" t="s">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F55" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D56" t="s">
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F56" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="H56" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -3133,68 +3133,238 @@
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D57" t="s">
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G57" t="s">
-        <v>185</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
       </c>
       <c r="I57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B58" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>22</v>
+      </c>
+      <c r="F58" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" t="s">
+        <v>92</v>
+      </c>
+      <c r="H58" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J58" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B59" t="s">
+        <v>79</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D59" t="s">
+        <v>88</v>
+      </c>
+      <c r="E59" t="s">
+        <v>47</v>
+      </c>
+      <c r="F59" t="s">
+        <v>47</v>
+      </c>
+      <c r="G59" t="s">
+        <v>181</v>
+      </c>
+      <c r="H59" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J59" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B60" t="s">
         <v>84</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C60" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" t="s">
+        <v>24</v>
+      </c>
+      <c r="G60" t="s">
+        <v>106</v>
+      </c>
+      <c r="H60" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B61" t="s">
+        <v>84</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>14</v>
+      </c>
+      <c r="F61" t="s">
+        <v>90</v>
+      </c>
+      <c r="G61" t="s">
+        <v>85</v>
+      </c>
+      <c r="H61" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B62" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" t="s">
+        <v>14</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>185</v>
+      </c>
+      <c r="H62" t="s">
+        <v>11</v>
+      </c>
+      <c r="I62" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J62" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B63" t="s">
+        <v>84</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="D58" t="s">
-        <v>87</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>10</v>
-      </c>
-      <c r="G58" t="s">
-        <v>183</v>
-      </c>
-      <c r="H58" t="s">
-        <v>68</v>
-      </c>
-      <c r="I58" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J58" t="str">
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s">
+        <v>59</v>
+      </c>
+      <c r="F63" t="s">
+        <v>59</v>
+      </c>
+      <c r="G63" t="s">
+        <v>113</v>
+      </c>
+      <c r="H63" t="s">
+        <v>11</v>
+      </c>
+      <c r="I63" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J63" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C418593E-BD0B-4958-8553-6A85E3D0E514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FF4DD5-9FEE-40A6-AFDC-DE927A8CE534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="188">
   <si>
     <t>Fecha</t>
   </si>
@@ -264,9 +264,6 @@
     <t>Síntesis</t>
   </si>
   <si>
-    <t>Marfeca</t>
-  </si>
-  <si>
     <t>Milenio Hidalgo</t>
   </si>
   <si>
@@ -282,15 +279,9 @@
     <t>Tarifario de taxis</t>
   </si>
   <si>
-    <t>OEEH</t>
-  </si>
-  <si>
     <t>Feria Pachuca</t>
   </si>
   <si>
-    <t>Cintillo</t>
-  </si>
-  <si>
     <t>Plaza Juárez</t>
   </si>
   <si>
@@ -306,298 +297,310 @@
     <t>Publicidad</t>
   </si>
   <si>
-    <t>Elecciones</t>
-  </si>
-  <si>
-    <t>FGR</t>
-  </si>
-  <si>
-    <t>Laboratorio STEM</t>
-  </si>
-  <si>
-    <t>Combate Al Huachicol</t>
-  </si>
-  <si>
-    <t>ILE</t>
-  </si>
-  <si>
-    <t>Simey</t>
-  </si>
-  <si>
-    <t>SSPH asegura hidrocarburo de procedencia ilícita en la capital</t>
-  </si>
-  <si>
     <t>Tu voz cuenta</t>
   </si>
   <si>
     <t>El Sol de Hidalgo</t>
   </si>
   <si>
-    <t>Reajusta ayuntamiento su prespuesto anual</t>
-  </si>
-  <si>
-    <t>Presupuesto De Egresos</t>
-  </si>
-  <si>
-    <t>Señalan afectaciones en caminos y accesos</t>
-  </si>
-  <si>
-    <t>SICT</t>
-  </si>
-  <si>
-    <t>Tren México Querétaro</t>
-  </si>
-  <si>
-    <t>Hay menos ninis en México, OCDE</t>
-  </si>
-  <si>
-    <t>Tasa de desocupación</t>
-  </si>
-  <si>
-    <t>Apuesta Menchaca por coordinación interestatal</t>
-  </si>
-  <si>
-    <t>Coordinación interestatal</t>
-  </si>
-  <si>
-    <t>Feria San Francisco mantendrá formato</t>
-  </si>
-  <si>
     <t>Feria tradicional</t>
   </si>
   <si>
-    <t>Exponen talento artesanan</t>
-  </si>
-  <si>
-    <t>Acuerdan trabajo coordinado en seguridad</t>
-  </si>
-  <si>
-    <t>Caen 10 al día por alcoholímetro</t>
-  </si>
-  <si>
-    <t>Detienen en Argentina a hija de Gerardo Sosa</t>
-  </si>
-  <si>
-    <t>Grupo Universidad</t>
-  </si>
-  <si>
-    <t>Obligan a aspirantes a transparentar trayectoria</t>
-  </si>
-  <si>
-    <t>Candidaturas</t>
-  </si>
-  <si>
-    <t>Recortan 38 mdp a Pachuca</t>
-  </si>
-  <si>
-    <t>25 años de vestirse de Pueblo Mágico</t>
-  </si>
-  <si>
-    <t>Pueblos Mágicos</t>
-  </si>
-  <si>
-    <t>Hidalgo, de los estados con tarifa fija para taxi</t>
-  </si>
-  <si>
-    <t>Lizbeth Ordaz destaca avances en la paridad de género</t>
-  </si>
-  <si>
-    <t>GLMorena</t>
-  </si>
-  <si>
-    <t>Paridad de género</t>
-  </si>
-  <si>
-    <t>Analiza IEEH distribución de acciones afirmativas</t>
-  </si>
-  <si>
-    <t>Acción afirmativa</t>
-  </si>
-  <si>
-    <t>La ofensiva sin brújula</t>
-  </si>
-  <si>
-    <t>A petición del os usuarios, baja el costo del estacionamiento</t>
-  </si>
-  <si>
-    <t>Regularán en Congreso tema de asesores</t>
-  </si>
-  <si>
     <t>Junta de Gobierno</t>
   </si>
   <si>
-    <t>Asesores</t>
-  </si>
-  <si>
-    <t>Destrucción de túneles; nueva era del combate al huachicol</t>
-  </si>
-  <si>
-    <t>Huachitúnel</t>
-  </si>
-  <si>
-    <t>Reportan la detención de Ana Carmen Sosa</t>
-  </si>
-  <si>
-    <t>El IEEH sin aumento, a dos meses del año electoral</t>
-  </si>
-  <si>
-    <t>Presupuesto IEEH</t>
-  </si>
-  <si>
-    <t>Estiman 55 mil visitantes durante primeros cuatro días de feria</t>
-  </si>
-  <si>
-    <t>Vende terreno 9 veces más caro a empresa sancionada</t>
-  </si>
-  <si>
     <t>Viggiano</t>
   </si>
   <si>
     <t>Enriquecimiento ilícito</t>
   </si>
   <si>
-    <t>Eligen al estado para industria cinematográfica</t>
-  </si>
-  <si>
-    <t>Producción audiovisual</t>
-  </si>
-  <si>
-    <t>Clara Luz repite en Nuevo León y el Verde concreta dos estados... más QR y SLP</t>
-  </si>
-  <si>
-    <t>Cuarenta horas de carretera después, Ruffo llegó a su casa</t>
-  </si>
-  <si>
-    <t>Preparan en La Reforma a nuevos agentes K9</t>
-  </si>
-  <si>
-    <t>Unidad canina</t>
-  </si>
-  <si>
-    <t>Ante recortes, Pachuca cambia su presupuesto para mantener servicios</t>
-  </si>
-  <si>
-    <t>SCJN da marcha atrás a alternancia de género en Durango y S.L. Potosí</t>
-  </si>
-  <si>
-    <t>Morena define operadores rumbo a 2027</t>
-  </si>
-  <si>
-    <t>Todavía persisten expresiones de racismo y clasismo que pretenden reducir a nuestros pueblos a una  fotografía, artesanía o celebración, cuando son comunidades con voz, derechos y capacidad para decidir su  propio futuro”</t>
-  </si>
-  <si>
-    <t>Apoyo a pueblos originarios</t>
-  </si>
-  <si>
-    <t>Feria San Francsico supera 55 mil visitantes; baja costo de estacionamiento</t>
-  </si>
-  <si>
-    <t>Menchaca destaca combate al huachicol en reunión Interestatal de paz y seguridad</t>
-  </si>
-  <si>
-    <t>A más de 5 años de la despenalización, persisten barreras para el aborto seguro en Hidalgo</t>
-  </si>
-  <si>
-    <t>Recorte de 38 mdp obliga a Pachuca a ajustar presupuesto y postergar proyectos</t>
-  </si>
-  <si>
-    <t>Recorte federal de 38 millones a Pachuca</t>
-  </si>
-  <si>
-    <t>Hidalgo refuerza coordinación en seguridad con cuatro estados</t>
-  </si>
-  <si>
-    <t>Alcoholímetro deja 38 detenidos en el primer fin de semana de Feria: Estacionamiento de la Feria San Francisco baja a 120 pesos</t>
-  </si>
-  <si>
-    <t>Candidatos de Hidalgo deberán transparentar su perfil</t>
-  </si>
-  <si>
-    <t>Ningún turista ha dejado de venir"": Turismo minimiza impacto del tráfico en la México-Pachuca</t>
-  </si>
-  <si>
-    <t>Afluencia Turística</t>
-  </si>
-  <si>
-    <t>Bajan a 120 pesos tarifa de estacionamiento en el Feria de Pachuca</t>
-  </si>
-  <si>
-    <t>Clausuran túnel y cinco tomas clandestinas para sustracción de hidrocarburo</t>
-  </si>
-  <si>
-    <t>Reunión Gabinete De Seguridad</t>
-  </si>
-  <si>
-    <t>Coordianción entre estados, respuesta clara y contundente para la paz y seguridad: Julio Menchaca</t>
-  </si>
-  <si>
-    <t>Zitlaly Zúñiga entrega apoyos para mejorar la movilidad y calidad de vida de las familias de Ajacuba</t>
-  </si>
-  <si>
-    <t>Movilidad incluyente</t>
-  </si>
-  <si>
-    <t>Tere Olivares inicia obra de más de 1 mdp en calle Arnulfo Morel de Tlaxcoapan</t>
-  </si>
-  <si>
-    <t>Rehabilitación Vial</t>
-  </si>
-  <si>
-    <t>Taxistas piden tarifa mínima de 50 pesos</t>
-  </si>
-  <si>
-    <t>IEEH aprueba implementación y operación del Sistema "Candidatas y Candidatos, Conóceles"</t>
-  </si>
-  <si>
-    <t>Artesanos Tlaxcoapanenses presentes en la feria Pachuca 2026</t>
-  </si>
-  <si>
-    <t>Escuela de Muralismo para la Transformación abre convocatoria en Pachuca</t>
-  </si>
-  <si>
-    <t>Muralismo</t>
-  </si>
-  <si>
-    <t>Claudia Sandoval conmemora el 205 Aniversario de la Consumación de la Independencia con desfile cívico</t>
-  </si>
-  <si>
-    <t>Desfile cívico</t>
-  </si>
-  <si>
-    <t>Emprendimiento que florece</t>
-  </si>
-  <si>
-    <t>Apoyo a emprendedores</t>
-  </si>
-  <si>
-    <t>Coordinación entre estados, respuesta clara y contundente para la paz y seguridad: Julio Menchaca</t>
-  </si>
-  <si>
-    <t>Trío Aurora Hidalguenses y Calibre 50 llenan de tradición la Feria Pachuca</t>
-  </si>
-  <si>
-    <t>Escuela de Muralismo para la transformación abre convocatoria en Pachuca</t>
-  </si>
-  <si>
-    <t>SEPH inaugura nuevos laboratorios STEM en San Agustín Metzquittitlán Huazalingo</t>
-  </si>
-  <si>
     <t>Desarrollo Urbano</t>
   </si>
   <si>
-    <t>Coordinación de estados para la paz y seguridad</t>
-  </si>
-  <si>
-    <t>Rastrearán funerarias por caso Ayotzinapan</t>
-  </si>
-  <si>
-    <t>Alertan sobre falsificación y adulteración de medicamentos</t>
-  </si>
-  <si>
-    <t>Farmacovigilancia</t>
-  </si>
-  <si>
-    <t>Cayó en Argentina hija de Gerardo Sosa, iba a volar a Chile</t>
+    <t>Arranca restauración de Jardín Colón en Pachuca</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Rehabilitación de espacios públicos</t>
+  </si>
+  <si>
+    <t>Persisten los cobros elevados en taxis</t>
+  </si>
+  <si>
+    <t>Expropian terrenos para el Tren AIFA-Pachuca</t>
+  </si>
+  <si>
+    <t>Tren AIFA</t>
+  </si>
+  <si>
+    <t>Emprendedores nacionales se reúnen en UPMH</t>
+  </si>
+  <si>
+    <t>Economía social</t>
+  </si>
+  <si>
+    <t>Inicia Xantolo en Huejutla con primera ofrenda</t>
+  </si>
+  <si>
+    <t>Xantolo</t>
+  </si>
+  <si>
+    <t>Supervisará Protección Civil puestos semifijos</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Perfilan policía y un C5 metropolitanos</t>
+  </si>
+  <si>
+    <t>Policía Metropolitana</t>
+  </si>
+  <si>
+    <t>En Cuautepec, un policía para cada 2 mil habitantes</t>
+  </si>
+  <si>
+    <t>Déficit policial</t>
+  </si>
+  <si>
+    <t>Tolvanera arrasa con tianguis de Actopan</t>
+  </si>
+  <si>
+    <t>Saquean biznagas en tres municipios</t>
+  </si>
+  <si>
+    <t>Robo de especies protegidas</t>
+  </si>
+  <si>
+    <t>Pendiente 55% de iniciativas en Congreso</t>
+  </si>
+  <si>
+    <t>Trabajo legislativo</t>
+  </si>
+  <si>
+    <t>Ubican salarios duplicados en dependencias</t>
+  </si>
+  <si>
+    <t>Doble Plaza</t>
+  </si>
+  <si>
+    <t>El ascenso es identidad""</t>
+  </si>
+  <si>
+    <t>Hidalgo responde en la Paralimpiada</t>
+  </si>
+  <si>
+    <t>Inhide</t>
+  </si>
+  <si>
+    <t>Paranacionales Conade</t>
+  </si>
+  <si>
+    <t>Descartan ajustes a la tarifa de los taxis</t>
+  </si>
+  <si>
+    <t>Por contraloría interna, auditor estatal cuestiona al titular del TEEH</t>
+  </si>
+  <si>
+    <t>ASEH</t>
+  </si>
+  <si>
+    <t>Órgano Interno de Control</t>
+  </si>
+  <si>
+    <t>Junta de Gobierno presume más de m il iniciativas</t>
+  </si>
+  <si>
+    <t>Informe Legislativo</t>
+  </si>
+  <si>
+    <t>Caen las ventas 30% en la zona centro debido a la feria, dicen</t>
+  </si>
+  <si>
+    <t>Advierten retos sobre justicia para la niñez y adolescentes</t>
+  </si>
+  <si>
+    <t>Protección del menor</t>
+  </si>
+  <si>
+    <t>Analizan entre estados proyecto para crear la policía de la ZMVM</t>
+  </si>
+  <si>
+    <t>México es un país donde hay que estar</t>
+  </si>
+  <si>
+    <t>Cooperación para potenciar Norteamérica</t>
+  </si>
+  <si>
+    <t>Temas internacionales</t>
+  </si>
+  <si>
+    <t>La información financiera coloca al estado en top 3 nacional: SHCP</t>
+  </si>
+  <si>
+    <t>Disciplina financiera</t>
+  </si>
+  <si>
+    <t>Las travesuras del Niño ya se reflejan en salud, finanzas, energía...</t>
+  </si>
+  <si>
+    <t>Expropian 107 hectáreas para obras del tren</t>
+  </si>
+  <si>
+    <t>Analizarán creación de policía metropolitana</t>
+  </si>
+  <si>
+    <t>Vigilarán a municipios que omitieron entregar sus leyes de ingresos</t>
+  </si>
+  <si>
+    <t>Ley De Ingresos</t>
+  </si>
+  <si>
+    <t>Aumentan presiones de EU a políticos mexicanos</t>
+  </si>
+  <si>
+    <t>Celebran encuentro nacional para impulsar economía social</t>
+  </si>
+  <si>
+    <t>Viggiano ha pasado por el gobierno estatal, el Poder Judicial, la Cámara de  Diputados, la candidatura a la gubernatura y el Senado, además de la dirigencia  nacional de su partido. Cuatro décadas de poder y un patrimonio que crece más  rápido que cualquier explicación”</t>
+  </si>
+  <si>
+    <t>Proponen crear una Policía Metropolitana entre Hidalgo y estados vecinos</t>
+  </si>
+  <si>
+    <t>Hidalgo destaca a nivel nacional en calidad de la información financiera</t>
+  </si>
+  <si>
+    <t>Congreso de Hidalgo reporta resultados de sus segundo año legislativo</t>
+  </si>
+  <si>
+    <t>Menchaca descarta ajuste a la tarifa de taxis ante petición de incremento</t>
+  </si>
+  <si>
+    <t>"El que nada debe, nada teme": Valverde confirma auditoría al TEEH</t>
+  </si>
+  <si>
+    <t>Un corazón, una nueva oportunidad</t>
+  </si>
+  <si>
+    <t>Puente aéreo</t>
+  </si>
+  <si>
+    <t>Evacúan bachillerato tras reporte de estudiante armado</t>
+  </si>
+  <si>
+    <t>Alumno Armado</t>
+  </si>
+  <si>
+    <t>Congreso reporta más de mil iniciativas</t>
+  </si>
+  <si>
+    <t>Banderazo no subirá a 50 pesos</t>
+  </si>
+  <si>
+    <t>Hidalgo analiza sumarse a Policía Metropolitana</t>
+  </si>
+  <si>
+    <t>CDHEH y UNIDEH convocan al Diplomado en Derechos Humanos y Género</t>
+  </si>
+  <si>
+    <t>Universidades</t>
+  </si>
+  <si>
+    <t>Derechos humanos</t>
+  </si>
+  <si>
+    <t>Gobierno de Hidalgo logra nuevo operativo de procuración de traslado aéreo de un corazón</t>
+  </si>
+  <si>
+    <t>Hidalgo fortalece economía social con Encuentro Nacional de Nodess 2026</t>
+  </si>
+  <si>
+    <t>Formalizan Procuraduría Municipal de Protección de Niñas, Niños y Adolescentes en Tula</t>
+  </si>
+  <si>
+    <t>Procuraduría municipal del menor</t>
+  </si>
+  <si>
+    <t>Tere Olivares entrega pavimentación en cerrada Juan de la Barrera</t>
+  </si>
+  <si>
+    <t>alcalde</t>
+  </si>
+  <si>
+    <t>Pavimentación</t>
+  </si>
+  <si>
+    <t>Formalizan Procuraduría Municipal de Protección de Niñas, Niños y Adolescentes en Tezontepec de Aldama</t>
+  </si>
+  <si>
+    <t>Sheinbaum entregará apoyos a 2 mil 185 familias que perdieron su casa</t>
+  </si>
+  <si>
+    <t>Huracán Priscilla</t>
+  </si>
+  <si>
+    <t>Entrega Jorge Reyes al Congreso la iniciativa de ley de ingresos en Pachuca</t>
+  </si>
+  <si>
+    <t>Tlaxcoapan, sede del foro institucional Campo y Cultura</t>
+  </si>
+  <si>
+    <t>Said Vargas encabezo en Tulancingo el Segundo Encuentro Fraterno del Jubilado</t>
+  </si>
+  <si>
+    <t>Reunión con sindicato</t>
+  </si>
+  <si>
+    <t>¿Quieres participar en la beca?</t>
+  </si>
+  <si>
+    <t>Becas</t>
+  </si>
+  <si>
+    <t>Este jueves comenzará la feria tradicional en iglesia de San Francisco</t>
+  </si>
+  <si>
+    <t>Entrega Jorge Reyes la Iniciativa de Ley de Ingresos</t>
+  </si>
+  <si>
+    <t>Hidalgo supera los 3.2 millones de habitantes; en Pachuca, 317 mil 480</t>
+  </si>
+  <si>
+    <t>Coespo</t>
+  </si>
+  <si>
+    <t>Dinámica demográfica</t>
+  </si>
+  <si>
+    <t>El estado fortalece economía social con Encuentro Nacional de Nodess 2026</t>
+  </si>
+  <si>
+    <t>Entrega Natividad Castrejón equipamiento educativo por más de 2.4 mdp en Huejutla</t>
+  </si>
+  <si>
+    <t>Infraestructura escolar</t>
+  </si>
+  <si>
+    <t>Logra Hidalgo alto nivel en información financiera</t>
+  </si>
+  <si>
+    <t>Abiertas pesquisas sobre exfuncionarios por caso Ayotiznapan</t>
+  </si>
+  <si>
+    <t>Presenta Junta de Gobierno su segundo informe</t>
+  </si>
+  <si>
+    <t>Descarta Julio Menchaca nuevo aumento de tarifa de taxis</t>
+  </si>
+  <si>
+    <t>Lo de siempre, PT y Verde supuestamente se distancian y hasta se confrontan con Morena, como estrategia para negociar. Ah, y falta el cantante</t>
+  </si>
+  <si>
+    <t>Alianzas Electorales</t>
   </si>
 </sst>
 </file>
@@ -1263,84 +1266,84 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="H3" t="s">
         <v>68</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>103</v>
-      </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
@@ -1349,10 +1352,10 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1365,16 +1368,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
@@ -1383,10 +1386,10 @@
         <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1399,32 +1402,32 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1433,25 +1436,25 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="G7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -1467,16 +1470,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
         <v>24</v>
@@ -1501,13 +1504,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -1516,13 +1519,13 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1535,28 +1538,28 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1569,32 +1572,32 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1603,32 +1606,32 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B12" t="s">
         <v>69</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="G12" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="H12" t="s">
         <v>68</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1637,25 +1640,25 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B13" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
@@ -1671,127 +1674,127 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B14" t="s">
         <v>71</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H14" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H15" t="s">
         <v>72</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
@@ -1805,64 +1808,64 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B18" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B19" t="s">
         <v>71</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>128</v>
+        <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1875,338 +1878,338 @@
     </row>
     <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J20" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" t="s">
         <v>13</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E21" t="s">
         <v>24</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F21" t="s">
         <v>24</v>
       </c>
-      <c r="G20" t="s">
-        <v>131</v>
-      </c>
-      <c r="H20" t="s">
-        <v>72</v>
-      </c>
-      <c r="I20" t="str">
+      <c r="G21" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J20" t="str">
+      <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" t="s">
-        <v>113</v>
-      </c>
-      <c r="H21" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J21" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J22" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" t="s">
+        <v>132</v>
+      </c>
+      <c r="H23" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J23" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" t="s">
-        <v>40</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" t="s">
         <v>134</v>
       </c>
-      <c r="H22" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J22" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="H24" t="s">
+        <v>72</v>
+      </c>
+      <c r="I24" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J24" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" t="s">
-        <v>81</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s">
         <v>82</v>
       </c>
-      <c r="H23" t="s">
-        <v>72</v>
-      </c>
-      <c r="I23" t="str">
+      <c r="H25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J25" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>98</v>
+      </c>
+      <c r="H26" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J26" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" t="s">
+        <v>106</v>
+      </c>
+      <c r="H27" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J23" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" t="s">
-        <v>137</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="J27" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="H24" t="s">
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" t="s">
+        <v>122</v>
+      </c>
+      <c r="G28" t="s">
+        <v>139</v>
+      </c>
+      <c r="H28" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J28" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" t="s">
+        <v>132</v>
+      </c>
+      <c r="H29" t="s">
         <v>68</v>
       </c>
-      <c r="I24" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Sucesión gubernamental</v>
-      </c>
-      <c r="J24" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D25" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" t="s">
-        <v>29</v>
-      </c>
-      <c r="F25" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25" t="s">
-        <v>140</v>
-      </c>
-      <c r="H25" t="s">
-        <v>72</v>
-      </c>
-      <c r="I25" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J25" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D26" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F26" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" t="s">
-        <v>115</v>
-      </c>
-      <c r="H26" t="s">
-        <v>68</v>
-      </c>
-      <c r="I26" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
-      </c>
-      <c r="J26" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B27" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" t="s">
-        <v>92</v>
-      </c>
-      <c r="H27" t="s">
-        <v>11</v>
-      </c>
-      <c r="I27" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J27" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D28" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" t="s">
-        <v>144</v>
-      </c>
-      <c r="H28" t="s">
-        <v>11</v>
-      </c>
-      <c r="I28" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J28" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B29" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D29" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G29" t="s">
-        <v>99</v>
-      </c>
-      <c r="H29" t="s">
-        <v>11</v>
-      </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2215,183 +2218,183 @@
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" t="s">
+        <v>100</v>
+      </c>
+      <c r="H30" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J30" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A31" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" t="s">
+        <v>91</v>
+      </c>
+      <c r="H31" t="s">
+        <v>68</v>
+      </c>
+      <c r="I31" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Sucesión gubernamental</v>
+      </c>
+      <c r="J31" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" t="s">
         <v>13</v>
       </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" t="s">
-        <v>115</v>
-      </c>
-      <c r="H30" t="s">
-        <v>11</v>
-      </c>
-      <c r="I30" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J30" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B31" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" t="s">
-        <v>89</v>
-      </c>
-      <c r="H31" t="s">
-        <v>11</v>
-      </c>
-      <c r="I31" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
-      </c>
-      <c r="J31" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B32" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" t="s">
-        <v>9</v>
-      </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="G32" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H32" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="F33" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="H33" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Sucesión gubernamental</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B34" t="s">
         <v>74</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="H34" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B35" t="s">
         <v>74</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
@@ -2403,7 +2406,7 @@
         <v>24</v>
       </c>
       <c r="G35" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s">
         <v>72</v>
@@ -2419,161 +2422,161 @@
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36" t="s">
+        <v>122</v>
+      </c>
+      <c r="G36" t="s">
+        <v>123</v>
+      </c>
+      <c r="H36" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J36" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" t="s">
         <v>15</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F37" t="s">
         <v>15</v>
       </c>
-      <c r="G36" t="s">
-        <v>93</v>
-      </c>
-      <c r="H36" t="s">
-        <v>68</v>
-      </c>
-      <c r="I36" t="str">
+      <c r="G37" t="s">
+        <v>149</v>
+      </c>
+      <c r="H37" t="s">
+        <v>72</v>
+      </c>
+      <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J36" t="str">
+      <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B37" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" t="s">
-        <v>16</v>
-      </c>
-      <c r="F37" t="s">
-        <v>16</v>
-      </c>
-      <c r="G37" t="s">
-        <v>99</v>
-      </c>
-      <c r="H37" t="s">
-        <v>68</v>
-      </c>
-      <c r="I37" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J37" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B38" t="s">
         <v>73</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G38" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="H38" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B39" t="s">
         <v>73</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F39" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="H39" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B40" t="s">
         <v>73</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F40" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="G40" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s">
         <v>72</v>
@@ -2584,64 +2587,64 @@
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B41" t="s">
         <v>73</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D41" t="s">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F41" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G41" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B42" t="s">
         <v>73</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>29</v>
+        <v>156</v>
       </c>
       <c r="G42" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H42" t="s">
         <v>11</v>
@@ -2657,25 +2660,25 @@
     </row>
     <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D43" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F43" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="H43" t="s">
         <v>72</v>
@@ -2691,16 +2694,16 @@
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B44" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E44" t="s">
         <v>24</v>
@@ -2709,10 +2712,10 @@
         <v>24</v>
       </c>
       <c r="G44" t="s">
-        <v>162</v>
+        <v>100</v>
       </c>
       <c r="H44" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2725,28 +2728,28 @@
     </row>
     <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>106</v>
+        <v>161</v>
       </c>
       <c r="H45" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2754,18 +2757,18 @@
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D46" t="s">
         <v>12</v>
@@ -2774,10 +2777,10 @@
         <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="G46" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
@@ -2793,100 +2796,100 @@
     </row>
     <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C47" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" t="s">
+        <v>161</v>
+      </c>
+      <c r="H47" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J47" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B48" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="D47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" t="s">
-        <v>16</v>
-      </c>
-      <c r="F47" t="s">
-        <v>77</v>
-      </c>
-      <c r="G47" t="s">
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" t="s">
         <v>167</v>
       </c>
-      <c r="H47" t="s">
-        <v>11</v>
-      </c>
-      <c r="I47" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J47" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B48" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D48" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" t="s">
-        <v>27</v>
-      </c>
-      <c r="F48" t="s">
-        <v>27</v>
-      </c>
-      <c r="G48" t="s">
-        <v>80</v>
-      </c>
       <c r="H48" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="G49" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
       </c>
       <c r="I49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2895,13 +2898,13 @@
     </row>
     <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
@@ -2929,50 +2932,50 @@
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B51" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C51" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" t="s">
         <v>171</v>
       </c>
-      <c r="D51" t="s">
-        <v>12</v>
-      </c>
-      <c r="E51" t="s">
-        <v>16</v>
-      </c>
-      <c r="F51" t="s">
-        <v>16</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
+        <v>11</v>
+      </c>
+      <c r="I51" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J51" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="H51" t="s">
-        <v>11</v>
-      </c>
-      <c r="I51" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J51" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B52" t="s">
-        <v>75</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>173</v>
-      </c>
       <c r="D52" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="E52" t="s">
         <v>16</v>
@@ -2981,112 +2984,112 @@
         <v>16</v>
       </c>
       <c r="G52" t="s">
+        <v>173</v>
+      </c>
+      <c r="H52" t="s">
+        <v>11</v>
+      </c>
+      <c r="I52" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J52" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H52" t="s">
-        <v>11</v>
-      </c>
-      <c r="I52" t="str">
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" t="s">
+        <v>88</v>
+      </c>
+      <c r="H53" t="s">
+        <v>11</v>
+      </c>
+      <c r="I53" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J53" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B54" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" t="s">
+        <v>76</v>
+      </c>
+      <c r="G54" t="s">
+        <v>139</v>
+      </c>
+      <c r="H54" t="s">
+        <v>11</v>
+      </c>
+      <c r="I54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Alcaldías</v>
       </c>
-      <c r="J52" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B53" t="s">
-        <v>75</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E53" t="s">
-        <v>53</v>
-      </c>
-      <c r="F53" t="s">
-        <v>53</v>
-      </c>
-      <c r="G53" t="s">
-        <v>176</v>
-      </c>
-      <c r="H53" t="s">
-        <v>11</v>
-      </c>
-      <c r="I53" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J53" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="11">
-        <v>46294</v>
-      </c>
-      <c r="B54" t="s">
-        <v>79</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D54" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" t="s">
-        <v>24</v>
-      </c>
-      <c r="F54" t="s">
-        <v>24</v>
-      </c>
-      <c r="G54" t="s">
-        <v>106</v>
-      </c>
-      <c r="H54" t="s">
-        <v>11</v>
-      </c>
-      <c r="I54" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
       <c r="J54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C55" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" t="s">
+        <v>177</v>
+      </c>
+      <c r="G55" t="s">
         <v>178</v>
       </c>
-      <c r="D55" t="s">
-        <v>12</v>
-      </c>
-      <c r="E55" t="s">
-        <v>29</v>
-      </c>
-      <c r="F55" t="s">
-        <v>81</v>
-      </c>
-      <c r="G55" t="s">
-        <v>82</v>
-      </c>
       <c r="H55" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3099,10 +3102,10 @@
     </row>
     <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B56" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>179</v>
@@ -3111,32 +3114,32 @@
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F56" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G56" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
       </c>
       <c r="I56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>180</v>
@@ -3151,7 +3154,7 @@
         <v>2</v>
       </c>
       <c r="G57" t="s">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
@@ -3165,24 +3168,24 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D58" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="E58" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F58" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G58" t="s">
         <v>92</v>
@@ -3201,25 +3204,25 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B59" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="D59" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="E59" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F59" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G59" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="H59" t="s">
         <v>11</v>
@@ -3233,68 +3236,68 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B60" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F60" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s">
         <v>11</v>
       </c>
       <c r="I60" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J60" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B61" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D61" t="s">
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F61" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G61" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="H61" t="s">
         <v>11</v>
       </c>
       <c r="I61" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J61" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -3303,44 +3306,44 @@
     </row>
     <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D62" t="s">
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F62" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G62" t="s">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I62" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J62" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="11">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>186</v>
@@ -3349,20 +3352,20 @@
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="G63" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="H63" t="s">
         <v>11</v>
       </c>
       <c r="I63" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J63" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -3936,7 +3939,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B49" t="s">
         <v>44</v>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FF4DD5-9FEE-40A6-AFDC-DE927A8CE534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D516C631-5C41-450D-A3FD-88152FCC19C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="185">
   <si>
     <t>Fecha</t>
   </si>
@@ -276,9 +276,6 @@
     <t>Pachuca Brilla</t>
   </si>
   <si>
-    <t>Tarifario de taxis</t>
-  </si>
-  <si>
     <t>Feria Pachuca</t>
   </si>
   <si>
@@ -291,316 +288,310 @@
     <t>La Jornada Hidalgo</t>
   </si>
   <si>
-    <t>Policía municipal</t>
-  </si>
-  <si>
     <t>Publicidad</t>
   </si>
   <si>
-    <t>Tu voz cuenta</t>
-  </si>
-  <si>
     <t>El Sol de Hidalgo</t>
   </si>
   <si>
-    <t>Feria tradicional</t>
-  </si>
-  <si>
-    <t>Junta de Gobierno</t>
-  </si>
-  <si>
-    <t>Viggiano</t>
-  </si>
-  <si>
-    <t>Enriquecimiento ilícito</t>
-  </si>
-  <si>
-    <t>Desarrollo Urbano</t>
-  </si>
-  <si>
-    <t>Arranca restauración de Jardín Colón en Pachuca</t>
-  </si>
-  <si>
     <t>Sipdus</t>
   </si>
   <si>
-    <t>Rehabilitación de espacios públicos</t>
-  </si>
-  <si>
-    <t>Persisten los cobros elevados en taxis</t>
-  </si>
-  <si>
-    <t>Expropian terrenos para el Tren AIFA-Pachuca</t>
-  </si>
-  <si>
     <t>Tren AIFA</t>
   </si>
   <si>
-    <t>Emprendedores nacionales se reúnen en UPMH</t>
-  </si>
-  <si>
-    <t>Economía social</t>
-  </si>
-  <si>
-    <t>Inicia Xantolo en Huejutla con primera ofrenda</t>
-  </si>
-  <si>
     <t>Xantolo</t>
   </si>
   <si>
-    <t>Supervisará Protección Civil puestos semifijos</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>Perfilan policía y un C5 metropolitanos</t>
-  </si>
-  <si>
-    <t>Policía Metropolitana</t>
-  </si>
-  <si>
-    <t>En Cuautepec, un policía para cada 2 mil habitantes</t>
-  </si>
-  <si>
-    <t>Déficit policial</t>
-  </si>
-  <si>
-    <t>Tolvanera arrasa con tianguis de Actopan</t>
-  </si>
-  <si>
-    <t>Saquean biznagas en tres municipios</t>
-  </si>
-  <si>
-    <t>Robo de especies protegidas</t>
-  </si>
-  <si>
-    <t>Pendiente 55% de iniciativas en Congreso</t>
-  </si>
-  <si>
-    <t>Trabajo legislativo</t>
-  </si>
-  <si>
-    <t>Ubican salarios duplicados en dependencias</t>
-  </si>
-  <si>
-    <t>Doble Plaza</t>
-  </si>
-  <si>
-    <t>El ascenso es identidad""</t>
-  </si>
-  <si>
-    <t>Hidalgo responde en la Paralimpiada</t>
-  </si>
-  <si>
-    <t>Inhide</t>
-  </si>
-  <si>
-    <t>Paranacionales Conade</t>
-  </si>
-  <si>
-    <t>Descartan ajustes a la tarifa de los taxis</t>
-  </si>
-  <si>
-    <t>Por contraloría interna, auditor estatal cuestiona al titular del TEEH</t>
-  </si>
-  <si>
     <t>ASEH</t>
   </si>
   <si>
     <t>Órgano Interno de Control</t>
   </si>
   <si>
-    <t>Junta de Gobierno presume más de m il iniciativas</t>
-  </si>
-  <si>
-    <t>Informe Legislativo</t>
-  </si>
-  <si>
-    <t>Caen las ventas 30% en la zona centro debido a la feria, dicen</t>
-  </si>
-  <si>
-    <t>Advierten retos sobre justicia para la niñez y adolescentes</t>
-  </si>
-  <si>
-    <t>Protección del menor</t>
-  </si>
-  <si>
-    <t>Analizan entre estados proyecto para crear la policía de la ZMVM</t>
-  </si>
-  <si>
-    <t>México es un país donde hay que estar</t>
-  </si>
-  <si>
-    <t>Cooperación para potenciar Norteamérica</t>
-  </si>
-  <si>
-    <t>Temas internacionales</t>
-  </si>
-  <si>
-    <t>La información financiera coloca al estado en top 3 nacional: SHCP</t>
-  </si>
-  <si>
-    <t>Disciplina financiera</t>
-  </si>
-  <si>
-    <t>Las travesuras del Niño ya se reflejan en salud, finanzas, energía...</t>
-  </si>
-  <si>
-    <t>Expropian 107 hectáreas para obras del tren</t>
-  </si>
-  <si>
-    <t>Analizarán creación de policía metropolitana</t>
-  </si>
-  <si>
-    <t>Vigilarán a municipios que omitieron entregar sus leyes de ingresos</t>
-  </si>
-  <si>
-    <t>Ley De Ingresos</t>
-  </si>
-  <si>
-    <t>Aumentan presiones de EU a políticos mexicanos</t>
-  </si>
-  <si>
-    <t>Celebran encuentro nacional para impulsar economía social</t>
-  </si>
-  <si>
-    <t>Viggiano ha pasado por el gobierno estatal, el Poder Judicial, la Cámara de  Diputados, la candidatura a la gubernatura y el Senado, además de la dirigencia  nacional de su partido. Cuatro décadas de poder y un patrimonio que crece más  rápido que cualquier explicación”</t>
-  </si>
-  <si>
-    <t>Proponen crear una Policía Metropolitana entre Hidalgo y estados vecinos</t>
-  </si>
-  <si>
-    <t>Hidalgo destaca a nivel nacional en calidad de la información financiera</t>
-  </si>
-  <si>
-    <t>Congreso de Hidalgo reporta resultados de sus segundo año legislativo</t>
-  </si>
-  <si>
-    <t>Menchaca descarta ajuste a la tarifa de taxis ante petición de incremento</t>
-  </si>
-  <si>
-    <t>"El que nada debe, nada teme": Valverde confirma auditoría al TEEH</t>
-  </si>
-  <si>
-    <t>Un corazón, una nueva oportunidad</t>
-  </si>
-  <si>
-    <t>Puente aéreo</t>
-  </si>
-  <si>
-    <t>Evacúan bachillerato tras reporte de estudiante armado</t>
-  </si>
-  <si>
-    <t>Alumno Armado</t>
-  </si>
-  <si>
-    <t>Congreso reporta más de mil iniciativas</t>
-  </si>
-  <si>
-    <t>Banderazo no subirá a 50 pesos</t>
-  </si>
-  <si>
-    <t>Hidalgo analiza sumarse a Policía Metropolitana</t>
-  </si>
-  <si>
-    <t>CDHEH y UNIDEH convocan al Diplomado en Derechos Humanos y Género</t>
-  </si>
-  <si>
-    <t>Universidades</t>
-  </si>
-  <si>
-    <t>Derechos humanos</t>
-  </si>
-  <si>
-    <t>Gobierno de Hidalgo logra nuevo operativo de procuración de traslado aéreo de un corazón</t>
-  </si>
-  <si>
-    <t>Hidalgo fortalece economía social con Encuentro Nacional de Nodess 2026</t>
-  </si>
-  <si>
-    <t>Formalizan Procuraduría Municipal de Protección de Niñas, Niños y Adolescentes en Tula</t>
-  </si>
-  <si>
-    <t>Procuraduría municipal del menor</t>
-  </si>
-  <si>
-    <t>Tere Olivares entrega pavimentación en cerrada Juan de la Barrera</t>
-  </si>
-  <si>
-    <t>alcalde</t>
-  </si>
-  <si>
-    <t>Pavimentación</t>
-  </si>
-  <si>
-    <t>Formalizan Procuraduría Municipal de Protección de Niñas, Niños y Adolescentes en Tezontepec de Aldama</t>
-  </si>
-  <si>
-    <t>Sheinbaum entregará apoyos a 2 mil 185 familias que perdieron su casa</t>
-  </si>
-  <si>
-    <t>Huracán Priscilla</t>
-  </si>
-  <si>
-    <t>Entrega Jorge Reyes al Congreso la iniciativa de ley de ingresos en Pachuca</t>
-  </si>
-  <si>
-    <t>Tlaxcoapan, sede del foro institucional Campo y Cultura</t>
-  </si>
-  <si>
-    <t>Said Vargas encabezo en Tulancingo el Segundo Encuentro Fraterno del Jubilado</t>
-  </si>
-  <si>
-    <t>Reunión con sindicato</t>
-  </si>
-  <si>
-    <t>¿Quieres participar en la beca?</t>
-  </si>
-  <si>
-    <t>Becas</t>
-  </si>
-  <si>
-    <t>Este jueves comenzará la feria tradicional en iglesia de San Francisco</t>
-  </si>
-  <si>
-    <t>Entrega Jorge Reyes la Iniciativa de Ley de Ingresos</t>
-  </si>
-  <si>
-    <t>Hidalgo supera los 3.2 millones de habitantes; en Pachuca, 317 mil 480</t>
-  </si>
-  <si>
-    <t>Coespo</t>
-  </si>
-  <si>
     <t>Dinámica demográfica</t>
   </si>
   <si>
-    <t>El estado fortalece economía social con Encuentro Nacional de Nodess 2026</t>
-  </si>
-  <si>
-    <t>Entrega Natividad Castrejón equipamiento educativo por más de 2.4 mdp en Huejutla</t>
-  </si>
-  <si>
-    <t>Infraestructura escolar</t>
-  </si>
-  <si>
-    <t>Logra Hidalgo alto nivel en información financiera</t>
-  </si>
-  <si>
-    <t>Abiertas pesquisas sobre exfuncionarios por caso Ayotiznapan</t>
-  </si>
-  <si>
-    <t>Presenta Junta de Gobierno su segundo informe</t>
-  </si>
-  <si>
-    <t>Descarta Julio Menchaca nuevo aumento de tarifa de taxis</t>
-  </si>
-  <si>
-    <t>Lo de siempre, PT y Verde supuestamente se distancian y hasta se confrontan con Morena, como estrategia para negociar. Ah, y falta el cantante</t>
-  </si>
-  <si>
-    <t>Alianzas Electorales</t>
+    <t>Más de cuatro mil divorcios en 2025</t>
+  </si>
+  <si>
+    <t>Piden mejorar condiciones de trabajo</t>
+  </si>
+  <si>
+    <t>IMSS</t>
+  </si>
+  <si>
+    <t>Protesta sindical</t>
+  </si>
+  <si>
+    <t>La Cruz Azul alista producción en Tula</t>
+  </si>
+  <si>
+    <t>Cruz Azul</t>
+  </si>
+  <si>
+    <t>Finaliza huelga del Montepío</t>
+  </si>
+  <si>
+    <t>Presentan Xantolo 2026</t>
+  </si>
+  <si>
+    <t>Pulque eleva su valor</t>
+  </si>
+  <si>
+    <t>Aprueba el IEEH tope de gastos para las precampañas locales</t>
+  </si>
+  <si>
+    <t>Avala Congreso estatal iniciativa de nacionalidad única para Presidente y gobernadores</t>
+  </si>
+  <si>
+    <t>Doble nacionalidad</t>
+  </si>
+  <si>
+    <t>Van 1.5 millones de vacunas contra influenza y Covid-19</t>
+  </si>
+  <si>
+    <t>Vacunación</t>
+  </si>
+  <si>
+    <t>Abre Morena registros para diputaciones</t>
+  </si>
+  <si>
+    <t>Elecciones</t>
+  </si>
+  <si>
+    <t>Destina Semarnat $75 millones para sanear la presa Endhó</t>
+  </si>
+  <si>
+    <t>Medio ambiente</t>
+  </si>
+  <si>
+    <t>Presa Endhó</t>
+  </si>
+  <si>
+    <t>Invitan a 4 días de vivir la fiesta del Xantolo</t>
+  </si>
+  <si>
+    <t>Tuzos perfilan futuro olímpico</t>
+  </si>
+  <si>
+    <t>Listo para su último baile</t>
+  </si>
+  <si>
+    <t>Expropian 98 inmuebles para Tren AIFA-Pachuca</t>
+  </si>
+  <si>
+    <t>Sedena</t>
+  </si>
+  <si>
+    <t>Reconstrucción del bulevar las Torres tiene un avance de 52%</t>
+  </si>
+  <si>
+    <t>Rehabilitación Vial</t>
+  </si>
+  <si>
+    <t>Preparan un Mijkailjuitl con memoria y tradición</t>
+  </si>
+  <si>
+    <t>Protestan contra acuerdo salarial</t>
+  </si>
+  <si>
+    <t>INE Hidalgo prevé la instalación de 4 mil 400 casillas para la próxima jornada</t>
+  </si>
+  <si>
+    <t>Cuesta a hidalguenses más de $120 mil cada resolución del TEEH</t>
+  </si>
+  <si>
+    <t>Resolución de juicio</t>
+  </si>
+  <si>
+    <t>Revisa ASEH recursos en medio de crisis por el OIC</t>
+  </si>
+  <si>
+    <t>Arranca Morena registro; al estado corresponden siete defensores distritales</t>
+  </si>
+  <si>
+    <t>Xantolo: una tradición y espectáculo</t>
+  </si>
+  <si>
+    <t>Captan en imágenes las expresiones culturales</t>
+  </si>
+  <si>
+    <t>Concurso de fotografía</t>
+  </si>
+  <si>
+    <t>Cuenta el estado con más de cinco mil policías</t>
+  </si>
+  <si>
+    <t>Tasa de policías</t>
+  </si>
+  <si>
+    <t>Segob activará el rastreo de personas desaparecidas con 32 centros de mando</t>
+  </si>
+  <si>
+    <t>Gobernación</t>
+  </si>
+  <si>
+    <t>Personas desaparecidas</t>
+  </si>
+  <si>
+    <t>Unidad antisecuestro de la PGJEH consigue sentencias récord</t>
+  </si>
+  <si>
+    <t>UECS</t>
+  </si>
+  <si>
+    <t>Combate Al Secuestro</t>
+  </si>
+  <si>
+    <t>Exportaciones caen 18.7% en segundo trimestre: Mientras en 2025 la entidad obtuvo 811 mil 441 dólares, en 2026 decreció a 659 mil 328</t>
+  </si>
+  <si>
+    <t>Exportaciones</t>
+  </si>
+  <si>
+    <t>Partidos piden piso parejo al arranque del proceso federal</t>
+  </si>
+  <si>
+    <t>Tizayuca cuadruplicó su población; “urge ajustar presupuesto”</t>
+  </si>
+  <si>
+    <t>Envíos al exterior de crudo de Pemex se desploma 45%</t>
+  </si>
+  <si>
+    <t>Pemex</t>
+  </si>
+  <si>
+    <t>Hidalgo necesita planear pensando en dónde vive hoy la gente y en dónde vivirá mañana, no en dónde vivía hace diez años. De lo contrario, el crecimiento seguirá siendo sinónimo de rezago</t>
+  </si>
+  <si>
+    <t>Ordenamiento Territorial</t>
+  </si>
+  <si>
+    <t>Más de 2.5 millones de hidalguenses podrán votar en las elecciones federales de 2027</t>
+  </si>
+  <si>
+    <t>Dota DIFH de reequipamiento a espacios de alimentación para personas vulnerables</t>
+  </si>
+  <si>
+    <t>Espacios de alimentación</t>
+  </si>
+  <si>
+    <t>Invierten 75 mdp en Presa Endhó; Semarnat asegura reducción de 47% del mosco Culex</t>
+  </si>
+  <si>
+    <t>Exigen trabajadores del IMSS Hidalgo insumos y mejores condiciones laborales</t>
+  </si>
+  <si>
+    <t>Cerca de 2.5 millones de hidalguenses podrán votar en 2027</t>
+  </si>
+  <si>
+    <t>Miradas de Hidalgo</t>
+  </si>
+  <si>
+    <t>Freno a doble nacionalidad</t>
+  </si>
+  <si>
+    <t>Rescate de ríos</t>
+  </si>
+  <si>
+    <t>Plan Hídrico</t>
+  </si>
+  <si>
+    <t>INE arranca organización de elección federal en Hidalgo</t>
+  </si>
+  <si>
+    <t>Pachuca tendrá tope de 1.4 millones para precampañas</t>
+  </si>
+  <si>
+    <t>Marfeca</t>
+  </si>
+  <si>
+    <t>Primeros días de feria Pachuca deja 38 detenidos en alcoholímetro</t>
+  </si>
+  <si>
+    <t>Cintillo</t>
+  </si>
+  <si>
+    <t>Capturando Hidalgo 2026 premia con 132  mil pesos trabajo fotográfico de culturas vivas</t>
+  </si>
+  <si>
+    <t>La SCJN falla a favor de La Cruz Azul y protege de forma definitiva su patrimonio</t>
+  </si>
+  <si>
+    <t>Continúa Jorge Reyes impulsando en Pachuca las jornadas gratuitas de esterilización y vacunación antirrábica</t>
+  </si>
+  <si>
+    <t>Campaña de esterilización</t>
+  </si>
+  <si>
+    <t>Arranca jornada de esterilización gratuita</t>
+  </si>
+  <si>
+    <t>Con Claudia Sandoval, Atitalaquia planea y transforma con el corazón por su gente</t>
+  </si>
+  <si>
+    <t>Tlahuelilpan recibe equipamiento del DIFH para Espacios de Alimentación</t>
+  </si>
+  <si>
+    <t>Emprendimiento que florece</t>
+  </si>
+  <si>
+    <t>Apoyo a emprendedores</t>
+  </si>
+  <si>
+    <t>Xantolo 2026: preparan cuatro días de fiesta en Huejutla</t>
+  </si>
+  <si>
+    <t>Beneficia SEPH con apoyos e infraestructura a estudiantes de San Felipe Orizatlán</t>
+  </si>
+  <si>
+    <t>Entrega de infraestructura escolar</t>
+  </si>
+  <si>
+    <t>Continúa Jorge Reyes impulsando jornadas gratuitas de esterilización y vacunación antirrábica</t>
+  </si>
+  <si>
+    <t>Personal del IMSS pide igualdad salarial; se manifiestan en Madero</t>
+  </si>
+  <si>
+    <t>Óscar Maydon y Víctor Mendívil prendieron la Feria de Pachuca</t>
+  </si>
+  <si>
+    <t>OEEH</t>
+  </si>
+  <si>
+    <t>Haz una parada diferente</t>
+  </si>
+  <si>
+    <t>Recuerda: la detección temprana salva vidas</t>
+  </si>
+  <si>
+    <t>Prevención cáncer de mama</t>
+  </si>
+  <si>
+    <t>Colectiva arrolla a adulta mayor y choca</t>
+  </si>
+  <si>
+    <t>STCH</t>
+  </si>
+  <si>
+    <t>Accidente transporte público</t>
+  </si>
+  <si>
+    <t>Prohíben la doble nacionalidad para Presidente</t>
+  </si>
+  <si>
+    <t>EE.UU. tiende las redes contra funcionarios mexicanos ligados con los narcos de Sinaloa; muchos seguro ya no comen ni duermen por la preocupación</t>
+  </si>
+  <si>
+    <t>Editorial</t>
+  </si>
+  <si>
+    <t>Intervención extranjera</t>
+  </si>
+  <si>
+    <t>Gobernador pide reforzar seguridad en Feria San Francisco</t>
   </si>
 </sst>
 </file>
@@ -847,8 +838,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J63" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J63" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J62" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J62" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1217,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1266,372 +1257,372 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="H3" t="s">
         <v>68</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" t="s">
-        <v>102</v>
-      </c>
       <c r="H6" t="s">
         <v>11</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Partidos</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B12" t="s">
         <v>69</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="G12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1640,25 +1631,25 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B13" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G13" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
@@ -1674,13 +1665,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B14" t="s">
         <v>71</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
@@ -1708,127 +1699,127 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="G16" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="F17" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="G17" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B18" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
@@ -1842,34 +1833,34 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B19" t="s">
         <v>71</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1878,13 +1869,13 @@
     </row>
     <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B20" t="s">
         <v>71</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
         <v>12</v>
@@ -1896,7 +1887,7 @@
         <v>10</v>
       </c>
       <c r="G20" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
@@ -1912,59 +1903,59 @@
     </row>
     <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B21" t="s">
         <v>75</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
         <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H21" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B22" t="s">
         <v>75</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
@@ -1978,370 +1969,370 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B23" t="s">
         <v>75</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G23" t="s">
-        <v>132</v>
+        <v>42</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B24" t="s">
         <v>75</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B25" t="s">
         <v>75</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G25" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="H25" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B26" t="s">
         <v>75</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
       </c>
       <c r="E26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" t="s">
+        <v>128</v>
+      </c>
+      <c r="H26" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J26" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
+        <v>46296</v>
+      </c>
+      <c r="B27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
         <v>14</v>
       </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" t="s">
-        <v>98</v>
-      </c>
-      <c r="H26" t="s">
-        <v>11</v>
-      </c>
-      <c r="I26" t="str">
+      <c r="F27" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" t="s">
+        <v>131</v>
+      </c>
+      <c r="H27" t="s">
+        <v>72</v>
+      </c>
+      <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Presidencia de la República</v>
       </c>
-      <c r="J26" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
-        <v>46295</v>
-      </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" t="s">
-        <v>24</v>
-      </c>
-      <c r="F27" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" t="s">
-        <v>106</v>
-      </c>
-      <c r="H27" t="s">
-        <v>11</v>
-      </c>
-      <c r="I27" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="G28" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H28" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="G29" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H29" t="s">
         <v>68</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" t="s">
+        <v>42</v>
+      </c>
+      <c r="H30" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J30" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="11">
+        <v>46296</v>
+      </c>
+      <c r="B31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" t="s">
+        <v>90</v>
+      </c>
+      <c r="H31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J31" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="11">
+        <v>46296</v>
+      </c>
+      <c r="B32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" t="s">
+        <v>136</v>
+      </c>
+      <c r="H32" t="s">
+        <v>68</v>
+      </c>
+      <c r="I32" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J32" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="11">
+        <v>46296</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" t="s">
-        <v>24</v>
-      </c>
-      <c r="G30" t="s">
-        <v>100</v>
-      </c>
-      <c r="H30" t="s">
-        <v>11</v>
-      </c>
-      <c r="I30" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J30" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A31" s="11">
-        <v>46295</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" s="5" t="s">
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33" t="s">
+        <v>38</v>
+      </c>
+      <c r="G33" t="s">
         <v>142</v>
       </c>
-      <c r="D31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" t="s">
-        <v>90</v>
-      </c>
-      <c r="G31" t="s">
-        <v>91</v>
-      </c>
-      <c r="H31" t="s">
-        <v>68</v>
-      </c>
-      <c r="I31" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Sucesión gubernamental</v>
-      </c>
-      <c r="J31" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="11">
-        <v>46295</v>
-      </c>
-      <c r="B32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D32" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" t="s">
-        <v>106</v>
-      </c>
-      <c r="H32" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J32" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
-        <v>46295</v>
-      </c>
-      <c r="B33" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D33" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" t="s">
-        <v>39</v>
-      </c>
-      <c r="F33" t="s">
-        <v>39</v>
-      </c>
-      <c r="G33" t="s">
-        <v>134</v>
-      </c>
       <c r="H33" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2354,25 +2345,25 @@
     </row>
     <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B34" t="s">
         <v>74</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="G34" t="s">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -2388,28 +2379,28 @@
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B35" t="s">
         <v>74</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="H35" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2417,336 +2408,336 @@
       </c>
       <c r="J35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C36" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" t="s">
+        <v>108</v>
+      </c>
+      <c r="G36" t="s">
+        <v>109</v>
+      </c>
+      <c r="H36" t="s">
+        <v>72</v>
+      </c>
+      <c r="I36" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J36" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="11">
+        <v>46296</v>
+      </c>
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D36" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" t="s">
-        <v>33</v>
-      </c>
-      <c r="F36" t="s">
-        <v>122</v>
-      </c>
-      <c r="G36" t="s">
-        <v>123</v>
-      </c>
-      <c r="H36" t="s">
-        <v>11</v>
-      </c>
-      <c r="I36" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J36" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="11">
-        <v>46295</v>
-      </c>
-      <c r="B37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>148</v>
-      </c>
       <c r="D37" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F37" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="G37" t="s">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B38" t="s">
         <v>73</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G38" t="s">
-        <v>151</v>
+        <v>42</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B39" t="s">
         <v>73</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F39" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="G39" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H39" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B40" t="s">
         <v>73</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G40" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="H40" t="s">
         <v>72</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B41" t="s">
         <v>73</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D41" t="s">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F41" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B42" t="s">
         <v>73</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G42" t="s">
-        <v>157</v>
+        <v>42</v>
       </c>
       <c r="H42" t="s">
         <v>11</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B43" t="s">
         <v>73</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F43" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G43" t="s">
-        <v>149</v>
+        <v>42</v>
       </c>
       <c r="H43" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="E44" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D45" t="s">
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F45" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G45" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
@@ -2762,56 +2753,56 @@
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D46" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" t="s">
+        <v>96</v>
+      </c>
+      <c r="H46" t="s">
+        <v>72</v>
+      </c>
+      <c r="I46" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J46" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A47" s="11">
+        <v>46296</v>
+      </c>
+      <c r="B47" t="s">
+        <v>155</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
         <v>16</v>
       </c>
-      <c r="F46" t="s">
-        <v>163</v>
-      </c>
-      <c r="G46" t="s">
-        <v>164</v>
-      </c>
-      <c r="H46" t="s">
-        <v>11</v>
-      </c>
-      <c r="I46" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J46" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="11">
-        <v>46295</v>
-      </c>
-      <c r="B47" t="s">
-        <v>73</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" t="s">
-        <v>36</v>
-      </c>
       <c r="F47" t="s">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="G47" t="s">
         <v>161</v>
@@ -2821,41 +2812,41 @@
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B48" t="s">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D48" t="s">
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F48" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2864,13 +2855,13 @@
     </row>
     <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B49" t="s">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
@@ -2879,10 +2870,10 @@
         <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -2898,149 +2889,149 @@
     </row>
     <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G50" t="s">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D51" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F51" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G51" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B52" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D52" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F52" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G52" t="s">
-        <v>173</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B53" t="s">
         <v>78</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F53" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G53" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B54" t="s">
         <v>78</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D54" t="s">
         <v>12</v>
@@ -3052,7 +3043,7 @@
         <v>76</v>
       </c>
       <c r="G54" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="H54" t="s">
         <v>11</v>
@@ -3068,59 +3059,59 @@
     </row>
     <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B55" t="s">
         <v>78</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D55" t="s">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F55" t="s">
-        <v>177</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s">
-        <v>178</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B56" t="s">
         <v>78</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D56" t="s">
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F56" t="s">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="G56" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
@@ -3131,30 +3122,30 @@
       </c>
       <c r="J56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B57" t="s">
         <v>78</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D57" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="E57" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G57" t="s">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
@@ -3170,62 +3161,62 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B58" t="s">
         <v>78</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>86</v>
+        <v>175</v>
       </c>
       <c r="D58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E58" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F58" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="H58" t="s">
         <v>11</v>
       </c>
       <c r="I58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B59" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D59" t="s">
         <v>13</v>
       </c>
       <c r="E59" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F59" t="s">
-        <v>39</v>
+        <v>178</v>
       </c>
       <c r="G59" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="H59" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3236,15 +3227,15 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D60" t="s">
         <v>12</v>
@@ -3256,10 +3247,10 @@
         <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="H60" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I60" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3270,30 +3261,30 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D61" t="s">
-        <v>12</v>
+        <v>182</v>
       </c>
       <c r="E61" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F61" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="G61" t="s">
-        <v>125</v>
+        <v>183</v>
       </c>
       <c r="H61" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I61" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3306,13 +3297,13 @@
     </row>
     <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D62" t="s">
         <v>12</v>
@@ -3327,7 +3318,7 @@
         <v>79</v>
       </c>
       <c r="H62" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I62" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3336,40 +3327,6 @@
       <c r="J62" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A63" s="11">
-        <v>46295</v>
-      </c>
-      <c r="B63" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D63" t="s">
-        <v>12</v>
-      </c>
-      <c r="E63" t="s">
-        <v>18</v>
-      </c>
-      <c r="F63" t="s">
-        <v>18</v>
-      </c>
-      <c r="G63" t="s">
-        <v>187</v>
-      </c>
-      <c r="H63" t="s">
-        <v>11</v>
-      </c>
-      <c r="I63" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
-      </c>
-      <c r="J63" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
       </c>
     </row>
   </sheetData>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D516C631-5C41-450D-A3FD-88152FCC19C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF16740D-60A4-4625-90B4-982E96EDAB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="186">
   <si>
     <t>Fecha</t>
   </si>
@@ -273,9 +273,6 @@
     <t>PAZ</t>
   </si>
   <si>
-    <t>Pachuca Brilla</t>
-  </si>
-  <si>
     <t>Feria Pachuca</t>
   </si>
   <si>
@@ -294,270 +291,30 @@
     <t>El Sol de Hidalgo</t>
   </si>
   <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
-    <t>Tren AIFA</t>
-  </si>
-  <si>
-    <t>Xantolo</t>
-  </si>
-  <si>
-    <t>ASEH</t>
-  </si>
-  <si>
     <t>Órgano Interno de Control</t>
   </si>
   <si>
-    <t>Dinámica demográfica</t>
-  </si>
-  <si>
-    <t>Más de cuatro mil divorcios en 2025</t>
-  </si>
-  <si>
-    <t>Piden mejorar condiciones de trabajo</t>
-  </si>
-  <si>
     <t>IMSS</t>
   </si>
   <si>
-    <t>Protesta sindical</t>
-  </si>
-  <si>
-    <t>La Cruz Azul alista producción en Tula</t>
-  </si>
-  <si>
     <t>Cruz Azul</t>
   </si>
   <si>
-    <t>Finaliza huelga del Montepío</t>
-  </si>
-  <si>
-    <t>Presentan Xantolo 2026</t>
-  </si>
-  <si>
-    <t>Pulque eleva su valor</t>
-  </si>
-  <si>
-    <t>Aprueba el IEEH tope de gastos para las precampañas locales</t>
-  </si>
-  <si>
-    <t>Avala Congreso estatal iniciativa de nacionalidad única para Presidente y gobernadores</t>
-  </si>
-  <si>
-    <t>Doble nacionalidad</t>
-  </si>
-  <si>
-    <t>Van 1.5 millones de vacunas contra influenza y Covid-19</t>
-  </si>
-  <si>
-    <t>Vacunación</t>
-  </si>
-  <si>
-    <t>Abre Morena registros para diputaciones</t>
-  </si>
-  <si>
-    <t>Elecciones</t>
-  </si>
-  <si>
-    <t>Destina Semarnat $75 millones para sanear la presa Endhó</t>
-  </si>
-  <si>
     <t>Medio ambiente</t>
   </si>
   <si>
     <t>Presa Endhó</t>
   </si>
   <si>
-    <t>Invitan a 4 días de vivir la fiesta del Xantolo</t>
-  </si>
-  <si>
-    <t>Tuzos perfilan futuro olímpico</t>
-  </si>
-  <si>
-    <t>Listo para su último baile</t>
-  </si>
-  <si>
-    <t>Expropian 98 inmuebles para Tren AIFA-Pachuca</t>
-  </si>
-  <si>
     <t>Sedena</t>
   </si>
   <si>
-    <t>Reconstrucción del bulevar las Torres tiene un avance de 52%</t>
-  </si>
-  <si>
-    <t>Rehabilitación Vial</t>
-  </si>
-  <si>
-    <t>Preparan un Mijkailjuitl con memoria y tradición</t>
-  </si>
-  <si>
-    <t>Protestan contra acuerdo salarial</t>
-  </si>
-  <si>
-    <t>INE Hidalgo prevé la instalación de 4 mil 400 casillas para la próxima jornada</t>
-  </si>
-  <si>
-    <t>Cuesta a hidalguenses más de $120 mil cada resolución del TEEH</t>
-  </si>
-  <si>
-    <t>Resolución de juicio</t>
-  </si>
-  <si>
-    <t>Revisa ASEH recursos en medio de crisis por el OIC</t>
-  </si>
-  <si>
-    <t>Arranca Morena registro; al estado corresponden siete defensores distritales</t>
-  </si>
-  <si>
-    <t>Xantolo: una tradición y espectáculo</t>
-  </si>
-  <si>
-    <t>Captan en imágenes las expresiones culturales</t>
-  </si>
-  <si>
-    <t>Concurso de fotografía</t>
-  </si>
-  <si>
-    <t>Cuenta el estado con más de cinco mil policías</t>
-  </si>
-  <si>
-    <t>Tasa de policías</t>
-  </si>
-  <si>
-    <t>Segob activará el rastreo de personas desaparecidas con 32 centros de mando</t>
-  </si>
-  <si>
-    <t>Gobernación</t>
-  </si>
-  <si>
-    <t>Personas desaparecidas</t>
-  </si>
-  <si>
-    <t>Unidad antisecuestro de la PGJEH consigue sentencias récord</t>
-  </si>
-  <si>
-    <t>UECS</t>
-  </si>
-  <si>
-    <t>Combate Al Secuestro</t>
-  </si>
-  <si>
-    <t>Exportaciones caen 18.7% en segundo trimestre: Mientras en 2025 la entidad obtuvo 811 mil 441 dólares, en 2026 decreció a 659 mil 328</t>
-  </si>
-  <si>
-    <t>Exportaciones</t>
-  </si>
-  <si>
-    <t>Partidos piden piso parejo al arranque del proceso federal</t>
-  </si>
-  <si>
-    <t>Tizayuca cuadruplicó su población; “urge ajustar presupuesto”</t>
-  </si>
-  <si>
-    <t>Envíos al exterior de crudo de Pemex se desploma 45%</t>
-  </si>
-  <si>
-    <t>Pemex</t>
-  </si>
-  <si>
-    <t>Hidalgo necesita planear pensando en dónde vive hoy la gente y en dónde vivirá mañana, no en dónde vivía hace diez años. De lo contrario, el crecimiento seguirá siendo sinónimo de rezago</t>
-  </si>
-  <si>
-    <t>Ordenamiento Territorial</t>
-  </si>
-  <si>
-    <t>Más de 2.5 millones de hidalguenses podrán votar en las elecciones federales de 2027</t>
-  </si>
-  <si>
-    <t>Dota DIFH de reequipamiento a espacios de alimentación para personas vulnerables</t>
-  </si>
-  <si>
-    <t>Espacios de alimentación</t>
-  </si>
-  <si>
-    <t>Invierten 75 mdp en Presa Endhó; Semarnat asegura reducción de 47% del mosco Culex</t>
-  </si>
-  <si>
-    <t>Exigen trabajadores del IMSS Hidalgo insumos y mejores condiciones laborales</t>
-  </si>
-  <si>
-    <t>Cerca de 2.5 millones de hidalguenses podrán votar en 2027</t>
-  </si>
-  <si>
-    <t>Miradas de Hidalgo</t>
-  </si>
-  <si>
-    <t>Freno a doble nacionalidad</t>
-  </si>
-  <si>
-    <t>Rescate de ríos</t>
-  </si>
-  <si>
-    <t>Plan Hídrico</t>
-  </si>
-  <si>
-    <t>INE arranca organización de elección federal en Hidalgo</t>
-  </si>
-  <si>
-    <t>Pachuca tendrá tope de 1.4 millones para precampañas</t>
-  </si>
-  <si>
     <t>Marfeca</t>
   </si>
   <si>
-    <t>Primeros días de feria Pachuca deja 38 detenidos en alcoholímetro</t>
-  </si>
-  <si>
     <t>Cintillo</t>
   </si>
   <si>
-    <t>Capturando Hidalgo 2026 premia con 132  mil pesos trabajo fotográfico de culturas vivas</t>
-  </si>
-  <si>
-    <t>La SCJN falla a favor de La Cruz Azul y protege de forma definitiva su patrimonio</t>
-  </si>
-  <si>
-    <t>Continúa Jorge Reyes impulsando en Pachuca las jornadas gratuitas de esterilización y vacunación antirrábica</t>
-  </si>
-  <si>
-    <t>Campaña de esterilización</t>
-  </si>
-  <si>
-    <t>Arranca jornada de esterilización gratuita</t>
-  </si>
-  <si>
-    <t>Con Claudia Sandoval, Atitalaquia planea y transforma con el corazón por su gente</t>
-  </si>
-  <si>
-    <t>Tlahuelilpan recibe equipamiento del DIFH para Espacios de Alimentación</t>
-  </si>
-  <si>
-    <t>Emprendimiento que florece</t>
-  </si>
-  <si>
-    <t>Apoyo a emprendedores</t>
-  </si>
-  <si>
-    <t>Xantolo 2026: preparan cuatro días de fiesta en Huejutla</t>
-  </si>
-  <si>
-    <t>Beneficia SEPH con apoyos e infraestructura a estudiantes de San Felipe Orizatlán</t>
-  </si>
-  <si>
-    <t>Entrega de infraestructura escolar</t>
-  </si>
-  <si>
-    <t>Continúa Jorge Reyes impulsando jornadas gratuitas de esterilización y vacunación antirrábica</t>
-  </si>
-  <si>
-    <t>Personal del IMSS pide igualdad salarial; se manifiestan en Madero</t>
-  </si>
-  <si>
-    <t>Óscar Maydon y Víctor Mendívil prendieron la Feria de Pachuca</t>
-  </si>
-  <si>
     <t>OEEH</t>
   </si>
   <si>
@@ -570,28 +327,274 @@
     <t>Prevención cáncer de mama</t>
   </si>
   <si>
-    <t>Colectiva arrolla a adulta mayor y choca</t>
-  </si>
-  <si>
-    <t>STCH</t>
-  </si>
-  <si>
-    <t>Accidente transporte público</t>
-  </si>
-  <si>
-    <t>Prohíben la doble nacionalidad para Presidente</t>
-  </si>
-  <si>
-    <t>EE.UU. tiende las redes contra funcionarios mexicanos ligados con los narcos de Sinaloa; muchos seguro ya no comen ni duermen por la preocupación</t>
-  </si>
-  <si>
-    <t>Editorial</t>
-  </si>
-  <si>
-    <t>Intervención extranjera</t>
-  </si>
-  <si>
-    <t>Gobernador pide reforzar seguridad en Feria San Francisco</t>
+    <t>Reconocen a 18 jóvnes del estado</t>
+  </si>
+  <si>
+    <t>Premio Estatal De La Juventud</t>
+  </si>
+  <si>
+    <t>José Alfredo Jiménez, su legado perdura en Hidalgo</t>
+  </si>
+  <si>
+    <t>Arranca la fiesta en honor a San Francisco</t>
+  </si>
+  <si>
+    <t>Feria tradicional</t>
+  </si>
+  <si>
+    <t>Gusano barrenador afecta a 26 personas</t>
+  </si>
+  <si>
+    <t>Gusano barrenador</t>
+  </si>
+  <si>
+    <t>Buscan PES y PAZ alianza en la entidad</t>
+  </si>
+  <si>
+    <t>Alianzas Electorales</t>
+  </si>
+  <si>
+    <t>Incautan arma en secundaria</t>
+  </si>
+  <si>
+    <t>Básica</t>
+  </si>
+  <si>
+    <t>Alumno Armado</t>
+  </si>
+  <si>
+    <t>Reconoce gobernador a jóvenes</t>
+  </si>
+  <si>
+    <t>Ordena Suprema Corte restituir 647 mdp a la Cruz Azul</t>
+  </si>
+  <si>
+    <t>Arranca la Feria tradicional de San Francisco en el centro de Pachuca</t>
+  </si>
+  <si>
+    <t>Ensayo olímpico en la Bella Airosa</t>
+  </si>
+  <si>
+    <t>Del Reloj al Big Ben</t>
+  </si>
+  <si>
+    <t>En una semana, dos presuntos ingresos de armas a escuelas</t>
+  </si>
+  <si>
+    <t>Pide Morena Hidalgo renuncias a aspirantes a cargos de elección</t>
+  </si>
+  <si>
+    <t>Difh entrega tres niños a sus nuevas familias</t>
+  </si>
+  <si>
+    <t>Adopción De Menores</t>
+  </si>
+  <si>
+    <t>Morena deja la puerta abierta a Israel Félix y Shadia Martínez</t>
+  </si>
+  <si>
+    <t>Afiliación Partidista</t>
+  </si>
+  <si>
+    <t>Un secretario estatal podría ir por candidatura para 2027: JMS</t>
+  </si>
+  <si>
+    <t>Candidaturas</t>
+  </si>
+  <si>
+    <t>Vuelve la feria de los pachuqueños</t>
+  </si>
+  <si>
+    <t>Piden partidos respeto al voto, seguridad y austeridad en TEEH</t>
+  </si>
+  <si>
+    <t>Reunión con partidos</t>
+  </si>
+  <si>
+    <t>Entregan el Premio Estatal de la Juventud 2026</t>
+  </si>
+  <si>
+    <t>Joven dona órganos y salva a tres pacientes</t>
+  </si>
+  <si>
+    <t>Donación De Órganos</t>
+  </si>
+  <si>
+    <t>Apuestan por la mediación para la solución de conflictos</t>
+  </si>
+  <si>
+    <t>Mediación</t>
+  </si>
+  <si>
+    <t>Cementos Cruz Azul:  SCJN blinda patrimonio e impide pago de 1,600 mdp</t>
+  </si>
+  <si>
+    <t>EL pacto sobre autorregulación de la IA, a debate</t>
+  </si>
+  <si>
+    <t>Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>"Todo está armado", yo solo soy accionista de la empresa: Ernesto Ruffo</t>
+  </si>
+  <si>
+    <t>Combate Al Huachicol</t>
+  </si>
+  <si>
+    <t>Contabilizan 5 millones de ciberataques sobre la Corte</t>
+  </si>
+  <si>
+    <t>Hackeo</t>
+  </si>
+  <si>
+    <t>Llaman a valorar el legado de las fuerzas armadas</t>
+  </si>
+  <si>
+    <t>Conmemoración Aniversario</t>
+  </si>
+  <si>
+    <t>Aprobación presidenta Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>Aprobación Sheinbaum</t>
+  </si>
+  <si>
+    <t>Cierra Sheinbaum su segundo año con aprobación de 70.3%</t>
+  </si>
+  <si>
+    <t>Hoy Morena enfrenta retos internos, como el de ordenar sus estructuras, contener  fricciones entre corrientes y con los partidos aliados, además de sacudirse los  señalamientos de la oposición”.</t>
+  </si>
+  <si>
+    <t>Trabajo partidista</t>
+  </si>
+  <si>
+    <t>Invierten 6.2 mdp en programas para jóvenes</t>
+  </si>
+  <si>
+    <t>Violencia sacude secundarias; muere subdirectora en Torreón</t>
+  </si>
+  <si>
+    <t>DIFH concreta 61 adopciones en cuatro años; 16 adolescentes en espera</t>
+  </si>
+  <si>
+    <t>Menchaca confirma que un integrante de su gabinete analiza contender en las elecciones 2027</t>
+  </si>
+  <si>
+    <t>Arranca en pachuca la tradicional Feria de San Francisco</t>
+  </si>
+  <si>
+    <t>Reconocen a 18 jóvenes con el Premio Estatal de la Juventud</t>
+  </si>
+  <si>
+    <t>Morena exige a Viggiano aclarar venta de terreno por 17.9 millones</t>
+  </si>
+  <si>
+    <t>Viggiano</t>
+  </si>
+  <si>
+    <t>Enriquecimiento ilícito</t>
+  </si>
+  <si>
+    <t>Hidalgo refuerza vigilancia por enfermedades respiratorias</t>
+  </si>
+  <si>
+    <t>titular</t>
+  </si>
+  <si>
+    <t>Vigilancia Epidemiológica</t>
+  </si>
+  <si>
+    <t>Genio en el Conalep</t>
+  </si>
+  <si>
+    <t>Media superior</t>
+  </si>
+  <si>
+    <t>Innovación tecnológica</t>
+  </si>
+  <si>
+    <t>Tula estrena C2 con inteligencia artificial</t>
+  </si>
+  <si>
+    <t>Videovigilancia</t>
+  </si>
+  <si>
+    <t>Congreso analiza nueva ruta para contralor del TEEH</t>
+  </si>
+  <si>
+    <t>Alcaldesa de Tepetitlán acusa falta de avances en Endhó</t>
+  </si>
+  <si>
+    <t>Preparan agua y transporte para viviendas del Bienestar en Hidalgo</t>
+  </si>
+  <si>
+    <t>Plan Nacional De Vivienda</t>
+  </si>
+  <si>
+    <t>Menchaca Salazar respalda transformación de juventud hidalguense</t>
+  </si>
+  <si>
+    <t>Tula da un paso histórico en seguridad con la puesta en operación de su Centro de Control y Comando</t>
+  </si>
+  <si>
+    <t>Con inversión superior a 3 mdp, Atotonilco fortalece infraestructura de la Unidad Médica Integra</t>
+  </si>
+  <si>
+    <t>Refuerzan seguridad para la Feria San Francisco Tlahuelilpan 2026 con coordinación entre Estado y Municipio</t>
+  </si>
+  <si>
+    <t>Policía municipal</t>
+  </si>
+  <si>
+    <t>61 familias hidalguenses cruzaron el Puente de Amor para brindar un hogar a niñas, niños y adolescentes en Hidalgo</t>
+  </si>
+  <si>
+    <t>Zitlaly Zúñiga impulsa nuevos espacios para el bienestar de los adultos mayores de Ajacuba</t>
+  </si>
+  <si>
+    <t>Atención a adultos mayores</t>
+  </si>
+  <si>
+    <t>¿Tu negocio crece, pero tu contabilidad no te sigue el ritmo?</t>
+  </si>
+  <si>
+    <t>otor</t>
+  </si>
+  <si>
+    <t>Publicidad comercial</t>
+  </si>
+  <si>
+    <t>Jorge Reyes inaugura la feria tradicional de San Francisco</t>
+  </si>
+  <si>
+    <t>Alex Lora y El Tri rockean a lo grande en teatro del Pueblo</t>
+  </si>
+  <si>
+    <t>DIF Pachuca abre registro para jornada de mastografías gratuitas</t>
+  </si>
+  <si>
+    <t>Julio Menchaca respalda transformación de juventud hidalguense</t>
+  </si>
+  <si>
+    <t>María José arrasa en el Palenque 2026</t>
+  </si>
+  <si>
+    <t>Funcionarios estatales ""analizan"" participar en las elecciones de 2027</t>
+  </si>
+  <si>
+    <t>Huracán Rachel gana fuerza y alcanza categoría 3</t>
+  </si>
+  <si>
+    <t>Alerta Meteorológica</t>
+  </si>
+  <si>
+    <t>Cuatro Tuzas al Tri Femenil</t>
+  </si>
+  <si>
+    <t>Entregan Premio Estatal de la Juventud 2026</t>
+  </si>
+  <si>
+    <t>Ejidatarios exigen participación en Festival de Flores</t>
   </si>
 </sst>
 </file>
@@ -1257,66 +1260,66 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1325,195 +1328,195 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="G7" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -1529,168 +1532,168 @@
     </row>
     <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J11" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J12" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J13" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B14" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="C14" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
         <v>18</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F14" t="s">
         <v>18</v>
       </c>
-      <c r="G11" t="s">
-        <v>106</v>
-      </c>
-      <c r="H11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" t="str">
+      <c r="G14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Partidos</v>
-      </c>
-      <c r="J11" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
-        <v>46296</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" t="s">
-        <v>108</v>
-      </c>
-      <c r="G12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" t="s">
-        <v>72</v>
-      </c>
-      <c r="I12" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J12" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <v>46296</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J13" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <v>46296</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1699,66 +1702,66 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="H15" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>114</v>
+        <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Partidos</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1767,25 +1770,25 @@
     </row>
     <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
@@ -1796,166 +1799,166 @@
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B18" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G20" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="H20" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B21" t="s">
         <v>75</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="G21" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H21" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B22" t="s">
         <v>75</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="F22" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="G22" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
@@ -1971,32 +1974,32 @@
     </row>
     <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B23" t="s">
         <v>75</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2005,115 +2008,115 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B24" t="s">
         <v>75</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B25" t="s">
         <v>75</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H25" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B26" t="s">
         <v>75</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="H26" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B27" t="s">
         <v>75</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
@@ -2122,13 +2125,13 @@
         <v>14</v>
       </c>
       <c r="F27" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2139,151 +2142,151 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F28" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H28" t="s">
         <v>72</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J28" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>139</v>
+      </c>
+      <c r="H29" t="s">
+        <v>72</v>
+      </c>
+      <c r="I29" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J29" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>142</v>
+      </c>
+      <c r="H30" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J30" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B31" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J28" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="11">
-        <v>46296</v>
-      </c>
-      <c r="B29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D29" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" t="s">
-        <v>54</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29" t="s">
-        <v>136</v>
-      </c>
-      <c r="H29" t="s">
-        <v>68</v>
-      </c>
-      <c r="I29" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J29" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="11">
-        <v>46296</v>
-      </c>
-      <c r="B30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D30" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" t="s">
-        <v>42</v>
-      </c>
-      <c r="H30" t="s">
-        <v>11</v>
-      </c>
-      <c r="I30" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J30" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="11">
-        <v>46296</v>
-      </c>
-      <c r="B31" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" t="s">
-        <v>90</v>
-      </c>
-      <c r="H31" t="s">
-        <v>11</v>
-      </c>
-      <c r="I31" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D32" t="s">
         <v>12</v>
@@ -2292,10 +2295,10 @@
         <v>14</v>
       </c>
       <c r="F32" t="s">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="H32" t="s">
         <v>68</v>
@@ -2309,30 +2312,30 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="H33" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2345,134 +2348,134 @@
     </row>
     <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B34" t="s">
         <v>74</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G34" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
       </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B35" t="s">
         <v>74</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F35" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B36" t="s">
         <v>74</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D36" t="s">
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F36" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="G36" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="H36" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="F37" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="G37" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="H37" t="s">
         <v>68</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Sucesión gubernamental</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2481,59 +2484,59 @@
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B38" t="s">
         <v>73</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>153</v>
       </c>
       <c r="G38" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B39" t="s">
         <v>73</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>28</v>
+        <v>156</v>
       </c>
       <c r="G39" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="H39" t="s">
         <v>72</v>
@@ -2549,32 +2552,32 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B40" t="s">
         <v>73</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="H40" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2583,32 +2586,32 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B41" t="s">
         <v>73</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D41" t="s">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G41" t="s">
-        <v>152</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2617,32 +2620,32 @@
     </row>
     <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B42" t="s">
         <v>73</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="G42" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2651,32 +2654,32 @@
     </row>
     <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D43" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="E43" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F43" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>42</v>
+        <v>163</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2685,100 +2688,100 @@
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B44" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D44" t="s">
-        <v>157</v>
+        <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G44" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B45" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B46" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2787,13 +2790,13 @@
     </row>
     <row r="47" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B47" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
@@ -2802,10 +2805,10 @@
         <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="G47" t="s">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
@@ -2819,49 +2822,49 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B48" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D48" t="s">
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G48" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="H48" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B49" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
@@ -2870,10 +2873,10 @@
         <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="G49" t="s">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -2889,93 +2892,93 @@
     </row>
     <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B50" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D50" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="E50" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>2</v>
+        <v>173</v>
       </c>
       <c r="G50" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B51" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D51" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="G51" t="s">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B52" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52" t="s">
+        <v>92</v>
+      </c>
+      <c r="G52" t="s">
         <v>78</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D52" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" t="s">
-        <v>28</v>
-      </c>
-      <c r="F52" t="s">
-        <v>28</v>
-      </c>
-      <c r="G52" t="s">
-        <v>87</v>
       </c>
       <c r="H52" t="s">
         <v>72</v>
@@ -2991,127 +2994,127 @@
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="D53" t="s">
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>169</v>
+        <v>95</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B54" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
+        <v>24</v>
+      </c>
+      <c r="F54" t="s">
+        <v>24</v>
+      </c>
+      <c r="G54" t="s">
+        <v>97</v>
+      </c>
+      <c r="H54" t="s">
+        <v>11</v>
+      </c>
+      <c r="I54" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J54" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B55" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" t="s">
+        <v>29</v>
+      </c>
+      <c r="F55" t="s">
+        <v>92</v>
+      </c>
+      <c r="G55" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D54" t="s">
-        <v>12</v>
-      </c>
-      <c r="E54" t="s">
-        <v>16</v>
-      </c>
-      <c r="F54" t="s">
-        <v>76</v>
-      </c>
-      <c r="G54" t="s">
-        <v>161</v>
-      </c>
-      <c r="H54" t="s">
-        <v>11</v>
-      </c>
-      <c r="I54" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J54" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="11">
-        <v>46296</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="H55" t="s">
+        <v>72</v>
+      </c>
+      <c r="I55" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J55" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B56" t="s">
+        <v>90</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D56" t="s">
+        <v>82</v>
+      </c>
+      <c r="E56" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" t="s">
         <v>78</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D55" t="s">
-        <v>12</v>
-      </c>
-      <c r="E55" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55" t="s">
-        <v>93</v>
-      </c>
-      <c r="G55" t="s">
-        <v>94</v>
-      </c>
-      <c r="H55" t="s">
-        <v>68</v>
-      </c>
-      <c r="I55" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J55" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="11">
-        <v>46296</v>
-      </c>
-      <c r="B56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D56" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" t="s">
-        <v>29</v>
-      </c>
-      <c r="F56" t="s">
-        <v>173</v>
-      </c>
-      <c r="G56" t="s">
-        <v>79</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
@@ -3127,206 +3130,206 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>174</v>
+        <v>94</v>
       </c>
       <c r="D57" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E57" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G57" t="s">
+        <v>95</v>
+      </c>
+      <c r="H57" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J57" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B58" t="s">
         <v>79</v>
       </c>
-      <c r="H57" t="s">
-        <v>11</v>
-      </c>
-      <c r="I57" t="str">
+      <c r="C58" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>24</v>
+      </c>
+      <c r="F58" t="s">
+        <v>24</v>
+      </c>
+      <c r="G58" t="s">
+        <v>61</v>
+      </c>
+      <c r="H58" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J57" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="11">
-        <v>46296</v>
-      </c>
-      <c r="B58" t="s">
-        <v>78</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D58" t="s">
-        <v>83</v>
-      </c>
-      <c r="E58" t="s">
-        <v>16</v>
-      </c>
-      <c r="F58" t="s">
-        <v>16</v>
-      </c>
-      <c r="G58" t="s">
-        <v>176</v>
-      </c>
-      <c r="H58" t="s">
-        <v>11</v>
-      </c>
-      <c r="I58" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
       <c r="J58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B59" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F59" t="s">
-        <v>178</v>
+        <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H59" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B60" t="s">
+        <v>79</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" t="s">
+        <v>70</v>
+      </c>
+      <c r="H60" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B61" t="s">
+        <v>79</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>24</v>
+      </c>
+      <c r="F61" t="s">
+        <v>24</v>
+      </c>
+      <c r="G61" t="s">
+        <v>97</v>
+      </c>
+      <c r="H61" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B62" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" t="s">
         <v>80</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D60" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" t="s">
-        <v>14</v>
-      </c>
-      <c r="F60" t="s">
-        <v>14</v>
-      </c>
-      <c r="G60" t="s">
-        <v>102</v>
-      </c>
-      <c r="H60" t="s">
-        <v>72</v>
-      </c>
-      <c r="I60" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J60" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A61" s="11">
-        <v>46296</v>
-      </c>
-      <c r="B61" t="s">
-        <v>80</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D61" t="s">
-        <v>182</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" t="s">
-        <v>183</v>
-      </c>
-      <c r="H61" t="s">
-        <v>68</v>
-      </c>
-      <c r="I61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="11">
-        <v>46296</v>
-      </c>
-      <c r="B62" t="s">
-        <v>80</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D62" t="s">
-        <v>12</v>
-      </c>
-      <c r="E62" t="s">
-        <v>24</v>
-      </c>
-      <c r="F62" t="s">
-        <v>24</v>
-      </c>
-      <c r="G62" t="s">
-        <v>79</v>
-      </c>
       <c r="H62" t="s">
         <v>11</v>
       </c>
       <c r="I62" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J62" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
   </sheetData>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF16740D-60A4-4625-90B4-982E96EDAB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78933FF-5FBC-4D18-AA38-B87100F57C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="196">
   <si>
     <t>Fecha</t>
   </si>
@@ -291,24 +291,6 @@
     <t>El Sol de Hidalgo</t>
   </si>
   <si>
-    <t>Órgano Interno de Control</t>
-  </si>
-  <si>
-    <t>IMSS</t>
-  </si>
-  <si>
-    <t>Cruz Azul</t>
-  </si>
-  <si>
-    <t>Medio ambiente</t>
-  </si>
-  <si>
-    <t>Presa Endhó</t>
-  </si>
-  <si>
-    <t>Sedena</t>
-  </si>
-  <si>
     <t>Marfeca</t>
   </si>
   <si>
@@ -318,283 +300,331 @@
     <t>OEEH</t>
   </si>
   <si>
-    <t>Haz una parada diferente</t>
-  </si>
-  <si>
     <t>Recuerda: la detección temprana salva vidas</t>
   </si>
   <si>
     <t>Prevención cáncer de mama</t>
   </si>
   <si>
-    <t>Reconocen a 18 jóvnes del estado</t>
-  </si>
-  <si>
-    <t>Premio Estatal De La Juventud</t>
-  </si>
-  <si>
-    <t>José Alfredo Jiménez, su legado perdura en Hidalgo</t>
-  </si>
-  <si>
-    <t>Arranca la fiesta en honor a San Francisco</t>
-  </si>
-  <si>
-    <t>Feria tradicional</t>
-  </si>
-  <si>
-    <t>Gusano barrenador afecta a 26 personas</t>
-  </si>
-  <si>
-    <t>Gusano barrenador</t>
-  </si>
-  <si>
-    <t>Buscan PES y PAZ alianza en la entidad</t>
-  </si>
-  <si>
     <t>Alianzas Electorales</t>
   </si>
   <si>
-    <t>Incautan arma en secundaria</t>
-  </si>
-  <si>
-    <t>Básica</t>
-  </si>
-  <si>
-    <t>Alumno Armado</t>
-  </si>
-  <si>
-    <t>Reconoce gobernador a jóvenes</t>
-  </si>
-  <si>
-    <t>Ordena Suprema Corte restituir 647 mdp a la Cruz Azul</t>
-  </si>
-  <si>
-    <t>Arranca la Feria tradicional de San Francisco en el centro de Pachuca</t>
-  </si>
-  <si>
-    <t>Ensayo olímpico en la Bella Airosa</t>
-  </si>
-  <si>
-    <t>Del Reloj al Big Ben</t>
-  </si>
-  <si>
-    <t>En una semana, dos presuntos ingresos de armas a escuelas</t>
-  </si>
-  <si>
-    <t>Pide Morena Hidalgo renuncias a aspirantes a cargos de elección</t>
-  </si>
-  <si>
-    <t>Difh entrega tres niños a sus nuevas familias</t>
-  </si>
-  <si>
-    <t>Adopción De Menores</t>
-  </si>
-  <si>
-    <t>Morena deja la puerta abierta a Israel Félix y Shadia Martínez</t>
-  </si>
-  <si>
-    <t>Afiliación Partidista</t>
-  </si>
-  <si>
-    <t>Un secretario estatal podría ir por candidatura para 2027: JMS</t>
-  </si>
-  <si>
-    <t>Candidaturas</t>
-  </si>
-  <si>
-    <t>Vuelve la feria de los pachuqueños</t>
-  </si>
-  <si>
-    <t>Piden partidos respeto al voto, seguridad y austeridad en TEEH</t>
-  </si>
-  <si>
-    <t>Reunión con partidos</t>
-  </si>
-  <si>
-    <t>Entregan el Premio Estatal de la Juventud 2026</t>
-  </si>
-  <si>
-    <t>Joven dona órganos y salva a tres pacientes</t>
-  </si>
-  <si>
-    <t>Donación De Órganos</t>
-  </si>
-  <si>
-    <t>Apuestan por la mediación para la solución de conflictos</t>
-  </si>
-  <si>
-    <t>Mediación</t>
-  </si>
-  <si>
-    <t>Cementos Cruz Azul:  SCJN blinda patrimonio e impide pago de 1,600 mdp</t>
-  </si>
-  <si>
-    <t>EL pacto sobre autorregulación de la IA, a debate</t>
-  </si>
-  <si>
-    <t>Inteligencia Artificial</t>
-  </si>
-  <si>
-    <t>"Todo está armado", yo solo soy accionista de la empresa: Ernesto Ruffo</t>
-  </si>
-  <si>
-    <t>Combate Al Huachicol</t>
-  </si>
-  <si>
-    <t>Contabilizan 5 millones de ciberataques sobre la Corte</t>
-  </si>
-  <si>
-    <t>Hackeo</t>
-  </si>
-  <si>
-    <t>Llaman a valorar el legado de las fuerzas armadas</t>
-  </si>
-  <si>
     <t>Conmemoración Aniversario</t>
   </si>
   <si>
-    <t>Aprobación presidenta Claudia Sheinbaum</t>
-  </si>
-  <si>
-    <t>Aprobación Sheinbaum</t>
-  </si>
-  <si>
-    <t>Cierra Sheinbaum su segundo año con aprobación de 70.3%</t>
-  </si>
-  <si>
-    <t>Hoy Morena enfrenta retos internos, como el de ordenar sus estructuras, contener  fricciones entre corrientes y con los partidos aliados, además de sacudirse los  señalamientos de la oposición”.</t>
-  </si>
-  <si>
-    <t>Trabajo partidista</t>
-  </si>
-  <si>
-    <t>Invierten 6.2 mdp en programas para jóvenes</t>
-  </si>
-  <si>
-    <t>Violencia sacude secundarias; muere subdirectora en Torreón</t>
-  </si>
-  <si>
-    <t>DIFH concreta 61 adopciones en cuatro años; 16 adolescentes en espera</t>
-  </si>
-  <si>
-    <t>Menchaca confirma que un integrante de su gabinete analiza contender en las elecciones 2027</t>
-  </si>
-  <si>
-    <t>Arranca en pachuca la tradicional Feria de San Francisco</t>
-  </si>
-  <si>
-    <t>Reconocen a 18 jóvenes con el Premio Estatal de la Juventud</t>
-  </si>
-  <si>
-    <t>Morena exige a Viggiano aclarar venta de terreno por 17.9 millones</t>
-  </si>
-  <si>
-    <t>Viggiano</t>
-  </si>
-  <si>
     <t>Enriquecimiento ilícito</t>
   </si>
   <si>
-    <t>Hidalgo refuerza vigilancia por enfermedades respiratorias</t>
-  </si>
-  <si>
-    <t>titular</t>
-  </si>
-  <si>
-    <t>Vigilancia Epidemiológica</t>
-  </si>
-  <si>
-    <t>Genio en el Conalep</t>
-  </si>
-  <si>
-    <t>Media superior</t>
-  </si>
-  <si>
     <t>Innovación tecnológica</t>
   </si>
   <si>
-    <t>Tula estrena C2 con inteligencia artificial</t>
-  </si>
-  <si>
-    <t>Videovigilancia</t>
-  </si>
-  <si>
-    <t>Congreso analiza nueva ruta para contralor del TEEH</t>
-  </si>
-  <si>
-    <t>Alcaldesa de Tepetitlán acusa falta de avances en Endhó</t>
-  </si>
-  <si>
-    <t>Preparan agua y transporte para viviendas del Bienestar en Hidalgo</t>
-  </si>
-  <si>
-    <t>Plan Nacional De Vivienda</t>
-  </si>
-  <si>
-    <t>Menchaca Salazar respalda transformación de juventud hidalguense</t>
-  </si>
-  <si>
-    <t>Tula da un paso histórico en seguridad con la puesta en operación de su Centro de Control y Comando</t>
-  </si>
-  <si>
-    <t>Con inversión superior a 3 mdp, Atotonilco fortalece infraestructura de la Unidad Médica Integra</t>
-  </si>
-  <si>
-    <t>Refuerzan seguridad para la Feria San Francisco Tlahuelilpan 2026 con coordinación entre Estado y Municipio</t>
-  </si>
-  <si>
     <t>Policía municipal</t>
   </si>
   <si>
-    <t>61 familias hidalguenses cruzaron el Puente de Amor para brindar un hogar a niñas, niños y adolescentes en Hidalgo</t>
-  </si>
-  <si>
-    <t>Zitlaly Zúñiga impulsa nuevos espacios para el bienestar de los adultos mayores de Ajacuba</t>
-  </si>
-  <si>
-    <t>Atención a adultos mayores</t>
-  </si>
-  <si>
-    <t>¿Tu negocio crece, pero tu contabilidad no te sigue el ritmo?</t>
-  </si>
-  <si>
-    <t>otor</t>
-  </si>
-  <si>
-    <t>Publicidad comercial</t>
-  </si>
-  <si>
-    <t>Jorge Reyes inaugura la feria tradicional de San Francisco</t>
-  </si>
-  <si>
-    <t>Alex Lora y El Tri rockean a lo grande en teatro del Pueblo</t>
-  </si>
-  <si>
-    <t>DIF Pachuca abre registro para jornada de mastografías gratuitas</t>
-  </si>
-  <si>
-    <t>Julio Menchaca respalda transformación de juventud hidalguense</t>
-  </si>
-  <si>
-    <t>María José arrasa en el Palenque 2026</t>
-  </si>
-  <si>
-    <t>Funcionarios estatales ""analizan"" participar en las elecciones de 2027</t>
-  </si>
-  <si>
-    <t>Huracán Rachel gana fuerza y alcanza categoría 3</t>
-  </si>
-  <si>
     <t>Alerta Meteorológica</t>
   </si>
   <si>
-    <t>Cuatro Tuzas al Tri Femenil</t>
-  </si>
-  <si>
-    <t>Entregan Premio Estatal de la Juventud 2026</t>
-  </si>
-  <si>
-    <t>Ejidatarios exigen participación en Festival de Flores</t>
+    <t>Definirán a coordinadores rumbo a 2027</t>
+  </si>
+  <si>
+    <t>Celebran a San Francisco en Pachuca</t>
+  </si>
+  <si>
+    <t>Fiesta patronal</t>
+  </si>
+  <si>
+    <t>Concurrido Festival del Pulque y Maíz</t>
+  </si>
+  <si>
+    <t>Festival Gastronómico</t>
+  </si>
+  <si>
+    <t>Aumentan delitos de violencia familiar</t>
+  </si>
+  <si>
+    <t>Violencia familiar</t>
+  </si>
+  <si>
+    <t>Salario mínimo no cubre costo de vida</t>
+  </si>
+  <si>
+    <t>Pobreza laboral</t>
+  </si>
+  <si>
+    <t>Ferias son el sustento de los comerciantes</t>
+  </si>
+  <si>
+    <t>Más de dos mil pesos para armar un disfraz</t>
+  </si>
+  <si>
+    <t>Lluvias dejan vías cerradas y dos heridos</t>
+  </si>
+  <si>
+    <t>Afectaciones Por Lluvias</t>
+  </si>
+  <si>
+    <t>Reactiva Tribunal Colegiado proceso contra Sosa</t>
+  </si>
+  <si>
+    <t>Grupo Universidad</t>
+  </si>
+  <si>
+    <t>Más de 30 se registran por coordinaciones de Morena</t>
+  </si>
+  <si>
+    <t>El Xantolo, una herencia de familia</t>
+  </si>
+  <si>
+    <t>Xantolo</t>
+  </si>
+  <si>
+    <t>Destaca Sheinbaum a las fuerzas armadas</t>
+  </si>
+  <si>
+    <t>Toluca amarga debut de Tomé</t>
+  </si>
+  <si>
+    <t>Por título en paralimpiada</t>
+  </si>
+  <si>
+    <t>Inhide</t>
+  </si>
+  <si>
+    <t>Paranacionales Conade</t>
+  </si>
+  <si>
+    <t>Gabinete de Menchaca ha cambiado 13 veces</t>
+  </si>
+  <si>
+    <t>Cambios En El Gabinete</t>
+  </si>
+  <si>
+    <t>Se reportaron en septiembre 34 personas desaparecidas</t>
+  </si>
+  <si>
+    <t>CBPEH</t>
+  </si>
+  <si>
+    <t>Personas desaparecidas</t>
+  </si>
+  <si>
+    <t>Celebra el partido guinda un húmedo XV aniversario</t>
+  </si>
+  <si>
+    <t>Confirma PAZ y PES en Hidalgo la conformación de alianza para 2027</t>
+  </si>
+  <si>
+    <t>Anticipa Rico Mercado más renuncias de funcionarios</t>
+  </si>
+  <si>
+    <t>La 4T perfila a casi una veintena para 7 coordinaciones distritales</t>
+  </si>
+  <si>
+    <t>Busca Miguel Tello coordinar el Ditrito seis</t>
+  </si>
+  <si>
+    <t>Extitular</t>
+  </si>
+  <si>
+    <t>Asociación de Alcaldes pugna por entrega clara</t>
+  </si>
+  <si>
+    <t>Asociación de Alcaldes</t>
+  </si>
+  <si>
+    <t>Nueve de cada diez imputados son vinculados a proceso: Inegi</t>
+  </si>
+  <si>
+    <t>Vinculación A Proceso</t>
+  </si>
+  <si>
+    <t>En 2025 registró el estado 497 víctimas de homicidio</t>
+  </si>
+  <si>
+    <t>Homicidios</t>
+  </si>
+  <si>
+    <t>Declara Protección Civil alerta amarilla en el estado</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Niegan un amparo a Sosa Castelán y reactivan juicio por lavado de dinero</t>
+  </si>
+  <si>
+    <t>Readme, la app de las "citas de amor" entre lectores y libros</t>
+  </si>
+  <si>
+    <t>Bolsonaro sacude a Lula y van a segunda vuelta</t>
+  </si>
+  <si>
+    <t>Temas internacionales</t>
+  </si>
+  <si>
+    <t>Orden a fuerzas armadas para reprimir, nunca</t>
+  </si>
+  <si>
+    <t>Destinan 499.8 mdp para encauzar el Río de las Avenidas</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Rehabilitación Vial</t>
+  </si>
+  <si>
+    <t>Dirigente morenista desconoce estatus de proceso para diputaciones</t>
+  </si>
+  <si>
+    <t>Bolsonaro junior manda a Lula a segunda vuelta</t>
+  </si>
+  <si>
+    <t>Trabajan para reparar puente en Tepehuacán</t>
+  </si>
+  <si>
+    <t>Atención Afectaciones Por Lluvias</t>
+  </si>
+  <si>
+    <t>La amenaza ya no necesita una estructura criminal tradicional. No requiere jerarquías,  territorios ni financiamiento sofisticado. Puede bastar un teléfono, aislamiento,  resentimiento acumulado y una red de espacios virtuales que refuercen de forma  constante narrativas de victimización y agravios compartidos”.</t>
+  </si>
+  <si>
+    <t>Lluvias provocan daños en más de 10 municipios de Hidalgo</t>
+  </si>
+  <si>
+    <t>Nueve de cada 10 imputados por la PGJEH fueron vinculados a proceso</t>
+  </si>
+  <si>
+    <t>Morena Hidalgo conmemora 15 años; llama a la unidad rumbo a 2027</t>
+  </si>
+  <si>
+    <t>Sancionan al 80% de los notarios públicos en Hidlago al inicio de la administración</t>
+  </si>
+  <si>
+    <t>Rojo busca frente opositor para 2028</t>
+  </si>
+  <si>
+    <t>Lluvias provocan deslaves y cierres carreteros</t>
+  </si>
+  <si>
+    <t>Cinco notarios de Hidalgo enfrentan procedimientos</t>
+  </si>
+  <si>
+    <t>PAZ cofirma alianza con PES rumbo a 2027</t>
+  </si>
+  <si>
+    <t>Defender a Viggiano siempre ha sido su papel""</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>Susana y Tania confirman registro en Morena</t>
+  </si>
+  <si>
+    <t>Alertan nuevamente por fuertes lluvias en Hidalgo</t>
+  </si>
+  <si>
+    <t>Mantienen Protección Civil atención y monitoreo por lluvias</t>
+  </si>
+  <si>
+    <t>informa</t>
+  </si>
+  <si>
+    <t>Más de 6.6 mdp fortalecen la productividad del campo de 8 municipios</t>
+  </si>
+  <si>
+    <t>Entrega De Apoyos</t>
+  </si>
+  <si>
+    <t>Lety Reyes inaugura la Expo Feria Tlahuelilpan 2026</t>
+  </si>
+  <si>
+    <t>alcal</t>
+  </si>
+  <si>
+    <t>Expo feria</t>
+  </si>
+  <si>
+    <t>Zitlaly entrega material para mejorar la infraestructura vial en Rincón Norte de Tecomatlán</t>
+  </si>
+  <si>
+    <t>Infraestructura vial</t>
+  </si>
+  <si>
+    <t>Estudiantes de la UTVM participan en Master Class de Gastronomía</t>
+  </si>
+  <si>
+    <t>Universidades</t>
+  </si>
+  <si>
+    <t>Encuentro académico</t>
+  </si>
+  <si>
+    <t>Refuerzan inclusión en la Feria de San Francisco Pachuca 2026</t>
+  </si>
+  <si>
+    <t>ITESA desarrolla herramienta para mejorar el bienestar laboral en empresas</t>
+  </si>
+  <si>
+    <t>Caravana Cultural llevará siete presentaciones de música y danza en Tlahuelilpan</t>
+  </si>
+  <si>
+    <t>Caravanas Culturales</t>
+  </si>
+  <si>
+    <t>Realizan trabajos para habilitar puente en la comunidad de Tamada</t>
+  </si>
+  <si>
+    <t>Emprendimiento que fortalece</t>
+  </si>
+  <si>
+    <t>Apoyo a emprendedores</t>
+  </si>
+  <si>
+    <t>Pachuca Brilla</t>
+  </si>
+  <si>
+    <t>Lluvias dejan estragos en regiones de Hidalgo</t>
+  </si>
+  <si>
+    <t>Horóscopos pusieron el duranguense en el Palenque</t>
+  </si>
+  <si>
+    <t>Costeño, Norteño y Teo hicieron reír a la feria</t>
+  </si>
+  <si>
+    <t>Desmantelan puntos de narcomenudeo en Pachuca y Tizayuca</t>
+  </si>
+  <si>
+    <t>Combate Al Narcomenudeo</t>
+  </si>
+  <si>
+    <t>SEPH promueve bienestar animal con caminata ""Dejando Huella""</t>
+  </si>
+  <si>
+    <t>Croquetón</t>
+  </si>
+  <si>
+    <t>Tradición que sorprende</t>
+  </si>
+  <si>
+    <t>Comparecerán 17 funcionarios por cuarto informe de gobierno</t>
+  </si>
+  <si>
+    <t>Comparecencias</t>
+  </si>
+  <si>
+    <t>Un total de 12 municipios afectados por las lluvias de ayer</t>
+  </si>
+  <si>
+    <t>Como decían en otros  tiempos, la caballada está  flaca entre los suspirantes  a puestos de  elección popular,  de todos  los partidos  políticos…</t>
+  </si>
+  <si>
+    <t>La SSPH desarticuló tres puntos de venta de drogas</t>
+  </si>
+  <si>
+    <t>Bolsonaro y Lula irán a segunda vuelta en Brasil</t>
   </si>
 </sst>
 </file>
@@ -841,8 +871,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J62" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J62" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J68" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J68" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1211,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1260,47 +1290,47 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B2" t="s">
         <v>83</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B3" t="s">
         <v>83</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -1312,7 +1342,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -1328,32 +1358,32 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B4" t="s">
         <v>83</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
         <v>99</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" t="s">
-        <v>100</v>
-      </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1362,96 +1392,96 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B5" t="s">
         <v>83</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
         <v>101</v>
       </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" t="s">
-        <v>102</v>
-      </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" t="s">
         <v>103</v>
       </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" t="s">
-        <v>104</v>
-      </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="G7" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1464,93 +1494,93 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="G9" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
@@ -1566,32 +1596,32 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1600,13 +1630,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
@@ -1618,7 +1648,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
@@ -1632,68 +1662,68 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>113</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
       </c>
       <c r="I14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1702,7 +1732,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
@@ -1711,19 +1741,19 @@
         <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="G15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1734,64 +1764,64 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="G16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="G17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H17" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1799,37 +1829,37 @@
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B18" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Partidos</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1838,109 +1868,109 @@
     </row>
     <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="G19" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="H20" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B21" t="s">
         <v>75</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="G21" t="s">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Partidos</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B22" t="s">
         <v>75</v>
@@ -1952,29 +1982,29 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="G22" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
       </c>
       <c r="I22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B23" t="s">
         <v>75</v>
@@ -1992,10 +2022,10 @@
         <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2006,216 +2036,216 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B24" t="s">
         <v>75</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B25" t="s">
         <v>75</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H25" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B26" t="s">
         <v>75</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="G26" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B27" t="s">
         <v>75</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="F27" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G27" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>138</v>
       </c>
       <c r="D28" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G28" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J28" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="H28" t="s">
-        <v>72</v>
-      </c>
-      <c r="I28" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J28" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="11">
-        <v>46297</v>
-      </c>
-      <c r="B29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" t="s">
         <v>140</v>
       </c>
-      <c r="D29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" t="s">
-        <v>139</v>
-      </c>
       <c r="H29" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>141</v>
@@ -2224,47 +2254,47 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B31" t="s">
         <v>81</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
         <v>143</v>
       </c>
-      <c r="D31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" t="s">
-        <v>24</v>
-      </c>
       <c r="F31" t="s">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="G31" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
@@ -2275,139 +2305,139 @@
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B32" t="s">
         <v>81</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D32" t="s">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="H32" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J32" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" t="s">
+        <v>140</v>
+      </c>
+      <c r="H33" t="s">
         <v>68</v>
       </c>
-      <c r="I32" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J32" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
-        <v>46297</v>
-      </c>
-      <c r="B33" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G33" t="s">
-        <v>116</v>
-      </c>
-      <c r="H33" t="s">
-        <v>72</v>
-      </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J33" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B34" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s">
+        <v>143</v>
+      </c>
+      <c r="F34" t="s">
+        <v>143</v>
+      </c>
+      <c r="G34" t="s">
+        <v>148</v>
+      </c>
+      <c r="H34" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J33" t="str">
+      <c r="J34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="11">
-        <v>46297</v>
-      </c>
-      <c r="B34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34" t="s">
-        <v>61</v>
-      </c>
-      <c r="H34" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J34" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G35" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2416,25 +2446,25 @@
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B36" t="s">
         <v>74</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="G36" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
@@ -2445,49 +2475,49 @@
       </c>
       <c r="J36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F37" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="G37" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="H37" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Sucesión gubernamental</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>152</v>
@@ -2496,88 +2526,88 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>90</v>
+      </c>
+      <c r="H38" t="s">
+        <v>11</v>
+      </c>
+      <c r="I38" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J38" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="G38" t="s">
-        <v>154</v>
-      </c>
-      <c r="H38" t="s">
-        <v>11</v>
-      </c>
-      <c r="I38" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J38" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
-        <v>46297</v>
-      </c>
-      <c r="B39" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>155</v>
-      </c>
       <c r="D39" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G39" t="s">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B40" t="s">
         <v>73</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G40" t="s">
-        <v>159</v>
+        <v>42</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2586,285 +2616,285 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B41" t="s">
         <v>73</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D41" t="s">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="F41" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="G41" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B42" t="s">
         <v>73</v>
       </c>
       <c r="C42" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" t="s">
+        <v>80</v>
+      </c>
+      <c r="H42" t="s">
+        <v>11</v>
+      </c>
+      <c r="I42" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J42" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>64</v>
+      </c>
+      <c r="F43" t="s">
+        <v>64</v>
+      </c>
+      <c r="G43" t="s">
+        <v>89</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J43" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B44" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" t="s">
+        <v>159</v>
+      </c>
+      <c r="F44" t="s">
+        <v>159</v>
+      </c>
+      <c r="G44" t="s">
+        <v>91</v>
+      </c>
+      <c r="H44" t="s">
+        <v>68</v>
+      </c>
+      <c r="I44" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J44" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B45" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>61</v>
+      </c>
+      <c r="H45" t="s">
+        <v>11</v>
+      </c>
+      <c r="I45" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J45" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B46" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D42" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" t="s">
-        <v>87</v>
-      </c>
-      <c r="G42" t="s">
-        <v>88</v>
-      </c>
-      <c r="H42" t="s">
-        <v>68</v>
-      </c>
-      <c r="I42" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J42" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="11">
-        <v>46297</v>
-      </c>
-      <c r="B43" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="5" t="s">
+      <c r="D46" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" t="s">
+        <v>136</v>
+      </c>
+      <c r="G46" t="s">
+        <v>94</v>
+      </c>
+      <c r="H46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I46" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J46" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B47" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D43" t="s">
-        <v>91</v>
-      </c>
-      <c r="E43" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" t="s">
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" t="s">
+        <v>136</v>
+      </c>
+      <c r="G47" t="s">
+        <v>148</v>
+      </c>
+      <c r="H47" t="s">
         <v>163</v>
       </c>
-      <c r="H43" t="s">
-        <v>11</v>
-      </c>
-      <c r="I43" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J43" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="11">
-        <v>46297</v>
-      </c>
-      <c r="B44" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" s="5" t="s">
+      <c r="I47" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J47" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B48" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D44" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" t="s">
-        <v>24</v>
-      </c>
-      <c r="F44" t="s">
-        <v>24</v>
-      </c>
-      <c r="G44" t="s">
-        <v>97</v>
-      </c>
-      <c r="H44" t="s">
-        <v>11</v>
-      </c>
-      <c r="I44" t="str">
+      <c r="D48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>53</v>
+      </c>
+      <c r="F48" t="s">
+        <v>53</v>
+      </c>
+      <c r="G48" t="s">
+        <v>165</v>
+      </c>
+      <c r="H48" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J44" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="11">
-        <v>46297</v>
-      </c>
-      <c r="B45" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D45" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" t="s">
-        <v>16</v>
-      </c>
-      <c r="F45" t="s">
-        <v>16</v>
-      </c>
-      <c r="G45" t="s">
-        <v>159</v>
-      </c>
-      <c r="H45" t="s">
-        <v>11</v>
-      </c>
-      <c r="I45" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J45" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="11">
-        <v>46297</v>
-      </c>
-      <c r="B46" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="5" t="s">
+      <c r="J48" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B49" t="s">
+        <v>84</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>166</v>
-      </c>
-      <c r="D46" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" t="s">
-        <v>16</v>
-      </c>
-      <c r="F46" t="s">
-        <v>16</v>
-      </c>
-      <c r="G46" t="s">
-        <v>80</v>
-      </c>
-      <c r="H46" t="s">
-        <v>11</v>
-      </c>
-      <c r="I46" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J46" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A47" s="11">
-        <v>46297</v>
-      </c>
-      <c r="B47" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" t="s">
-        <v>16</v>
-      </c>
-      <c r="F47" t="s">
-        <v>168</v>
-      </c>
-      <c r="G47" t="s">
-        <v>100</v>
-      </c>
-      <c r="H47" t="s">
-        <v>11</v>
-      </c>
-      <c r="I47" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J47" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A48" s="11">
-        <v>46297</v>
-      </c>
-      <c r="B48" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D48" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" t="s">
-        <v>36</v>
-      </c>
-      <c r="F48" t="s">
-        <v>2</v>
-      </c>
-      <c r="G48" t="s">
-        <v>116</v>
-      </c>
-      <c r="H48" t="s">
-        <v>72</v>
-      </c>
-      <c r="I48" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J48" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="11">
-        <v>46297</v>
-      </c>
-      <c r="B49" t="s">
-        <v>90</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>170</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
@@ -2873,10 +2903,10 @@
         <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>76</v>
+        <v>167</v>
       </c>
       <c r="G49" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -2892,32 +2922,32 @@
     </row>
     <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B50" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D50" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="G50" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2926,47 +2956,47 @@
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F51" t="s">
-        <v>76</v>
+        <v>172</v>
       </c>
       <c r="G51" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D52" t="s">
         <v>12</v>
@@ -2975,13 +3005,13 @@
         <v>29</v>
       </c>
       <c r="F52" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G52" t="s">
         <v>78</v>
       </c>
       <c r="H52" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2994,96 +3024,96 @@
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B53" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D53" t="s">
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="G53" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C54" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" t="s">
+        <v>28</v>
+      </c>
+      <c r="F54" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" t="s">
+        <v>177</v>
+      </c>
+      <c r="H54" t="s">
+        <v>11</v>
+      </c>
+      <c r="I54" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J54" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B55" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D54" t="s">
-        <v>12</v>
-      </c>
-      <c r="E54" t="s">
-        <v>24</v>
-      </c>
-      <c r="F54" t="s">
-        <v>24</v>
-      </c>
-      <c r="G54" t="s">
-        <v>97</v>
-      </c>
-      <c r="H54" t="s">
-        <v>11</v>
-      </c>
-      <c r="I54" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J54" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="11">
-        <v>46297</v>
-      </c>
-      <c r="B55" t="s">
-        <v>90</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>179</v>
-      </c>
       <c r="D55" t="s">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="F55" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="G55" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="H55" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3096,25 +3126,25 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B56" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="D56" t="s">
         <v>82</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G56" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
@@ -3130,59 +3160,59 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B57" t="s">
-        <v>90</v>
+        <v>181</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="D57" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G57" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
       </c>
       <c r="I57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B58" t="s">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F58" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="G58" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s">
         <v>11</v>
@@ -3193,98 +3223,98 @@
       </c>
       <c r="J58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B59" t="s">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="C59" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F59" t="s">
+        <v>86</v>
+      </c>
+      <c r="G59" t="s">
+        <v>78</v>
+      </c>
+      <c r="H59" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J59" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B60" t="s">
         <v>181</v>
       </c>
-      <c r="D59" t="s">
-        <v>12</v>
-      </c>
-      <c r="E59" t="s">
-        <v>14</v>
-      </c>
-      <c r="F59" t="s">
-        <v>14</v>
-      </c>
-      <c r="G59" t="s">
-        <v>182</v>
-      </c>
-      <c r="H59" t="s">
-        <v>11</v>
-      </c>
-      <c r="I59" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J59" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="11">
-        <v>46297</v>
-      </c>
-      <c r="B60" t="s">
-        <v>79</v>
-      </c>
       <c r="C60" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D60" t="s">
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F60" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G60" t="s">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="H60" t="s">
         <v>11</v>
       </c>
       <c r="I60" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J60" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D61" t="s">
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="H61" t="s">
         <v>11</v>
@@ -3295,39 +3325,243 @@
       </c>
       <c r="J61" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B62" t="s">
+        <v>181</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D62" t="s">
+        <v>82</v>
+      </c>
+      <c r="E62" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" t="s">
+        <v>78</v>
+      </c>
+      <c r="H62" t="s">
+        <v>11</v>
+      </c>
+      <c r="I62" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J62" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B63" t="s">
+        <v>181</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D63" t="s">
+        <v>82</v>
+      </c>
+      <c r="E63" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" t="s">
+        <v>88</v>
+      </c>
+      <c r="H63" t="s">
+        <v>11</v>
+      </c>
+      <c r="I63" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J63" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B64" t="s">
         <v>79</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D62" t="s">
-        <v>12</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="C64" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" t="s">
+        <v>38</v>
+      </c>
+      <c r="F64" t="s">
+        <v>66</v>
+      </c>
+      <c r="G64" t="s">
+        <v>191</v>
+      </c>
+      <c r="H64" t="s">
+        <v>11</v>
+      </c>
+      <c r="I64" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J64" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B65" t="s">
+        <v>79</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D65" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" t="s">
+        <v>23</v>
+      </c>
+      <c r="F65" t="s">
+        <v>136</v>
+      </c>
+      <c r="G65" t="s">
+        <v>107</v>
+      </c>
+      <c r="H65" t="s">
+        <v>11</v>
+      </c>
+      <c r="I65" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J65" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A66" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B66" t="s">
+        <v>79</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" t="s">
         <v>10</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F66" t="s">
         <v>10</v>
       </c>
-      <c r="G62" t="s">
-        <v>80</v>
-      </c>
-      <c r="H62" t="s">
-        <v>11</v>
-      </c>
-      <c r="I62" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J62" t="str">
+      <c r="G66" t="s">
+        <v>61</v>
+      </c>
+      <c r="H66" t="s">
+        <v>68</v>
+      </c>
+      <c r="I66" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J66" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B67" t="s">
+        <v>79</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D67" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" t="s">
+        <v>22</v>
+      </c>
+      <c r="F67" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67" t="s">
+        <v>186</v>
+      </c>
+      <c r="H67" t="s">
+        <v>11</v>
+      </c>
+      <c r="I67" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J67" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B68" t="s">
+        <v>79</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D68" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" t="s">
+        <v>140</v>
+      </c>
+      <c r="H68" t="s">
+        <v>68</v>
+      </c>
+      <c r="I68" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J68" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78933FF-5FBC-4D18-AA38-B87100F57C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF983891-8ED4-477E-A75A-372FB0A7DD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="187">
   <si>
     <t>Fecha</t>
   </si>
@@ -273,9 +273,6 @@
     <t>PAZ</t>
   </si>
   <si>
-    <t>Feria Pachuca</t>
-  </si>
-  <si>
     <t>Plaza Juárez</t>
   </si>
   <si>
@@ -297,334 +294,310 @@
     <t>Cintillo</t>
   </si>
   <si>
-    <t>OEEH</t>
-  </si>
-  <si>
-    <t>Recuerda: la detección temprana salva vidas</t>
-  </si>
-  <si>
     <t>Prevención cáncer de mama</t>
   </si>
   <si>
-    <t>Alianzas Electorales</t>
-  </si>
-  <si>
-    <t>Conmemoración Aniversario</t>
-  </si>
-  <si>
     <t>Enriquecimiento ilícito</t>
   </si>
   <si>
-    <t>Innovación tecnológica</t>
-  </si>
-  <si>
     <t>Policía municipal</t>
   </si>
   <si>
     <t>Alerta Meteorológica</t>
   </si>
   <si>
-    <t>Definirán a coordinadores rumbo a 2027</t>
-  </si>
-  <si>
-    <t>Celebran a San Francisco en Pachuca</t>
-  </si>
-  <si>
-    <t>Fiesta patronal</t>
-  </si>
-  <si>
-    <t>Concurrido Festival del Pulque y Maíz</t>
-  </si>
-  <si>
-    <t>Festival Gastronómico</t>
-  </si>
-  <si>
-    <t>Aumentan delitos de violencia familiar</t>
-  </si>
-  <si>
-    <t>Violencia familiar</t>
-  </si>
-  <si>
-    <t>Salario mínimo no cubre costo de vida</t>
-  </si>
-  <si>
-    <t>Pobreza laboral</t>
-  </si>
-  <si>
-    <t>Ferias son el sustento de los comerciantes</t>
-  </si>
-  <si>
-    <t>Más de dos mil pesos para armar un disfraz</t>
-  </si>
-  <si>
-    <t>Lluvias dejan vías cerradas y dos heridos</t>
-  </si>
-  <si>
     <t>Afectaciones Por Lluvias</t>
   </si>
   <si>
-    <t>Reactiva Tribunal Colegiado proceso contra Sosa</t>
-  </si>
-  <si>
     <t>Grupo Universidad</t>
   </si>
   <si>
-    <t>Más de 30 se registran por coordinaciones de Morena</t>
-  </si>
-  <si>
-    <t>El Xantolo, una herencia de familia</t>
-  </si>
-  <si>
-    <t>Xantolo</t>
-  </si>
-  <si>
-    <t>Destaca Sheinbaum a las fuerzas armadas</t>
-  </si>
-  <si>
-    <t>Toluca amarga debut de Tomé</t>
-  </si>
-  <si>
-    <t>Por título en paralimpiada</t>
-  </si>
-  <si>
-    <t>Inhide</t>
-  </si>
-  <si>
-    <t>Paranacionales Conade</t>
-  </si>
-  <si>
-    <t>Gabinete de Menchaca ha cambiado 13 veces</t>
-  </si>
-  <si>
-    <t>Cambios En El Gabinete</t>
-  </si>
-  <si>
-    <t>Se reportaron en septiembre 34 personas desaparecidas</t>
-  </si>
-  <si>
-    <t>CBPEH</t>
-  </si>
-  <si>
-    <t>Personas desaparecidas</t>
-  </si>
-  <si>
-    <t>Celebra el partido guinda un húmedo XV aniversario</t>
-  </si>
-  <si>
-    <t>Confirma PAZ y PES en Hidalgo la conformación de alianza para 2027</t>
-  </si>
-  <si>
-    <t>Anticipa Rico Mercado más renuncias de funcionarios</t>
-  </si>
-  <si>
-    <t>La 4T perfila a casi una veintena para 7 coordinaciones distritales</t>
-  </si>
-  <si>
-    <t>Busca Miguel Tello coordinar el Ditrito seis</t>
-  </si>
-  <si>
-    <t>Extitular</t>
-  </si>
-  <si>
-    <t>Asociación de Alcaldes pugna por entrega clara</t>
-  </si>
-  <si>
-    <t>Asociación de Alcaldes</t>
-  </si>
-  <si>
-    <t>Nueve de cada diez imputados son vinculados a proceso: Inegi</t>
-  </si>
-  <si>
-    <t>Vinculación A Proceso</t>
-  </si>
-  <si>
-    <t>En 2025 registró el estado 497 víctimas de homicidio</t>
-  </si>
-  <si>
-    <t>Homicidios</t>
-  </si>
-  <si>
-    <t>Declara Protección Civil alerta amarilla en el estado</t>
-  </si>
-  <si>
     <t>PC</t>
   </si>
   <si>
-    <t>Niegan un amparo a Sosa Castelán y reactivan juicio por lavado de dinero</t>
-  </si>
-  <si>
-    <t>Readme, la app de las "citas de amor" entre lectores y libros</t>
-  </si>
-  <si>
-    <t>Bolsonaro sacude a Lula y van a segunda vuelta</t>
-  </si>
-  <si>
     <t>Temas internacionales</t>
   </si>
   <si>
-    <t>Orden a fuerzas armadas para reprimir, nunca</t>
-  </si>
-  <si>
-    <t>Destinan 499.8 mdp para encauzar el Río de las Avenidas</t>
-  </si>
-  <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
-    <t>Rehabilitación Vial</t>
-  </si>
-  <si>
-    <t>Dirigente morenista desconoce estatus de proceso para diputaciones</t>
-  </si>
-  <si>
-    <t>Bolsonaro junior manda a Lula a segunda vuelta</t>
-  </si>
-  <si>
-    <t>Trabajan para reparar puente en Tepehuacán</t>
-  </si>
-  <si>
     <t>Atención Afectaciones Por Lluvias</t>
   </si>
   <si>
-    <t>La amenaza ya no necesita una estructura criminal tradicional. No requiere jerarquías,  territorios ni financiamiento sofisticado. Puede bastar un teléfono, aislamiento,  resentimiento acumulado y una red de espacios virtuales que refuercen de forma  constante narrativas de victimización y agravios compartidos”.</t>
-  </si>
-  <si>
-    <t>Lluvias provocan daños en más de 10 municipios de Hidalgo</t>
-  </si>
-  <si>
-    <t>Nueve de cada 10 imputados por la PGJEH fueron vinculados a proceso</t>
-  </si>
-  <si>
-    <t>Morena Hidalgo conmemora 15 años; llama a la unidad rumbo a 2027</t>
-  </si>
-  <si>
-    <t>Sancionan al 80% de los notarios públicos en Hidlago al inicio de la administración</t>
-  </si>
-  <si>
-    <t>Rojo busca frente opositor para 2028</t>
-  </si>
-  <si>
-    <t>Lluvias provocan deslaves y cierres carreteros</t>
-  </si>
-  <si>
-    <t>Cinco notarios de Hidalgo enfrentan procedimientos</t>
-  </si>
-  <si>
-    <t>PAZ cofirma alianza con PES rumbo a 2027</t>
-  </si>
-  <si>
-    <t>Defender a Viggiano siempre ha sido su papel""</t>
-  </si>
-  <si>
     <t>PRI</t>
   </si>
   <si>
-    <t>Susana y Tania confirman registro en Morena</t>
-  </si>
-  <si>
-    <t>Alertan nuevamente por fuertes lluvias en Hidalgo</t>
-  </si>
-  <si>
-    <t>Mantienen Protección Civil atención y monitoreo por lluvias</t>
-  </si>
-  <si>
-    <t>informa</t>
-  </si>
-  <si>
-    <t>Más de 6.6 mdp fortalecen la productividad del campo de 8 municipios</t>
-  </si>
-  <si>
-    <t>Entrega De Apoyos</t>
-  </si>
-  <si>
-    <t>Lety Reyes inaugura la Expo Feria Tlahuelilpan 2026</t>
-  </si>
-  <si>
-    <t>alcal</t>
-  </si>
-  <si>
-    <t>Expo feria</t>
-  </si>
-  <si>
-    <t>Zitlaly entrega material para mejorar la infraestructura vial en Rincón Norte de Tecomatlán</t>
-  </si>
-  <si>
-    <t>Infraestructura vial</t>
-  </si>
-  <si>
-    <t>Estudiantes de la UTVM participan en Master Class de Gastronomía</t>
-  </si>
-  <si>
-    <t>Universidades</t>
-  </si>
-  <si>
-    <t>Encuentro académico</t>
-  </si>
-  <si>
-    <t>Refuerzan inclusión en la Feria de San Francisco Pachuca 2026</t>
-  </si>
-  <si>
-    <t>ITESA desarrolla herramienta para mejorar el bienestar laboral en empresas</t>
-  </si>
-  <si>
-    <t>Caravana Cultural llevará siete presentaciones de música y danza en Tlahuelilpan</t>
-  </si>
-  <si>
-    <t>Caravanas Culturales</t>
-  </si>
-  <si>
-    <t>Realizan trabajos para habilitar puente en la comunidad de Tamada</t>
-  </si>
-  <si>
-    <t>Emprendimiento que fortalece</t>
-  </si>
-  <si>
-    <t>Apoyo a emprendedores</t>
-  </si>
-  <si>
-    <t>Pachuca Brilla</t>
-  </si>
-  <si>
-    <t>Lluvias dejan estragos en regiones de Hidalgo</t>
-  </si>
-  <si>
-    <t>Horóscopos pusieron el duranguense en el Palenque</t>
-  </si>
-  <si>
-    <t>Costeño, Norteño y Teo hicieron reír a la feria</t>
-  </si>
-  <si>
-    <t>Desmantelan puntos de narcomenudeo en Pachuca y Tizayuca</t>
-  </si>
-  <si>
-    <t>Combate Al Narcomenudeo</t>
-  </si>
-  <si>
-    <t>SEPH promueve bienestar animal con caminata ""Dejando Huella""</t>
-  </si>
-  <si>
-    <t>Croquetón</t>
-  </si>
-  <si>
-    <t>Tradición que sorprende</t>
-  </si>
-  <si>
-    <t>Comparecerán 17 funcionarios por cuarto informe de gobierno</t>
-  </si>
-  <si>
-    <t>Comparecencias</t>
-  </si>
-  <si>
-    <t>Un total de 12 municipios afectados por las lluvias de ayer</t>
-  </si>
-  <si>
-    <t>Como decían en otros  tiempos, la caballada está  flaca entre los suspirantes  a puestos de  elección popular,  de todos  los partidos  políticos…</t>
-  </si>
-  <si>
-    <t>La SSPH desarticuló tres puntos de venta de drogas</t>
-  </si>
-  <si>
-    <t>Bolsonaro y Lula irán a segunda vuelta en Brasil</t>
+    <t>Presa Endhó y Rojo Gómez superan 100% de capacidad</t>
+  </si>
+  <si>
+    <t>Conagua</t>
+  </si>
+  <si>
+    <t>Monitoreo De Presas</t>
+  </si>
+  <si>
+    <t>Demandan espacios en el próximo Festival del Paste</t>
+  </si>
+  <si>
+    <t>Festival Del Paste</t>
+  </si>
+  <si>
+    <t>Hay 32 comunidades aisladas por las lluvias</t>
+  </si>
+  <si>
+    <t>Bajó el precio de la mandarina en Pachuca</t>
+  </si>
+  <si>
+    <t>Canasta básica</t>
+  </si>
+  <si>
+    <t>Jóvenes ven inviable formar una familia</t>
+  </si>
+  <si>
+    <t>Dinámica demográfica</t>
+  </si>
+  <si>
+    <t>Construyendo el Futuro pausa inscripciones</t>
+  </si>
+  <si>
+    <t>Programas Del Bienestar</t>
+  </si>
+  <si>
+    <t>Denuncian falta de apoyos</t>
+  </si>
+  <si>
+    <t>Impulso Al Turismo</t>
+  </si>
+  <si>
+    <t>Colapsa barda en un jardín de niños</t>
+  </si>
+  <si>
+    <t>Básica</t>
+  </si>
+  <si>
+    <t>Lluvia bloquea acceso para 37 comunidades</t>
+  </si>
+  <si>
+    <t>Muestra gastronómica dejó 22.6 mdp</t>
+  </si>
+  <si>
+    <t>Muestra gastronómica</t>
+  </si>
+  <si>
+    <t>Piden activar el seguro catastrófico</t>
+  </si>
+  <si>
+    <t>Apoyo por catástrofes agropecuarias</t>
+  </si>
+  <si>
+    <t>Tribunal de Disciplina Judicial suspende a juez</t>
+  </si>
+  <si>
+    <t>Partidos urgen al IEEH a acelerar las reglas de postulación 2027</t>
+  </si>
+  <si>
+    <t>Afrontan Tuzos un mes decisivo</t>
+  </si>
+  <si>
+    <t>Sueña con la puerta grande</t>
+  </si>
+  <si>
+    <t>Tauromaquia</t>
+  </si>
+  <si>
+    <t>Recurrieron 11 municipios a la deuda pública</t>
+  </si>
+  <si>
+    <t>Deuda Pública</t>
+  </si>
+  <si>
+    <t>Prevé el TEEH una ""lluvia"" de impugnaciones rumbo al 2027</t>
+  </si>
+  <si>
+    <t>Demandan renovación del SNTSA</t>
+  </si>
+  <si>
+    <t>Protesta sindical</t>
+  </si>
+  <si>
+    <t>Se registraron en septiembre cuatro muertes con violencia</t>
+  </si>
+  <si>
+    <t>Incidencia Delictiva</t>
+  </si>
+  <si>
+    <t>Buscará Tello la unidad en Morena de cara a comicios</t>
+  </si>
+  <si>
+    <t>Alerta roja por lluvias regresa... a casi un año de la vaguada</t>
+  </si>
+  <si>
+    <t>Fenómeno de 2025 cuesta al estado $10 mil millones</t>
+  </si>
+  <si>
+    <t>Huracán Priscilla</t>
+  </si>
+  <si>
+    <t>Clima obliga a 40 escuelas a suspender la presencia</t>
+  </si>
+  <si>
+    <t>Suspensión De Clases</t>
+  </si>
+  <si>
+    <t>Suspenden a un juez por liberar cuentas con amparo</t>
+  </si>
+  <si>
+    <t>Sanción a juez</t>
+  </si>
+  <si>
+    <t>Sin fecha para reapertura de vía Real del Monte-Huasca tras fallas en la obra</t>
+  </si>
+  <si>
+    <t>SICT</t>
+  </si>
+  <si>
+    <t>Carretera Huasca</t>
+  </si>
+  <si>
+    <t>Diligencia obliga a pausar actividades en Atotonilco</t>
+  </si>
+  <si>
+    <t>Suspensión de labores</t>
+  </si>
+  <si>
+    <t>El río Achiquixtla llegó a su máxima capacidad y en el sitio personal de protección civil rescató a pescadores</t>
+  </si>
+  <si>
+    <t>Fotonota</t>
+  </si>
+  <si>
+    <t>Huasca: a 25 años del primer Pueblo Mágico</t>
+  </si>
+  <si>
+    <t>Pueblos Mágicos</t>
+  </si>
+  <si>
+    <t>Kuri sí entero de visita de Johnson, pero no de cooperación, aclara SRE}</t>
+  </si>
+  <si>
+    <t>"Que anden por buen camino", pide Rosa Icela</t>
+  </si>
+  <si>
+    <t>Gobernación</t>
+  </si>
+  <si>
+    <t>Bachillerato Margarita Maza inicia actividades</t>
+  </si>
+  <si>
+    <t>Bachillerato Nacional</t>
+  </si>
+  <si>
+    <t>Marchan contra continuidad de Sonia Ocampo en el SNTSA</t>
+  </si>
+  <si>
+    <t>Lluvias dañan caminos; autoridades en alerta ya prearan refugios</t>
+  </si>
+  <si>
+    <t>Pablo Octavio Olvera, director de la SICT en Hidalgo, informó que este fin de semana las lluvias causaron daños en los municipios de Tepehuacán  de Guerrero, Huautla, Tianguistengo, Huejutla, San Bartolo Tutotepec, Tenango de Doria y Xochiatipan, donde se construyeron pasos provisionales  por los daños causados a puentes durante la vaguada monzónica del año pasado. En el puente Zoquitipán–Los Naranjos, personal de la SICT, en  coordinación con el gobierno de Yahualica, llevó a cabo trabajos de relleno provisional con maquinaria pesada para restablecer el paso de manera  temporal y continuar con la reparación integral del puente.</t>
+  </si>
+  <si>
+    <t>Exige Sheinbaum explicaciones a Kuri y Johnson</t>
+  </si>
+  <si>
+    <t>La elección de 2027 comenzó con la inscripción de militantes para poder contender hacia una diputación  (…) Aún falta negociar con los partidos aliados, cumplir la cuota de género y, por supuesto, conseguir  la palomita de Morena nacional a los perfiles”.</t>
+  </si>
+  <si>
+    <t>Lluivas dejan afectaciones en 10 municipios; un desaparecido y dos menores hospitalizados</t>
+  </si>
+  <si>
+    <t>DIFH cuenta con 446 albergues ante posible emergencia</t>
+  </si>
+  <si>
+    <t>Huasca de Ocampo cumple 25 años como el primer Pueblo Mágico de México</t>
+  </si>
+  <si>
+    <t>Arranca disputa interna de Morena por distritos federales de Hidalgo</t>
+  </si>
+  <si>
+    <t>Atribuyen a senadora presunta compra de inmueble por medio de ""facturera""</t>
+  </si>
+  <si>
+    <t>Cruz Azul reactiva al 100% su planta en Hidalgo</t>
+  </si>
+  <si>
+    <t>Cruz Azul</t>
+  </si>
+  <si>
+    <t>Siguen las lluvias</t>
+  </si>
+  <si>
+    <t>Gerardo Sosa libra proceso por defraudación fiscal</t>
+  </si>
+  <si>
+    <t>DIF Hidalgo prepara 446 albergues ante lluvias</t>
+  </si>
+  <si>
+    <t>Alcalde de Ixmiquilpan reclama ausencia de diputada federal en municipios del distrito</t>
+  </si>
+  <si>
+    <t>Inatención</t>
+  </si>
+  <si>
+    <t>Conagua realiza desfogue controlado de la presa Endhó</t>
+  </si>
+  <si>
+    <t>Desfogue De Presa</t>
+  </si>
+  <si>
+    <t>De noche y en territorio: Claudia Sandoval supervisa alumbrado público para garantizar vialidades seguras</t>
+  </si>
+  <si>
+    <t>Luminarias</t>
+  </si>
+  <si>
+    <t>Investigación de El Universal vincula a empresas señaladas por el SAT con mansión de Carolina Viggiano</t>
+  </si>
+  <si>
+    <t>La Cruz Azul agradece el apoyo de Julio Menchaca para reactivación de la cementera</t>
+  </si>
+  <si>
+    <t>Mujeres que laten"": acerca servicios de prevención y salud a mujeres de Tula</t>
+  </si>
+  <si>
+    <t>Conducción responsable: arranca la nueva capacitación vial en Pachuca</t>
+  </si>
+  <si>
+    <t>Educación vial</t>
+  </si>
+  <si>
+    <t>Said Vargas reconoce a quienes acompañan a las comunidades educativas</t>
+  </si>
+  <si>
+    <t>Reunión con sindicato</t>
+  </si>
+  <si>
+    <t>Comité de Emergencias de Hidalgo está activo durante próximas lluvias</t>
+  </si>
+  <si>
+    <t>Reunión Gabinete De Seguridad</t>
+  </si>
+  <si>
+    <t>Semáforo rojo</t>
+  </si>
+  <si>
+    <t>Declaran alerta roja por lluvias en municipios del norte de Hidalgo</t>
+  </si>
+  <si>
+    <t>Vinculan a Carolina Viggiano con casa de más de 40 mdp</t>
+  </si>
+  <si>
+    <t>Mientras la relación de México con EE.UU. se tensa en aspectos comerciales, el loco de Trump coquetea descaradamente con Sheinbaum ... vaya personaje.</t>
+  </si>
+  <si>
+    <t>Editorial</t>
+  </si>
+  <si>
+    <t>Bolsonaro logró 47.03% de los votos y Lula, el 45.16%</t>
+  </si>
+  <si>
+    <t>Intervención extranjera</t>
   </si>
 </sst>
 </file>
@@ -871,8 +844,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J68" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J68" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J60" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J60" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1241,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1290,10 +1263,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>95</v>
@@ -1302,20 +1275,20 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1324,32 +1297,32 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1358,66 +1331,66 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="G4" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H5" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1426,202 +1399,202 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G9" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="G10" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1630,32 +1603,32 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B12" t="s">
         <v>69</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1664,59 +1637,59 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B13" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
       </c>
       <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
@@ -1732,109 +1705,109 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>116</v>
+        <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="G16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H16" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>121</v>
+        <v>16</v>
       </c>
       <c r="G17" t="s">
         <v>122</v>
       </c>
       <c r="H17" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B18" t="s">
         <v>71</v>
@@ -1843,32 +1816,32 @@
         <v>123</v>
       </c>
       <c r="D18" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B19" t="s">
         <v>71</v>
@@ -1880,72 +1853,72 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B20" t="s">
         <v>71</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
         <v>18</v>
@@ -1968,27 +1941,27 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B22" t="s">
         <v>75</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
@@ -2004,59 +1977,59 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B23" t="s">
         <v>75</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B24" t="s">
         <v>75</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
@@ -2072,100 +2045,100 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B25" t="s">
         <v>75</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H25" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B26" t="s">
         <v>75</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G26" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="H26" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B27" t="s">
         <v>75</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="F27" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2174,81 +2147,81 @@
     </row>
     <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B28" t="s">
         <v>75</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>142</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B29" t="s">
         <v>75</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H29" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B30" t="s">
         <v>75</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
@@ -2260,7 +2233,7 @@
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
@@ -2274,83 +2247,83 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>143</v>
+        <v>14</v>
       </c>
       <c r="F31" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G31" t="s">
-        <v>144</v>
+        <v>42</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J31" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="11">
+        <v>46301</v>
+      </c>
+      <c r="B32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" t="s">
+        <v>149</v>
+      </c>
+      <c r="H32" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J31" t="str">
+      <c r="J32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="11">
-        <v>46300</v>
-      </c>
-      <c r="B32" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D32" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" t="s">
-        <v>2</v>
-      </c>
-      <c r="G32" t="s">
-        <v>42</v>
-      </c>
-      <c r="H32" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
-      </c>
-      <c r="J32" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
@@ -2362,10 +2335,10 @@
         <v>10</v>
       </c>
       <c r="G33" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="H33" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2376,30 +2349,30 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D34" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="F34" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="G34" t="s">
-        <v>148</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2410,136 +2383,136 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="195" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D35" t="s">
-        <v>12</v>
+        <v>142</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="G35" t="s">
+        <v>93</v>
+      </c>
+      <c r="H35" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J35" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="11">
+        <v>46301</v>
+      </c>
+      <c r="B36" t="s">
         <v>80</v>
       </c>
-      <c r="H35" t="s">
-        <v>11</v>
-      </c>
-      <c r="I35" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J35" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="11">
-        <v>46300</v>
-      </c>
-      <c r="B36" t="s">
-        <v>74</v>
-      </c>
       <c r="C36" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>143</v>
+        <v>14</v>
       </c>
       <c r="F36" t="s">
-        <v>143</v>
+        <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
       </c>
       <c r="I36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G37" t="s">
-        <v>132</v>
+        <v>42</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B38" t="s">
         <v>74</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2548,134 +2521,134 @@
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B39" t="s">
         <v>74</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="G39" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>42</v>
+        <v>144</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D41" t="s">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="F41" t="s">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="G41" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G42" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2684,32 +2657,32 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B43" t="s">
         <v>73</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G43" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="H43" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2718,32 +2691,32 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B44" t="s">
         <v>73</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>159</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>159</v>
+        <v>10</v>
       </c>
       <c r="G44" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2752,32 +2725,32 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B45" t="s">
         <v>73</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D45" t="s">
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="F45" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="G45" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2786,25 +2759,25 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D46" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F46" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="G46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
@@ -2820,81 +2793,81 @@
     </row>
     <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="G47" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H47" t="s">
-        <v>163</v>
+        <v>11</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B48" t="s">
+        <v>83</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D48" t="s">
         <v>84</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D48" t="s">
-        <v>13</v>
-      </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F48" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="G48" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
@@ -2903,10 +2876,10 @@
         <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="G49" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -2920,34 +2893,34 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="F50" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="G50" t="s">
-        <v>170</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Partidos</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2956,28 +2929,28 @@
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F51" t="s">
-        <v>172</v>
+        <v>24</v>
       </c>
       <c r="G51" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="H51" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2985,83 +2958,83 @@
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D52" t="s">
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F52" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
       </c>
       <c r="I52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C53" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" t="s">
+        <v>87</v>
+      </c>
+      <c r="G53" t="s">
         <v>175</v>
       </c>
-      <c r="D53" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" t="s">
-        <v>26</v>
-      </c>
-      <c r="F53" t="s">
-        <v>172</v>
-      </c>
-      <c r="G53" t="s">
-        <v>92</v>
-      </c>
       <c r="H53" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>176</v>
@@ -3070,10 +3043,10 @@
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G54" t="s">
         <v>177</v>
@@ -3083,19 +3056,19 @@
       </c>
       <c r="I54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>178</v>
@@ -3104,13 +3077,13 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="F55" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="G55" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="H55" t="s">
         <v>11</v>
@@ -3121,30 +3094,30 @@
       </c>
       <c r="J55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E56" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="F56" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="G56" t="s">
-        <v>180</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
@@ -3158,114 +3131,114 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B57" t="s">
+        <v>78</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>182</v>
       </c>
       <c r="D57" t="s">
         <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F57" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="G57" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
       </c>
       <c r="I57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B58" t="s">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="C58" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>94</v>
+      </c>
+      <c r="F58" t="s">
+        <v>94</v>
+      </c>
+      <c r="G58" t="s">
+        <v>86</v>
+      </c>
+      <c r="H58" t="s">
+        <v>68</v>
+      </c>
+      <c r="I58" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J58" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A59" s="11">
+        <v>46301</v>
+      </c>
+      <c r="B59" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D58" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" t="s">
-        <v>29</v>
-      </c>
-      <c r="F58" t="s">
-        <v>86</v>
-      </c>
-      <c r="G58" t="s">
+      <c r="D59" t="s">
+        <v>184</v>
+      </c>
+      <c r="E59" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" t="s">
+        <v>92</v>
+      </c>
+      <c r="H59" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J59" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="11">
+        <v>46301</v>
+      </c>
+      <c r="B60" t="s">
         <v>78</v>
-      </c>
-      <c r="H58" t="s">
-        <v>11</v>
-      </c>
-      <c r="I58" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J58" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="11">
-        <v>46300</v>
-      </c>
-      <c r="B59" t="s">
-        <v>181</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D59" t="s">
-        <v>12</v>
-      </c>
-      <c r="E59" t="s">
-        <v>29</v>
-      </c>
-      <c r="F59" t="s">
-        <v>86</v>
-      </c>
-      <c r="G59" t="s">
-        <v>78</v>
-      </c>
-      <c r="H59" t="s">
-        <v>11</v>
-      </c>
-      <c r="I59" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J59" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="11">
-        <v>46300</v>
-      </c>
-      <c r="B60" t="s">
-        <v>181</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>185</v>
@@ -3274,294 +3247,22 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F60" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G60" t="s">
         <v>186</v>
       </c>
       <c r="H60" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I60" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J60" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="11">
-        <v>46300</v>
-      </c>
-      <c r="B61" t="s">
-        <v>181</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D61" t="s">
-        <v>12</v>
-      </c>
-      <c r="E61" t="s">
-        <v>26</v>
-      </c>
-      <c r="F61" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" t="s">
-        <v>188</v>
-      </c>
-      <c r="H61" t="s">
-        <v>11</v>
-      </c>
-      <c r="I61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="11">
-        <v>46300</v>
-      </c>
-      <c r="B62" t="s">
-        <v>181</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D62" t="s">
-        <v>82</v>
-      </c>
-      <c r="E62" t="s">
-        <v>19</v>
-      </c>
-      <c r="F62" t="s">
-        <v>19</v>
-      </c>
-      <c r="G62" t="s">
-        <v>78</v>
-      </c>
-      <c r="H62" t="s">
-        <v>11</v>
-      </c>
-      <c r="I62" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J62" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="11">
-        <v>46300</v>
-      </c>
-      <c r="B63" t="s">
-        <v>181</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D63" t="s">
-        <v>82</v>
-      </c>
-      <c r="E63" t="s">
-        <v>16</v>
-      </c>
-      <c r="F63" t="s">
-        <v>16</v>
-      </c>
-      <c r="G63" t="s">
-        <v>88</v>
-      </c>
-      <c r="H63" t="s">
-        <v>11</v>
-      </c>
-      <c r="I63" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J63" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="11">
-        <v>46300</v>
-      </c>
-      <c r="B64" t="s">
-        <v>79</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D64" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" t="s">
-        <v>38</v>
-      </c>
-      <c r="F64" t="s">
-        <v>66</v>
-      </c>
-      <c r="G64" t="s">
-        <v>191</v>
-      </c>
-      <c r="H64" t="s">
-        <v>11</v>
-      </c>
-      <c r="I64" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J64" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="11">
-        <v>46300</v>
-      </c>
-      <c r="B65" t="s">
-        <v>79</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D65" t="s">
-        <v>12</v>
-      </c>
-      <c r="E65" t="s">
-        <v>23</v>
-      </c>
-      <c r="F65" t="s">
-        <v>136</v>
-      </c>
-      <c r="G65" t="s">
-        <v>107</v>
-      </c>
-      <c r="H65" t="s">
-        <v>11</v>
-      </c>
-      <c r="I65" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J65" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A66" s="11">
-        <v>46300</v>
-      </c>
-      <c r="B66" t="s">
-        <v>79</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D66" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" t="s">
-        <v>10</v>
-      </c>
-      <c r="G66" t="s">
-        <v>61</v>
-      </c>
-      <c r="H66" t="s">
-        <v>68</v>
-      </c>
-      <c r="I66" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J66" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="11">
-        <v>46300</v>
-      </c>
-      <c r="B67" t="s">
-        <v>79</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D67" t="s">
-        <v>12</v>
-      </c>
-      <c r="E67" t="s">
-        <v>22</v>
-      </c>
-      <c r="F67" t="s">
-        <v>22</v>
-      </c>
-      <c r="G67" t="s">
-        <v>186</v>
-      </c>
-      <c r="H67" t="s">
-        <v>11</v>
-      </c>
-      <c r="I67" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J67" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="11">
-        <v>46300</v>
-      </c>
-      <c r="B68" t="s">
-        <v>79</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D68" t="s">
-        <v>12</v>
-      </c>
-      <c r="E68" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" t="s">
-        <v>10</v>
-      </c>
-      <c r="G68" t="s">
-        <v>140</v>
-      </c>
-      <c r="H68" t="s">
-        <v>68</v>
-      </c>
-      <c r="I68" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J68" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF983891-8ED4-477E-A75A-372FB0A7DD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD68777-3C9A-4575-B706-2BDA3E10E3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="194">
   <si>
     <t>Fecha</t>
   </si>
@@ -267,9 +267,6 @@
     <t>Milenio Hidalgo</t>
   </si>
   <si>
-    <t>Alcalde</t>
-  </si>
-  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -297,9 +294,6 @@
     <t>Prevención cáncer de mama</t>
   </si>
   <si>
-    <t>Enriquecimiento ilícito</t>
-  </si>
-  <si>
     <t>Policía municipal</t>
   </si>
   <si>
@@ -309,295 +303,322 @@
     <t>Afectaciones Por Lluvias</t>
   </si>
   <si>
-    <t>Grupo Universidad</t>
-  </si>
-  <si>
     <t>PC</t>
   </si>
   <si>
     <t>Temas internacionales</t>
   </si>
   <si>
-    <t>Atención Afectaciones Por Lluvias</t>
-  </si>
-  <si>
-    <t>PRI</t>
-  </si>
-  <si>
-    <t>Presa Endhó y Rojo Gómez superan 100% de capacidad</t>
-  </si>
-  <si>
-    <t>Conagua</t>
-  </si>
-  <si>
-    <t>Monitoreo De Presas</t>
-  </si>
-  <si>
-    <t>Demandan espacios en el próximo Festival del Paste</t>
-  </si>
-  <si>
-    <t>Festival Del Paste</t>
-  </si>
-  <si>
-    <t>Hay 32 comunidades aisladas por las lluvias</t>
-  </si>
-  <si>
-    <t>Bajó el precio de la mandarina en Pachuca</t>
-  </si>
-  <si>
-    <t>Canasta básica</t>
-  </si>
-  <si>
-    <t>Jóvenes ven inviable formar una familia</t>
-  </si>
-  <si>
-    <t>Dinámica demográfica</t>
-  </si>
-  <si>
-    <t>Construyendo el Futuro pausa inscripciones</t>
-  </si>
-  <si>
-    <t>Programas Del Bienestar</t>
-  </si>
-  <si>
-    <t>Denuncian falta de apoyos</t>
-  </si>
-  <si>
-    <t>Impulso Al Turismo</t>
-  </si>
-  <si>
-    <t>Colapsa barda en un jardín de niños</t>
-  </si>
-  <si>
-    <t>Básica</t>
-  </si>
-  <si>
-    <t>Lluvia bloquea acceso para 37 comunidades</t>
-  </si>
-  <si>
-    <t>Muestra gastronómica dejó 22.6 mdp</t>
-  </si>
-  <si>
-    <t>Muestra gastronómica</t>
-  </si>
-  <si>
-    <t>Piden activar el seguro catastrófico</t>
-  </si>
-  <si>
-    <t>Apoyo por catástrofes agropecuarias</t>
-  </si>
-  <si>
-    <t>Tribunal de Disciplina Judicial suspende a juez</t>
-  </si>
-  <si>
-    <t>Partidos urgen al IEEH a acelerar las reglas de postulación 2027</t>
-  </si>
-  <si>
-    <t>Afrontan Tuzos un mes decisivo</t>
-  </si>
-  <si>
-    <t>Sueña con la puerta grande</t>
-  </si>
-  <si>
-    <t>Tauromaquia</t>
-  </si>
-  <si>
-    <t>Recurrieron 11 municipios a la deuda pública</t>
-  </si>
-  <si>
-    <t>Deuda Pública</t>
-  </si>
-  <si>
-    <t>Prevé el TEEH una ""lluvia"" de impugnaciones rumbo al 2027</t>
-  </si>
-  <si>
-    <t>Demandan renovación del SNTSA</t>
-  </si>
-  <si>
     <t>Protesta sindical</t>
   </si>
   <si>
-    <t>Se registraron en septiembre cuatro muertes con violencia</t>
-  </si>
-  <si>
-    <t>Incidencia Delictiva</t>
-  </si>
-  <si>
-    <t>Buscará Tello la unidad en Morena de cara a comicios</t>
-  </si>
-  <si>
-    <t>Alerta roja por lluvias regresa... a casi un año de la vaguada</t>
-  </si>
-  <si>
-    <t>Fenómeno de 2025 cuesta al estado $10 mil millones</t>
-  </si>
-  <si>
-    <t>Huracán Priscilla</t>
-  </si>
-  <si>
-    <t>Clima obliga a 40 escuelas a suspender la presencia</t>
-  </si>
-  <si>
     <t>Suspensión De Clases</t>
   </si>
   <si>
-    <t>Suspenden a un juez por liberar cuentas con amparo</t>
-  </si>
-  <si>
-    <t>Sanción a juez</t>
-  </si>
-  <si>
-    <t>Sin fecha para reapertura de vía Real del Monte-Huasca tras fallas en la obra</t>
-  </si>
-  <si>
     <t>SICT</t>
   </si>
   <si>
-    <t>Carretera Huasca</t>
-  </si>
-  <si>
-    <t>Diligencia obliga a pausar actividades en Atotonilco</t>
-  </si>
-  <si>
-    <t>Suspensión de labores</t>
-  </si>
-  <si>
-    <t>El río Achiquixtla llegó a su máxima capacidad y en el sitio personal de protección civil rescató a pescadores</t>
-  </si>
-  <si>
-    <t>Fotonota</t>
-  </si>
-  <si>
-    <t>Huasca: a 25 años del primer Pueblo Mágico</t>
-  </si>
-  <si>
-    <t>Pueblos Mágicos</t>
-  </si>
-  <si>
-    <t>Kuri sí entero de visita de Johnson, pero no de cooperación, aclara SRE}</t>
-  </si>
-  <si>
-    <t>"Que anden por buen camino", pide Rosa Icela</t>
-  </si>
-  <si>
-    <t>Gobernación</t>
-  </si>
-  <si>
-    <t>Bachillerato Margarita Maza inicia actividades</t>
-  </si>
-  <si>
     <t>Bachillerato Nacional</t>
   </si>
   <si>
-    <t>Marchan contra continuidad de Sonia Ocampo en el SNTSA</t>
-  </si>
-  <si>
-    <t>Lluvias dañan caminos; autoridades en alerta ya prearan refugios</t>
-  </si>
-  <si>
-    <t>Pablo Octavio Olvera, director de la SICT en Hidalgo, informó que este fin de semana las lluvias causaron daños en los municipios de Tepehuacán  de Guerrero, Huautla, Tianguistengo, Huejutla, San Bartolo Tutotepec, Tenango de Doria y Xochiatipan, donde se construyeron pasos provisionales  por los daños causados a puentes durante la vaguada monzónica del año pasado. En el puente Zoquitipán–Los Naranjos, personal de la SICT, en  coordinación con el gobierno de Yahualica, llevó a cabo trabajos de relleno provisional con maquinaria pesada para restablecer el paso de manera  temporal y continuar con la reparación integral del puente.</t>
-  </si>
-  <si>
-    <t>Exige Sheinbaum explicaciones a Kuri y Johnson</t>
-  </si>
-  <si>
-    <t>La elección de 2027 comenzó con la inscripción de militantes para poder contender hacia una diputación  (…) Aún falta negociar con los partidos aliados, cumplir la cuota de género y, por supuesto, conseguir  la palomita de Morena nacional a los perfiles”.</t>
-  </si>
-  <si>
-    <t>Lluivas dejan afectaciones en 10 municipios; un desaparecido y dos menores hospitalizados</t>
-  </si>
-  <si>
-    <t>DIFH cuenta con 446 albergues ante posible emergencia</t>
-  </si>
-  <si>
-    <t>Huasca de Ocampo cumple 25 años como el primer Pueblo Mágico de México</t>
-  </si>
-  <si>
-    <t>Arranca disputa interna de Morena por distritos federales de Hidalgo</t>
-  </si>
-  <si>
-    <t>Atribuyen a senadora presunta compra de inmueble por medio de ""facturera""</t>
-  </si>
-  <si>
-    <t>Cruz Azul reactiva al 100% su planta en Hidalgo</t>
-  </si>
-  <si>
     <t>Cruz Azul</t>
   </si>
   <si>
-    <t>Siguen las lluvias</t>
-  </si>
-  <si>
-    <t>Gerardo Sosa libra proceso por defraudación fiscal</t>
-  </si>
-  <si>
-    <t>DIF Hidalgo prepara 446 albergues ante lluvias</t>
-  </si>
-  <si>
-    <t>Alcalde de Ixmiquilpan reclama ausencia de diputada federal en municipios del distrito</t>
-  </si>
-  <si>
-    <t>Inatención</t>
-  </si>
-  <si>
-    <t>Conagua realiza desfogue controlado de la presa Endhó</t>
-  </si>
-  <si>
-    <t>Desfogue De Presa</t>
-  </si>
-  <si>
-    <t>De noche y en territorio: Claudia Sandoval supervisa alumbrado público para garantizar vialidades seguras</t>
-  </si>
-  <si>
-    <t>Luminarias</t>
-  </si>
-  <si>
-    <t>Investigación de El Universal vincula a empresas señaladas por el SAT con mansión de Carolina Viggiano</t>
-  </si>
-  <si>
-    <t>La Cruz Azul agradece el apoyo de Julio Menchaca para reactivación de la cementera</t>
-  </si>
-  <si>
-    <t>Mujeres que laten"": acerca servicios de prevención y salud a mujeres de Tula</t>
-  </si>
-  <si>
-    <t>Conducción responsable: arranca la nueva capacitación vial en Pachuca</t>
-  </si>
-  <si>
-    <t>Educación vial</t>
-  </si>
-  <si>
-    <t>Said Vargas reconoce a quienes acompañan a las comunidades educativas</t>
-  </si>
-  <si>
     <t>Reunión con sindicato</t>
   </si>
   <si>
-    <t>Comité de Emergencias de Hidalgo está activo durante próximas lluvias</t>
-  </si>
-  <si>
-    <t>Reunión Gabinete De Seguridad</t>
-  </si>
-  <si>
-    <t>Semáforo rojo</t>
-  </si>
-  <si>
-    <t>Declaran alerta roja por lluvias en municipios del norte de Hidalgo</t>
-  </si>
-  <si>
-    <t>Vinculan a Carolina Viggiano con casa de más de 40 mdp</t>
-  </si>
-  <si>
-    <t>Mientras la relación de México con EE.UU. se tensa en aspectos comerciales, el loco de Trump coquetea descaradamente con Sheinbaum ... vaya personaje.</t>
-  </si>
-  <si>
-    <t>Editorial</t>
-  </si>
-  <si>
-    <t>Bolsonaro logró 47.03% de los votos y Lula, el 45.16%</t>
-  </si>
-  <si>
-    <t>Intervención extranjera</t>
+    <t>Protestan trabajadores de Educación Especial</t>
+  </si>
+  <si>
+    <t>Suman 50 comunidades aisladas por las lluvias</t>
+  </si>
+  <si>
+    <t>Colapso de puente</t>
+  </si>
+  <si>
+    <t>Reactivan la planta Cruz Azul en Hidalgo</t>
+  </si>
+  <si>
+    <t>El 26% de cigarros en México es ilegal</t>
+  </si>
+  <si>
+    <t>Contrabando</t>
+  </si>
+  <si>
+    <t>Aprueban nuevo modelo de transparencia</t>
+  </si>
+  <si>
+    <t>Transparencia</t>
+  </si>
+  <si>
+    <t>Desplazan a veladoras tradicionales</t>
+  </si>
+  <si>
+    <t>Día De Muertos</t>
+  </si>
+  <si>
+    <t>Suspenden 177 escuelas las clases presenciales</t>
+  </si>
+  <si>
+    <t>Confirman una desbandada de subsecretarios por elecciones</t>
+  </si>
+  <si>
+    <t>Llega nuevo jefe de la GN</t>
+  </si>
+  <si>
+    <t>GN</t>
+  </si>
+  <si>
+    <t>Nombramientos</t>
+  </si>
+  <si>
+    <t>Huehuetla: inicia el éxodo forzado</t>
+  </si>
+  <si>
+    <t>Reubicación de viviendas</t>
+  </si>
+  <si>
+    <t>A dos años de multihomicidio, familia espera justicia; mañana la audiencia.</t>
+  </si>
+  <si>
+    <t>Sentencia multihomicida</t>
+  </si>
+  <si>
+    <t>SEPH reporta dos escuelas con daños por las precipitaciones</t>
+  </si>
+  <si>
+    <t>Congreso quita candados a los alcaldes para firmar contratos</t>
+  </si>
+  <si>
+    <t>Reforma De Ley</t>
+  </si>
+  <si>
+    <t>Es ""ilegal"" supuesto anuncio de Uber: JMS</t>
+  </si>
+  <si>
+    <t>Apps de transporte</t>
+  </si>
+  <si>
+    <t>El pararrayos de la liga MX</t>
+  </si>
+  <si>
+    <t>Toma protesta comandante de la Guardia Nacional</t>
+  </si>
+  <si>
+    <t>Toma de protesta</t>
+  </si>
+  <si>
+    <t>Abigail trasciende fronteras</t>
+  </si>
+  <si>
+    <t>Giovani González alza la mano por Huichapan</t>
+  </si>
+  <si>
+    <t>Sucesión alcaldía</t>
+  </si>
+  <si>
+    <t>Lluvias dejan aisladas más de 30 poblaciones y se reporta un deceso</t>
+  </si>
+  <si>
+    <t>Operaciones de la Cruz Azul están al 100%</t>
+  </si>
+  <si>
+    <t>Por mal clima suspenden clases en 177 escuelas</t>
+  </si>
+  <si>
+    <t>Reciben en la entidad a Raúl Meneses, al frente de la GN</t>
+  </si>
+  <si>
+    <t>Atienden casos de violencia</t>
+  </si>
+  <si>
+    <t>Violencia familiar</t>
+  </si>
+  <si>
+    <t>Achacan a Iván, el Tanque, huachicol, extorsión, lavado de dinero, narcotráfico</t>
+  </si>
+  <si>
+    <t>Crimen Organizado</t>
+  </si>
+  <si>
+    <t>México alerta a Ucrania de ""voluntarios"" de cárteles</t>
+  </si>
+  <si>
+    <t>Elecciones anticipadas en España en medio de crisis política y escándalos</t>
+  </si>
+  <si>
+    <t>Hay dos líneas de investigación por crimen contra sacerdote: PGJEH</t>
+  </si>
+  <si>
+    <t>Homicidio de sacerdote</t>
+  </si>
+  <si>
+    <t>Hidalgo sube 12.4% en graduaciones en el nivel bachillerato</t>
+  </si>
+  <si>
+    <t>Media superior</t>
+  </si>
+  <si>
+    <t>Eficiencia terminal</t>
+  </si>
+  <si>
+    <t>Congreso avala que ediles firmen convenios sin autorización del cabildo</t>
+  </si>
+  <si>
+    <t>Presume Harfuch detención de El Tanque</t>
+  </si>
+  <si>
+    <t>Seguridad Ciudadana</t>
+  </si>
+  <si>
+    <t>Combate a la delincuencia</t>
+  </si>
+  <si>
+    <t>El secretario Natividad Castrejón detalló avances en todos los niveles y atribuyó los resultados al trabajo conjunto de padres de  familia, alumnos, maestros y autoridades. Resaltó que 5 mil 926 jóvenes más terminaron la prepa en tres años.</t>
+  </si>
+  <si>
+    <t>Cuando supe de la (…) decapitación simbólica del exmandatario, no pude más que  sentir alegría. No es absolutamente comparable a la devastación y el dolor que él y  su gabinete causaron en este país. Déjense de ridiculeces y de llorarle a una estatua:  FeCalH está intacto”.</t>
+  </si>
+  <si>
+    <t>Uber no puede operar en Hidalgo; su llegada sería ilegal</t>
+  </si>
+  <si>
+    <t>Aumenta infraestructura educativa en Hidalgo con Bachillerato Nacional ""Margarita Maza""</t>
+  </si>
+  <si>
+    <t>Alcaldes podrán celebrar contratos sin autorización del Cabildo</t>
+  </si>
+  <si>
+    <t>Persiste batalla legal del SNTE para recuperar 123 mdp del caso Mirna García</t>
+  </si>
+  <si>
+    <t>Cerca de esclarecer crimen de sacerdote</t>
+  </si>
+  <si>
+    <t>Mosquitos de presa Endhó llaegan a la cámara de diputados</t>
+  </si>
+  <si>
+    <t>Medio ambiente</t>
+  </si>
+  <si>
+    <t>Mosco Culex</t>
+  </si>
+  <si>
+    <t>Lluvias dejan sin clases presenciales a 177 escuelas</t>
+  </si>
+  <si>
+    <t>¿Van juntos en 2027?</t>
+  </si>
+  <si>
+    <t>Alianzas Electorales</t>
+  </si>
+  <si>
+    <t>Quitan freno a alcaldes</t>
+  </si>
+  <si>
+    <t>¿Uber llegará a Pachuca?</t>
+  </si>
+  <si>
+    <t>Uber no puede operar en Hidalgo; ley no permite su llegada: Menchaca</t>
+  </si>
+  <si>
+    <t>Ecología de Ajacuba rescata ejemplar de Águila Harris</t>
+  </si>
+  <si>
+    <t>Rescate Animal</t>
+  </si>
+  <si>
+    <t>Tlaxcoapan, sede de entrega regional de apoyos para fortalecer al campo hidalguense</t>
+  </si>
+  <si>
+    <t>Impulso al agro</t>
+  </si>
+  <si>
+    <t>DIFH fortalece la protección de niñas, niños y adolescentes con el Modelo de Gestión de Casos</t>
+  </si>
+  <si>
+    <t>Protección del menor</t>
+  </si>
+  <si>
+    <t>Julio Menchaca respalda llegada de Raúl Meneses, nuevo coordinador estatal de la GN</t>
+  </si>
+  <si>
+    <t>Coloca Natividad Castrejón primera piedra del Bachillerato Nacional ""Margarita Maza"" en Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>Said Vargas acompaña el encuentro de la Organización V para fortalecer estructuras sindicales</t>
+  </si>
+  <si>
+    <t>Notariado hidaluense se prepara para la entrada en vigor de la nueva Ley del Notariado</t>
+  </si>
+  <si>
+    <t>Notarías</t>
+  </si>
+  <si>
+    <t>Registro el Estado Familiar expide actas certificadas en el estado de Hidalgo y de otras entidades federativas</t>
+  </si>
+  <si>
+    <t>Onésimo Serrano queda al frente de Planeación tras renuncia de Miguel Tello</t>
+  </si>
+  <si>
+    <t>Pachuca Brilla</t>
+  </si>
+  <si>
+    <t>Se mantienen lluvia y bajas temperaturas en Hidalgo</t>
+  </si>
+  <si>
+    <t>SSPH detienen en Huasca a dos personas con 45 billetes falsos</t>
+  </si>
+  <si>
+    <t>Detienen a dos hombres por presunto robo de medidor de agua en Pachuca</t>
+  </si>
+  <si>
+    <t>Detención</t>
+  </si>
+  <si>
+    <t>Coloca Natividad Castrejón primera piedra del Bachillerato Nacional Margarita Maza en La Reforma</t>
+  </si>
+  <si>
+    <t>Julio Menchaca respalda llegada de nuevo coordinador estatal de la Guardia Nacional</t>
+  </si>
+  <si>
+    <t>Tradición que sorprende</t>
+  </si>
+  <si>
+    <t>Feria Pachuca</t>
+  </si>
+  <si>
+    <t>Recuerda: la detección temprana salva vidas</t>
+  </si>
+  <si>
+    <t>Ediles podrán celebrar contratos sin autorización del cabildo</t>
+  </si>
+  <si>
+    <t>Nuevo titular de la Guardia Nacional en Hidalgo</t>
+  </si>
+  <si>
+    <t>Volvió a perder México, ahora frente a Chile</t>
+  </si>
+  <si>
+    <t>Amenazan con bloquear Boulevard Colosio</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Caasim</t>
+  </si>
+  <si>
+    <t>Abasto de agua</t>
+  </si>
+  <si>
+    <t>Logra cuautepequense medalla de bronce</t>
+  </si>
+  <si>
+    <t>Inhide</t>
+  </si>
+  <si>
+    <t>Paranacionales Conade</t>
   </si>
 </sst>
 </file>
@@ -751,6 +772,12 @@
   </cellStyles>
   <dxfs count="6">
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="d/m/yy;@"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -792,12 +819,6 @@
           <color theme="4" tint="0.39997558519241921"/>
         </left>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="d/m/yy;@"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -844,15 +865,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J60" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J60" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J65" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J65" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{9D9ACAF2-1710-400E-A0E5-0A5BB378D4A0}" name="Fecha" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{9D9ACAF2-1710-400E-A0E5-0A5BB378D4A0}" name="Fecha" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{03A139BE-A997-45E6-81E6-5F7467162FC5}" name="Medio"/>
-    <tableColumn id="3" xr3:uid="{4CA37DD5-010E-43EE-907D-87C1845DB2AB}" name="Titular" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{4CA37DD5-010E-43EE-907D-87C1845DB2AB}" name="Titular" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{1E763E28-25D7-4FE7-AD1A-91C7A0FE0E7A}" name="Recurso editorial"/>
     <tableColumn id="5" xr3:uid="{F8C19AF2-6D19-449B-9F8B-6424964B1BCF}" name="Dependencia"/>
     <tableColumn id="6" xr3:uid="{46DF0510-7A9A-4625-979E-4EBC30CC7AA3}" name="Organismo"/>
@@ -884,13 +905,13 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}" name="Tabla3" displayName="Tabla3" ref="D1:E27" totalsRowShown="0" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}" name="Tabla3" displayName="Tabla3" ref="D1:E27" totalsRowShown="0" tableBorderDxfId="3">
   <autoFilter ref="D1:E27" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:E27">
     <sortCondition ref="D1:D27"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A040A308-8C62-4D4B-B3BE-EC124A9B961C}" name="Dependencia" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{A040A308-8C62-4D4B-B3BE-EC124A9B961C}" name="Dependencia" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{2B2FFCF1-496A-4D37-8C8B-790A66FD9968}" name="Nivel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1214,7 +1235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1263,66 +1284,66 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" t="s">
         <v>98</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>99</v>
       </c>
       <c r="H3" t="s">
         <v>68</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1331,47 +1352,47 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -1383,7 +1404,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -1399,25 +1420,25 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
         <v>103</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" t="s">
-        <v>104</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -1433,32 +1454,32 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
         <v>105</v>
       </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>106</v>
-      </c>
       <c r="H7" t="s">
         <v>11</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1467,28 +1488,28 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1499,27 +1520,27 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -1530,166 +1551,166 @@
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="G10" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" t="s">
         <v>112</v>
       </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" t="s">
-        <v>113</v>
-      </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B12" t="s">
         <v>69</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" t="s">
         <v>114</v>
       </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J12" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="H12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J12" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <v>46301</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>116</v>
-      </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
       </c>
       <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" t="s">
         <v>117</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" t="s">
-        <v>42</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
@@ -1705,7 +1726,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
@@ -1714,38 +1735,38 @@
         <v>118</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
         <v>12</v>
@@ -1757,10 +1778,10 @@
         <v>10</v>
       </c>
       <c r="G16" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="H16" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1773,7 +1794,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
@@ -1782,13 +1803,13 @@
         <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
         <v>122</v>
@@ -1798,16 +1819,16 @@
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B18" t="s">
         <v>71</v>
@@ -1819,13 +1840,13 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
@@ -1841,7 +1862,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B19" t="s">
         <v>71</v>
@@ -1853,10 +1874,10 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G19" t="s">
         <v>125</v>
@@ -1866,7 +1887,7 @@
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1875,25 +1896,25 @@
     </row>
     <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>126</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
@@ -1909,60 +1930,60 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="H21" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B22" t="s">
         <v>75</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" t="s">
         <v>91</v>
       </c>
-      <c r="G22" t="s">
-        <v>88</v>
-      </c>
       <c r="H22" t="s">
         <v>11</v>
       </c>
@@ -1975,27 +1996,27 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B23" t="s">
         <v>75</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G23" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
@@ -2006,86 +2027,86 @@
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B24" t="s">
         <v>75</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B25" t="s">
         <v>75</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B26" t="s">
         <v>75</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
@@ -2094,13 +2115,13 @@
         <v>14</v>
       </c>
       <c r="F26" t="s">
-        <v>137</v>
+        <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2111,34 +2132,34 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B27" t="s">
         <v>75</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2147,25 +2168,25 @@
     </row>
     <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B28" t="s">
         <v>75</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="G28" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
@@ -2179,68 +2200,68 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>139</v>
       </c>
       <c r="G29" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H29" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G30" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2249,13 +2270,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s">
         <v>12</v>
@@ -2264,10 +2285,10 @@
         <v>14</v>
       </c>
       <c r="F31" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G31" t="s">
-        <v>42</v>
+        <v>144</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
@@ -2281,30 +2302,30 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E32" t="s">
         <v>26</v>
       </c>
       <c r="F32" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="H32" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2315,15 +2336,15 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
@@ -2335,7 +2356,7 @@
         <v>10</v>
       </c>
       <c r="G33" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -2351,28 +2372,28 @@
     </row>
     <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D34" t="s">
         <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F34" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G34" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="H34" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2380,275 +2401,275 @@
       </c>
       <c r="J34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="195" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D35" t="s">
-        <v>142</v>
+        <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="G35" t="s">
         <v>93</v>
       </c>
       <c r="H35" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D36" t="s">
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G36" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
       </c>
       <c r="I36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="H38" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C39" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" t="s">
+        <v>153</v>
+      </c>
+      <c r="G39" t="s">
+        <v>154</v>
+      </c>
+      <c r="H39" t="s">
+        <v>68</v>
+      </c>
+      <c r="I39" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J39" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>26</v>
+      </c>
+      <c r="F40" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" t="s">
+        <v>91</v>
+      </c>
+      <c r="H40" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J40" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D39" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" t="s">
-        <v>36</v>
-      </c>
-      <c r="F39" t="s">
-        <v>36</v>
-      </c>
-      <c r="G39" t="s">
-        <v>93</v>
-      </c>
-      <c r="H39" t="s">
-        <v>72</v>
-      </c>
-      <c r="I39" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J39" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="11">
-        <v>46301</v>
-      </c>
-      <c r="B40" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" s="5" t="s">
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" t="s">
+        <v>46</v>
+      </c>
+      <c r="G41" t="s">
         <v>157</v>
       </c>
-      <c r="D40" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" t="s">
-        <v>14</v>
-      </c>
-      <c r="F40" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" t="s">
-        <v>144</v>
-      </c>
-      <c r="H40" t="s">
-        <v>11</v>
-      </c>
-      <c r="I40" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J40" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="11">
-        <v>46301</v>
-      </c>
-      <c r="B41" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" s="5" t="s">
+      <c r="H41" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J41" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D41" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" t="s">
-        <v>18</v>
-      </c>
-      <c r="F41" t="s">
-        <v>18</v>
-      </c>
-      <c r="G41" t="s">
-        <v>61</v>
-      </c>
-      <c r="H41" t="s">
-        <v>11</v>
-      </c>
-      <c r="I41" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
-      </c>
-      <c r="J41" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="11">
-        <v>46301</v>
-      </c>
-      <c r="B42" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="D42" t="s">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="G42" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="H42" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2657,146 +2678,146 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B43" t="s">
         <v>73</v>
       </c>
       <c r="C43" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" t="s">
+        <v>119</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J43" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B44" t="s">
+        <v>82</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D43" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" t="s">
-        <v>161</v>
-      </c>
-      <c r="H43" t="s">
-        <v>72</v>
-      </c>
-      <c r="I43" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J43" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="11">
-        <v>46301</v>
-      </c>
-      <c r="B44" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>162</v>
-      </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G44" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C45" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" t="s">
+        <v>162</v>
+      </c>
+      <c r="H45" t="s">
+        <v>11</v>
+      </c>
+      <c r="I45" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J45" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B46" t="s">
+        <v>82</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="D45" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" t="s">
-        <v>59</v>
-      </c>
-      <c r="F45" t="s">
-        <v>59</v>
-      </c>
-      <c r="G45" t="s">
-        <v>90</v>
-      </c>
-      <c r="H45" t="s">
-        <v>11</v>
-      </c>
-      <c r="I45" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J45" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="11">
-        <v>46301</v>
-      </c>
-      <c r="B46" t="s">
-        <v>73</v>
-      </c>
-      <c r="C46" s="5" t="s">
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" t="s">
         <v>164</v>
       </c>
-      <c r="D46" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" t="s">
-        <v>36</v>
-      </c>
-      <c r="F46" t="s">
-        <v>36</v>
-      </c>
-      <c r="G46" t="s">
-        <v>93</v>
-      </c>
       <c r="H46" t="s">
         <v>11</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>165</v>
@@ -2805,10 +2826,10 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F47" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="G47" t="s">
         <v>166</v>
@@ -2818,109 +2839,109 @@
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>167</v>
       </c>
       <c r="D48" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F48" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="G48" t="s">
+        <v>122</v>
+      </c>
+      <c r="H48" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J48" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B49" t="s">
+        <v>82</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="H48" t="s">
-        <v>11</v>
-      </c>
-      <c r="I48" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J48" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="11">
-        <v>46301</v>
-      </c>
-      <c r="B49" t="s">
-        <v>83</v>
-      </c>
-      <c r="C49" s="5" t="s">
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" t="s">
+        <v>26</v>
+      </c>
+      <c r="F49" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" t="s">
+        <v>93</v>
+      </c>
+      <c r="H49" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J49" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B50" t="s">
+        <v>82</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D49" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" t="s">
-        <v>16</v>
-      </c>
-      <c r="F49" t="s">
-        <v>76</v>
-      </c>
-      <c r="G49" t="s">
-        <v>170</v>
-      </c>
-      <c r="H49" t="s">
-        <v>11</v>
-      </c>
-      <c r="I49" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J49" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A50" s="11">
-        <v>46301</v>
-      </c>
-      <c r="B50" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G50" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H50" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2929,66 +2950,66 @@
     </row>
     <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G51" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="H51" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B52" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D52" t="s">
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G52" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
       </c>
       <c r="I52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2997,50 +3018,50 @@
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C53" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" t="s">
+        <v>47</v>
+      </c>
+      <c r="F53" t="s">
+        <v>47</v>
+      </c>
+      <c r="G53" t="s">
+        <v>110</v>
+      </c>
+      <c r="H53" t="s">
+        <v>11</v>
+      </c>
+      <c r="I53" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J53" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B54" t="s">
         <v>174</v>
       </c>
-      <c r="D53" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" t="s">
-        <v>16</v>
-      </c>
-      <c r="F53" t="s">
-        <v>87</v>
-      </c>
-      <c r="G53" t="s">
+      <c r="C54" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="H53" t="s">
-        <v>72</v>
-      </c>
-      <c r="I53" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J53" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="11">
-        <v>46301</v>
-      </c>
-      <c r="B54" t="s">
-        <v>83</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>176</v>
-      </c>
       <c r="D54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
@@ -3049,7 +3070,7 @@
         <v>10</v>
       </c>
       <c r="G54" t="s">
-        <v>177</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s">
         <v>11</v>
@@ -3065,93 +3086,93 @@
     </row>
     <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B55" t="s">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="C55" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" t="s">
+        <v>22</v>
+      </c>
+      <c r="F55" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" t="s">
+        <v>144</v>
+      </c>
+      <c r="H55" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J55" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B56" t="s">
+        <v>174</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56" t="s">
+        <v>85</v>
+      </c>
+      <c r="G56" t="s">
         <v>178</v>
       </c>
-      <c r="D55" t="s">
-        <v>12</v>
-      </c>
-      <c r="E55" t="s">
-        <v>24</v>
-      </c>
-      <c r="F55" t="s">
-        <v>24</v>
-      </c>
-      <c r="G55" t="s">
-        <v>179</v>
-      </c>
-      <c r="H55" t="s">
-        <v>11</v>
-      </c>
-      <c r="I55" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J55" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="11">
-        <v>46301</v>
-      </c>
-      <c r="B56" t="s">
-        <v>83</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D56" t="s">
-        <v>81</v>
-      </c>
-      <c r="E56" t="s">
-        <v>23</v>
-      </c>
-      <c r="F56" t="s">
-        <v>91</v>
-      </c>
-      <c r="G56" t="s">
-        <v>88</v>
-      </c>
       <c r="H56" t="s">
         <v>11</v>
       </c>
       <c r="I56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F57" t="s">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="G57" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
@@ -3167,104 +3188,274 @@
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="C58" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" t="s">
+        <v>24</v>
+      </c>
+      <c r="F58" t="s">
+        <v>24</v>
+      </c>
+      <c r="G58" t="s">
+        <v>122</v>
+      </c>
+      <c r="H58" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J58" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B59" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D59" t="s">
+        <v>80</v>
+      </c>
+      <c r="E59" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" t="s">
         <v>182</v>
       </c>
-      <c r="D58" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" t="s">
-        <v>94</v>
-      </c>
-      <c r="F58" t="s">
-        <v>94</v>
-      </c>
-      <c r="G58" t="s">
-        <v>86</v>
-      </c>
-      <c r="H58" t="s">
-        <v>68</v>
-      </c>
-      <c r="I58" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
-      </c>
-      <c r="J58" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A59" s="11">
-        <v>46301</v>
-      </c>
-      <c r="B59" t="s">
-        <v>78</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D59" t="s">
-        <v>184</v>
-      </c>
-      <c r="E59" t="s">
-        <v>14</v>
-      </c>
-      <c r="F59" t="s">
-        <v>14</v>
-      </c>
-      <c r="G59" t="s">
-        <v>92</v>
-      </c>
       <c r="H59" t="s">
         <v>11</v>
       </c>
       <c r="I59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="C60" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D60" t="s">
+        <v>80</v>
+      </c>
+      <c r="E60" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" t="s">
+        <v>84</v>
+      </c>
+      <c r="H60" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B61" t="s">
+        <v>77</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" t="s">
+        <v>117</v>
+      </c>
+      <c r="H61" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B62" t="s">
+        <v>77</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="D60" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" t="s">
+        <v>122</v>
+      </c>
+      <c r="H62" t="s">
+        <v>11</v>
+      </c>
+      <c r="I62" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J62" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B63" t="s">
+        <v>77</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s">
         <v>10</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F63" t="s">
         <v>10</v>
       </c>
-      <c r="G60" t="s">
-        <v>186</v>
-      </c>
-      <c r="H60" t="s">
+      <c r="G63" t="s">
+        <v>70</v>
+      </c>
+      <c r="H63" t="s">
         <v>68</v>
       </c>
-      <c r="I60" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J60" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+      <c r="I63" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J63" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B64" t="s">
+        <v>77</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" t="s">
+        <v>188</v>
+      </c>
+      <c r="F64" t="s">
+        <v>189</v>
+      </c>
+      <c r="G64" t="s">
+        <v>190</v>
+      </c>
+      <c r="H64" t="s">
+        <v>68</v>
+      </c>
+      <c r="I64" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J64" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B65" t="s">
+        <v>77</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D65" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" t="s">
+        <v>26</v>
+      </c>
+      <c r="F65" t="s">
+        <v>192</v>
+      </c>
+      <c r="G65" t="s">
+        <v>193</v>
+      </c>
+      <c r="H65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I65" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J65" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
       </c>
     </row>
   </sheetData>
@@ -3834,7 +4025,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s">
         <v>44</v>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD68777-3C9A-4575-B706-2BDA3E10E3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AD4B36-7F4C-4B7C-A212-52E81B9E72F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="188">
   <si>
     <t>Fecha</t>
   </si>
@@ -297,291 +297,33 @@
     <t>Policía municipal</t>
   </si>
   <si>
-    <t>Alerta Meteorológica</t>
-  </si>
-  <si>
     <t>Afectaciones Por Lluvias</t>
   </si>
   <si>
-    <t>PC</t>
-  </si>
-  <si>
     <t>Temas internacionales</t>
   </si>
   <si>
-    <t>Protesta sindical</t>
-  </si>
-  <si>
-    <t>Suspensión De Clases</t>
-  </si>
-  <si>
-    <t>SICT</t>
-  </si>
-  <si>
     <t>Bachillerato Nacional</t>
   </si>
   <si>
     <t>Cruz Azul</t>
   </si>
   <si>
-    <t>Reunión con sindicato</t>
-  </si>
-  <si>
-    <t>Protestan trabajadores de Educación Especial</t>
-  </si>
-  <si>
-    <t>Suman 50 comunidades aisladas por las lluvias</t>
-  </si>
-  <si>
-    <t>Colapso de puente</t>
-  </si>
-  <si>
-    <t>Reactivan la planta Cruz Azul en Hidalgo</t>
-  </si>
-  <si>
-    <t>El 26% de cigarros en México es ilegal</t>
-  </si>
-  <si>
-    <t>Contrabando</t>
-  </si>
-  <si>
-    <t>Aprueban nuevo modelo de transparencia</t>
-  </si>
-  <si>
-    <t>Transparencia</t>
-  </si>
-  <si>
-    <t>Desplazan a veladoras tradicionales</t>
-  </si>
-  <si>
-    <t>Día De Muertos</t>
-  </si>
-  <si>
-    <t>Suspenden 177 escuelas las clases presenciales</t>
-  </si>
-  <si>
-    <t>Confirman una desbandada de subsecretarios por elecciones</t>
-  </si>
-  <si>
-    <t>Llega nuevo jefe de la GN</t>
-  </si>
-  <si>
-    <t>GN</t>
-  </si>
-  <si>
-    <t>Nombramientos</t>
-  </si>
-  <si>
-    <t>Huehuetla: inicia el éxodo forzado</t>
-  </si>
-  <si>
-    <t>Reubicación de viviendas</t>
-  </si>
-  <si>
-    <t>A dos años de multihomicidio, familia espera justicia; mañana la audiencia.</t>
-  </si>
-  <si>
-    <t>Sentencia multihomicida</t>
-  </si>
-  <si>
-    <t>SEPH reporta dos escuelas con daños por las precipitaciones</t>
-  </si>
-  <si>
-    <t>Congreso quita candados a los alcaldes para firmar contratos</t>
-  </si>
-  <si>
     <t>Reforma De Ley</t>
   </si>
   <si>
-    <t>Es ""ilegal"" supuesto anuncio de Uber: JMS</t>
-  </si>
-  <si>
-    <t>Apps de transporte</t>
-  </si>
-  <si>
-    <t>El pararrayos de la liga MX</t>
-  </si>
-  <si>
-    <t>Toma protesta comandante de la Guardia Nacional</t>
-  </si>
-  <si>
-    <t>Toma de protesta</t>
-  </si>
-  <si>
-    <t>Abigail trasciende fronteras</t>
-  </si>
-  <si>
-    <t>Giovani González alza la mano por Huichapan</t>
-  </si>
-  <si>
-    <t>Sucesión alcaldía</t>
-  </si>
-  <si>
-    <t>Lluvias dejan aisladas más de 30 poblaciones y se reporta un deceso</t>
-  </si>
-  <si>
-    <t>Operaciones de la Cruz Azul están al 100%</t>
-  </si>
-  <si>
-    <t>Por mal clima suspenden clases en 177 escuelas</t>
-  </si>
-  <si>
-    <t>Reciben en la entidad a Raúl Meneses, al frente de la GN</t>
-  </si>
-  <si>
-    <t>Atienden casos de violencia</t>
-  </si>
-  <si>
-    <t>Violencia familiar</t>
-  </si>
-  <si>
-    <t>Achacan a Iván, el Tanque, huachicol, extorsión, lavado de dinero, narcotráfico</t>
-  </si>
-  <si>
-    <t>Crimen Organizado</t>
-  </si>
-  <si>
-    <t>México alerta a Ucrania de ""voluntarios"" de cárteles</t>
-  </si>
-  <si>
-    <t>Elecciones anticipadas en España en medio de crisis política y escándalos</t>
-  </si>
-  <si>
-    <t>Hay dos líneas de investigación por crimen contra sacerdote: PGJEH</t>
-  </si>
-  <si>
-    <t>Homicidio de sacerdote</t>
-  </si>
-  <si>
-    <t>Hidalgo sube 12.4% en graduaciones en el nivel bachillerato</t>
-  </si>
-  <si>
-    <t>Media superior</t>
-  </si>
-  <si>
     <t>Eficiencia terminal</t>
   </si>
   <si>
-    <t>Congreso avala que ediles firmen convenios sin autorización del cabildo</t>
-  </si>
-  <si>
-    <t>Presume Harfuch detención de El Tanque</t>
-  </si>
-  <si>
-    <t>Seguridad Ciudadana</t>
-  </si>
-  <si>
-    <t>Combate a la delincuencia</t>
-  </si>
-  <si>
-    <t>El secretario Natividad Castrejón detalló avances en todos los niveles y atribuyó los resultados al trabajo conjunto de padres de  familia, alumnos, maestros y autoridades. Resaltó que 5 mil 926 jóvenes más terminaron la prepa en tres años.</t>
-  </si>
-  <si>
-    <t>Cuando supe de la (…) decapitación simbólica del exmandatario, no pude más que  sentir alegría. No es absolutamente comparable a la devastación y el dolor que él y  su gabinete causaron en este país. Déjense de ridiculeces y de llorarle a una estatua:  FeCalH está intacto”.</t>
-  </si>
-  <si>
-    <t>Uber no puede operar en Hidalgo; su llegada sería ilegal</t>
-  </si>
-  <si>
-    <t>Aumenta infraestructura educativa en Hidalgo con Bachillerato Nacional ""Margarita Maza""</t>
-  </si>
-  <si>
-    <t>Alcaldes podrán celebrar contratos sin autorización del Cabildo</t>
-  </si>
-  <si>
-    <t>Persiste batalla legal del SNTE para recuperar 123 mdp del caso Mirna García</t>
-  </si>
-  <si>
-    <t>Cerca de esclarecer crimen de sacerdote</t>
-  </si>
-  <si>
-    <t>Mosquitos de presa Endhó llaegan a la cámara de diputados</t>
-  </si>
-  <si>
-    <t>Medio ambiente</t>
-  </si>
-  <si>
-    <t>Mosco Culex</t>
-  </si>
-  <si>
-    <t>Lluvias dejan sin clases presenciales a 177 escuelas</t>
-  </si>
-  <si>
-    <t>¿Van juntos en 2027?</t>
-  </si>
-  <si>
-    <t>Alianzas Electorales</t>
-  </si>
-  <si>
-    <t>Quitan freno a alcaldes</t>
-  </si>
-  <si>
-    <t>¿Uber llegará a Pachuca?</t>
-  </si>
-  <si>
-    <t>Uber no puede operar en Hidalgo; ley no permite su llegada: Menchaca</t>
-  </si>
-  <si>
-    <t>Ecología de Ajacuba rescata ejemplar de Águila Harris</t>
-  </si>
-  <si>
     <t>Rescate Animal</t>
   </si>
   <si>
-    <t>Tlaxcoapan, sede de entrega regional de apoyos para fortalecer al campo hidalguense</t>
-  </si>
-  <si>
-    <t>Impulso al agro</t>
-  </si>
-  <si>
-    <t>DIFH fortalece la protección de niñas, niños y adolescentes con el Modelo de Gestión de Casos</t>
-  </si>
-  <si>
-    <t>Protección del menor</t>
-  </si>
-  <si>
-    <t>Julio Menchaca respalda llegada de Raúl Meneses, nuevo coordinador estatal de la GN</t>
-  </si>
-  <si>
-    <t>Coloca Natividad Castrejón primera piedra del Bachillerato Nacional ""Margarita Maza"" en Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Said Vargas acompaña el encuentro de la Organización V para fortalecer estructuras sindicales</t>
-  </si>
-  <si>
-    <t>Notariado hidaluense se prepara para la entrada en vigor de la nueva Ley del Notariado</t>
-  </si>
-  <si>
-    <t>Notarías</t>
-  </si>
-  <si>
-    <t>Registro el Estado Familiar expide actas certificadas en el estado de Hidalgo y de otras entidades federativas</t>
-  </si>
-  <si>
-    <t>Onésimo Serrano queda al frente de Planeación tras renuncia de Miguel Tello</t>
-  </si>
-  <si>
     <t>Pachuca Brilla</t>
   </si>
   <si>
-    <t>Se mantienen lluvia y bajas temperaturas en Hidalgo</t>
-  </si>
-  <si>
-    <t>SSPH detienen en Huasca a dos personas con 45 billetes falsos</t>
-  </si>
-  <si>
-    <t>Detienen a dos hombres por presunto robo de medidor de agua en Pachuca</t>
-  </si>
-  <si>
     <t>Detención</t>
   </si>
   <si>
-    <t>Coloca Natividad Castrejón primera piedra del Bachillerato Nacional Margarita Maza en La Reforma</t>
-  </si>
-  <si>
-    <t>Julio Menchaca respalda llegada de nuevo coordinador estatal de la Guardia Nacional</t>
-  </si>
-  <si>
     <t>Tradición que sorprende</t>
   </si>
   <si>
@@ -591,34 +333,274 @@
     <t>Recuerda: la detección temprana salva vidas</t>
   </si>
   <si>
-    <t>Ediles podrán celebrar contratos sin autorización del cabildo</t>
-  </si>
-  <si>
-    <t>Nuevo titular de la Guardia Nacional en Hidalgo</t>
-  </si>
-  <si>
-    <t>Volvió a perder México, ahora frente a Chile</t>
-  </si>
-  <si>
-    <t>Amenazan con bloquear Boulevard Colosio</t>
-  </si>
-  <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
-    <t>Caasim</t>
-  </si>
-  <si>
-    <t>Abasto de agua</t>
-  </si>
-  <si>
-    <t>Logra cuautepequense medalla de bronce</t>
-  </si>
-  <si>
     <t>Inhide</t>
   </si>
   <si>
     <t>Paranacionales Conade</t>
+  </si>
+  <si>
+    <t>Economía mejorará con cementera</t>
+  </si>
+  <si>
+    <t>Bajan los reportes de desaparición</t>
+  </si>
+  <si>
+    <t>Personas desaparecidas</t>
+  </si>
+  <si>
+    <t>Celebran 15 años de fundación de Morena</t>
+  </si>
+  <si>
+    <t>Conmemoración Aniversario</t>
+  </si>
+  <si>
+    <t>Pantallas causan daños irreversibles a la vista</t>
+  </si>
+  <si>
+    <t>Prevención De Enfermedades</t>
+  </si>
+  <si>
+    <t>Molestia en usuarios del Monte de Piedad</t>
+  </si>
+  <si>
+    <t>Paro laboral</t>
+  </si>
+  <si>
+    <t>Recuperan el paso tras dos días incomunicadas</t>
+  </si>
+  <si>
+    <t>Atención Afectaciones Por Lluvias</t>
+  </si>
+  <si>
+    <t>Apoyan descuentos en licencias de negocios</t>
+  </si>
+  <si>
+    <t>Lluvias llenaron 4 de las 7 presas en la entidad</t>
+  </si>
+  <si>
+    <t>Conagua</t>
+  </si>
+  <si>
+    <t>Monitoreo De Presas</t>
+  </si>
+  <si>
+    <t>Clausuran gimnasio tras muerte de réferi</t>
+  </si>
+  <si>
+    <t>Clausura De Establecimiento</t>
+  </si>
+  <si>
+    <t>Espacios históricos, en el olvido</t>
+  </si>
+  <si>
+    <t>Conservación del Patrimonio Cultural</t>
+  </si>
+  <si>
+    <t>Buscan aún a 5 desaparecidos por la vaguada</t>
+  </si>
+  <si>
+    <t>Huracán Priscilla</t>
+  </si>
+  <si>
+    <t>Luego de la tragedia llega la reconstrucción</t>
+  </si>
+  <si>
+    <t>Apuesta por mentalidad</t>
+  </si>
+  <si>
+    <t>Aumentan cosecha en Paralimpiada Nacional</t>
+  </si>
+  <si>
+    <t>Avanza reconstrucción y reubicación de escuelas</t>
+  </si>
+  <si>
+    <t>En espera de recursos federales, a un año de la vaguada monzónica</t>
+  </si>
+  <si>
+    <t>Eficiencia educativa coloca al estado en top 10 nacional</t>
+  </si>
+  <si>
+    <t>Un avance de 30% en rezago reporta PGJEH</t>
+  </si>
+  <si>
+    <t>Rezago de carpetas de investigación</t>
+  </si>
+  <si>
+    <t>Apuestan en el Congreso por seguridad y salud: Velázquez; no descartó participar en el proceso electoral de 2027</t>
+  </si>
+  <si>
+    <t>Junta de Gobierno</t>
+  </si>
+  <si>
+    <t>La tragedia no doblegó a habitantes de Tianguistengo</t>
+  </si>
+  <si>
+    <t>Julio Menchaca ve más salidas de su equipo</t>
+  </si>
+  <si>
+    <t>Congreso da luz verde a la comparecencia del oficial mayor</t>
+  </si>
+  <si>
+    <t>Comparecencias</t>
+  </si>
+  <si>
+    <t>Familias de la Otomí-Tepehua dejan sus casas ante un nuevo temporal</t>
+  </si>
+  <si>
+    <t>Rusia descarta riesgo epidemiológico tras muerte de mujer por peste</t>
+  </si>
+  <si>
+    <t>Festeja Morena 15 años en el Auditorio Nacional</t>
+  </si>
+  <si>
+    <t>Fotonota</t>
+  </si>
+  <si>
+    <t>(A Gerardo Sosa) le acaban de revocar la vinculación en el juicio por defraudación  fiscal, uno de los que se le siguen (…); pero con todo y sus virtudes para librar  situaciones difíciles y mantenerse como grupo de permanencia, ahora, a través  del PT, parece que no cristalizará su obsesión: gobernar Hidalgo”.</t>
+  </si>
+  <si>
+    <t>Grupo Universidad</t>
+  </si>
+  <si>
+    <t>Refuerzan detección oportuna del cáncer de mama con 4 mil mastografías</t>
+  </si>
+  <si>
+    <t>IMSS</t>
+  </si>
+  <si>
+    <t>Urgen acciones contra mosco Culex ligado a proliferación de lirio en Endhó</t>
+  </si>
+  <si>
+    <t>Fumigación mosco Culex</t>
+  </si>
+  <si>
+    <t>Suman a oficial mayor a las comparecencias ante diputados locales</t>
+  </si>
+  <si>
+    <t>Arrestan a ""El Hijo de Fishman"" por presunto homicidio culposo</t>
+  </si>
+  <si>
+    <t>Detienen a ""El Hijo de Fishman"" por muerte de ""El Búho""</t>
+  </si>
+  <si>
+    <t>Oficial Mayor comparecerá ante la 66 Legislatura</t>
+  </si>
+  <si>
+    <t>El drama de la vida se dibujó  ayer en Pachuca, en un ring  donde un luchador quitó la  vida al réferi y a la altura de  un puente del Río de  las Avenidas desde  donde se aventó una  persona…</t>
+  </si>
+  <si>
+    <t>Editorial</t>
+  </si>
+  <si>
+    <t>Se tiró del puente vehicular de Viaducto Río Avenidas y murió</t>
+  </si>
+  <si>
+    <t>Suicidio</t>
+  </si>
+  <si>
+    <t>Se adelanta la disputa electoral: IEEH ya tiene 31 quejas</t>
+  </si>
+  <si>
+    <t>¿Tu CURP dice que estás desaparecido?</t>
+  </si>
+  <si>
+    <t>CBPEH</t>
+  </si>
+  <si>
+    <t>Detienen al Hijo de Fishman en Hidalgo</t>
+  </si>
+  <si>
+    <t>Tragedia en Pachuca</t>
+  </si>
+  <si>
+    <t>Tlanalapa se queda sin Ley de Ingresos 2027</t>
+  </si>
+  <si>
+    <t>Ley De Ingresos</t>
+  </si>
+  <si>
+    <t>Baja participación</t>
+  </si>
+  <si>
+    <t>Consulta Indígena</t>
+  </si>
+  <si>
+    <t>Analizan ampliar horario del Tuzobús ante mayor demanda</t>
+  </si>
+  <si>
+    <t>Sitmah</t>
+  </si>
+  <si>
+    <t>Ampliación de turno</t>
+  </si>
+  <si>
+    <t>Cruz Azul reactiva al 100% planta de Tula: Menchaca</t>
+  </si>
+  <si>
+    <t>Colocan primera piedra de nuevo Bachillerato Nacional en Tezontepec de Aldama, invertirán 20.4 mdp</t>
+  </si>
+  <si>
+    <t>Jorge Reyes fortalece la presencia municipal en Bugambilias a través de colonia x colonia</t>
+  </si>
+  <si>
+    <t>Alcalde</t>
+  </si>
+  <si>
+    <t>Atención a la ciudadanía</t>
+  </si>
+  <si>
+    <t>Más de 30 buscan coordinaciones distritales de Morena en Hidalgo</t>
+  </si>
+  <si>
+    <t>Referee hidalguense pierde la vida tras ""martinete"" en Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>Homicidios</t>
+  </si>
+  <si>
+    <t>Said Vargas asegura que permanecerá al frente de la Sección 15 hasta junio de 2027</t>
+  </si>
+  <si>
+    <t>Oficial Mayor de Hidalgo comparecerá ante Congreso</t>
+  </si>
+  <si>
+    <t>Interviene Policía de Pachuca ante reporte de presunta venta de droga</t>
+  </si>
+  <si>
+    <t>Combate Al Narcomenudeo</t>
+  </si>
+  <si>
+    <t>Resguarda Seguridad Pública de Pachuca a perrita</t>
+  </si>
+  <si>
+    <t>Ajacuba supera las 150 vacunas antirrábicas aplicadas</t>
+  </si>
+  <si>
+    <t>Vacunación Antirrábica</t>
+  </si>
+  <si>
+    <t>Octubre, mes de la prevención de cáncer de mama</t>
+  </si>
+  <si>
+    <t>Investigan la muerte de réferi El Búho en la 11 de julio; detienen a El Hijo de Fishman</t>
+  </si>
+  <si>
+    <t>Automovilista agrede a inspectores de transporte en Pachuca</t>
+  </si>
+  <si>
+    <t>Agresión a funcionario público</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón coloca primera piedra de Bachillerato Nacional en Tezontepec</t>
+  </si>
+  <si>
+    <t>Jorge Reyese fortalece la presencia municipal a través de Colonia x Colonia</t>
+  </si>
+  <si>
+    <t>Abarrotan Panteón Rococó y Moy Bobadilla la feria de San Francisco</t>
+  </si>
+  <si>
+    <t>OEEH</t>
   </si>
 </sst>
 </file>
@@ -772,12 +754,6 @@
   </cellStyles>
   <dxfs count="6">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="d/m/yy;@"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -819,6 +795,12 @@
           <color theme="4" tint="0.39997558519241921"/>
         </left>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="d/m/yy;@"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -865,15 +847,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J65" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J65" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J60" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J60" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{9D9ACAF2-1710-400E-A0E5-0A5BB378D4A0}" name="Fecha" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{9D9ACAF2-1710-400E-A0E5-0A5BB378D4A0}" name="Fecha" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{03A139BE-A997-45E6-81E6-5F7467162FC5}" name="Medio"/>
-    <tableColumn id="3" xr3:uid="{4CA37DD5-010E-43EE-907D-87C1845DB2AB}" name="Titular" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{4CA37DD5-010E-43EE-907D-87C1845DB2AB}" name="Titular" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{1E763E28-25D7-4FE7-AD1A-91C7A0FE0E7A}" name="Recurso editorial"/>
     <tableColumn id="5" xr3:uid="{F8C19AF2-6D19-449B-9F8B-6424964B1BCF}" name="Dependencia"/>
     <tableColumn id="6" xr3:uid="{46DF0510-7A9A-4625-979E-4EBC30CC7AA3}" name="Organismo"/>
@@ -905,13 +887,13 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}" name="Tabla3" displayName="Tabla3" ref="D1:E27" totalsRowShown="0" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}" name="Tabla3" displayName="Tabla3" ref="D1:E27" totalsRowShown="0" tableBorderDxfId="1">
   <autoFilter ref="D1:E27" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:E27">
     <sortCondition ref="D1:D27"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A040A308-8C62-4D4B-B3BE-EC124A9B961C}" name="Dependencia" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{A040A308-8C62-4D4B-B3BE-EC124A9B961C}" name="Dependencia" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{2B2FFCF1-496A-4D37-8C8B-790A66FD9968}" name="Nivel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1235,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1284,100 +1266,100 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B3" t="s">
         <v>81</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B4" t="s">
         <v>81</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1386,13 +1368,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B5" t="s">
         <v>81</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -1404,7 +1386,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -1420,32 +1402,32 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B6" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1454,32 +1436,32 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B7" t="s">
         <v>81</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1488,100 +1470,100 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="G9" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1590,127 +1572,127 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B12" t="s">
         <v>69</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
       </c>
       <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B14" t="s">
         <v>71</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
@@ -1726,28 +1708,28 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="G15" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="H15" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1755,188 +1737,188 @@
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
         <v>120</v>
       </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" t="s">
-        <v>70</v>
-      </c>
       <c r="H16" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H17" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J17" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
+        <v>46303</v>
+      </c>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J17" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
-        <v>46302</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18" t="s">
-        <v>11</v>
-      </c>
-      <c r="I18" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H19" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B20" t="s">
         <v>75</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="G20" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B21" t="s">
         <v>75</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
@@ -1948,10 +1930,10 @@
         <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1964,25 +1946,25 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B22" t="s">
         <v>75</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G22" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
@@ -1993,30 +1975,30 @@
       </c>
       <c r="J22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
@@ -2027,37 +2009,37 @@
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2066,32 +2048,32 @@
     </row>
     <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2100,66 +2082,66 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="E26" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G26" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Partidos</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="G27" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2168,297 +2150,297 @@
     </row>
     <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c r="G28" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="G29" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H29" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F30" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G30" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D31" t="s">
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="G31" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D32" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F32" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" t="s">
+        <v>94</v>
+      </c>
+      <c r="H32" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J32" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="11">
+        <v>46303</v>
+      </c>
+      <c r="B33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" t="s">
         <v>2</v>
       </c>
-      <c r="G32" t="s">
-        <v>140</v>
-      </c>
-      <c r="H32" t="s">
-        <v>72</v>
-      </c>
-      <c r="I32" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J32" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
-        <v>46302</v>
-      </c>
-      <c r="B33" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D33" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>10</v>
-      </c>
       <c r="G33" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="E34" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G34" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
       </c>
       <c r="I34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F35" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="H35" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G36" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
@@ -2472,102 +2454,102 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="G37" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B38" t="s">
         <v>73</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="G38" t="s">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B39" t="s">
         <v>73</v>
       </c>
       <c r="C39" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" t="s">
+        <v>85</v>
+      </c>
+      <c r="G39" t="s">
         <v>152</v>
       </c>
-      <c r="D39" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" t="s">
-        <v>153</v>
-      </c>
-      <c r="G39" t="s">
-        <v>154</v>
-      </c>
       <c r="H39" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2576,115 +2558,115 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B40" t="s">
         <v>73</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="H40" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B41" t="s">
         <v>73</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D41" t="s">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F41" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G41" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H41" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D42" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="E42" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F42" t="s">
-        <v>33</v>
+        <v>163</v>
       </c>
       <c r="G42" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="H42" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
@@ -2696,10 +2678,10 @@
         <v>24</v>
       </c>
       <c r="G43" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2712,28 +2694,28 @@
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B44" t="s">
         <v>82</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D44" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G44" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2741,18 +2723,18 @@
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B45" t="s">
         <v>82</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D45" t="s">
         <v>12</v>
@@ -2761,13 +2743,13 @@
         <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="G45" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H45" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2780,32 +2762,32 @@
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B46" t="s">
         <v>82</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G46" t="s">
-        <v>164</v>
+        <v>61</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Partidos</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2814,93 +2796,93 @@
     </row>
     <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B47" t="s">
         <v>82</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="G47" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B48" t="s">
         <v>82</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D48" t="s">
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B49" t="s">
         <v>82</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F49" t="s">
         <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -2916,66 +2898,66 @@
     </row>
     <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B50" t="s">
         <v>82</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="G50" t="s">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B51" t="s">
         <v>82</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="G51" t="s">
-        <v>171</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2984,100 +2966,100 @@
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B52" t="s">
         <v>82</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D52" t="s">
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F52" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
       </c>
       <c r="I52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B53" t="s">
         <v>82</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="D53" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="E53" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B54" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D54" t="s">
         <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F54" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="G54" t="s">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="H54" t="s">
         <v>11</v>
       </c>
       <c r="I54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -3086,25 +3068,25 @@
     </row>
     <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B55" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D55" t="s">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F55" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G55" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="H55" t="s">
         <v>11</v>
@@ -3120,96 +3102,96 @@
     </row>
     <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B56" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D56" t="s">
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F56" t="s">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="G56" t="s">
-        <v>178</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B57" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D57" t="s">
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>2</v>
+        <v>168</v>
       </c>
       <c r="G57" t="s">
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="H57" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B58" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D58" t="s">
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F58" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="G58" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="H58" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3217,18 +3199,18 @@
       </c>
       <c r="J58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B59" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>181</v>
+        <v>95</v>
       </c>
       <c r="D59" t="s">
         <v>80</v>
@@ -3240,7 +3222,7 @@
         <v>19</v>
       </c>
       <c r="G59" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="H59" t="s">
         <v>11</v>
@@ -3256,13 +3238,13 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B60" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>183</v>
+        <v>97</v>
       </c>
       <c r="D60" t="s">
         <v>80</v>
@@ -3286,176 +3268,6 @@
       <c r="J60" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="11">
-        <v>46302</v>
-      </c>
-      <c r="B61" t="s">
-        <v>77</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D61" t="s">
-        <v>12</v>
-      </c>
-      <c r="E61" t="s">
-        <v>33</v>
-      </c>
-      <c r="F61" t="s">
-        <v>33</v>
-      </c>
-      <c r="G61" t="s">
-        <v>117</v>
-      </c>
-      <c r="H61" t="s">
-        <v>11</v>
-      </c>
-      <c r="I61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="11">
-        <v>46302</v>
-      </c>
-      <c r="B62" t="s">
-        <v>77</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D62" t="s">
-        <v>12</v>
-      </c>
-      <c r="E62" t="s">
-        <v>24</v>
-      </c>
-      <c r="F62" t="s">
-        <v>24</v>
-      </c>
-      <c r="G62" t="s">
-        <v>122</v>
-      </c>
-      <c r="H62" t="s">
-        <v>11</v>
-      </c>
-      <c r="I62" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J62" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="11">
-        <v>46302</v>
-      </c>
-      <c r="B63" t="s">
-        <v>77</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D63" t="s">
-        <v>12</v>
-      </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" t="s">
-        <v>10</v>
-      </c>
-      <c r="G63" t="s">
-        <v>70</v>
-      </c>
-      <c r="H63" t="s">
-        <v>68</v>
-      </c>
-      <c r="I63" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J63" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="11">
-        <v>46302</v>
-      </c>
-      <c r="B64" t="s">
-        <v>77</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D64" t="s">
-        <v>12</v>
-      </c>
-      <c r="E64" t="s">
-        <v>188</v>
-      </c>
-      <c r="F64" t="s">
-        <v>189</v>
-      </c>
-      <c r="G64" t="s">
-        <v>190</v>
-      </c>
-      <c r="H64" t="s">
-        <v>68</v>
-      </c>
-      <c r="I64" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J64" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="11">
-        <v>46302</v>
-      </c>
-      <c r="B65" t="s">
-        <v>77</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="D65" t="s">
-        <v>12</v>
-      </c>
-      <c r="E65" t="s">
-        <v>26</v>
-      </c>
-      <c r="F65" t="s">
-        <v>192</v>
-      </c>
-      <c r="G65" t="s">
-        <v>193</v>
-      </c>
-      <c r="H65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I65" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J65" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
       </c>
     </row>
   </sheetData>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AD4B36-7F4C-4B7C-A212-52E81B9E72F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB28767-0DE7-40B3-B751-C56D8C89A3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="217">
   <si>
     <t>Fecha</t>
   </si>
@@ -294,313 +294,400 @@
     <t>Prevención cáncer de mama</t>
   </si>
   <si>
-    <t>Policía municipal</t>
-  </si>
-  <si>
-    <t>Afectaciones Por Lluvias</t>
-  </si>
-  <si>
     <t>Temas internacionales</t>
   </si>
   <si>
-    <t>Bachillerato Nacional</t>
-  </si>
-  <si>
-    <t>Cruz Azul</t>
-  </si>
-  <si>
     <t>Reforma De Ley</t>
   </si>
   <si>
-    <t>Eficiencia terminal</t>
-  </si>
-  <si>
-    <t>Rescate Animal</t>
-  </si>
-  <si>
     <t>Pachuca Brilla</t>
   </si>
   <si>
     <t>Detención</t>
   </si>
   <si>
-    <t>Tradición que sorprende</t>
-  </si>
-  <si>
     <t>Feria Pachuca</t>
   </si>
   <si>
     <t>Recuerda: la detección temprana salva vidas</t>
   </si>
   <si>
-    <t>Inhide</t>
-  </si>
-  <si>
-    <t>Paranacionales Conade</t>
-  </si>
-  <si>
-    <t>Economía mejorará con cementera</t>
-  </si>
-  <si>
-    <t>Bajan los reportes de desaparición</t>
-  </si>
-  <si>
-    <t>Personas desaparecidas</t>
-  </si>
-  <si>
-    <t>Celebran 15 años de fundación de Morena</t>
-  </si>
-  <si>
-    <t>Conmemoración Aniversario</t>
-  </si>
-  <si>
-    <t>Pantallas causan daños irreversibles a la vista</t>
-  </si>
-  <si>
     <t>Prevención De Enfermedades</t>
   </si>
   <si>
-    <t>Molestia en usuarios del Monte de Piedad</t>
-  </si>
-  <si>
-    <t>Paro laboral</t>
-  </si>
-  <si>
-    <t>Recuperan el paso tras dos días incomunicadas</t>
-  </si>
-  <si>
     <t>Atención Afectaciones Por Lluvias</t>
   </si>
   <si>
-    <t>Apoyan descuentos en licencias de negocios</t>
-  </si>
-  <si>
-    <t>Lluvias llenaron 4 de las 7 presas en la entidad</t>
-  </si>
-  <si>
-    <t>Conagua</t>
-  </si>
-  <si>
-    <t>Monitoreo De Presas</t>
-  </si>
-  <si>
-    <t>Clausuran gimnasio tras muerte de réferi</t>
-  </si>
-  <si>
-    <t>Clausura De Establecimiento</t>
-  </si>
-  <si>
-    <t>Espacios históricos, en el olvido</t>
-  </si>
-  <si>
-    <t>Conservación del Patrimonio Cultural</t>
-  </si>
-  <si>
-    <t>Buscan aún a 5 desaparecidos por la vaguada</t>
-  </si>
-  <si>
     <t>Huracán Priscilla</t>
   </si>
   <si>
-    <t>Luego de la tragedia llega la reconstrucción</t>
-  </si>
-  <si>
-    <t>Apuesta por mentalidad</t>
-  </si>
-  <si>
-    <t>Aumentan cosecha en Paralimpiada Nacional</t>
-  </si>
-  <si>
-    <t>Avanza reconstrucción y reubicación de escuelas</t>
-  </si>
-  <si>
-    <t>En espera de recursos federales, a un año de la vaguada monzónica</t>
-  </si>
-  <si>
-    <t>Eficiencia educativa coloca al estado en top 10 nacional</t>
-  </si>
-  <si>
-    <t>Un avance de 30% en rezago reporta PGJEH</t>
-  </si>
-  <si>
-    <t>Rezago de carpetas de investigación</t>
-  </si>
-  <si>
-    <t>Apuestan en el Congreso por seguridad y salud: Velázquez; no descartó participar en el proceso electoral de 2027</t>
-  </si>
-  <si>
     <t>Junta de Gobierno</t>
   </si>
   <si>
-    <t>La tragedia no doblegó a habitantes de Tianguistengo</t>
-  </si>
-  <si>
-    <t>Julio Menchaca ve más salidas de su equipo</t>
-  </si>
-  <si>
-    <t>Congreso da luz verde a la comparecencia del oficial mayor</t>
-  </si>
-  <si>
-    <t>Comparecencias</t>
-  </si>
-  <si>
-    <t>Familias de la Otomí-Tepehua dejan sus casas ante un nuevo temporal</t>
-  </si>
-  <si>
-    <t>Rusia descarta riesgo epidemiológico tras muerte de mujer por peste</t>
-  </si>
-  <si>
-    <t>Festeja Morena 15 años en el Auditorio Nacional</t>
-  </si>
-  <si>
     <t>Fotonota</t>
   </si>
   <si>
-    <t>(A Gerardo Sosa) le acaban de revocar la vinculación en el juicio por defraudación  fiscal, uno de los que se le siguen (…); pero con todo y sus virtudes para librar  situaciones difíciles y mantenerse como grupo de permanencia, ahora, a través  del PT, parece que no cristalizará su obsesión: gobernar Hidalgo”.</t>
-  </si>
-  <si>
-    <t>Grupo Universidad</t>
-  </si>
-  <si>
-    <t>Refuerzan detección oportuna del cáncer de mama con 4 mil mastografías</t>
-  </si>
-  <si>
     <t>IMSS</t>
   </si>
   <si>
-    <t>Urgen acciones contra mosco Culex ligado a proliferación de lirio en Endhó</t>
-  </si>
-  <si>
-    <t>Fumigación mosco Culex</t>
-  </si>
-  <si>
-    <t>Suman a oficial mayor a las comparecencias ante diputados locales</t>
-  </si>
-  <si>
-    <t>Arrestan a ""El Hijo de Fishman"" por presunto homicidio culposo</t>
-  </si>
-  <si>
-    <t>Detienen a ""El Hijo de Fishman"" por muerte de ""El Búho""</t>
-  </si>
-  <si>
-    <t>Oficial Mayor comparecerá ante la 66 Legislatura</t>
-  </si>
-  <si>
-    <t>El drama de la vida se dibujó  ayer en Pachuca, en un ring  donde un luchador quitó la  vida al réferi y a la altura de  un puente del Río de  las Avenidas desde  donde se aventó una  persona…</t>
-  </si>
-  <si>
-    <t>Editorial</t>
-  </si>
-  <si>
-    <t>Se tiró del puente vehicular de Viaducto Río Avenidas y murió</t>
-  </si>
-  <si>
-    <t>Suicidio</t>
-  </si>
-  <si>
-    <t>Se adelanta la disputa electoral: IEEH ya tiene 31 quejas</t>
-  </si>
-  <si>
-    <t>¿Tu CURP dice que estás desaparecido?</t>
-  </si>
-  <si>
     <t>CBPEH</t>
   </si>
   <si>
-    <t>Detienen al Hijo de Fishman en Hidalgo</t>
-  </si>
-  <si>
-    <t>Tragedia en Pachuca</t>
-  </si>
-  <si>
-    <t>Tlanalapa se queda sin Ley de Ingresos 2027</t>
-  </si>
-  <si>
-    <t>Ley De Ingresos</t>
-  </si>
-  <si>
-    <t>Baja participación</t>
-  </si>
-  <si>
-    <t>Consulta Indígena</t>
-  </si>
-  <si>
-    <t>Analizan ampliar horario del Tuzobús ante mayor demanda</t>
-  </si>
-  <si>
-    <t>Sitmah</t>
-  </si>
-  <si>
-    <t>Ampliación de turno</t>
-  </si>
-  <si>
-    <t>Cruz Azul reactiva al 100% planta de Tula: Menchaca</t>
-  </si>
-  <si>
-    <t>Colocan primera piedra de nuevo Bachillerato Nacional en Tezontepec de Aldama, invertirán 20.4 mdp</t>
-  </si>
-  <si>
-    <t>Jorge Reyes fortalece la presencia municipal en Bugambilias a través de colonia x colonia</t>
-  </si>
-  <si>
     <t>Alcalde</t>
   </si>
   <si>
-    <t>Atención a la ciudadanía</t>
-  </si>
-  <si>
-    <t>Más de 30 buscan coordinaciones distritales de Morena en Hidalgo</t>
-  </si>
-  <si>
-    <t>Referee hidalguense pierde la vida tras ""martinete"" en Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Homicidios</t>
-  </si>
-  <si>
-    <t>Said Vargas asegura que permanecerá al frente de la Sección 15 hasta junio de 2027</t>
-  </si>
-  <si>
-    <t>Oficial Mayor de Hidalgo comparecerá ante Congreso</t>
-  </si>
-  <si>
-    <t>Interviene Policía de Pachuca ante reporte de presunta venta de droga</t>
-  </si>
-  <si>
     <t>Combate Al Narcomenudeo</t>
   </si>
   <si>
-    <t>Resguarda Seguridad Pública de Pachuca a perrita</t>
-  </si>
-  <si>
-    <t>Ajacuba supera las 150 vacunas antirrábicas aplicadas</t>
-  </si>
-  <si>
-    <t>Vacunación Antirrábica</t>
-  </si>
-  <si>
-    <t>Octubre, mes de la prevención de cáncer de mama</t>
-  </si>
-  <si>
-    <t>Investigan la muerte de réferi El Búho en la 11 de julio; detienen a El Hijo de Fishman</t>
-  </si>
-  <si>
-    <t>Automovilista agrede a inspectores de transporte en Pachuca</t>
-  </si>
-  <si>
-    <t>Agresión a funcionario público</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón coloca primera piedra de Bachillerato Nacional en Tezontepec</t>
-  </si>
-  <si>
-    <t>Jorge Reyese fortalece la presencia municipal a través de Colonia x Colonia</t>
-  </si>
-  <si>
-    <t>Abarrotan Panteón Rococó y Moy Bobadilla la feria de San Francisco</t>
-  </si>
-  <si>
     <t>OEEH</t>
+  </si>
+  <si>
+    <t>Chinicuiles tienen propiedades curativas</t>
+  </si>
+  <si>
+    <t>En marcha los registros municipales en Morena</t>
+  </si>
+  <si>
+    <t>García Harfuch niega pesquisas contra Olán</t>
+  </si>
+  <si>
+    <t>Seguridad Ciudadana</t>
+  </si>
+  <si>
+    <t>Crimen Organizado</t>
+  </si>
+  <si>
+    <t>Necesario frenar la mancha urbana: Tello</t>
+  </si>
+  <si>
+    <t>Extitular</t>
+  </si>
+  <si>
+    <t>Ordenamiento Territorial</t>
+  </si>
+  <si>
+    <t>Escuelas en riesgo por falta de alumnos</t>
+  </si>
+  <si>
+    <t>Dinámica demográfica</t>
+  </si>
+  <si>
+    <t>Rechazan el proyecto de nuevo plantel</t>
+  </si>
+  <si>
+    <t>Conflicto predio escolar</t>
+  </si>
+  <si>
+    <t>Lanza Morena convocatoria para ayuntamientos</t>
+  </si>
+  <si>
+    <t>El Búho emprende el vuelo</t>
+  </si>
+  <si>
+    <t>Homenaje póstumo</t>
+  </si>
+  <si>
+    <t>Huehuetla se levanta a un año de la vaguada</t>
+  </si>
+  <si>
+    <t>Muestra su obra en Nueva York</t>
+  </si>
+  <si>
+    <t>Exposición Artística</t>
+  </si>
+  <si>
+    <t>Ubican a 10 desaparecidos por su CURP</t>
+  </si>
+  <si>
+    <t>Localización de persona</t>
+  </si>
+  <si>
+    <t>Pide Instituto Electoral 23 mdp extra por elecciones</t>
+  </si>
+  <si>
+    <t>Presupuesto IEEH</t>
+  </si>
+  <si>
+    <t>Pide Olivares atender alertas ante lluvias</t>
+  </si>
+  <si>
+    <t>Alerta Meteorológica</t>
+  </si>
+  <si>
+    <t>Defiende Moreno reforma para que alcaldes firmen sin el aval de regidores</t>
+  </si>
+  <si>
+    <t>Sexoservicio, actividad con riesgos y sacrificio</t>
+  </si>
+  <si>
+    <t>Salud sexual</t>
+  </si>
+  <si>
+    <t>Chivas, base del nuevo TRI</t>
+  </si>
+  <si>
+    <t>Emprende vuelo a la inmortalidad</t>
+  </si>
+  <si>
+    <t>Presentan el Xantolo en la Ciudad de México</t>
+  </si>
+  <si>
+    <t>Xantolo</t>
+  </si>
+  <si>
+    <t>A un año de la vaguada, siguen desaparecidas cinco personas</t>
+  </si>
+  <si>
+    <t>Damnificados acusan poco recurso para reubicación</t>
+  </si>
+  <si>
+    <t>Reubicación de viviendas</t>
+  </si>
+  <si>
+    <t>Se restablece el aso en cruces afectados por lluvias</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Tribunal señala excesos en sentencias del TEEH</t>
+  </si>
+  <si>
+    <t>Sentencia</t>
+  </si>
+  <si>
+    <t>Despiden a El Búho, réferi fallecido durante lucha libre</t>
+  </si>
+  <si>
+    <t>Inicia el lunes la campaña de vacunación contra el Covid</t>
+  </si>
+  <si>
+    <t>Vacunación</t>
+  </si>
+  <si>
+    <t>Harfuch rechaza tener ""agenda paralela"" a 2030</t>
+  </si>
+  <si>
+    <t>Buscan evitar la fuga de talento hidalguense</t>
+  </si>
+  <si>
+    <t>Fuga de cerebros</t>
+  </si>
+  <si>
+    <t>Dice Morena a PT: ""ni presión de EU ni recesiones a los grupos de interés""</t>
+  </si>
+  <si>
+    <t>Intervención extranjera</t>
+  </si>
+  <si>
+    <t>Destrabar inversiones, pide la Amcham a la Presidenta</t>
+  </si>
+  <si>
+    <t>Exhorto</t>
+  </si>
+  <si>
+    <t>Brasil es un presagio del futuro para América Latina</t>
+  </si>
+  <si>
+    <t>Morena emite convocatoria para coordinadores municipales</t>
+  </si>
+  <si>
+    <t>Avanzan trabajos para construir nuevo Salón de Plenos</t>
+  </si>
+  <si>
+    <t>Salón De Plenos</t>
+  </si>
+  <si>
+    <t>Segob niega retención de sindicalistas</t>
+  </si>
+  <si>
+    <t>Gobernación</t>
+  </si>
+  <si>
+    <t>Retención</t>
+  </si>
+  <si>
+    <t>Zonas Metropolitanas encabezan denuncias por delitos sexuales</t>
+  </si>
+  <si>
+    <t>Abuso Sexual</t>
+  </si>
+  <si>
+    <t>Riña en penal de Mazatlán deja 10 muertos</t>
+  </si>
+  <si>
+    <t>Deficiencias en penales</t>
+  </si>
+  <si>
+    <t>Amistad, cooperación, resiliencia, buena voluntad, transparencia y rendición de cuentas: retos  mundiales contra el patriarcado”.</t>
+  </si>
+  <si>
+    <t>Erradicación Violencia De Género</t>
+  </si>
+  <si>
+    <t>Dan último adiós a Gerado Germán Pineda, "El Búho", en Pachuca</t>
+  </si>
+  <si>
+    <t>A un año de la vaguada monzónica, sigue la búsqueda de cinco personas</t>
+  </si>
+  <si>
+    <t>Ordena Tribunal Electoral repetir elección de autoridades auxiliares en San Ildefonso</t>
+  </si>
+  <si>
+    <t>Impugnación</t>
+  </si>
+  <si>
+    <t>Orden ministerial derivó en exhumación de cuerpos en presuntas tumbas clandestinas en Atotonilco</t>
+  </si>
+  <si>
+    <t>Exhumación</t>
+  </si>
+  <si>
+    <t>Destruyen droga y material vinculado a actividades delictivas</t>
+  </si>
+  <si>
+    <t>FGR</t>
+  </si>
+  <si>
+    <t>Combate a la delincuencia</t>
+  </si>
+  <si>
+    <t>Restablecen parcialmente circulación en carreteras de Hidalgo</t>
+  </si>
+  <si>
+    <t>Hidalgo, con el mayor porcentaje de beneficiados de programas de justicia social</t>
+  </si>
+  <si>
+    <t>ISSSTE</t>
+  </si>
+  <si>
+    <t>Justicia social</t>
+  </si>
+  <si>
+    <t>Zafarrancho en el penal de Mazatlán 10 muertos y 16 heridos</t>
+  </si>
+  <si>
+    <t>Cayeron cinco; suplantaban y extorsionaban a sus víctimas</t>
+  </si>
+  <si>
+    <t>El empleo formal alcanza récord de 22. millones de puestos</t>
+  </si>
+  <si>
+    <t>Generación de empleos</t>
+  </si>
+  <si>
+    <t>SNTE Hidalgo busca regularizar plazas de docentes</t>
+  </si>
+  <si>
+    <t>Derechos laborales</t>
+  </si>
+  <si>
+    <t>INE busca 48 consejeros distritales en Hidalgo</t>
+  </si>
+  <si>
+    <t>Morena abre registro para coordinadores municipales en Hidalgo</t>
+  </si>
+  <si>
+    <t>Congreso aplaza nombramiento en el TEEH</t>
+  </si>
+  <si>
+    <t>Nombramientos</t>
+  </si>
+  <si>
+    <t>Pleito interno en el IEEH</t>
+  </si>
+  <si>
+    <t>Fortalecen la detección oportuna de cardiopatías en recién nacidos</t>
+  </si>
+  <si>
+    <t>Transparencia para el Pueblo de Hidalgo: más con menos presupuesto</t>
+  </si>
+  <si>
+    <t>Extinción ITAIH</t>
+  </si>
+  <si>
+    <t>Menchaca revisa proyectos para la construcción de viviendas en Hidalgo</t>
+  </si>
+  <si>
+    <t>Plan Nacional De Vivienda</t>
+  </si>
+  <si>
+    <t>Metepec y Acaxochitlán se suman a la Ruta Hidalgo Inspira de la CDHEH</t>
+  </si>
+  <si>
+    <t>Coordinación Interinstitucional</t>
+  </si>
+  <si>
+    <t>Zitlaly Zúñiga instala el Consejo Municipal de participación escolar en la educación</t>
+  </si>
+  <si>
+    <t>Instalación de consejo municipal</t>
+  </si>
+  <si>
+    <t>El IEEH presenta informe sobre los Foros Regionales de Diálogo en materia indígena para la implementación de la Acción Afirmativa en el PEL</t>
+  </si>
+  <si>
+    <t>Acción afirmativa</t>
+  </si>
+  <si>
+    <t>Hidalgo alcanza 93.26% de efectividad en localización de personas</t>
+  </si>
+  <si>
+    <t>Miguel Tello inicia recorridos en Pachuca para defender la Transformación y Soberanía</t>
+  </si>
+  <si>
+    <t>Con más de 10 mdp, Sebiso impulsa la autonomía y bienestar de personas cuidadorsas y comunidad LGBTTTI</t>
+  </si>
+  <si>
+    <t>Inhjuve</t>
+  </si>
+  <si>
+    <t>Inclusión sexogenérica</t>
+  </si>
+  <si>
+    <t>Invitan a jóvenes de hidalgo a formarse como auditores en 2027</t>
+  </si>
+  <si>
+    <t>Convocatoria</t>
+  </si>
+  <si>
+    <t>61 niñas, niños y adolescentes encontraron un hogar a través de la adopción</t>
+  </si>
+  <si>
+    <t>Adopción De Menores</t>
+  </si>
+  <si>
+    <t>Julio Menchaca revisa proyectos para la construcción de viviendas en Hidalgo</t>
+  </si>
+  <si>
+    <t>Conquista Banda MS el Palenque</t>
+  </si>
+  <si>
+    <t>tur</t>
+  </si>
+  <si>
+    <t>oee</t>
+  </si>
+  <si>
+    <t>En Pachuca y Huasca, SSPH asegura cera de 4 mil dosos de presunta droga</t>
+  </si>
+  <si>
+    <t>Investigación de la UTEC será publicada en revista internacional</t>
+  </si>
+  <si>
+    <t>Universidades</t>
+  </si>
+  <si>
+    <t>Innovación tecnológica</t>
+  </si>
+  <si>
+    <t>90s Pop Tuour contagió energía en la feria</t>
+  </si>
+  <si>
+    <t>3,328 niñas, niños y adolescentes recibieron atención médica gratuita con Código Guinda</t>
+  </si>
+  <si>
+    <t>Informe de actividades</t>
   </si>
 </sst>
 </file>
@@ -847,8 +934,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J60" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J60" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J69" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J69" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1217,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1266,13 +1353,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -1284,10 +1371,10 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1300,41 +1387,41 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B3" t="s">
         <v>81</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B4" t="s">
         <v>81</v>
@@ -1346,20 +1433,20 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="G4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1368,50 +1455,50 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B5" t="s">
         <v>81</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="G5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B6" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -1420,10 +1507,10 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1436,66 +1523,66 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B7" t="s">
         <v>81</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1504,32 +1591,32 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1538,32 +1625,32 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1572,7 +1659,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
@@ -1584,20 +1671,20 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1606,7 +1693,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B12" t="s">
         <v>69</v>
@@ -1621,13 +1708,13 @@
         <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="G12" t="s">
         <v>120</v>
       </c>
       <c r="H12" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1640,7 +1727,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B13" t="s">
         <v>69</v>
@@ -1652,20 +1739,20 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G13" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
       </c>
       <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1674,96 +1761,96 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B14" t="s">
         <v>71</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
       </c>
       <c r="I14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1774,98 +1861,98 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G17" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1876,68 +1963,68 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B20" t="s">
         <v>75</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="G20" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B21" t="s">
         <v>75</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="H21" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1946,28 +2033,28 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B22" t="s">
         <v>75</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="F22" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="G22" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="H22" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1975,55 +2062,55 @@
       </c>
       <c r="J22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -2032,10 +2119,10 @@
         <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="H24" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2048,270 +2135,270 @@
     </row>
     <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F26" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="G26" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H27" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>146</v>
+      </c>
+      <c r="H28" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J28" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
         <v>14</v>
       </c>
-      <c r="F28" t="s">
-        <v>142</v>
-      </c>
-      <c r="G28" t="s">
-        <v>84</v>
-      </c>
-      <c r="H28" t="s">
-        <v>11</v>
-      </c>
-      <c r="I28" t="str">
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>148</v>
+      </c>
+      <c r="H29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Presidencia de la República</v>
       </c>
-      <c r="J28" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="11">
-        <v>46303</v>
-      </c>
-      <c r="B29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D29" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" t="s">
-        <v>33</v>
-      </c>
-      <c r="F29" t="s">
-        <v>33</v>
-      </c>
-      <c r="G29" t="s">
-        <v>144</v>
-      </c>
-      <c r="H29" t="s">
-        <v>11</v>
-      </c>
-      <c r="I29" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D31" t="s">
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="G31" t="s">
+        <v>61</v>
+      </c>
+      <c r="H31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J31" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D32" t="s">
+        <v>95</v>
+      </c>
+      <c r="E32" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" t="s">
         <v>94</v>
       </c>
-      <c r="H31" t="s">
-        <v>11</v>
-      </c>
-      <c r="I31" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J31" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="11">
-        <v>46303</v>
-      </c>
-      <c r="B32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D32" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" t="s">
-        <v>16</v>
-      </c>
-      <c r="F32" t="s">
-        <v>85</v>
-      </c>
       <c r="G32" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2320,304 +2407,304 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F33" t="s">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="G33" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="H33" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J33" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" t="s">
+        <v>157</v>
+      </c>
+      <c r="H34" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J33" t="str">
+      <c r="J34" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A34" s="11">
-        <v>46303</v>
-      </c>
-      <c r="B34" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D34" t="s">
-        <v>150</v>
-      </c>
-      <c r="E34" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
         <v>10</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F35" t="s">
         <v>10</v>
       </c>
-      <c r="G34" t="s">
-        <v>78</v>
-      </c>
-      <c r="H34" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J34" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="11">
-        <v>46303</v>
-      </c>
-      <c r="B35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D35" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" t="s">
-        <v>16</v>
-      </c>
       <c r="G35" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" t="s">
+        <v>161</v>
+      </c>
+      <c r="H36" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J36" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B37" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D37" t="s">
         <v>13</v>
       </c>
-      <c r="E36" t="s">
-        <v>40</v>
-      </c>
-      <c r="F36" t="s">
-        <v>40</v>
-      </c>
-      <c r="G36" t="s">
-        <v>42</v>
-      </c>
-      <c r="H36" t="s">
-        <v>11</v>
-      </c>
-      <c r="I36" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J36" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="11">
-        <v>46303</v>
-      </c>
-      <c r="B37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D37" t="s">
-        <v>12</v>
-      </c>
       <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" t="s">
+        <v>115</v>
+      </c>
+      <c r="H37" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J37" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" t="s">
         <v>23</v>
       </c>
-      <c r="F37" t="s">
-        <v>155</v>
-      </c>
-      <c r="G37" t="s">
-        <v>102</v>
-      </c>
-      <c r="H37" t="s">
-        <v>11</v>
-      </c>
-      <c r="I37" t="str">
+      <c r="F38" t="s">
+        <v>97</v>
+      </c>
+      <c r="G38" t="s">
+        <v>93</v>
+      </c>
+      <c r="H38" t="s">
+        <v>11</v>
+      </c>
+      <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J37" t="str">
+      <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="11">
-        <v>46303</v>
-      </c>
-      <c r="B38" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D38" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" t="s">
-        <v>16</v>
-      </c>
-      <c r="F38" t="s">
-        <v>85</v>
-      </c>
-      <c r="G38" t="s">
-        <v>94</v>
-      </c>
-      <c r="H38" t="s">
-        <v>11</v>
-      </c>
-      <c r="I38" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J38" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="F39" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="G39" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G40" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H40" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D41" t="s">
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F41" t="s">
-        <v>40</v>
+        <v>169</v>
       </c>
       <c r="G41" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H41" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2626,25 +2713,25 @@
     </row>
     <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="D42" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="F42" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="G42" t="s">
-        <v>164</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s">
         <v>72</v>
@@ -2658,102 +2745,102 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F43" t="s">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="G43" t="s">
-        <v>89</v>
+        <v>174</v>
       </c>
       <c r="H43" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B44" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F44" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="H44" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B45" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="D45" t="s">
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F45" t="s">
-        <v>168</v>
+        <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>169</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2762,84 +2849,84 @@
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B46" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D46" t="s">
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F46" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="G46" t="s">
-        <v>61</v>
+        <v>178</v>
       </c>
       <c r="H46" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B47" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="G47" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H47" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B48" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D48" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
@@ -2848,7 +2935,7 @@
         <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
@@ -2862,68 +2949,68 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B49" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D49" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F49" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G49" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
       </c>
       <c r="I49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B50" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F50" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="G50" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2932,32 +3019,32 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B51" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F51" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="G51" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2966,202 +3053,202 @@
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B52" t="s">
         <v>82</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D52" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="E52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="H52" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B53" t="s">
         <v>82</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D53" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G53" t="s">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="H53" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D54" t="s">
         <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F54" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="G54" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="H54" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B55" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D55" t="s">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="F55" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G55" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H55" t="s">
         <v>11</v>
       </c>
       <c r="I55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B56" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D56" t="s">
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F56" t="s">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="G56" t="s">
-        <v>88</v>
+        <v>194</v>
       </c>
       <c r="H56" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D57" t="s">
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F57" t="s">
-        <v>168</v>
+        <v>40</v>
       </c>
       <c r="G57" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="H57" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -3170,25 +3257,25 @@
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D58" t="s">
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F58" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="G58" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="H58" t="s">
         <v>72</v>
@@ -3202,70 +3289,376 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" t="s">
+        <v>47</v>
+      </c>
+      <c r="F59" t="s">
+        <v>107</v>
+      </c>
+      <c r="G59" t="s">
+        <v>61</v>
+      </c>
+      <c r="H59" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J59" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A60" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B60" t="s">
+        <v>82</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" t="s">
+        <v>200</v>
+      </c>
+      <c r="G60" t="s">
+        <v>201</v>
+      </c>
+      <c r="H60" t="s">
+        <v>72</v>
+      </c>
+      <c r="I60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J60" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B61" t="s">
+        <v>82</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F61" t="s">
+        <v>34</v>
+      </c>
+      <c r="G61" t="s">
+        <v>203</v>
+      </c>
+      <c r="H61" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B62" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D62" t="s">
         <v>80</v>
       </c>
-      <c r="E59" t="s">
-        <v>19</v>
-      </c>
-      <c r="F59" t="s">
-        <v>19</v>
-      </c>
-      <c r="G59" t="s">
-        <v>96</v>
-      </c>
-      <c r="H59" t="s">
-        <v>11</v>
-      </c>
-      <c r="I59" t="str">
+      <c r="E62" t="s">
+        <v>36</v>
+      </c>
+      <c r="F62" t="s">
+        <v>36</v>
+      </c>
+      <c r="G62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H62" t="s">
+        <v>72</v>
+      </c>
+      <c r="I62" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Gobierno del estado</v>
       </c>
-      <c r="J59" t="str">
+      <c r="J62" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="11">
-        <v>46303</v>
-      </c>
-      <c r="B60" t="s">
-        <v>93</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D60" t="s">
+    <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B63" t="s">
+        <v>87</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" t="s">
+        <v>24</v>
+      </c>
+      <c r="G63" t="s">
+        <v>190</v>
+      </c>
+      <c r="H63" t="s">
+        <v>72</v>
+      </c>
+      <c r="I63" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J63" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B64" t="s">
+        <v>87</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" t="s">
+        <v>208</v>
+      </c>
+      <c r="F64" t="s">
+        <v>209</v>
+      </c>
+      <c r="G64" t="s">
+        <v>89</v>
+      </c>
+      <c r="H64" t="s">
+        <v>72</v>
+      </c>
+      <c r="I64" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>XXX</v>
+      </c>
+      <c r="J64" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B65" t="s">
+        <v>87</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D65" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" t="s">
+        <v>22</v>
+      </c>
+      <c r="F65" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65" t="s">
+        <v>99</v>
+      </c>
+      <c r="H65" t="s">
+        <v>11</v>
+      </c>
+      <c r="I65" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J65" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B66" t="s">
+        <v>87</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F66" t="s">
+        <v>212</v>
+      </c>
+      <c r="G66" t="s">
+        <v>213</v>
+      </c>
+      <c r="H66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I66" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J66" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B67" t="s">
+        <v>87</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D67" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67" t="s">
+        <v>100</v>
+      </c>
+      <c r="G67" t="s">
+        <v>89</v>
+      </c>
+      <c r="H67" t="s">
+        <v>72</v>
+      </c>
+      <c r="I67" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J67" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B68" t="s">
+        <v>87</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D68" t="s">
         <v>80</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E68" t="s">
+        <v>36</v>
+      </c>
+      <c r="F68" t="s">
+        <v>36</v>
+      </c>
+      <c r="G68" t="s">
+        <v>216</v>
+      </c>
+      <c r="H68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I68" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J68" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B69" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D69" t="s">
+        <v>80</v>
+      </c>
+      <c r="E69" t="s">
         <v>16</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F69" t="s">
         <v>16</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G69" t="s">
         <v>84</v>
       </c>
-      <c r="H60" t="s">
-        <v>11</v>
-      </c>
-      <c r="I60" t="str">
+      <c r="H69" t="s">
+        <v>11</v>
+      </c>
+      <c r="I69" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Alcaldías</v>
       </c>
-      <c r="J60" t="str">
+      <c r="J69" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB28767-0DE7-40B3-B751-C56D8C89A3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB62FED0-40E9-454A-A6F6-18281D7B56DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="206">
   <si>
     <t>Fecha</t>
   </si>
@@ -294,9 +294,6 @@
     <t>Prevención cáncer de mama</t>
   </si>
   <si>
-    <t>Temas internacionales</t>
-  </si>
-  <si>
     <t>Reforma De Ley</t>
   </si>
   <si>
@@ -309,12 +306,6 @@
     <t>Feria Pachuca</t>
   </si>
   <si>
-    <t>Recuerda: la detección temprana salva vidas</t>
-  </si>
-  <si>
-    <t>Prevención De Enfermedades</t>
-  </si>
-  <si>
     <t>Atención Afectaciones Por Lluvias</t>
   </si>
   <si>
@@ -324,370 +315,346 @@
     <t>Junta de Gobierno</t>
   </si>
   <si>
-    <t>Fotonota</t>
-  </si>
-  <si>
     <t>IMSS</t>
   </si>
   <si>
-    <t>CBPEH</t>
-  </si>
-  <si>
     <t>Alcalde</t>
   </si>
   <si>
-    <t>Combate Al Narcomenudeo</t>
-  </si>
-  <si>
     <t>OEEH</t>
   </si>
   <si>
-    <t>Chinicuiles tienen propiedades curativas</t>
-  </si>
-  <si>
-    <t>En marcha los registros municipales en Morena</t>
-  </si>
-  <si>
-    <t>García Harfuch niega pesquisas contra Olán</t>
-  </si>
-  <si>
-    <t>Seguridad Ciudadana</t>
-  </si>
-  <si>
-    <t>Crimen Organizado</t>
-  </si>
-  <si>
-    <t>Necesario frenar la mancha urbana: Tello</t>
-  </si>
-  <si>
     <t>Extitular</t>
   </si>
   <si>
-    <t>Ordenamiento Territorial</t>
-  </si>
-  <si>
-    <t>Escuelas en riesgo por falta de alumnos</t>
-  </si>
-  <si>
-    <t>Dinámica demográfica</t>
-  </si>
-  <si>
-    <t>Rechazan el proyecto de nuevo plantel</t>
-  </si>
-  <si>
-    <t>Conflicto predio escolar</t>
-  </si>
-  <si>
-    <t>Lanza Morena convocatoria para ayuntamientos</t>
-  </si>
-  <si>
-    <t>El Búho emprende el vuelo</t>
-  </si>
-  <si>
-    <t>Homenaje póstumo</t>
-  </si>
-  <si>
-    <t>Huehuetla se levanta a un año de la vaguada</t>
-  </si>
-  <si>
-    <t>Muestra su obra en Nueva York</t>
-  </si>
-  <si>
     <t>Exposición Artística</t>
   </si>
   <si>
-    <t>Ubican a 10 desaparecidos por su CURP</t>
-  </si>
-  <si>
-    <t>Localización de persona</t>
-  </si>
-  <si>
-    <t>Pide Instituto Electoral 23 mdp extra por elecciones</t>
-  </si>
-  <si>
-    <t>Presupuesto IEEH</t>
-  </si>
-  <si>
-    <t>Pide Olivares atender alertas ante lluvias</t>
-  </si>
-  <si>
-    <t>Alerta Meteorológica</t>
-  </si>
-  <si>
-    <t>Defiende Moreno reforma para que alcaldes firmen sin el aval de regidores</t>
-  </si>
-  <si>
-    <t>Sexoservicio, actividad con riesgos y sacrificio</t>
-  </si>
-  <si>
-    <t>Salud sexual</t>
-  </si>
-  <si>
-    <t>Chivas, base del nuevo TRI</t>
-  </si>
-  <si>
-    <t>Emprende vuelo a la inmortalidad</t>
-  </si>
-  <si>
-    <t>Presentan el Xantolo en la Ciudad de México</t>
-  </si>
-  <si>
-    <t>Xantolo</t>
-  </si>
-  <si>
-    <t>A un año de la vaguada, siguen desaparecidas cinco personas</t>
-  </si>
-  <si>
-    <t>Damnificados acusan poco recurso para reubicación</t>
-  </si>
-  <si>
-    <t>Reubicación de viviendas</t>
-  </si>
-  <si>
-    <t>Se restablece el aso en cruces afectados por lluvias</t>
-  </si>
-  <si>
     <t>Sipdus</t>
   </si>
   <si>
-    <t>Tribunal señala excesos en sentencias del TEEH</t>
-  </si>
-  <si>
-    <t>Sentencia</t>
-  </si>
-  <si>
-    <t>Despiden a El Búho, réferi fallecido durante lucha libre</t>
-  </si>
-  <si>
-    <t>Inicia el lunes la campaña de vacunación contra el Covid</t>
-  </si>
-  <si>
-    <t>Vacunación</t>
-  </si>
-  <si>
-    <t>Harfuch rechaza tener ""agenda paralela"" a 2030</t>
-  </si>
-  <si>
-    <t>Buscan evitar la fuga de talento hidalguense</t>
-  </si>
-  <si>
-    <t>Fuga de cerebros</t>
-  </si>
-  <si>
-    <t>Dice Morena a PT: ""ni presión de EU ni recesiones a los grupos de interés""</t>
-  </si>
-  <si>
-    <t>Intervención extranjera</t>
-  </si>
-  <si>
-    <t>Destrabar inversiones, pide la Amcham a la Presidenta</t>
-  </si>
-  <si>
-    <t>Exhorto</t>
-  </si>
-  <si>
-    <t>Brasil es un presagio del futuro para América Latina</t>
-  </si>
-  <si>
-    <t>Morena emite convocatoria para coordinadores municipales</t>
-  </si>
-  <si>
-    <t>Avanzan trabajos para construir nuevo Salón de Plenos</t>
-  </si>
-  <si>
-    <t>Salón De Plenos</t>
-  </si>
-  <si>
-    <t>Segob niega retención de sindicalistas</t>
-  </si>
-  <si>
-    <t>Gobernación</t>
-  </si>
-  <si>
-    <t>Retención</t>
-  </si>
-  <si>
-    <t>Zonas Metropolitanas encabezan denuncias por delitos sexuales</t>
-  </si>
-  <si>
-    <t>Abuso Sexual</t>
-  </si>
-  <si>
-    <t>Riña en penal de Mazatlán deja 10 muertos</t>
-  </si>
-  <si>
-    <t>Deficiencias en penales</t>
-  </si>
-  <si>
-    <t>Amistad, cooperación, resiliencia, buena voluntad, transparencia y rendición de cuentas: retos  mundiales contra el patriarcado”.</t>
-  </si>
-  <si>
-    <t>Erradicación Violencia De Género</t>
-  </si>
-  <si>
-    <t>Dan último adiós a Gerado Germán Pineda, "El Búho", en Pachuca</t>
-  </si>
-  <si>
-    <t>A un año de la vaguada monzónica, sigue la búsqueda de cinco personas</t>
-  </si>
-  <si>
-    <t>Ordena Tribunal Electoral repetir elección de autoridades auxiliares en San Ildefonso</t>
-  </si>
-  <si>
-    <t>Impugnación</t>
-  </si>
-  <si>
-    <t>Orden ministerial derivó en exhumación de cuerpos en presuntas tumbas clandestinas en Atotonilco</t>
-  </si>
-  <si>
-    <t>Exhumación</t>
-  </si>
-  <si>
-    <t>Destruyen droga y material vinculado a actividades delictivas</t>
-  </si>
-  <si>
     <t>FGR</t>
   </si>
   <si>
     <t>Combate a la delincuencia</t>
   </si>
   <si>
-    <t>Restablecen parcialmente circulación en carreteras de Hidalgo</t>
-  </si>
-  <si>
-    <t>Hidalgo, con el mayor porcentaje de beneficiados de programas de justicia social</t>
-  </si>
-  <si>
-    <t>ISSSTE</t>
-  </si>
-  <si>
-    <t>Justicia social</t>
-  </si>
-  <si>
-    <t>Zafarrancho en el penal de Mazatlán 10 muertos y 16 heridos</t>
-  </si>
-  <si>
-    <t>Cayeron cinco; suplantaban y extorsionaban a sus víctimas</t>
-  </si>
-  <si>
-    <t>El empleo formal alcanza récord de 22. millones de puestos</t>
-  </si>
-  <si>
-    <t>Generación de empleos</t>
-  </si>
-  <si>
-    <t>SNTE Hidalgo busca regularizar plazas de docentes</t>
-  </si>
-  <si>
-    <t>Derechos laborales</t>
-  </si>
-  <si>
-    <t>INE busca 48 consejeros distritales en Hidalgo</t>
-  </si>
-  <si>
-    <t>Morena abre registro para coordinadores municipales en Hidalgo</t>
-  </si>
-  <si>
-    <t>Congreso aplaza nombramiento en el TEEH</t>
-  </si>
-  <si>
-    <t>Nombramientos</t>
-  </si>
-  <si>
-    <t>Pleito interno en el IEEH</t>
-  </si>
-  <si>
-    <t>Fortalecen la detección oportuna de cardiopatías en recién nacidos</t>
-  </si>
-  <si>
-    <t>Transparencia para el Pueblo de Hidalgo: más con menos presupuesto</t>
-  </si>
-  <si>
-    <t>Extinción ITAIH</t>
-  </si>
-  <si>
-    <t>Menchaca revisa proyectos para la construcción de viviendas en Hidalgo</t>
-  </si>
-  <si>
     <t>Plan Nacional De Vivienda</t>
   </si>
   <si>
-    <t>Metepec y Acaxochitlán se suman a la Ruta Hidalgo Inspira de la CDHEH</t>
-  </si>
-  <si>
-    <t>Coordinación Interinstitucional</t>
-  </si>
-  <si>
-    <t>Zitlaly Zúñiga instala el Consejo Municipal de participación escolar en la educación</t>
-  </si>
-  <si>
-    <t>Instalación de consejo municipal</t>
-  </si>
-  <si>
-    <t>El IEEH presenta informe sobre los Foros Regionales de Diálogo en materia indígena para la implementación de la Acción Afirmativa en el PEL</t>
-  </si>
-  <si>
-    <t>Acción afirmativa</t>
-  </si>
-  <si>
-    <t>Hidalgo alcanza 93.26% de efectividad en localización de personas</t>
-  </si>
-  <si>
-    <t>Miguel Tello inicia recorridos en Pachuca para defender la Transformación y Soberanía</t>
-  </si>
-  <si>
-    <t>Con más de 10 mdp, Sebiso impulsa la autonomía y bienestar de personas cuidadorsas y comunidad LGBTTTI</t>
-  </si>
-  <si>
-    <t>Inhjuve</t>
-  </si>
-  <si>
-    <t>Inclusión sexogenérica</t>
-  </si>
-  <si>
-    <t>Invitan a jóvenes de hidalgo a formarse como auditores en 2027</t>
-  </si>
-  <si>
-    <t>Convocatoria</t>
-  </si>
-  <si>
-    <t>61 niñas, niños y adolescentes encontraron un hogar a través de la adopción</t>
-  </si>
-  <si>
-    <t>Adopción De Menores</t>
-  </si>
-  <si>
-    <t>Julio Menchaca revisa proyectos para la construcción de viviendas en Hidalgo</t>
-  </si>
-  <si>
-    <t>Conquista Banda MS el Palenque</t>
-  </si>
-  <si>
-    <t>tur</t>
-  </si>
-  <si>
-    <t>oee</t>
-  </si>
-  <si>
-    <t>En Pachuca y Huasca, SSPH asegura cera de 4 mil dosos de presunta droga</t>
-  </si>
-  <si>
-    <t>Investigación de la UTEC será publicada en revista internacional</t>
-  </si>
-  <si>
     <t>Universidades</t>
   </si>
   <si>
     <t>Innovación tecnológica</t>
   </si>
   <si>
-    <t>90s Pop Tuour contagió energía en la feria</t>
-  </si>
-  <si>
     <t>3,328 niñas, niños y adolescentes recibieron atención médica gratuita con Código Guinda</t>
   </si>
   <si>
     <t>Informe de actividades</t>
+  </si>
+  <si>
+    <t>Exhorta párroco a demostrar fe con actos</t>
+  </si>
+  <si>
+    <t>Reconocen a Hidalgo por fortalecer el arte</t>
+  </si>
+  <si>
+    <t>Aprueban vender sus tierras para el tren</t>
+  </si>
+  <si>
+    <t>SICT</t>
+  </si>
+  <si>
+    <t>Tren México Querétaro</t>
+  </si>
+  <si>
+    <t>Paste gigante deleita a miles de visitantes</t>
+  </si>
+  <si>
+    <t>Festival Del Paste</t>
+  </si>
+  <si>
+    <t>Exfuncionarios sin vinculación a proceso legal</t>
+  </si>
+  <si>
+    <t>Desvío de recursos</t>
+  </si>
+  <si>
+    <t>Reinstalan el portón de La Asuncioón tras reparaciones</t>
+  </si>
+  <si>
+    <t>Conservación del Patrimonio Cultural</t>
+  </si>
+  <si>
+    <t>Perfilan hasta 90 años de prisión a feminicidas</t>
+  </si>
+  <si>
+    <t>Sentencia Feminicida</t>
+  </si>
+  <si>
+    <t>Hornean el paste más grande del mundo</t>
+  </si>
+  <si>
+    <t>Abasto en hospitales del IMSS está en 95%</t>
+  </si>
+  <si>
+    <t>Abasto De Medicamentos</t>
+  </si>
+  <si>
+    <t>Rehabilitan caminos tras precipitaciones</t>
+  </si>
+  <si>
+    <t>Crece actividad industrial en la entidad 15.4%</t>
+  </si>
+  <si>
+    <t>Índice De Actividad Industrial</t>
+  </si>
+  <si>
+    <t>Inundan redes registros de morenistas para alcaldías</t>
+  </si>
+  <si>
+    <t>Sucesión alcaldía</t>
+  </si>
+  <si>
+    <t>El rey al rescate</t>
+  </si>
+  <si>
+    <t>Cayó consecha en la paralimpiada</t>
+  </si>
+  <si>
+    <t>Inhide</t>
+  </si>
+  <si>
+    <t>Paranacionales Conade</t>
+  </si>
+  <si>
+    <t>Bordados mantienen litigios por plagios</t>
+  </si>
+  <si>
+    <t>Plagio de diseños indígenas</t>
+  </si>
+  <si>
+    <t>Se requieren mil mdp para que se habilite el nuevo Hospital General</t>
+  </si>
+  <si>
+    <t>Nuevo Hospital General</t>
+  </si>
+  <si>
+    <t>En $6.9 millones, rehabilitación del pisal ubicado en el Ben Gurión</t>
+  </si>
+  <si>
+    <t>Pisal Ben Gurión</t>
+  </si>
+  <si>
+    <t>Diputada federal Mirna Rubio va por la reelección</t>
+  </si>
+  <si>
+    <t>Reelección</t>
+  </si>
+  <si>
+    <t>A fin de mes darán apoyos para reconstruir viviendas</t>
+  </si>
+  <si>
+    <t>Apuesta de Salud en el estado; la prevención y más servicios</t>
+  </si>
+  <si>
+    <t>titular</t>
+  </si>
+  <si>
+    <t>Estrategia sanitaria</t>
+  </si>
+  <si>
+    <t>En octubre serán entregadas las primeras Casas del Bienestar en el estado</t>
+  </si>
+  <si>
+    <t>Infonavit</t>
+  </si>
+  <si>
+    <t>Reconocen al programa cultural Tejido Vivo</t>
+  </si>
+  <si>
+    <t>Formación artística</t>
+  </si>
+  <si>
+    <t>Invertirán $7 millones en su mantenimiento</t>
+  </si>
+  <si>
+    <t>Propone Aladro en el Vaticano acceso a justicia medioambiental</t>
+  </si>
+  <si>
+    <t>Estrategia de cambio climático</t>
+  </si>
+  <si>
+    <t>Festival del Paste cierra actividades en el REal</t>
+  </si>
+  <si>
+    <t>Se agrava la violencia 103% en cárceles y en escuelas crece número de víctimas</t>
+  </si>
+  <si>
+    <t>Ola De Violencia</t>
+  </si>
+  <si>
+    <t>INAH: Evaluarán daños en tumbas del Panteón Inglés</t>
+  </si>
+  <si>
+    <t>INAH</t>
+  </si>
+  <si>
+    <t>Nissan refuerza producción en México con las Pick-ups</t>
+  </si>
+  <si>
+    <t>Mark Zuckerberg l anza su agente de Inteligencia Artificial sin protocolos</t>
+  </si>
+  <si>
+    <t>Hidalgo, segundo lugar nacional en expansión industrial</t>
+  </si>
+  <si>
+    <t>Aprobación de Brugada alcanza 66.4% en CDMX</t>
+  </si>
+  <si>
+    <t>Aprobación Gobernador</t>
+  </si>
+  <si>
+    <t>Falta de dinero complica tener atlas de riesgo en 19 municipios</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Atlas de Riesgos</t>
+  </si>
+  <si>
+    <t>Va por la unidad en Morena</t>
+  </si>
+  <si>
+    <t>Cae presunto líder ligado a Los Rususosv en Acapulco</t>
+  </si>
+  <si>
+    <t>Las universidades mexicanas tienen una oportunidad: incorporar la seguridad  integral como parte de su desarrollo educativo. Medir incidentes, identificar señales  de alerta, capacitar comunidades y evaluar lineamientos deben formar parte de sus  indicadores institucionales”.</t>
+  </si>
+  <si>
+    <t>Celebra Real del Monte su herencia minera con Festival Internacional del Paste</t>
+  </si>
+  <si>
+    <t>Rechazan regidores reforma que permite a alcaldes firmar contratos sin supervisión</t>
+  </si>
+  <si>
+    <t>Regidor</t>
+  </si>
+  <si>
+    <t>Anuncian campaña masiva de vacunación contra influenza y covid-19</t>
+  </si>
+  <si>
+    <t>Campaña de vacunación</t>
+  </si>
+  <si>
+    <t>Buscan que el cambio climático sea abordado por los tribunales</t>
+  </si>
+  <si>
+    <t>Anuncian 860 mdp para reconstrucción de viviendas</t>
+  </si>
+  <si>
+    <t>Protesta por agua contaminada deja decenas de heridos</t>
+  </si>
+  <si>
+    <t>Represión</t>
+  </si>
+  <si>
+    <t>E la política, como en la vida misma, hay que saber cuando el tiempo de resucitar rebasó los 3 días</t>
+  </si>
+  <si>
+    <t>Hoy inician las comparecencias de funcionarios</t>
+  </si>
+  <si>
+    <t>Comparecencias</t>
+  </si>
+  <si>
+    <t>Tras feminicidio, tres fueron declarados culpables</t>
+  </si>
+  <si>
+    <t>Sentencia multihomicida</t>
+  </si>
+  <si>
+    <t>Túnel lleva a hallazgo de narcolaboratorio</t>
+  </si>
+  <si>
+    <t>Narcolaboratorio</t>
+  </si>
+  <si>
+    <t>Vanessa Escalante descarta buscar candidatura en 2027</t>
+  </si>
+  <si>
+    <t>Gerardo Sosa reaparece, acusa persecución y apunta contra Omar Fayad</t>
+  </si>
+  <si>
+    <t>Gerardo Sosa</t>
+  </si>
+  <si>
+    <t>Consulta sobre corridas de toros costará 66 millones</t>
+  </si>
+  <si>
+    <t>Tauromaquia</t>
+  </si>
+  <si>
+    <t>David Penchyna sufre accidente en Pachuca</t>
+  </si>
+  <si>
+    <t>PAN acusa reparto desigual</t>
+  </si>
+  <si>
+    <t>Financiamiento a Partidos</t>
+  </si>
+  <si>
+    <t>Cae ""El Moco""</t>
+  </si>
+  <si>
+    <t>Sipdus continúa trabajos de rehabilitación de caminos afectados</t>
+  </si>
+  <si>
+    <t>Desarrolla UPT sistema de bajo costo para mejorar imágenes de retina</t>
+  </si>
+  <si>
+    <t>Sheinbaum y Menchaca transforman sistema de salud de Hidalgo</t>
+  </si>
+  <si>
+    <t>Visita Sheinbaum</t>
+  </si>
+  <si>
+    <t>Inaugura Cristhian Martínez nuevas canchas de tenis con inversión superior a los 3.8 mdp</t>
+  </si>
+  <si>
+    <t>Fomento Al Deporte</t>
+  </si>
+  <si>
+    <t>Sheinbaum entregará apoyos a damnificados el 29 de octubre</t>
+  </si>
+  <si>
+    <t>Hidalgo obtiene reconocimiento internacional por llevar clases de arte a los 84 municipios</t>
+  </si>
+  <si>
+    <t>Hidalgo incrementa metas de vacunación contra influenza y covid para el invierno</t>
+  </si>
+  <si>
+    <t>318 familias con personas con discapacidad recibieron proyectos productivos</t>
+  </si>
+  <si>
+    <t>Dejó intensa lluvia autos dañados y calles inundadas en La Reforma</t>
+  </si>
+  <si>
+    <t>Afectaciones Por Lluvias</t>
+  </si>
+  <si>
+    <t>Luis R. Conríquez puso bélico el Palenque 2026</t>
+  </si>
+  <si>
+    <t>Sonoras Dinamita y Santanera hacen bailar a la feria con sus éxitos</t>
+  </si>
+  <si>
+    <t>Salomón Ronddón rescata un punto para Tuzos</t>
+  </si>
+  <si>
+    <t>Recuerda: la detección temprana salva vidads</t>
   </si>
 </sst>
 </file>
@@ -934,8 +901,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J69" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J69" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J67" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
+  <autoFilter ref="A1:J67" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
@@ -1304,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1353,13 +1320,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B2" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -1387,59 +1354,59 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B3" t="s">
         <v>81</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B4" t="s">
         <v>81</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -1455,66 +1422,66 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B5" t="s">
         <v>81</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B6" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="G6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1523,66 +1490,66 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B7" t="s">
         <v>81</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1591,32 +1558,32 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1625,32 +1592,32 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="G10" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="H10" t="s">
         <v>72</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1659,59 +1626,59 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="G11" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B12" t="s">
         <v>69</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="G12" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H12" t="s">
         <v>72</v>
@@ -1727,32 +1694,32 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B13" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
       </c>
       <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1761,96 +1728,96 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B14" t="s">
         <v>71</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
       </c>
       <c r="I14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>128</v>
       </c>
       <c r="G15" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G16" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H16" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1861,408 +1828,408 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gobernador</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B18" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="G18" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B19" t="s">
         <v>71</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D19" t="s">
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B21" t="s">
         <v>75</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="G21" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="H21" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B22" t="s">
         <v>75</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D22" t="s">
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>136</v>
+        <v>14</v>
       </c>
       <c r="F22" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G22" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H22" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B23" t="s">
         <v>75</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G23" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B24" t="s">
         <v>75</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="G24" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B25" t="s">
         <v>75</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G25" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B26" t="s">
         <v>75</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B27" t="s">
         <v>75</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F27" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H27" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B28" t="s">
         <v>75</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>153</v>
       </c>
       <c r="G28" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2271,47 +2238,47 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B29" t="s">
         <v>75</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B30" t="s">
         <v>75</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
@@ -2323,7 +2290,7 @@
         <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
@@ -2339,59 +2306,59 @@
     </row>
     <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B31" t="s">
         <v>79</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F31" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="G31" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="H31" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B32" t="s">
         <v>79</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G32" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
@@ -2405,61 +2372,61 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B33" t="s">
         <v>79</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G33" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H33" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B34" t="s">
         <v>79</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F34" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="G34" t="s">
-        <v>157</v>
+        <v>61</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -2475,47 +2442,47 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B35" t="s">
         <v>79</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="G35" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B36" t="s">
         <v>79</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D36" t="s">
         <v>12</v>
@@ -2527,7 +2494,7 @@
         <v>10</v>
       </c>
       <c r="G36" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
@@ -2543,25 +2510,25 @@
     </row>
     <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B37" t="s">
         <v>74</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D37" t="s">
         <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G37" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
@@ -2577,127 +2544,127 @@
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B38" t="s">
         <v>74</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D38" t="s">
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="G38" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B39" t="s">
         <v>74</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="F39" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B40" t="s">
         <v>74</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="F40" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B41" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E41" t="s">
         <v>14</v>
       </c>
       <c r="F41" t="s">
-        <v>169</v>
+        <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
@@ -2713,75 +2680,75 @@
     </row>
     <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B42" t="s">
         <v>77</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="G42" t="s">
-        <v>92</v>
+        <v>173</v>
       </c>
       <c r="H42" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B43" t="s">
         <v>77</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="G43" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B44" t="s">
         <v>77</v>
@@ -2793,152 +2760,152 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F44" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="G44" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="H44" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B45" t="s">
         <v>77</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D45" t="s">
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="F45" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="G45" t="s">
-        <v>88</v>
+        <v>178</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D46" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F46" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="G46" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H46" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B47" t="s">
         <v>73</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G47" t="s">
-        <v>180</v>
+        <v>61</v>
       </c>
       <c r="H47" t="s">
         <v>72</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B48" t="s">
         <v>73</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D48" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E48" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="F48" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="G48" t="s">
-        <v>42</v>
+        <v>183</v>
       </c>
       <c r="H48" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2949,34 +2916,34 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B49" t="s">
         <v>73</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F49" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G49" t="s">
-        <v>61</v>
+        <v>185</v>
       </c>
       <c r="H49" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2985,25 +2952,25 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B50" t="s">
         <v>73</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G50" t="s">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
@@ -3019,93 +2986,93 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B51" t="s">
         <v>73</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F51" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G51" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B52" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D52" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F52" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="G52" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H52" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B53" t="s">
         <v>82</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D53" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="E53" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="F53" t="s">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="G53" t="s">
-        <v>188</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s">
         <v>72</v>
@@ -3121,25 +3088,25 @@
     </row>
     <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B54" t="s">
         <v>82</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G54" t="s">
-        <v>190</v>
+        <v>102</v>
       </c>
       <c r="H54" t="s">
         <v>72</v>
@@ -3150,52 +3117,52 @@
       </c>
       <c r="J54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B55" t="s">
         <v>82</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E55" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="F55" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="G55" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H55" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gobernador</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B56" t="s">
         <v>82</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D56" t="s">
         <v>12</v>
@@ -3204,10 +3171,10 @@
         <v>16</v>
       </c>
       <c r="F56" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
@@ -3221,34 +3188,34 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B57" t="s">
         <v>82</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D57" t="s">
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F57" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>196</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
       </c>
       <c r="I57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -3257,7 +3224,7 @@
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B58" t="s">
         <v>82</v>
@@ -3269,13 +3236,13 @@
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F58" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="G58" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="H58" t="s">
         <v>72</v>
@@ -3291,7 +3258,7 @@
     </row>
     <row r="59" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B59" t="s">
         <v>82</v>
@@ -3303,16 +3270,16 @@
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="F59" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>61</v>
+        <v>169</v>
       </c>
       <c r="H59" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3323,9 +3290,9 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B60" t="s">
         <v>82</v>
@@ -3334,19 +3301,19 @@
         <v>199</v>
       </c>
       <c r="D60" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="E60" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F60" t="s">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="G60" t="s">
-        <v>201</v>
+        <v>104</v>
       </c>
       <c r="H60" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I60" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3359,62 +3326,62 @@
     </row>
     <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B61" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C61" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" t="s">
+        <v>201</v>
+      </c>
+      <c r="H61" t="s">
+        <v>68</v>
+      </c>
+      <c r="I61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J61" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="11">
+        <v>46307</v>
+      </c>
+      <c r="B62" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="D61" t="s">
-        <v>12</v>
-      </c>
-      <c r="E61" t="s">
-        <v>34</v>
-      </c>
-      <c r="F61" t="s">
-        <v>34</v>
-      </c>
-      <c r="G61" t="s">
-        <v>203</v>
-      </c>
-      <c r="H61" t="s">
-        <v>11</v>
-      </c>
-      <c r="I61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J61" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="11">
-        <v>46304</v>
-      </c>
-      <c r="B62" t="s">
-        <v>82</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>204</v>
-      </c>
       <c r="D62" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F62" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="G62" t="s">
-        <v>205</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I62" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3427,25 +3394,25 @@
     </row>
     <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B63" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F63" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="G63" t="s">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s">
         <v>72</v>
@@ -3456,101 +3423,101 @@
       </c>
       <c r="J63" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="D64" t="s">
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>208</v>
+        <v>15</v>
       </c>
       <c r="F64" t="s">
-        <v>209</v>
+        <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="H64" t="s">
         <v>72</v>
       </c>
       <c r="I64" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>XXX</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J64" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D65" t="s">
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G65" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="H65" t="s">
         <v>11</v>
       </c>
       <c r="I65" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J65" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B66" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>211</v>
+        <v>103</v>
       </c>
       <c r="D66" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="E66" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F66" t="s">
-        <v>212</v>
+        <v>36</v>
       </c>
       <c r="G66" t="s">
-        <v>213</v>
+        <v>104</v>
       </c>
       <c r="H66" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I66" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3563,102 +3530,34 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="11">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B67" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="D67" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="E67" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F67" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G67" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H67" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I67" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J67" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="11">
-        <v>46304</v>
-      </c>
-      <c r="B68" t="s">
-        <v>87</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D68" t="s">
-        <v>80</v>
-      </c>
-      <c r="E68" t="s">
-        <v>36</v>
-      </c>
-      <c r="F68" t="s">
-        <v>36</v>
-      </c>
-      <c r="G68" t="s">
-        <v>216</v>
-      </c>
-      <c r="H68" t="s">
-        <v>11</v>
-      </c>
-      <c r="I68" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J68" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="11">
-        <v>46304</v>
-      </c>
-      <c r="B69" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D69" t="s">
-        <v>80</v>
-      </c>
-      <c r="E69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F69" t="s">
-        <v>16</v>
-      </c>
-      <c r="G69" t="s">
-        <v>84</v>
-      </c>
-      <c r="H69" t="s">
-        <v>11</v>
-      </c>
-      <c r="I69" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J69" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB62FED0-40E9-454A-A6F6-18281D7B56DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3745F476-EA23-42AA-843C-4F174A2F5422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="200">
   <si>
     <t>Fecha</t>
   </si>
@@ -297,24 +297,9 @@
     <t>Reforma De Ley</t>
   </si>
   <si>
-    <t>Pachuca Brilla</t>
-  </si>
-  <si>
-    <t>Detención</t>
-  </si>
-  <si>
     <t>Feria Pachuca</t>
   </si>
   <si>
-    <t>Atención Afectaciones Por Lluvias</t>
-  </si>
-  <si>
-    <t>Huracán Priscilla</t>
-  </si>
-  <si>
-    <t>Junta de Gobierno</t>
-  </si>
-  <si>
     <t>IMSS</t>
   </si>
   <si>
@@ -324,337 +309,334 @@
     <t>OEEH</t>
   </si>
   <si>
-    <t>Extitular</t>
-  </si>
-  <si>
-    <t>Exposición Artística</t>
-  </si>
-  <si>
     <t>Sipdus</t>
   </si>
   <si>
-    <t>FGR</t>
-  </si>
-  <si>
-    <t>Combate a la delincuencia</t>
-  </si>
-  <si>
     <t>Plan Nacional De Vivienda</t>
   </si>
   <si>
-    <t>Universidades</t>
-  </si>
-  <si>
-    <t>Innovación tecnológica</t>
-  </si>
-  <si>
-    <t>3,328 niñas, niños y adolescentes recibieron atención médica gratuita con Código Guinda</t>
-  </si>
-  <si>
     <t>Informe de actividades</t>
   </si>
   <si>
-    <t>Exhorta párroco a demostrar fe con actos</t>
-  </si>
-  <si>
-    <t>Reconocen a Hidalgo por fortalecer el arte</t>
-  </si>
-  <si>
-    <t>Aprueban vender sus tierras para el tren</t>
-  </si>
-  <si>
-    <t>SICT</t>
-  </si>
-  <si>
-    <t>Tren México Querétaro</t>
-  </si>
-  <si>
-    <t>Paste gigante deleita a miles de visitantes</t>
-  </si>
-  <si>
-    <t>Festival Del Paste</t>
-  </si>
-  <si>
-    <t>Exfuncionarios sin vinculación a proceso legal</t>
-  </si>
-  <si>
-    <t>Desvío de recursos</t>
-  </si>
-  <si>
-    <t>Reinstalan el portón de La Asuncioón tras reparaciones</t>
-  </si>
-  <si>
-    <t>Conservación del Patrimonio Cultural</t>
-  </si>
-  <si>
-    <t>Perfilan hasta 90 años de prisión a feminicidas</t>
-  </si>
-  <si>
-    <t>Sentencia Feminicida</t>
-  </si>
-  <si>
-    <t>Hornean el paste más grande del mundo</t>
-  </si>
-  <si>
-    <t>Abasto en hospitales del IMSS está en 95%</t>
-  </si>
-  <si>
-    <t>Abasto De Medicamentos</t>
-  </si>
-  <si>
-    <t>Rehabilitan caminos tras precipitaciones</t>
-  </si>
-  <si>
-    <t>Crece actividad industrial en la entidad 15.4%</t>
-  </si>
-  <si>
-    <t>Índice De Actividad Industrial</t>
-  </si>
-  <si>
-    <t>Inundan redes registros de morenistas para alcaldías</t>
-  </si>
-  <si>
-    <t>Sucesión alcaldía</t>
-  </si>
-  <si>
-    <t>El rey al rescate</t>
-  </si>
-  <si>
-    <t>Cayó consecha en la paralimpiada</t>
-  </si>
-  <si>
-    <t>Inhide</t>
-  </si>
-  <si>
-    <t>Paranacionales Conade</t>
-  </si>
-  <si>
-    <t>Bordados mantienen litigios por plagios</t>
-  </si>
-  <si>
-    <t>Plagio de diseños indígenas</t>
-  </si>
-  <si>
-    <t>Se requieren mil mdp para que se habilite el nuevo Hospital General</t>
-  </si>
-  <si>
     <t>Nuevo Hospital General</t>
   </si>
   <si>
-    <t>En $6.9 millones, rehabilitación del pisal ubicado en el Ben Gurión</t>
-  </si>
-  <si>
-    <t>Pisal Ben Gurión</t>
-  </si>
-  <si>
-    <t>Diputada federal Mirna Rubio va por la reelección</t>
-  </si>
-  <si>
-    <t>Reelección</t>
-  </si>
-  <si>
-    <t>A fin de mes darán apoyos para reconstruir viviendas</t>
-  </si>
-  <si>
-    <t>Apuesta de Salud en el estado; la prevención y más servicios</t>
-  </si>
-  <si>
-    <t>titular</t>
-  </si>
-  <si>
-    <t>Estrategia sanitaria</t>
-  </si>
-  <si>
-    <t>En octubre serán entregadas las primeras Casas del Bienestar en el estado</t>
-  </si>
-  <si>
-    <t>Infonavit</t>
-  </si>
-  <si>
-    <t>Reconocen al programa cultural Tejido Vivo</t>
-  </si>
-  <si>
-    <t>Formación artística</t>
-  </si>
-  <si>
-    <t>Invertirán $7 millones en su mantenimiento</t>
-  </si>
-  <si>
-    <t>Propone Aladro en el Vaticano acceso a justicia medioambiental</t>
-  </si>
-  <si>
-    <t>Estrategia de cambio climático</t>
-  </si>
-  <si>
-    <t>Festival del Paste cierra actividades en el REal</t>
-  </si>
-  <si>
-    <t>Se agrava la violencia 103% en cárceles y en escuelas crece número de víctimas</t>
-  </si>
-  <si>
     <t>Ola De Violencia</t>
   </si>
   <si>
-    <t>INAH: Evaluarán daños en tumbas del Panteón Inglés</t>
-  </si>
-  <si>
-    <t>INAH</t>
-  </si>
-  <si>
-    <t>Nissan refuerza producción en México con las Pick-ups</t>
-  </si>
-  <si>
-    <t>Mark Zuckerberg l anza su agente de Inteligencia Artificial sin protocolos</t>
-  </si>
-  <si>
-    <t>Hidalgo, segundo lugar nacional en expansión industrial</t>
-  </si>
-  <si>
-    <t>Aprobación de Brugada alcanza 66.4% en CDMX</t>
-  </si>
-  <si>
-    <t>Aprobación Gobernador</t>
-  </si>
-  <si>
-    <t>Falta de dinero complica tener atlas de riesgo en 19 municipios</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>Atlas de Riesgos</t>
-  </si>
-  <si>
-    <t>Va por la unidad en Morena</t>
-  </si>
-  <si>
-    <t>Cae presunto líder ligado a Los Rususosv en Acapulco</t>
-  </si>
-  <si>
-    <t>Las universidades mexicanas tienen una oportunidad: incorporar la seguridad  integral como parte de su desarrollo educativo. Medir incidentes, identificar señales  de alerta, capacitar comunidades y evaluar lineamientos deben formar parte de sus  indicadores institucionales”.</t>
-  </si>
-  <si>
-    <t>Celebra Real del Monte su herencia minera con Festival Internacional del Paste</t>
-  </si>
-  <si>
-    <t>Rechazan regidores reforma que permite a alcaldes firmar contratos sin supervisión</t>
-  </si>
-  <si>
-    <t>Regidor</t>
-  </si>
-  <si>
-    <t>Anuncian campaña masiva de vacunación contra influenza y covid-19</t>
-  </si>
-  <si>
     <t>Campaña de vacunación</t>
   </si>
   <si>
-    <t>Buscan que el cambio climático sea abordado por los tribunales</t>
-  </si>
-  <si>
-    <t>Anuncian 860 mdp para reconstrucción de viviendas</t>
-  </si>
-  <si>
-    <t>Protesta por agua contaminada deja decenas de heridos</t>
-  </si>
-  <si>
-    <t>Represión</t>
-  </si>
-  <si>
-    <t>E la política, como en la vida misma, hay que saber cuando el tiempo de resucitar rebasó los 3 días</t>
-  </si>
-  <si>
-    <t>Hoy inician las comparecencias de funcionarios</t>
-  </si>
-  <si>
     <t>Comparecencias</t>
   </si>
   <si>
-    <t>Tras feminicidio, tres fueron declarados culpables</t>
-  </si>
-  <si>
-    <t>Sentencia multihomicida</t>
-  </si>
-  <si>
-    <t>Túnel lleva a hallazgo de narcolaboratorio</t>
-  </si>
-  <si>
-    <t>Narcolaboratorio</t>
-  </si>
-  <si>
-    <t>Vanessa Escalante descarta buscar candidatura en 2027</t>
-  </si>
-  <si>
-    <t>Gerardo Sosa reaparece, acusa persecución y apunta contra Omar Fayad</t>
-  </si>
-  <si>
-    <t>Gerardo Sosa</t>
-  </si>
-  <si>
-    <t>Consulta sobre corridas de toros costará 66 millones</t>
-  </si>
-  <si>
     <t>Tauromaquia</t>
   </si>
   <si>
-    <t>David Penchyna sufre accidente en Pachuca</t>
-  </si>
-  <si>
-    <t>PAN acusa reparto desigual</t>
-  </si>
-  <si>
-    <t>Financiamiento a Partidos</t>
-  </si>
-  <si>
-    <t>Cae ""El Moco""</t>
-  </si>
-  <si>
-    <t>Sipdus continúa trabajos de rehabilitación de caminos afectados</t>
-  </si>
-  <si>
-    <t>Desarrolla UPT sistema de bajo costo para mejorar imágenes de retina</t>
-  </si>
-  <si>
-    <t>Sheinbaum y Menchaca transforman sistema de salud de Hidalgo</t>
-  </si>
-  <si>
-    <t>Visita Sheinbaum</t>
-  </si>
-  <si>
-    <t>Inaugura Cristhian Martínez nuevas canchas de tenis con inversión superior a los 3.8 mdp</t>
-  </si>
-  <si>
-    <t>Fomento Al Deporte</t>
-  </si>
-  <si>
-    <t>Sheinbaum entregará apoyos a damnificados el 29 de octubre</t>
-  </si>
-  <si>
-    <t>Hidalgo obtiene reconocimiento internacional por llevar clases de arte a los 84 municipios</t>
-  </si>
-  <si>
-    <t>Hidalgo incrementa metas de vacunación contra influenza y covid para el invierno</t>
-  </si>
-  <si>
-    <t>318 familias con personas con discapacidad recibieron proyectos productivos</t>
-  </si>
-  <si>
-    <t>Dejó intensa lluvia autos dañados y calles inundadas en La Reforma</t>
-  </si>
-  <si>
-    <t>Afectaciones Por Lluvias</t>
-  </si>
-  <si>
-    <t>Luis R. Conríquez puso bélico el Palenque 2026</t>
-  </si>
-  <si>
-    <t>Sonoras Dinamita y Santanera hacen bailar a la feria con sus éxitos</t>
-  </si>
-  <si>
-    <t>Salomón Ronddón rescata un punto para Tuzos</t>
-  </si>
-  <si>
-    <t>Recuerda: la detección temprana salva vidads</t>
+    <t>Aclaran que predio pertenece a Fovissste</t>
+  </si>
+  <si>
+    <t>ISSSTE</t>
+  </si>
+  <si>
+    <t>Registran cupo lleno en hoteles en el Huasteca</t>
+  </si>
+  <si>
+    <t>Xantolo</t>
+  </si>
+  <si>
+    <t>PAN rechaza nueva reforma</t>
+  </si>
+  <si>
+    <t>Hay 97 denuncias por posible corrupción</t>
+  </si>
+  <si>
+    <t>Combate a la corrupción</t>
+  </si>
+  <si>
+    <t>Estados Unidos abre más recortes de agua</t>
+  </si>
+  <si>
+    <t>Temas internacionales</t>
+  </si>
+  <si>
+    <t>Plantean limitar el alza al minisalario</t>
+  </si>
+  <si>
+    <t>Aumento salarial</t>
+  </si>
+  <si>
+    <t>Abren glosa Olivares y N. Naranjo</t>
+  </si>
+  <si>
+    <t>Denuncia Morena presuntos delitos fiscales de Viggiano</t>
+  </si>
+  <si>
+    <t>Denuncia por enriquecimiento ilícito</t>
+  </si>
+  <si>
+    <t>Afectan a la entidad males cardiacos</t>
+  </si>
+  <si>
+    <t>Control de enfermedades</t>
+  </si>
+  <si>
+    <t>Detecta la Contraloría desfalcos por 2.4 mmdp</t>
+  </si>
+  <si>
+    <t>Feria de los Angelitos dejó 400 mdp</t>
+  </si>
+  <si>
+    <t>Feria Patronal</t>
+  </si>
+  <si>
+    <t>Destaca Olivares avances en seguridad</t>
+  </si>
+  <si>
+    <t>Corte invalida cobros a las comunicaciones en Yahualica</t>
+  </si>
+  <si>
+    <t>Ayu</t>
+  </si>
+  <si>
+    <t>Ley De Ingresos</t>
+  </si>
+  <si>
+    <t>Asume deuda</t>
+  </si>
+  <si>
+    <t>Barsa, por otro golpe</t>
+  </si>
+  <si>
+    <t>Descartan represión vs personal del IMSS durante protestas</t>
+  </si>
+  <si>
+    <t>Chocan posturas por la refoirma que avala a ediles firmar contratos</t>
+  </si>
+  <si>
+    <t>Plagada de baches, calle 10 de Santa Julia</t>
+  </si>
+  <si>
+    <t>Caasim</t>
+  </si>
+  <si>
+    <t>Baches</t>
+  </si>
+  <si>
+    <t>Preliberaron a 10 personas de cárceles de la entidad: Reyna</t>
+  </si>
+  <si>
+    <t>Por la compra de mansión, Morenadenuncia a Caro Viggiano ante FGR</t>
+  </si>
+  <si>
+    <t>Denuncia enriquecimiento ilícito</t>
+  </si>
+  <si>
+    <t>Constructoras del Hospital General enfrentan sanciones</t>
+  </si>
+  <si>
+    <t>DIF de la entidad obtiene certificación internacional</t>
+  </si>
+  <si>
+    <t>Certificación</t>
+  </si>
+  <si>
+    <t>Llegan a Ciudad Sahagún exposiciones y espectáculos</t>
+  </si>
+  <si>
+    <t>Feria industrial</t>
+  </si>
+  <si>
+    <t>Reportan caída en homicidios ...y alza en las inversiones</t>
+  </si>
+  <si>
+    <t>Arrancan en el estado campaña de vacunación</t>
+  </si>
+  <si>
+    <t>Refuerzan vigilancia con cámaras y parador seguro</t>
+  </si>
+  <si>
+    <t>Impulsan la producción de flores de temporada</t>
+  </si>
+  <si>
+    <t>Impulso al agro</t>
+  </si>
+  <si>
+    <t>Piso por piso buscará el IMSS las deficiencias en 277 hospitales del país</t>
+  </si>
+  <si>
+    <t>Supervisión</t>
+  </si>
+  <si>
+    <t>Se guardan qué patógeno mató a científica rusa</t>
+  </si>
+  <si>
+    <t>Vigilancia Epidemiológica</t>
+  </si>
+  <si>
+    <t>Destaca SEP por lo menos 5 medidas contra violencia</t>
+  </si>
+  <si>
+    <t>Educación socioemocional</t>
+  </si>
+  <si>
+    <t>Legisladores de Morena denuncian a Carolina Viggiano</t>
+  </si>
+  <si>
+    <t>Reforma para agilizar contratos en alcaldías evita parálisis: contralor</t>
+  </si>
+  <si>
+    <t>Hubo pagos para frenar el parque circular: Olivares</t>
+  </si>
+  <si>
+    <t>Parque Ecológico Tula</t>
+  </si>
+  <si>
+    <t>Matan a exedil y amenazan escuela en Veracruz</t>
+  </si>
+  <si>
+    <t>Homicidios</t>
+  </si>
+  <si>
+    <t>Legisladores denuncian a Viggiano por enriquecimiento ilícito</t>
+  </si>
+  <si>
+    <t>La participación ciudadana, conciencia y organización de la población  son los factores que permiten consolidar el cambio verdadero, sin ello,  no importa qué se construya, simplemente no tendrá el soporte y  estructura que le permita crecer”.</t>
+  </si>
+  <si>
+    <t>Simey</t>
+  </si>
+  <si>
+    <t>Acumula Contraloría 97 denuncias penales por corrupción en cuatro años</t>
+  </si>
+  <si>
+    <t>Presentan denuncia contra Carolina Viggiano por presunto enriquecimiento ilícito</t>
+  </si>
+  <si>
+    <t>Personas en prisión preventiva podrán participar en consulta sobre corridas de toros</t>
+  </si>
+  <si>
+    <t>Jorge Reyes respalda reforma para modernizar la gestión administrativa municipal</t>
+  </si>
+  <si>
+    <t>Operativo policial contra trabajadores del IMSS fue por incumplimiento de acuerdo: Olivares Reyna</t>
+  </si>
+  <si>
+    <t>Caos, temor y muerte por balaceras en colonias de Tula</t>
+  </si>
+  <si>
+    <t>Morena denunca a Carolina Viggiano</t>
+  </si>
+  <si>
+    <t>Desgraciadamente la  violencia en su modo más  crudo llegó a Hidalgo,  se recrudece en Tula  donde prevalece el  huachicoleo. Es  momento de frenar  estos hechos  delincuenciales…</t>
+  </si>
+  <si>
+    <t>Editorial</t>
+  </si>
+  <si>
+    <t>Medidas para que sea eficaz la atención pública en salud</t>
+  </si>
+  <si>
+    <t>Atención médica</t>
+  </si>
+  <si>
+    <t>Morena denuncia a Viggiano ante la FGR</t>
+  </si>
+  <si>
+    <t>Gobierno privilegió el diálogo antes de usar fuerza pública: Olivares</t>
+  </si>
+  <si>
+    <t>Hallan tres calcinados en vivienda de Tepeapulco</t>
+  </si>
+  <si>
+    <t>Policía municipal</t>
+  </si>
+  <si>
+    <t>Localización de cuerpo</t>
+  </si>
+  <si>
+    <t>Regidores y síndicos del PAN rechazan reforma</t>
+  </si>
+  <si>
+    <t>Arranca vacunación masiva en Hidalgo</t>
+  </si>
+  <si>
+    <t>Destina Saderh apoyos al sector agropecuario en Lolotla</t>
+  </si>
+  <si>
+    <t>Apoyo Al Agro</t>
+  </si>
+  <si>
+    <t>Concluye tigrillo su rehabilitación en Pachuca y se prepara para regresar a su hábitat natural</t>
+  </si>
+  <si>
+    <t>Rehabilitación animal</t>
+  </si>
+  <si>
+    <t>Morena denuncia a Viggiano ante el SAT por presunta simulación fiscal</t>
+  </si>
+  <si>
+    <t>Hidalgo fortalece la paz, seguridad y el diálogo con atención cercana: Guillermo Olivares</t>
+  </si>
+  <si>
+    <t>Claudia Sandoval visita primaria</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>Entrega mobiliario escolar</t>
+  </si>
+  <si>
+    <t>Tlaxcoapan, sede del taller estratégico para el desarrollo regional</t>
+  </si>
+  <si>
+    <t>Desarrollo regional</t>
+  </si>
+  <si>
+    <t>El magisterio de Hidalgo fortalece sus estructuras sindicales con encuentros regionales</t>
+  </si>
+  <si>
+    <t>Reunión con sindicato</t>
+  </si>
+  <si>
+    <t>Ajacuba participa en taller estratégico para el desarrollo regional en Tlaxcoapan</t>
+  </si>
+  <si>
+    <t>Justifica Olivares uso de fuerza pública contra personas del IMSS</t>
+  </si>
+  <si>
+    <t>Cuernudos proyecta riqueza cultural de Hidalgo en Festival Cervantino</t>
+  </si>
+  <si>
+    <t>Festival Cultural</t>
+  </si>
+  <si>
+    <t>91 millones 600 mil desayunos escolares para niñas, niños y adolescentes</t>
+  </si>
+  <si>
+    <t>Fortalecen la paz, seguridad y el diálogo con atención cercana: Guillermo Olivares</t>
+  </si>
+  <si>
+    <t>Destaca Hidalgo en materia anticorrupción</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón entrega obra educativa por 12.9 mdp en Huichapan</t>
+  </si>
+  <si>
+    <t>Entrega de infraestructura escolar</t>
+  </si>
+  <si>
+    <t>Denuncia Morena a Carolina Viggiano por presunta simulación fiscal</t>
+  </si>
+  <si>
+    <t>¡Iuuuu!! El Recodo le puso sabor sinaloense a la Feria</t>
+  </si>
+  <si>
+    <t>61 niñas, niños y adolescentes encontraron un hogar a través de la adopción</t>
+  </si>
+  <si>
+    <t>Recuerda: la detección temprana salva vidas</t>
   </si>
 </sst>
 </file>
@@ -806,7 +788,102 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="d/m/yy;@"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="1"/>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -850,43 +927,6 @@
         </left>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="d/m/yy;@"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="1"/>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -901,15 +941,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J67" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4">
-  <autoFilter ref="A1:J67" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J69" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5">
+  <autoFilter ref="A1:J69" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{9D9ACAF2-1710-400E-A0E5-0A5BB378D4A0}" name="Fecha" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{9D9ACAF2-1710-400E-A0E5-0A5BB378D4A0}" name="Fecha" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{03A139BE-A997-45E6-81E6-5F7467162FC5}" name="Medio"/>
-    <tableColumn id="3" xr3:uid="{4CA37DD5-010E-43EE-907D-87C1845DB2AB}" name="Titular" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{4CA37DD5-010E-43EE-907D-87C1845DB2AB}" name="Titular" dataDxfId="3"/>
     <tableColumn id="4" xr3:uid="{1E763E28-25D7-4FE7-AD1A-91C7A0FE0E7A}" name="Recurso editorial"/>
     <tableColumn id="5" xr3:uid="{F8C19AF2-6D19-449B-9F8B-6424964B1BCF}" name="Dependencia"/>
     <tableColumn id="6" xr3:uid="{46DF0510-7A9A-4625-979E-4EBC30CC7AA3}" name="Organismo"/>
@@ -941,13 +981,13 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}" name="Tabla3" displayName="Tabla3" ref="D1:E27" totalsRowShown="0" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}" name="Tabla3" displayName="Tabla3" ref="D1:E27" totalsRowShown="0" tableBorderDxfId="12">
   <autoFilter ref="D1:E27" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:E27">
     <sortCondition ref="D1:D27"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A040A308-8C62-4D4B-B3BE-EC124A9B961C}" name="Dependencia" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{A040A308-8C62-4D4B-B3BE-EC124A9B961C}" name="Dependencia" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{2B2FFCF1-496A-4D37-8C8B-790A66FD9968}" name="Nivel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1271,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1320,32 +1360,32 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2" t="s">
         <v>81</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J2" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1354,25 +1394,25 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B3" t="s">
         <v>81</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H3" t="s">
         <v>72</v>
@@ -1388,32 +1428,32 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B4" t="s">
         <v>81</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="G4" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Partidos</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1422,59 +1462,59 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B5" t="s">
         <v>81</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B6" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H6" t="s">
         <v>68</v>
@@ -1490,16 +1530,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B7" t="s">
         <v>81</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -1508,10 +1548,10 @@
         <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1524,56 +1564,56 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
         <v>111</v>
@@ -1583,7 +1623,7 @@
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Partidos</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1592,13 +1632,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1607,13 +1647,13 @@
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G10" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1626,28 +1666,28 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1660,100 +1700,100 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B12" t="s">
         <v>69</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B13" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="H13" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J13" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
         <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="H14" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1762,93 +1802,93 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>128</v>
+        <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
       </c>
       <c r="I15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J15" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G16" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="H16" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
@@ -1859,203 +1899,203 @@
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B18" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B19" t="s">
         <v>71</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="G19" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="H19" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B20" t="s">
         <v>71</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="G21" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B22" t="s">
         <v>75</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="G22" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
       </c>
       <c r="I22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B23" t="s">
         <v>75</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F23" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="H23" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I23" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2068,22 +2108,22 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B24" t="s">
         <v>75</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="G24" t="s">
         <v>135</v>
@@ -2093,192 +2133,192 @@
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B25" t="s">
         <v>75</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
         <v>2</v>
       </c>
       <c r="G25" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="H25" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J25" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B26" t="s">
         <v>75</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B27" t="s">
         <v>75</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>151</v>
+        <v>96</v>
       </c>
       <c r="H27" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B28" t="s">
         <v>75</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B29" t="s">
         <v>75</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
       </c>
       <c r="I29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J29" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B30" t="s">
         <v>75</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="D30" t="s">
         <v>12</v>
@@ -2290,10 +2330,10 @@
         <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="H30" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -2304,68 +2344,68 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="H31" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D32" t="s">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G32" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2374,25 +2414,25 @@
     </row>
     <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B33" t="s">
         <v>79</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="D33" t="s">
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F33" t="s">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -2408,25 +2448,25 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B34" t="s">
         <v>79</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D34" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F34" t="s">
-        <v>95</v>
+        <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -2442,100 +2482,100 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B35" t="s">
         <v>79</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D35" t="s">
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="G35" t="s">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="H35" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B36" t="s">
         <v>79</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G36" t="s">
+        <v>111</v>
+      </c>
+      <c r="H36" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Partidos</v>
+      </c>
+      <c r="J36" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A37" s="11">
+        <v>46308</v>
+      </c>
+      <c r="B37" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" t="s">
+        <v>155</v>
+      </c>
+      <c r="G37" t="s">
         <v>78</v>
       </c>
-      <c r="H36" t="s">
-        <v>11</v>
-      </c>
-      <c r="I36" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
-      </c>
-      <c r="J36" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="11">
-        <v>46307</v>
-      </c>
-      <c r="B37" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D37" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F37" t="s">
-        <v>2</v>
-      </c>
-      <c r="G37" t="s">
-        <v>111</v>
-      </c>
       <c r="H37" t="s">
         <v>11</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Sucesión gubernamental</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2544,93 +2584,93 @@
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B38" t="s">
         <v>74</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E38" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F38" t="s">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="G38" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B39" t="s">
         <v>74</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D39" t="s">
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F39" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G39" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="H39" t="s">
         <v>11</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B40" t="s">
         <v>74</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F40" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="G40" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
@@ -2644,34 +2684,34 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2680,270 +2720,270 @@
     </row>
     <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B42" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G42" t="s">
-        <v>173</v>
+        <v>96</v>
       </c>
       <c r="H42" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B43" t="s">
         <v>77</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G43" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J43" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B44" t="s">
         <v>77</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F44" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G44" t="s">
-        <v>176</v>
+        <v>111</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B45" t="s">
         <v>77</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="E45" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="F45" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="G45" t="s">
-        <v>178</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="D46" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F46" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B47" t="s">
         <v>73</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="D47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F47" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="H47" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B48" t="s">
         <v>73</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="F48" t="s">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="G48" t="s">
-        <v>183</v>
+        <v>96</v>
       </c>
       <c r="H48" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B49" t="s">
         <v>73</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="G49" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H49" t="s">
         <v>68</v>
       </c>
       <c r="I49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2952,32 +2992,32 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B50" t="s">
         <v>73</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="F50" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G50" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Partidos</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2986,161 +3026,161 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B51" t="s">
         <v>73</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F51" t="s">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="G51" t="s">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B52" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="D52" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="E52" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="F52" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="G52" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
       </c>
       <c r="I52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B53" t="s">
         <v>82</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D53" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="H53" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B54" t="s">
         <v>82</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F54" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="G54" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H54" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B55" t="s">
         <v>82</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F55" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G55" t="s">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c r="H55" t="s">
         <v>72</v>
@@ -3151,30 +3191,30 @@
       </c>
       <c r="J55" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gobernador</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B56" t="s">
         <v>82</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="D56" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="E56" t="s">
         <v>16</v>
       </c>
       <c r="F56" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G56" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
@@ -3190,32 +3230,32 @@
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B57" t="s">
         <v>82</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="D57" t="s">
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="G57" t="s">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
       </c>
       <c r="I57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -3224,93 +3264,93 @@
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B58" t="s">
         <v>82</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D58" t="s">
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F58" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G58" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="H58" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B59" t="s">
         <v>82</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="D59" t="s">
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="H59" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J59" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B60" t="s">
         <v>82</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D60" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F60" t="s">
         <v>2</v>
       </c>
       <c r="G60" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="H60" t="s">
         <v>11</v>
@@ -3326,62 +3366,62 @@
     </row>
     <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B61" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="D61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F61" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G61" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="H61" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I61" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J61" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B62" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D62" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="E62" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F62" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="G62" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H62" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I62" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3394,25 +3434,25 @@
     </row>
     <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B63" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D63" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E63" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F63" t="s">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="G63" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H63" t="s">
         <v>72</v>
@@ -3426,27 +3466,27 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D64" t="s">
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F64" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G64" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="H64" t="s">
         <v>72</v>
@@ -3460,109 +3500,182 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B65" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="D65" t="s">
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F65" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G65" t="s">
-        <v>70</v>
+        <v>195</v>
       </c>
       <c r="H65" t="s">
         <v>11</v>
       </c>
       <c r="I65" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J65" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B66" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>103</v>
+        <v>196</v>
       </c>
       <c r="D66" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F66" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G66" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="H66" t="s">
         <v>11</v>
       </c>
       <c r="I66" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Partidos</v>
       </c>
       <c r="J66" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="11">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B67" t="s">
+        <v>82</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D67" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67" t="s">
+        <v>89</v>
+      </c>
+      <c r="G67" t="s">
         <v>86</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="H67" t="s">
+        <v>72</v>
+      </c>
+      <c r="I67" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J67" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="11">
+        <v>46308</v>
+      </c>
+      <c r="B68" t="s">
+        <v>82</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D68" t="s">
         <v>80</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E68" t="s">
+        <v>36</v>
+      </c>
+      <c r="F68" t="s">
+        <v>36</v>
+      </c>
+      <c r="G68" t="s">
+        <v>92</v>
+      </c>
+      <c r="H68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I68" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J68" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="11">
+        <v>46308</v>
+      </c>
+      <c r="B69" t="s">
+        <v>82</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D69" t="s">
+        <v>80</v>
+      </c>
+      <c r="E69" t="s">
         <v>16</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F69" t="s">
         <v>16</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G69" t="s">
         <v>84</v>
       </c>
-      <c r="H67" t="s">
-        <v>11</v>
-      </c>
-      <c r="I67" t="str">
+      <c r="H69" t="s">
+        <v>11</v>
+      </c>
+      <c r="I69" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Alcaldías</v>
       </c>
-      <c r="J67" t="str">
+      <c r="J69" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I2:I69">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$I2="XXX"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3745F476-EA23-42AA-843C-4F174A2F5422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A52FDD-D976-46D5-B397-6B4DCF415F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="187">
   <si>
     <t>Fecha</t>
   </si>
@@ -258,9 +258,6 @@
     <t>Positiva</t>
   </si>
   <si>
-    <t>Effetá</t>
-  </si>
-  <si>
     <t>Síntesis</t>
   </si>
   <si>
@@ -294,9 +291,6 @@
     <t>Prevención cáncer de mama</t>
   </si>
   <si>
-    <t>Reforma De Ley</t>
-  </si>
-  <si>
     <t>Feria Pachuca</t>
   </si>
   <si>
@@ -318,325 +312,292 @@
     <t>Informe de actividades</t>
   </si>
   <si>
-    <t>Nuevo Hospital General</t>
-  </si>
-  <si>
-    <t>Ola De Violencia</t>
-  </si>
-  <si>
-    <t>Campaña de vacunación</t>
-  </si>
-  <si>
     <t>Comparecencias</t>
   </si>
   <si>
-    <t>Tauromaquia</t>
-  </si>
-  <si>
-    <t>Aclaran que predio pertenece a Fovissste</t>
-  </si>
-  <si>
-    <t>ISSSTE</t>
-  </si>
-  <si>
-    <t>Registran cupo lleno en hoteles en el Huasteca</t>
-  </si>
-  <si>
-    <t>Xantolo</t>
-  </si>
-  <si>
-    <t>PAN rechaza nueva reforma</t>
-  </si>
-  <si>
-    <t>Hay 97 denuncias por posible corrupción</t>
-  </si>
-  <si>
-    <t>Combate a la corrupción</t>
-  </si>
-  <si>
-    <t>Estados Unidos abre más recortes de agua</t>
-  </si>
-  <si>
     <t>Temas internacionales</t>
   </si>
   <si>
-    <t>Plantean limitar el alza al minisalario</t>
-  </si>
-  <si>
-    <t>Aumento salarial</t>
-  </si>
-  <si>
-    <t>Abren glosa Olivares y N. Naranjo</t>
-  </si>
-  <si>
-    <t>Denuncia Morena presuntos delitos fiscales de Viggiano</t>
-  </si>
-  <si>
-    <t>Denuncia por enriquecimiento ilícito</t>
-  </si>
-  <si>
-    <t>Afectan a la entidad males cardiacos</t>
-  </si>
-  <si>
-    <t>Control de enfermedades</t>
-  </si>
-  <si>
-    <t>Detecta la Contraloría desfalcos por 2.4 mmdp</t>
-  </si>
-  <si>
-    <t>Feria de los Angelitos dejó 400 mdp</t>
-  </si>
-  <si>
-    <t>Feria Patronal</t>
-  </si>
-  <si>
-    <t>Destaca Olivares avances en seguridad</t>
-  </si>
-  <si>
-    <t>Corte invalida cobros a las comunicaciones en Yahualica</t>
-  </si>
-  <si>
-    <t>Ayu</t>
-  </si>
-  <si>
-    <t>Ley De Ingresos</t>
-  </si>
-  <si>
-    <t>Asume deuda</t>
-  </si>
-  <si>
-    <t>Barsa, por otro golpe</t>
-  </si>
-  <si>
-    <t>Descartan represión vs personal del IMSS durante protestas</t>
-  </si>
-  <si>
-    <t>Chocan posturas por la refoirma que avala a ediles firmar contratos</t>
-  </si>
-  <si>
-    <t>Plagada de baches, calle 10 de Santa Julia</t>
-  </si>
-  <si>
-    <t>Caasim</t>
-  </si>
-  <si>
-    <t>Baches</t>
-  </si>
-  <si>
-    <t>Preliberaron a 10 personas de cárceles de la entidad: Reyna</t>
-  </si>
-  <si>
-    <t>Por la compra de mansión, Morenadenuncia a Caro Viggiano ante FGR</t>
-  </si>
-  <si>
-    <t>Denuncia enriquecimiento ilícito</t>
-  </si>
-  <si>
-    <t>Constructoras del Hospital General enfrentan sanciones</t>
-  </si>
-  <si>
-    <t>DIF de la entidad obtiene certificación internacional</t>
-  </si>
-  <si>
-    <t>Certificación</t>
-  </si>
-  <si>
-    <t>Llegan a Ciudad Sahagún exposiciones y espectáculos</t>
-  </si>
-  <si>
-    <t>Feria industrial</t>
-  </si>
-  <si>
-    <t>Reportan caída en homicidios ...y alza en las inversiones</t>
-  </si>
-  <si>
-    <t>Arrancan en el estado campaña de vacunación</t>
-  </si>
-  <si>
-    <t>Refuerzan vigilancia con cámaras y parador seguro</t>
-  </si>
-  <si>
-    <t>Impulsan la producción de flores de temporada</t>
-  </si>
-  <si>
-    <t>Impulso al agro</t>
-  </si>
-  <si>
-    <t>Piso por piso buscará el IMSS las deficiencias en 277 hospitales del país</t>
-  </si>
-  <si>
-    <t>Supervisión</t>
-  </si>
-  <si>
-    <t>Se guardan qué patógeno mató a científica rusa</t>
-  </si>
-  <si>
-    <t>Vigilancia Epidemiológica</t>
-  </si>
-  <si>
-    <t>Destaca SEP por lo menos 5 medidas contra violencia</t>
-  </si>
-  <si>
-    <t>Educación socioemocional</t>
-  </si>
-  <si>
-    <t>Legisladores de Morena denuncian a Carolina Viggiano</t>
-  </si>
-  <si>
-    <t>Reforma para agilizar contratos en alcaldías evita parálisis: contralor</t>
-  </si>
-  <si>
-    <t>Hubo pagos para frenar el parque circular: Olivares</t>
-  </si>
-  <si>
-    <t>Parque Ecológico Tula</t>
-  </si>
-  <si>
-    <t>Matan a exedil y amenazan escuela en Veracruz</t>
-  </si>
-  <si>
-    <t>Homicidios</t>
-  </si>
-  <si>
-    <t>Legisladores denuncian a Viggiano por enriquecimiento ilícito</t>
-  </si>
-  <si>
-    <t>La participación ciudadana, conciencia y organización de la población  son los factores que permiten consolidar el cambio verdadero, sin ello,  no importa qué se construya, simplemente no tendrá el soporte y  estructura que le permita crecer”.</t>
-  </si>
-  <si>
-    <t>Simey</t>
-  </si>
-  <si>
-    <t>Acumula Contraloría 97 denuncias penales por corrupción en cuatro años</t>
-  </si>
-  <si>
-    <t>Presentan denuncia contra Carolina Viggiano por presunto enriquecimiento ilícito</t>
-  </si>
-  <si>
-    <t>Personas en prisión preventiva podrán participar en consulta sobre corridas de toros</t>
-  </si>
-  <si>
-    <t>Jorge Reyes respalda reforma para modernizar la gestión administrativa municipal</t>
-  </si>
-  <si>
-    <t>Operativo policial contra trabajadores del IMSS fue por incumplimiento de acuerdo: Olivares Reyna</t>
-  </si>
-  <si>
-    <t>Caos, temor y muerte por balaceras en colonias de Tula</t>
-  </si>
-  <si>
-    <t>Morena denunca a Carolina Viggiano</t>
-  </si>
-  <si>
-    <t>Desgraciadamente la  violencia en su modo más  crudo llegó a Hidalgo,  se recrudece en Tula  donde prevalece el  huachicoleo. Es  momento de frenar  estos hechos  delincuenciales…</t>
-  </si>
-  <si>
     <t>Editorial</t>
   </si>
   <si>
-    <t>Medidas para que sea eficaz la atención pública en salud</t>
-  </si>
-  <si>
     <t>Atención médica</t>
   </si>
   <si>
-    <t>Morena denuncia a Viggiano ante la FGR</t>
-  </si>
-  <si>
-    <t>Gobierno privilegió el diálogo antes de usar fuerza pública: Olivares</t>
-  </si>
-  <si>
-    <t>Hallan tres calcinados en vivienda de Tepeapulco</t>
-  </si>
-  <si>
-    <t>Policía municipal</t>
-  </si>
-  <si>
-    <t>Localización de cuerpo</t>
-  </si>
-  <si>
-    <t>Regidores y síndicos del PAN rechazan reforma</t>
-  </si>
-  <si>
-    <t>Arranca vacunación masiva en Hidalgo</t>
-  </si>
-  <si>
-    <t>Destina Saderh apoyos al sector agropecuario en Lolotla</t>
-  </si>
-  <si>
-    <t>Apoyo Al Agro</t>
-  </si>
-  <si>
-    <t>Concluye tigrillo su rehabilitación en Pachuca y se prepara para regresar a su hábitat natural</t>
-  </si>
-  <si>
-    <t>Rehabilitación animal</t>
-  </si>
-  <si>
-    <t>Morena denuncia a Viggiano ante el SAT por presunta simulación fiscal</t>
-  </si>
-  <si>
-    <t>Hidalgo fortalece la paz, seguridad y el diálogo con atención cercana: Guillermo Olivares</t>
-  </si>
-  <si>
-    <t>Claudia Sandoval visita primaria</t>
-  </si>
-  <si>
-    <t>info</t>
-  </si>
-  <si>
-    <t>Entrega mobiliario escolar</t>
-  </si>
-  <si>
-    <t>Tlaxcoapan, sede del taller estratégico para el desarrollo regional</t>
-  </si>
-  <si>
-    <t>Desarrollo regional</t>
-  </si>
-  <si>
-    <t>El magisterio de Hidalgo fortalece sus estructuras sindicales con encuentros regionales</t>
-  </si>
-  <si>
     <t>Reunión con sindicato</t>
   </si>
   <si>
-    <t>Ajacuba participa en taller estratégico para el desarrollo regional en Tlaxcoapan</t>
-  </si>
-  <si>
-    <t>Justifica Olivares uso de fuerza pública contra personas del IMSS</t>
-  </si>
-  <si>
-    <t>Cuernudos proyecta riqueza cultural de Hidalgo en Festival Cervantino</t>
-  </si>
-  <si>
-    <t>Festival Cultural</t>
-  </si>
-  <si>
-    <t>91 millones 600 mil desayunos escolares para niñas, niños y adolescentes</t>
-  </si>
-  <si>
-    <t>Fortalecen la paz, seguridad y el diálogo con atención cercana: Guillermo Olivares</t>
-  </si>
-  <si>
-    <t>Destaca Hidalgo en materia anticorrupción</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón entrega obra educativa por 12.9 mdp en Huichapan</t>
-  </si>
-  <si>
-    <t>Entrega de infraestructura escolar</t>
-  </si>
-  <si>
-    <t>Denuncia Morena a Carolina Viggiano por presunta simulación fiscal</t>
-  </si>
-  <si>
-    <t>¡Iuuuu!! El Recodo le puso sabor sinaloense a la Feria</t>
-  </si>
-  <si>
     <t>61 niñas, niños y adolescentes encontraron un hogar a través de la adopción</t>
   </si>
   <si>
-    <t>Recuerda: la detección temprana salva vidas</t>
+    <t>Acumula Hidalgo 160 homicidios dolosos</t>
+  </si>
+  <si>
+    <t>Incidencia Delictiva</t>
+  </si>
+  <si>
+    <t>Estiman entrega de viviendas en diciembre</t>
+  </si>
+  <si>
+    <t>Infonavit</t>
+  </si>
+  <si>
+    <t>Se manifiestan en contra de ajuste salarial</t>
+  </si>
+  <si>
+    <t>Protesta sindical</t>
+  </si>
+  <si>
+    <t>Aumenta 96% ingreso propio</t>
+  </si>
+  <si>
+    <t>Por viaje en tren, no pagarían más de $100</t>
+  </si>
+  <si>
+    <t>SICT</t>
+  </si>
+  <si>
+    <t>Tren AIFA</t>
+  </si>
+  <si>
+    <t>Delincuencia da nuevo uso al aceite comestible</t>
+  </si>
+  <si>
+    <t>Destacan estudiantes en Olimpiada de Informática</t>
+  </si>
+  <si>
+    <t>Olimpiada de informática</t>
+  </si>
+  <si>
+    <t>Crecen 96% recursos propios en la entidad</t>
+  </si>
+  <si>
+    <t>Homicidios dolosos bajan 52% en 2 años: Sheinbaum</t>
+  </si>
+  <si>
+    <t>Estiman ahorro de 238 mdp</t>
+  </si>
+  <si>
+    <t>Reforma a contrataciones municipales</t>
+  </si>
+  <si>
+    <t>Reprueban en turismo a Real del Monte</t>
+  </si>
+  <si>
+    <t>Van 50 municipios en bloque vs reforma a cabildos</t>
+  </si>
+  <si>
+    <t>Regidor</t>
+  </si>
+  <si>
+    <t>Desploman la esperanza</t>
+  </si>
+  <si>
+    <t>Los grandes marcan el paso en la Champions</t>
+  </si>
+  <si>
+    <t>Casas del Bienestar: Hidalgo donará a la Federación predios</t>
+  </si>
+  <si>
+    <t>Alma Carolina Viggiano acusa estrategia para desprestigiarla</t>
+  </si>
+  <si>
+    <t>Viggiano</t>
+  </si>
+  <si>
+    <t>Enriquecimiento ilícito</t>
+  </si>
+  <si>
+    <t>Siguen pendientes recursos para los afectados por la vaguada de 2025</t>
+  </si>
+  <si>
+    <t>Movilización del IMSS reúne a más de 1,500 trabajadores</t>
+  </si>
+  <si>
+    <t>Julio Soto levanta la mano: Buscará el ayuntamiento de Tulancingo en 2027</t>
+  </si>
+  <si>
+    <t>Despresurizan al Poder Judicial con 40% de asuntos a mediación</t>
+  </si>
+  <si>
+    <t>Procuración de Justicia</t>
+  </si>
+  <si>
+    <t>Stephen King cierra ciclo con Carrie en serie</t>
+  </si>
+  <si>
+    <t>Goza Hidalgo de estabilidad y finanzas sanas</t>
+  </si>
+  <si>
+    <t>Río de las Avenidas: Prevén que la ampliación costará $500 millones</t>
+  </si>
+  <si>
+    <t>Rehabilitación Vial</t>
+  </si>
+  <si>
+    <t>Instalan 556 nuevas cámaras para vigilar la ciudad</t>
+  </si>
+  <si>
+    <t>Videovigilancia</t>
+  </si>
+  <si>
+    <t>La FGR dobla recompensas por capos y proyectan seis nuevos penales en el país</t>
+  </si>
+  <si>
+    <t>FGR</t>
+  </si>
+  <si>
+    <t>Combate a la delincuencia</t>
+  </si>
+  <si>
+    <t>Infraestructura y vivienda: Espera Claudia inversión por 8.4 biilones de pesos</t>
+  </si>
+  <si>
+    <t>Proyectos Federales</t>
+  </si>
+  <si>
+    <t>Agrupaciones variopintas se unen a trabajadores del IMSS</t>
+  </si>
+  <si>
+    <t>Fideicomiso del Polo de desarrollo de Zapotlán para el mes de octubre</t>
+  </si>
+  <si>
+    <t>Polos del Bienestar</t>
+  </si>
+  <si>
+    <t>Asignan 800 mdp para obras que atiendan daños por la vaguada</t>
+  </si>
+  <si>
+    <t>Puntual, comparecencia de García Harfuch: Ochoa</t>
+  </si>
+  <si>
+    <t>Ochoa</t>
+  </si>
+  <si>
+    <t>NINDE MOLRE: La protesta  nunca debe ser leída de  forma aislada, todas sus  manifestaciones tienen un origen anterior,  en el que la mayoría de las veces las  autoridades han sido omisas o deficientes  frente a esa problemática mayor que nos  impacta a todas las personas”.</t>
+  </si>
+  <si>
+    <t>Omisión</t>
+  </si>
+  <si>
+    <t>Harfuch captura a más de 70 mil</t>
+  </si>
+  <si>
+    <t>Seguridad Ciudadana</t>
+  </si>
+  <si>
+    <t>Personal del IMSS sale a las calles por cuarta ocasión</t>
+  </si>
+  <si>
+    <t>Marchan en Pachuca más de mil trabajadores del IMSS contra aumento salarial de 2.9%</t>
+  </si>
+  <si>
+    <t>A un año de la vaguada, Hidalgo ejecuta el 82% de recursos estatales para reconstrucción</t>
+  </si>
+  <si>
+    <t>Hidalgo registra reducción del 30.1% en homicidios dolosos</t>
+  </si>
+  <si>
+    <t>Jorge Reyes supervisa funcionamiento de cámaras de videovigilancia en La Loma</t>
+  </si>
+  <si>
+    <t>Ingresos propios de Hidalgo crecieron 96 por ciento: Secretaría de Hacienda</t>
+  </si>
+  <si>
+    <t>En dos años, los homicidios dolosos en México disminuyeron un 52%</t>
+  </si>
+  <si>
+    <t>Es doloroso y vergonzoso  que los médicos tengan  que salir a las calles a pedir  medicamentos y  equipamiento y  peor que no sean  escuchados por la  federación…</t>
+  </si>
+  <si>
+    <t>Trabajadores del IMSS exigen mejores condiciones laborales</t>
+  </si>
+  <si>
+    <t>Primera condena por violencia vicaria en Hidalgo</t>
+  </si>
+  <si>
+    <t>Violencia Vicaria</t>
+  </si>
+  <si>
+    <t>Hidalgo, entre los 5 estados con mejor manejo de deuda pública</t>
+  </si>
+  <si>
+    <t>IMSS protagoniza tercera protesta en Pachuca</t>
+  </si>
+  <si>
+    <t>Andrés Velázquez reconoce interés electoral entre diputados</t>
+  </si>
+  <si>
+    <t>Junta de Gobierno</t>
+  </si>
+  <si>
+    <t>Real del Monte, el pueblo mágico peor calificado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Instalan nuevas cámaras de vigilancia en La Loma</t>
+  </si>
+  <si>
+    <t>Hidalgo reduce 30.1% los homicidios dolosos</t>
+  </si>
+  <si>
+    <t>2 lesionados tras accidentar 4 vehículos en la Jorobas-Tula</t>
+  </si>
+  <si>
+    <t>Accidente Carretero</t>
+  </si>
+  <si>
+    <t>Hidalgo vive un momento histórico: finanzas sólidas e inversión récord</t>
+  </si>
+  <si>
+    <t>El Vaticano confirma que el Papa León XIV padece cáncer de pulmón</t>
+  </si>
+  <si>
+    <t>Diálogo abierto y atención directa con la ciudadanía en la Mesa de Seguridad de Tenango de Doria</t>
+  </si>
+  <si>
+    <t>Mesas de acercamiento</t>
+  </si>
+  <si>
+    <t>Nuevas cámaras de videovigilancia en La Loma, Pachuca; Jorge Reyes supervisa su funcionamiento</t>
+  </si>
+  <si>
+    <t>Hidalgo fortalece la atención a la infancia desde sus primeros años de vida</t>
+  </si>
+  <si>
+    <t>titul</t>
+  </si>
+  <si>
+    <t>Desde Molango continúa la nueva historia del magisterio con encuentro de jubilados del SNTE</t>
+  </si>
+  <si>
+    <t>Marchan nuevamente trabajadores del IMSS en Pachuca; exigen destitución de líder sindical</t>
+  </si>
+  <si>
+    <t>25 años Pueblos Mágicos</t>
+  </si>
+  <si>
+    <t>Pueblos Mágicos</t>
+  </si>
+  <si>
+    <t>Nuevas cámaras de videeovigilancia en La Loma, Pachuca; Jorge Reyes supervisa su funcionamiento</t>
+  </si>
+  <si>
+    <t>Todo listo para Pachuca Rock Fest en su nueva sede</t>
+  </si>
+  <si>
+    <t>Cartelera De Eventos</t>
+  </si>
+  <si>
+    <t>Talento hidalguense destaca en las Olimpiadas Mexicanas de Informática 2026</t>
+  </si>
+  <si>
+    <t>Hidlago vive un momento histórico con finanzas sólidas e inversión récord: Hacienda</t>
+  </si>
+  <si>
+    <t>ariana Seoane y La Casetera hicieron bailar a la feria</t>
+  </si>
+  <si>
+    <t>Recuerda: La detección temprana salva vidas</t>
   </si>
 </sst>
 </file>
@@ -788,7 +749,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -797,87 +758,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="d/m/yy;@"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="1"/>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -927,6 +807,43 @@
         </left>
       </border>
     </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="d/m/yy;@"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="1"/>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -941,15 +858,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J69" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5">
-  <autoFilter ref="A1:J69" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J65" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6">
+  <autoFilter ref="A1:J65" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{9D9ACAF2-1710-400E-A0E5-0A5BB378D4A0}" name="Fecha" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{9D9ACAF2-1710-400E-A0E5-0A5BB378D4A0}" name="Fecha" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{03A139BE-A997-45E6-81E6-5F7467162FC5}" name="Medio"/>
-    <tableColumn id="3" xr3:uid="{4CA37DD5-010E-43EE-907D-87C1845DB2AB}" name="Titular" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{4CA37DD5-010E-43EE-907D-87C1845DB2AB}" name="Titular" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{1E763E28-25D7-4FE7-AD1A-91C7A0FE0E7A}" name="Recurso editorial"/>
     <tableColumn id="5" xr3:uid="{F8C19AF2-6D19-449B-9F8B-6424964B1BCF}" name="Dependencia"/>
     <tableColumn id="6" xr3:uid="{46DF0510-7A9A-4625-979E-4EBC30CC7AA3}" name="Organismo"/>
@@ -981,13 +898,13 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}" name="Tabla3" displayName="Tabla3" ref="D1:E27" totalsRowShown="0" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}" name="Tabla3" displayName="Tabla3" ref="D1:E27" totalsRowShown="0" tableBorderDxfId="3">
   <autoFilter ref="D1:E27" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:E27">
     <sortCondition ref="D1:D27"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A040A308-8C62-4D4B-B3BE-EC124A9B961C}" name="Dependencia" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{A040A308-8C62-4D4B-B3BE-EC124A9B961C}" name="Dependencia" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{2B2FFCF1-496A-4D37-8C8B-790A66FD9968}" name="Nivel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1311,7 +1228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1360,13 +1277,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -1375,10 +1292,10 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -1394,66 +1311,66 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
         <v>100</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J3" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" t="s">
         <v>102</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" t="s">
-        <v>85</v>
-      </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J4" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1462,28 +1379,28 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I5" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1496,32 +1413,32 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
         <v>105</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
       </c>
       <c r="G6" t="s">
         <v>106</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J6" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1530,10 +1447,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>107</v>
@@ -1548,10 +1465,10 @@
         <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I7" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1564,28 +1481,28 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I8" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1596,9 +1513,9 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
@@ -1607,38 +1524,38 @@
         <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J9" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1647,13 +1564,13 @@
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I10" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -1666,134 +1583,134 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
       </c>
       <c r="I11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J11" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B12" t="s">
         <v>69</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="H12" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J12" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B13" t="s">
         <v>69</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Alcaldías</v>
+      </c>
+      <c r="J13" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
+        <v>46309</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" t="s">
-        <v>96</v>
-      </c>
-      <c r="H13" t="s">
-        <v>72</v>
-      </c>
-      <c r="I13" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J13" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
-        <v>46308</v>
-      </c>
-      <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>118</v>
-      </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="H14" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="I14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J14" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1802,13 +1719,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D15" t="s">
         <v>12</v>
@@ -1834,34 +1751,34 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
       </c>
       <c r="I16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J16" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -1870,229 +1787,229 @@
     </row>
     <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
       </c>
       <c r="I17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Sucesión gubernamental</v>
       </c>
       <c r="J17" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B18" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
       </c>
       <c r="I18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J18" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B19" t="s">
         <v>71</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="G19" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="H19" t="s">
         <v>68</v>
       </c>
       <c r="I19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J19" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B20" t="s">
         <v>71</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G20" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
       </c>
       <c r="I20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J20" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H21" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J21" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
       </c>
       <c r="I22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J22" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s">
         <v>72</v>
@@ -2106,148 +2023,148 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D24" t="s">
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
       </c>
       <c r="I24" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J24" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="11">
+        <v>46309</v>
+      </c>
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" t="s">
+        <v>133</v>
+      </c>
+      <c r="H25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
         <v>Alcaldías</v>
       </c>
-      <c r="J24" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="11">
-        <v>46308</v>
-      </c>
-      <c r="B25" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="J25" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="11">
+        <v>46309</v>
+      </c>
+      <c r="B26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
+        <v>135</v>
+      </c>
+      <c r="G26" t="s">
         <v>136</v>
-      </c>
-      <c r="D25" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G25" t="s">
-        <v>96</v>
-      </c>
-      <c r="H25" t="s">
-        <v>72</v>
-      </c>
-      <c r="I25" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J25" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
-        <v>46308</v>
-      </c>
-      <c r="B26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" t="s">
-        <v>95</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
       </c>
       <c r="I26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J26" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
         <v>138</v>
       </c>
-      <c r="D27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" t="s">
-        <v>2</v>
-      </c>
-      <c r="G27" t="s">
-        <v>96</v>
-      </c>
       <c r="H27" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J27" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>139</v>
@@ -2256,20 +2173,20 @@
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="G28" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="H28" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J28" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2278,304 +2195,304 @@
     </row>
     <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" t="s">
         <v>141</v>
       </c>
-      <c r="D29" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" t="s">
-        <v>87</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
+        <v>72</v>
+      </c>
+      <c r="I29" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Gobierno del estado</v>
+      </c>
+      <c r="J29" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
+        <v>46309</v>
+      </c>
+      <c r="B30" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="H29" t="s">
-        <v>11</v>
-      </c>
-      <c r="I29" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
-      </c>
-      <c r="J29" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="11">
-        <v>46308</v>
-      </c>
-      <c r="B30" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>143</v>
-      </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G30" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J30" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D31" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="G31" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
       </c>
       <c r="I31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Sucesión gubernamental</v>
       </c>
       <c r="J31" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D32" t="s">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G32" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
       </c>
       <c r="I32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J32" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C33" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" t="s">
         <v>148</v>
       </c>
-      <c r="D33" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" t="s">
-        <v>2</v>
-      </c>
       <c r="G33" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
       </c>
       <c r="I33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J33" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>149</v>
       </c>
       <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" t="s">
+        <v>85</v>
+      </c>
+      <c r="G34" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" t="s">
+        <v>68</v>
+      </c>
+      <c r="I34" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Presidencia de la República</v>
+      </c>
+      <c r="J34" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="11">
+        <v>46309</v>
+      </c>
+      <c r="B35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" t="s">
         <v>13</v>
       </c>
-      <c r="E34" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" t="s">
-        <v>2</v>
-      </c>
-      <c r="G34" t="s">
-        <v>150</v>
-      </c>
-      <c r="H34" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J34" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="11">
-        <v>46308</v>
-      </c>
-      <c r="B35" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D35" t="s">
-        <v>12</v>
-      </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G35" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="H35" t="s">
         <v>68</v>
       </c>
       <c r="I35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J35" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D36" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F36" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G36" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
       </c>
       <c r="I36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J36" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D37" t="s">
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="F37" t="s">
-        <v>155</v>
+        <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="H37" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Sucesión gubernamental</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J37" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2584,134 +2501,134 @@
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="G38" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
       </c>
       <c r="I38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J38" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F39" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G39" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J39" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D40" t="s">
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F40" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H40" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J40" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B41" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D41" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="E41" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G41" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="H41" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J41" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -2720,334 +2637,334 @@
     </row>
     <row r="42" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B42" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D42" t="s">
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F42" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="G42" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H42" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J42" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F43" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43" t="s">
+        <v>159</v>
+      </c>
+      <c r="H43" t="s">
+        <v>72</v>
+      </c>
+      <c r="I43" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
+        <v>Otros</v>
+      </c>
+      <c r="J43" t="str">
+        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
+        <v>Otros</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="11">
+        <v>46309</v>
+      </c>
+      <c r="B44" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" t="s">
         <v>13</v>
       </c>
-      <c r="E43" t="s">
-        <v>22</v>
-      </c>
-      <c r="F43" t="s">
-        <v>22</v>
-      </c>
-      <c r="G43" t="s">
-        <v>94</v>
-      </c>
-      <c r="H43" t="s">
-        <v>68</v>
-      </c>
-      <c r="I43" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J43" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="11">
-        <v>46308</v>
-      </c>
-      <c r="B44" t="s">
-        <v>77</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D44" t="s">
-        <v>12</v>
-      </c>
       <c r="E44" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F44" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G44" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
       </c>
       <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J44" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D45" t="s">
-        <v>164</v>
+        <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F45" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="G45" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H45" t="s">
         <v>68</v>
       </c>
       <c r="I45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J45" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D46" t="s">
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F46" t="s">
-        <v>14</v>
+        <v>163</v>
       </c>
       <c r="G46" t="s">
-        <v>166</v>
+        <v>61</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
       </c>
       <c r="I46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Presidencia de la República</v>
+        <v>Otros</v>
       </c>
       <c r="J46" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F47" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G47" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
       </c>
       <c r="I47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J47" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>Gabinete</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B48" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D48" t="s">
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F48" t="s">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="G48" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
       </c>
       <c r="I48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J48" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B49" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F49" t="s">
-        <v>170</v>
+        <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>171</v>
+        <v>98</v>
       </c>
       <c r="H49" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J49" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D50" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="E50" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="G50" t="s">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="H50" t="s">
         <v>11</v>
       </c>
       <c r="I50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Otros</v>
       </c>
       <c r="J50" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F51" t="s">
         <v>2</v>
       </c>
       <c r="G51" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3060,100 +2977,100 @@
     </row>
     <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D52" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G52" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
       </c>
       <c r="I52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J52" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D53" t="s">
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G53" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H53" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J53" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F54" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="G54" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="H54" t="s">
         <v>11</v>
       </c>
       <c r="I54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J54" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -3162,25 +3079,25 @@
     </row>
     <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B55" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D55" t="s">
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F55" t="s">
-        <v>2</v>
+        <v>175</v>
       </c>
       <c r="G55" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s">
         <v>72</v>
@@ -3194,34 +3111,34 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D56" t="s">
-        <v>181</v>
+        <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F56" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="G56" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
       </c>
       <c r="I56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Otros</v>
       </c>
       <c r="J56" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
@@ -3230,93 +3147,93 @@
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B57" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D57" t="s">
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F57" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G57" t="s">
-        <v>184</v>
+        <v>102</v>
       </c>
       <c r="H57" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
+        <v>Presidencia de la República</v>
       </c>
       <c r="J57" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D58" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F58" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G58" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="H58" t="s">
         <v>11</v>
       </c>
       <c r="I58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Otros</v>
+        <v>Gobierno del estado</v>
       </c>
       <c r="J58" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
+        <v>Gabinete</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B59" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D59" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E59" t="s">
         <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="G59" t="s">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="H59" t="s">
         <v>11</v>
@@ -3330,64 +3247,64 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B60" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D60" t="s">
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F60" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G60" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="H60" t="s">
         <v>11</v>
       </c>
       <c r="I60" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Otros</v>
       </c>
       <c r="J60" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
+        <v>Otros</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B61" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D61" t="s">
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>190</v>
+        <v>109</v>
       </c>
       <c r="H61" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I61" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3400,28 +3317,28 @@
     </row>
     <row r="62" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B62" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D62" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F62" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="I62" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3432,27 +3349,27 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F63" t="s">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="G63" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H63" t="s">
         <v>72</v>
@@ -3466,30 +3383,30 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="E64" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F64" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="G64" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H64" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="I64" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
@@ -3500,179 +3417,43 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B65" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D65" t="s">
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F65" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="H65" t="s">
         <v>11</v>
       </c>
       <c r="I65" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
+        <v>Alcaldías</v>
       </c>
       <c r="J65" t="str">
         <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A66" s="11">
-        <v>46308</v>
-      </c>
-      <c r="B66" t="s">
-        <v>82</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D66" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" t="s">
-        <v>18</v>
-      </c>
-      <c r="F66" t="s">
-        <v>18</v>
-      </c>
-      <c r="G66" t="s">
-        <v>111</v>
-      </c>
-      <c r="H66" t="s">
-        <v>11</v>
-      </c>
-      <c r="I66" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Partidos</v>
-      </c>
-      <c r="J66" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Otros</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="11">
-        <v>46308</v>
-      </c>
-      <c r="B67" t="s">
-        <v>82</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D67" t="s">
-        <v>12</v>
-      </c>
-      <c r="E67" t="s">
-        <v>29</v>
-      </c>
-      <c r="F67" t="s">
-        <v>89</v>
-      </c>
-      <c r="G67" t="s">
-        <v>86</v>
-      </c>
-      <c r="H67" t="s">
-        <v>72</v>
-      </c>
-      <c r="I67" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J67" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="11">
-        <v>46308</v>
-      </c>
-      <c r="B68" t="s">
-        <v>82</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D68" t="s">
-        <v>80</v>
-      </c>
-      <c r="E68" t="s">
-        <v>36</v>
-      </c>
-      <c r="F68" t="s">
-        <v>36</v>
-      </c>
-      <c r="G68" t="s">
-        <v>92</v>
-      </c>
-      <c r="H68" t="s">
-        <v>11</v>
-      </c>
-      <c r="I68" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Gobierno del estado</v>
-      </c>
-      <c r="J68" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
-        <v>Gabinete</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="11">
-        <v>46308</v>
-      </c>
-      <c r="B69" t="s">
-        <v>82</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D69" t="s">
-        <v>80</v>
-      </c>
-      <c r="E69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F69" t="s">
-        <v>16</v>
-      </c>
-      <c r="G69" t="s">
-        <v>84</v>
-      </c>
-      <c r="H69" t="s">
-        <v>11</v>
-      </c>
-      <c r="I69" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla2[Dependencia],Tabla2[Clasificación],"XXX",0)</f>
-        <v>Alcaldías</v>
-      </c>
-      <c r="J69" t="str">
-        <f>_xlfn.XLOOKUP(Tabla1[[#This Row],[Dependencia]],Tabla3[Dependencia],Tabla3[Nivel],"Otros",0)</f>
         <v>Otros</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I69">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="I2:I65">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$I2="XXX"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4242,7 +4023,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s">
         <v>44</v>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A52FDD-D976-46D5-B397-6B4DCF415F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C3D48A-4BB3-4FA6-B3D3-96427DA14E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="4" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="191">
   <si>
     <t>Fecha</t>
   </si>
@@ -579,9 +583,6 @@
     <t>Pueblos Mágicos</t>
   </si>
   <si>
-    <t>Nuevas cámaras de videeovigilancia en La Loma, Pachuca; Jorge Reyes supervisa su funcionamiento</t>
-  </si>
-  <si>
     <t>Todo listo para Pachuca Rock Fest en su nueva sede</t>
   </si>
   <si>
@@ -598,6 +599,21 @@
   </si>
   <si>
     <t>Recuerda: La detección temprana salva vidas</t>
+  </si>
+  <si>
+    <t>Cuenta de Recurso editorial</t>
+  </si>
+  <si>
+    <t>Etiquetas de fila</t>
+  </si>
+  <si>
+    <t>Total general</t>
+  </si>
+  <si>
+    <t>Effetá</t>
+  </si>
+  <si>
+    <t>Pachuca Brilla</t>
   </si>
 </sst>
 </file>
@@ -730,7 +746,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -745,18 +761,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -857,16 +874,1025 @@
 </styleSheet>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Francisco Villeda Velazquez" refreshedDate="46309.394546875003" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="64" xr:uid="{24068B4B-A6D0-4CBB-8A00-540654793919}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Tabla1"/>
+  </cacheSource>
+  <cacheFields count="10">
+    <cacheField name="Fecha" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-10-14T00:00:00" maxDate="2026-10-15T00:00:00"/>
+    </cacheField>
+    <cacheField name="Medio" numFmtId="0">
+      <sharedItems count="8">
+        <s v="El Sol de Hidalgo"/>
+        <s v="El Universal Hidalgo"/>
+        <s v="Criterio"/>
+        <s v="Milenio Hidalgo"/>
+        <s v="La Jornada Hidalgo"/>
+        <s v="Síntesis"/>
+        <s v="Plaza Juárez"/>
+        <s v="Marfeca"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Titular" numFmtId="0">
+      <sharedItems longText="1"/>
+    </cacheField>
+    <cacheField name="Recurso editorial" numFmtId="0">
+      <sharedItems count="6">
+        <s v="Llamado"/>
+        <s v="Foco gráfico"/>
+        <s v="Ocho columnas"/>
+        <s v="Editorial"/>
+        <s v="Cintillo"/>
+        <s v="Publicidad"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Dependencia" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Organismo" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Tema" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Estatus" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Grupo" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Nivel" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="64">
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="0"/>
+    <s v="Acumula Hidalgo 160 homicidios dolosos"/>
+    <x v="0"/>
+    <s v="Presidencia"/>
+    <s v="Presidencia"/>
+    <s v="Incidencia Delictiva"/>
+    <s v="Informativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="0"/>
+    <s v="Estiman entrega de viviendas en diciembre"/>
+    <x v="0"/>
+    <s v="Presidencia"/>
+    <s v="Infonavit"/>
+    <s v="Plan Nacional De Vivienda"/>
+    <s v="Informativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="0"/>
+    <s v="Se manifiestan en contra de ajuste salarial"/>
+    <x v="1"/>
+    <s v="Presidencia"/>
+    <s v="IMSS"/>
+    <s v="Protesta sindical"/>
+    <s v="Negativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="0"/>
+    <s v="Aumenta 96% ingreso propio"/>
+    <x v="0"/>
+    <s v="Hacienda"/>
+    <s v="Titular"/>
+    <s v="Comparecencias"/>
+    <s v="Positiva"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="0"/>
+    <s v="Por viaje en tren, no pagarían más de $100"/>
+    <x v="2"/>
+    <s v="Presidencia"/>
+    <s v="SICT"/>
+    <s v="Tren AIFA"/>
+    <s v="Positiva"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="0"/>
+    <s v="Delincuencia da nuevo uso al aceite comestible"/>
+    <x v="0"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+    <s v="Temas varios"/>
+    <s v="Informativa"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="1"/>
+    <s v="Destacan estudiantes en Olimpiada de Informática"/>
+    <x v="1"/>
+    <s v="SEPH"/>
+    <s v="SEPH"/>
+    <s v="Olimpiada de informática"/>
+    <s v="Positiva"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="1"/>
+    <s v="Crecen 96% recursos propios en la entidad"/>
+    <x v="2"/>
+    <s v="Hacienda"/>
+    <s v="Titular"/>
+    <s v="Comparecencias"/>
+    <s v="Positiva"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="1"/>
+    <s v="Homicidios dolosos bajan 52% en 2 años: Sheinbaum"/>
+    <x v="0"/>
+    <s v="Presidencia"/>
+    <s v="Presidencia"/>
+    <s v="Incidencia Delictiva"/>
+    <s v="Positiva"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="1"/>
+    <s v="Estiman ahorro de 238 mdp"/>
+    <x v="0"/>
+    <s v="Ayuntamiento"/>
+    <s v="Ayuntamiento"/>
+    <s v="Reforma a contrataciones municipales"/>
+    <s v="Informativa"/>
+    <s v="Alcaldías"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="1"/>
+    <s v="Reprueban en turismo a Real del Monte"/>
+    <x v="0"/>
+    <s v="Turismo"/>
+    <s v="Titular"/>
+    <s v="Comparecencias"/>
+    <s v="Negativa"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="1"/>
+    <s v="Van 50 municipios en bloque vs reforma a cabildos"/>
+    <x v="0"/>
+    <s v="Ayuntamiento"/>
+    <s v="Regidor"/>
+    <s v="Reforma a contrataciones municipales"/>
+    <s v="Informativa"/>
+    <s v="Alcaldías"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="2"/>
+    <s v="Desploman la esperanza"/>
+    <x v="0"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+    <s v="Deportes"/>
+    <s v="Informativa"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="2"/>
+    <s v="Los grandes marcan el paso en la Champions"/>
+    <x v="0"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+    <s v="Deportes"/>
+    <s v="Informativa"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="2"/>
+    <s v="Casas del Bienestar: Hidalgo donará a la Federación predios"/>
+    <x v="2"/>
+    <s v="Presidencia"/>
+    <s v="Presidencia"/>
+    <s v="Plan Nacional De Vivienda"/>
+    <s v="Informativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="2"/>
+    <s v="Alma Carolina Viggiano acusa estrategia para desprestigiarla"/>
+    <x v="0"/>
+    <s v="Aspirantes"/>
+    <s v="Viggiano"/>
+    <s v="Enriquecimiento ilícito"/>
+    <s v="Informativa"/>
+    <s v="Sucesión gubernamental"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="2"/>
+    <s v="Siguen pendientes recursos para los afectados por la vaguada de 2025"/>
+    <x v="0"/>
+    <s v="Hacienda"/>
+    <s v="Titular"/>
+    <s v="Comparecencias"/>
+    <s v="Informativa"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="2"/>
+    <s v="Movilización del IMSS reúne a más de 1,500 trabajadores"/>
+    <x v="1"/>
+    <s v="Presidencia"/>
+    <s v="IMSS"/>
+    <s v="Protesta sindical"/>
+    <s v="Negativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="2"/>
+    <s v="Julio Soto levanta la mano: Buscará el ayuntamiento de Tulancingo en 2027"/>
+    <x v="0"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+    <s v="Aspirantes"/>
+    <s v="Informativa"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="3"/>
+    <s v="Despresurizan al Poder Judicial con 40% de asuntos a mediación"/>
+    <x v="2"/>
+    <s v="TSJEH"/>
+    <s v="Titular"/>
+    <s v="Procuración de Justicia"/>
+    <s v="Positiva"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="3"/>
+    <s v="Stephen King cierra ciclo con Carrie en serie"/>
+    <x v="0"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+    <s v="Temas varios"/>
+    <s v="Informativa"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="3"/>
+    <s v="Goza Hidalgo de estabilidad y finanzas sanas"/>
+    <x v="1"/>
+    <s v="Hacienda"/>
+    <s v="Titular"/>
+    <s v="Comparecencias"/>
+    <s v="Positiva"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="3"/>
+    <s v="Río de las Avenidas: Prevén que la ampliación costará $500 millones"/>
+    <x v="0"/>
+    <s v="Sipdus"/>
+    <s v="Sipdus"/>
+    <s v="Rehabilitación Vial"/>
+    <s v="Informativa"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="3"/>
+    <s v="Instalan 556 nuevas cámaras para vigilar la ciudad"/>
+    <x v="0"/>
+    <s v="Ayuntamiento"/>
+    <s v="Alcalde"/>
+    <s v="Videovigilancia"/>
+    <s v="Informativa"/>
+    <s v="Alcaldías"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="3"/>
+    <s v="La FGR dobla recompensas por capos y proyectan seis nuevos penales en el país"/>
+    <x v="0"/>
+    <s v="Presidencia"/>
+    <s v="FGR"/>
+    <s v="Combate a la delincuencia"/>
+    <s v="Informativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="3"/>
+    <s v="Infraestructura y vivienda: Espera Claudia inversión por 8.4 biilones de pesos"/>
+    <x v="0"/>
+    <s v="Presidencia"/>
+    <s v="Presidencia"/>
+    <s v="Proyectos Federales"/>
+    <s v="Informativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="3"/>
+    <s v="Agrupaciones variopintas se unen a trabajadores del IMSS"/>
+    <x v="0"/>
+    <s v="Presidencia"/>
+    <s v="IMSS"/>
+    <s v="Protesta sindical"/>
+    <s v="Negativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="3"/>
+    <s v="Fideicomiso del Polo de desarrollo de Zapotlán para el mes de octubre"/>
+    <x v="0"/>
+    <s v="Sedeco"/>
+    <s v="Sedeco"/>
+    <s v="Polos del Bienestar"/>
+    <s v="Positiva"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="4"/>
+    <s v="Asignan 800 mdp para obras que atiendan daños por la vaguada"/>
+    <x v="2"/>
+    <s v="Hacienda"/>
+    <s v="Titular"/>
+    <s v="Comparecencias"/>
+    <s v="Positiva"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="4"/>
+    <s v="Puntual, comparecencia de García Harfuch: Ochoa"/>
+    <x v="1"/>
+    <s v="Aspirantes"/>
+    <s v="Ochoa"/>
+    <s v="Comparecencias"/>
+    <s v="Informativa"/>
+    <s v="Sucesión gubernamental"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="4"/>
+    <s v="NINDE MOLRE: La protesta  nunca debe ser leída de  forma aislada, todas sus  manifestaciones tienen un origen anterior,  en el que la mayoría de las veces las  autoridades han sido omisas o deficientes  frente a esa problemática mayor que nos  impacta a todas las personas”."/>
+    <x v="0"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+    <s v="Omisión"/>
+    <s v="Informativa"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="4"/>
+    <s v="Harfuch captura a más de 70 mil"/>
+    <x v="0"/>
+    <s v="Presidencia"/>
+    <s v="Seguridad Ciudadana"/>
+    <s v="Combate a la delincuencia"/>
+    <s v="Informativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="4"/>
+    <s v="Personal del IMSS sale a las calles por cuarta ocasión"/>
+    <x v="0"/>
+    <s v="Presidencia"/>
+    <s v="IMSS"/>
+    <s v="Protesta sindical"/>
+    <s v="Negativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="5"/>
+    <s v="Marchan en Pachuca más de mil trabajadores del IMSS contra aumento salarial de 2.9%"/>
+    <x v="2"/>
+    <s v="Gobierno"/>
+    <s v="Gobierno"/>
+    <s v="Protesta sindical"/>
+    <s v="Negativa"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="5"/>
+    <s v="A un año de la vaguada, Hidalgo ejecuta el 82% de recursos estatales para reconstrucción"/>
+    <x v="0"/>
+    <s v="Hacienda"/>
+    <s v="Titular"/>
+    <s v="Comparecencias"/>
+    <s v="Informativa"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="5"/>
+    <s v="Hidalgo registra reducción del 30.1% en homicidios dolosos"/>
+    <x v="0"/>
+    <s v="Presidencia"/>
+    <s v="Presidencia"/>
+    <s v="Incidencia Delictiva"/>
+    <s v="Positiva"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="5"/>
+    <s v="Jorge Reyes supervisa funcionamiento de cámaras de videovigilancia en La Loma"/>
+    <x v="0"/>
+    <s v="Ayuntamiento"/>
+    <s v="Alcalde"/>
+    <s v="Videovigilancia"/>
+    <s v="Informativa"/>
+    <s v="Alcaldías"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Ingresos propios de Hidalgo crecieron 96 por ciento: Secretaría de Hacienda"/>
+    <x v="2"/>
+    <s v="Hacienda"/>
+    <s v="Titular"/>
+    <s v="Comparecencias"/>
+    <s v="Positiva"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="En dos años, los homicidios dolosos en México disminuyeron un 52%"/>
+    <x v="0"/>
+    <s v="Presidencia"/>
+    <s v="Presidencia"/>
+    <s v="Incidencia Delictiva"/>
+    <s v="Positiva"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Es doloroso y vergonzoso  que los médicos tengan  que salir a las calles a pedir  medicamentos y  equipamiento y  peor que no sean  escuchados por la  federación…"/>
+    <x v="3"/>
+    <s v="Presidencia"/>
+    <s v="IMSS"/>
+    <s v="Protesta sindical"/>
+    <s v="Negativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Trabajadores del IMSS exigen mejores condiciones laborales"/>
+    <x v="0"/>
+    <s v="Presidencia"/>
+    <s v="IMSS"/>
+    <s v="Protesta sindical"/>
+    <s v="Negativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Primera condena por violencia vicaria en Hidalgo"/>
+    <x v="0"/>
+    <s v="TSJEH"/>
+    <s v="TSJEH"/>
+    <s v="Violencia Vicaria"/>
+    <s v="Positiva"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Hidalgo, entre los 5 estados con mejor manejo de deuda pública"/>
+    <x v="2"/>
+    <s v="Hacienda"/>
+    <s v="Titular"/>
+    <s v="Comparecencias"/>
+    <s v="Informativa"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="IMSS protagoniza tercera protesta en Pachuca"/>
+    <x v="1"/>
+    <s v="Presidencia"/>
+    <s v="IMSS"/>
+    <s v="Protesta sindical"/>
+    <s v="Negativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Andrés Velázquez reconoce interés electoral entre diputados"/>
+    <x v="0"/>
+    <s v="Congreso"/>
+    <s v="Junta de Gobierno"/>
+    <s v="Aspirantes"/>
+    <s v="Informativa"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Real del Monte, el pueblo mágico peor calificado de Hidalgo"/>
+    <x v="0"/>
+    <s v="Turismo"/>
+    <s v="Titular"/>
+    <s v="Comparecencias"/>
+    <s v="Informativa"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Instalan nuevas cámaras de vigilancia en La Loma"/>
+    <x v="0"/>
+    <s v="Ayuntamiento"/>
+    <s v="Alcalde"/>
+    <s v="Videovigilancia"/>
+    <s v="Informativa"/>
+    <s v="Alcaldías"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Hidalgo reduce 30.1% los homicidios dolosos"/>
+    <x v="0"/>
+    <s v="Presidencia"/>
+    <s v="Presidencia"/>
+    <s v="Incidencia Delictiva"/>
+    <s v="Positiva"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="7"/>
+    <s v="2 lesionados tras accidentar 4 vehículos en la Jorobas-Tula"/>
+    <x v="4"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+    <s v="Accidente Carretero"/>
+    <s v="Informativa"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="7"/>
+    <s v="Hidalgo vive un momento histórico: finanzas sólidas e inversión récord"/>
+    <x v="0"/>
+    <s v="Hacienda"/>
+    <s v="Titular"/>
+    <s v="Comparecencias"/>
+    <s v="Positiva"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="7"/>
+    <s v="El Vaticano confirma que el Papa León XIV padece cáncer de pulmón"/>
+    <x v="2"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+    <s v="Temas internacionales"/>
+    <s v="Informativa"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="7"/>
+    <s v="Diálogo abierto y atención directa con la ciudadanía en la Mesa de Seguridad de Tenango de Doria"/>
+    <x v="0"/>
+    <s v="Segobh"/>
+    <s v="Titular"/>
+    <s v="Mesas de acercamiento"/>
+    <s v="Positiva"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="7"/>
+    <s v="Nuevas cámaras de videovigilancia en La Loma, Pachuca; Jorge Reyes supervisa su funcionamiento"/>
+    <x v="0"/>
+    <s v="Ayuntamiento"/>
+    <s v="Alcalde"/>
+    <s v="Videovigilancia"/>
+    <s v="Informativa"/>
+    <s v="Alcaldías"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="7"/>
+    <s v="Hidalgo fortalece la atención a la infancia desde sus primeros años de vida"/>
+    <x v="0"/>
+    <s v="SSH"/>
+    <s v="titul"/>
+    <s v="Atención médica"/>
+    <s v="Positiva"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="7"/>
+    <s v="Desde Molango continúa la nueva historia del magisterio con encuentro de jubilados del SNTE"/>
+    <x v="0"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+    <s v="Reunión con sindicato"/>
+    <s v="Informativa"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="7"/>
+    <s v="Marchan nuevamente trabajadores del IMSS en Pachuca; exigen destitución de líder sindical"/>
+    <x v="0"/>
+    <s v="Presidencia"/>
+    <s v="IMSS"/>
+    <s v="Protesta sindical"/>
+    <s v="Negativa"/>
+    <s v="Presidencia de la República"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="7"/>
+    <s v="25 años Pueblos Mágicos"/>
+    <x v="5"/>
+    <s v="Turismo"/>
+    <s v="Turismo"/>
+    <s v="Pueblos Mágicos"/>
+    <s v="Informativa"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Nuevas cámaras de videeovigilancia en La Loma, Pachuca; Jorge Reyes supervisa su funcionamiento"/>
+    <x v="2"/>
+    <s v="Ayuntamiento"/>
+    <s v="Alcalde"/>
+    <s v="Videovigilancia"/>
+    <s v="Informativa"/>
+    <s v="Alcaldías"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Todo listo para Pachuca Rock Fest en su nueva sede"/>
+    <x v="0"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+    <s v="Cartelera De Eventos"/>
+    <s v="Informativa"/>
+    <s v="Otros"/>
+    <s v="Otros"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Talento hidalguense destaca en las Olimpiadas Mexicanas de Informática 2026"/>
+    <x v="0"/>
+    <s v="SEPH"/>
+    <s v="SEPH"/>
+    <s v="Olimpiada de informática"/>
+    <s v="Positiva"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Hidlago vive un momento histórico con finanzas sólidas e inversión récord: Hacienda"/>
+    <x v="0"/>
+    <s v="Hacienda"/>
+    <s v="Titular"/>
+    <s v="Comparecencias"/>
+    <s v="Positiva"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="ariana Seoane y La Casetera hicieron bailar a la feria"/>
+    <x v="0"/>
+    <s v="Turismo"/>
+    <s v="OEEH"/>
+    <s v="Feria Pachuca"/>
+    <s v="Positiva"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="61 niñas, niños y adolescentes encontraron un hogar a través de la adopción"/>
+    <x v="5"/>
+    <s v="DIFH"/>
+    <s v="DIFH"/>
+    <s v="Informe de actividades"/>
+    <s v="Informativa"/>
+    <s v="Gobierno del estado"/>
+    <s v="Gabinete"/>
+  </r>
+  <r>
+    <d v="2026-10-14T00:00:00"/>
+    <x v="6"/>
+    <s v="Recuerda: La detección temprana salva vidas"/>
+    <x v="0"/>
+    <s v="Ayuntamiento"/>
+    <s v="Ayuntamiento"/>
+    <s v="Prevención cáncer de mama"/>
+    <s v="Informativa"/>
+    <s v="Alcaldías"/>
+    <s v="Otros"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DEEED8E4-C61E-4489-B373-2D4A90347DBF}" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A4:B39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="7">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="35">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Cuenta de Recurso editorial" fld="3" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J65" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6">
-  <autoFilter ref="A1:J65" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J65" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5">
+  <autoFilter ref="A1:J65" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Plaza Juárez"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J2">
     <sortCondition ref="C1:C2"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{9D9ACAF2-1710-400E-A0E5-0A5BB378D4A0}" name="Fecha" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{9D9ACAF2-1710-400E-A0E5-0A5BB378D4A0}" name="Fecha" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{03A139BE-A997-45E6-81E6-5F7467162FC5}" name="Medio"/>
-    <tableColumn id="3" xr3:uid="{4CA37DD5-010E-43EE-907D-87C1845DB2AB}" name="Titular" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{4CA37DD5-010E-43EE-907D-87C1845DB2AB}" name="Titular" dataDxfId="3"/>
     <tableColumn id="4" xr3:uid="{1E763E28-25D7-4FE7-AD1A-91C7A0FE0E7A}" name="Recurso editorial"/>
     <tableColumn id="5" xr3:uid="{F8C19AF2-6D19-449B-9F8B-6424964B1BCF}" name="Dependencia"/>
     <tableColumn id="6" xr3:uid="{46DF0510-7A9A-4625-979E-4EBC30CC7AA3}" name="Organismo"/>
@@ -898,13 +1924,13 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}" name="Tabla3" displayName="Tabla3" ref="D1:E27" totalsRowShown="0" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}" name="Tabla3" displayName="Tabla3" ref="D1:E27" totalsRowShown="0" tableBorderDxfId="2">
   <autoFilter ref="D1:E27" xr:uid="{80AFAA35-C663-4971-9820-992B55167F9C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:E27">
     <sortCondition ref="D1:D27"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A040A308-8C62-4D4B-B3BE-EC124A9B961C}" name="Dependencia" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{A040A308-8C62-4D4B-B3BE-EC124A9B961C}" name="Dependencia" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{2B2FFCF1-496A-4D37-8C8B-790A66FD9968}" name="Nivel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1227,6 +2253,308 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{987B67DB-D046-44C0-B978-386A50233412}">
+  <dimension ref="A4:B39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" s="13">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F590D41B-EE15-4091-8762-C3A670C9D896}">
   <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1275,7 +2603,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>46309</v>
       </c>
@@ -1309,7 +2637,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>46309</v>
       </c>
@@ -1343,7 +2671,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>46309</v>
       </c>
@@ -1377,7 +2705,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>46309</v>
       </c>
@@ -1411,7 +2739,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>46309</v>
       </c>
@@ -1445,7 +2773,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>46309</v>
       </c>
@@ -1479,7 +2807,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>46309</v>
       </c>
@@ -1513,7 +2841,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>46309</v>
       </c>
@@ -1547,7 +2875,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>46309</v>
       </c>
@@ -1581,7 +2909,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>46309</v>
       </c>
@@ -1615,7 +2943,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>46309</v>
       </c>
@@ -1649,7 +2977,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>46309</v>
       </c>
@@ -1683,7 +3011,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>46309</v>
       </c>
@@ -1717,7 +3045,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>46309</v>
       </c>
@@ -1751,7 +3079,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>46309</v>
       </c>
@@ -1785,7 +3113,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>46309</v>
       </c>
@@ -1819,7 +3147,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>46309</v>
       </c>
@@ -1853,7 +3181,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>46309</v>
       </c>
@@ -1887,7 +3215,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>46309</v>
       </c>
@@ -1921,7 +3249,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>46309</v>
       </c>
@@ -1955,7 +3283,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>46309</v>
       </c>
@@ -1989,7 +3317,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>46309</v>
       </c>
@@ -2023,7 +3351,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>46309</v>
       </c>
@@ -2057,7 +3385,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>46309</v>
       </c>
@@ -2091,7 +3419,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>46309</v>
       </c>
@@ -2125,7 +3453,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>46309</v>
       </c>
@@ -2159,7 +3487,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>46309</v>
       </c>
@@ -2193,7 +3521,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>46309</v>
       </c>
@@ -2227,7 +3555,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>46309</v>
       </c>
@@ -2261,7 +3589,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>46309</v>
       </c>
@@ -2295,7 +3623,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>46309</v>
       </c>
@@ -2329,7 +3657,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>46309</v>
       </c>
@@ -2363,7 +3691,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>46309</v>
       </c>
@@ -2397,7 +3725,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>46309</v>
       </c>
@@ -2431,7 +3759,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>46309</v>
       </c>
@@ -2465,7 +3793,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>46309</v>
       </c>
@@ -2499,7 +3827,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>46309</v>
       </c>
@@ -2708,7 +4036,7 @@
         <v>46309</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>160</v>
@@ -2742,7 +4070,7 @@
         <v>46309</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>161</v>
@@ -2776,7 +4104,7 @@
         <v>46309</v>
       </c>
       <c r="B46" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>162</v>
@@ -2810,7 +4138,7 @@
         <v>46309</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>164</v>
@@ -2844,7 +4172,7 @@
         <v>46309</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>165</v>
@@ -2878,7 +4206,7 @@
         <v>46309</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>166</v>
@@ -2907,7 +4235,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
         <v>46309</v>
       </c>
@@ -2941,7 +4269,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
         <v>46309</v>
       </c>
@@ -2975,7 +4303,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
         <v>46309</v>
       </c>
@@ -3009,7 +4337,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
         <v>46309</v>
       </c>
@@ -3043,7 +4371,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
         <v>46309</v>
       </c>
@@ -3077,7 +4405,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
         <v>46309</v>
       </c>
@@ -3111,7 +4439,7 @@
         <v>Gabinete</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
         <v>46309</v>
       </c>
@@ -3145,7 +4473,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
         <v>46309</v>
       </c>
@@ -3179,7 +4507,7 @@
         <v>Otros</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
         <v>46309</v>
       </c>
@@ -3218,10 +4546,10 @@
         <v>46309</v>
       </c>
       <c r="B59" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D59" t="s">
         <v>13</v>
@@ -3252,10 +4580,10 @@
         <v>46309</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D60" t="s">
         <v>12</v>
@@ -3267,7 +4595,7 @@
         <v>10</v>
       </c>
       <c r="G60" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H60" t="s">
         <v>11</v>
@@ -3286,10 +4614,10 @@
         <v>46309</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D61" t="s">
         <v>12</v>
@@ -3320,10 +4648,10 @@
         <v>46309</v>
       </c>
       <c r="B62" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D62" t="s">
         <v>12</v>
@@ -3354,10 +4682,10 @@
         <v>46309</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D63" t="s">
         <v>12</v>
@@ -3388,7 +4716,7 @@
         <v>46309</v>
       </c>
       <c r="B64" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>96</v>
@@ -3422,10 +4750,10 @@
         <v>46309</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D65" t="s">
         <v>12</v>
@@ -3453,7 +4781,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I65">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$I2="XXX"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3465,7 +4793,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8151DEFD-FF29-4969-B1FC-DF47C7CD743C}">
   <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C3D48A-4BB3-4FA6-B3D3-96427DA14E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81AB89A-7CC7-4064-ADAD-9D1CAB3C51CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja3" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId4"/>
+    <pivotCache cacheId="5" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="191">
   <si>
     <t>Fecha</t>
   </si>
@@ -762,13 +762,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -875,7 +875,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Francisco Villeda Velazquez" refreshedDate="46309.394546875003" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="64" xr:uid="{24068B4B-A6D0-4CBB-8A00-540654793919}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Francisco Villeda Velazquez" refreshedDate="46309.399708912038" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="64" xr:uid="{24068B4B-A6D0-4CBB-8A00-540654793919}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
@@ -884,7 +884,7 @@
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-10-14T00:00:00" maxDate="2026-10-15T00:00:00"/>
     </cacheField>
     <cacheField name="Medio" numFmtId="0">
-      <sharedItems count="8">
+      <sharedItems count="10">
         <s v="El Sol de Hidalgo"/>
         <s v="El Universal Hidalgo"/>
         <s v="Criterio"/>
@@ -892,7 +892,9 @@
         <s v="La Jornada Hidalgo"/>
         <s v="Síntesis"/>
         <s v="Plaza Juárez"/>
+        <s v="Effetá"/>
         <s v="Marfeca"/>
+        <s v="Pachuca Brilla"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Titular" numFmtId="0">
@@ -1446,7 +1448,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="6"/>
+    <x v="7"/>
     <s v="Hidalgo, entre los 5 estados con mejor manejo de deuda pública"/>
     <x v="2"/>
     <s v="Hacienda"/>
@@ -1458,7 +1460,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="6"/>
+    <x v="7"/>
     <s v="IMSS protagoniza tercera protesta en Pachuca"/>
     <x v="1"/>
     <s v="Presidencia"/>
@@ -1470,7 +1472,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="6"/>
+    <x v="7"/>
     <s v="Andrés Velázquez reconoce interés electoral entre diputados"/>
     <x v="0"/>
     <s v="Congreso"/>
@@ -1482,7 +1484,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="6"/>
+    <x v="7"/>
     <s v="Real del Monte, el pueblo mágico peor calificado de Hidalgo"/>
     <x v="0"/>
     <s v="Turismo"/>
@@ -1494,7 +1496,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="6"/>
+    <x v="7"/>
     <s v="Instalan nuevas cámaras de vigilancia en La Loma"/>
     <x v="0"/>
     <s v="Ayuntamiento"/>
@@ -1506,7 +1508,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="6"/>
+    <x v="7"/>
     <s v="Hidalgo reduce 30.1% los homicidios dolosos"/>
     <x v="0"/>
     <s v="Presidencia"/>
@@ -1518,7 +1520,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="7"/>
+    <x v="8"/>
     <s v="2 lesionados tras accidentar 4 vehículos en la Jorobas-Tula"/>
     <x v="4"/>
     <s v="Otros"/>
@@ -1530,7 +1532,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="7"/>
+    <x v="8"/>
     <s v="Hidalgo vive un momento histórico: finanzas sólidas e inversión récord"/>
     <x v="0"/>
     <s v="Hacienda"/>
@@ -1542,7 +1544,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="7"/>
+    <x v="8"/>
     <s v="El Vaticano confirma que el Papa León XIV padece cáncer de pulmón"/>
     <x v="2"/>
     <s v="Otros"/>
@@ -1554,7 +1556,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="7"/>
+    <x v="8"/>
     <s v="Diálogo abierto y atención directa con la ciudadanía en la Mesa de Seguridad de Tenango de Doria"/>
     <x v="0"/>
     <s v="Segobh"/>
@@ -1566,7 +1568,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="7"/>
+    <x v="8"/>
     <s v="Nuevas cámaras de videovigilancia en La Loma, Pachuca; Jorge Reyes supervisa su funcionamiento"/>
     <x v="0"/>
     <s v="Ayuntamiento"/>
@@ -1578,7 +1580,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="7"/>
+    <x v="8"/>
     <s v="Hidalgo fortalece la atención a la infancia desde sus primeros años de vida"/>
     <x v="0"/>
     <s v="SSH"/>
@@ -1590,7 +1592,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="7"/>
+    <x v="8"/>
     <s v="Desde Molango continúa la nueva historia del magisterio con encuentro de jubilados del SNTE"/>
     <x v="0"/>
     <s v="Otros"/>
@@ -1602,7 +1604,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="7"/>
+    <x v="8"/>
     <s v="Marchan nuevamente trabajadores del IMSS en Pachuca; exigen destitución de líder sindical"/>
     <x v="0"/>
     <s v="Presidencia"/>
@@ -1614,7 +1616,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="7"/>
+    <x v="8"/>
     <s v="25 años Pueblos Mágicos"/>
     <x v="5"/>
     <s v="Turismo"/>
@@ -1626,8 +1628,8 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="6"/>
-    <s v="Nuevas cámaras de videeovigilancia en La Loma, Pachuca; Jorge Reyes supervisa su funcionamiento"/>
+    <x v="9"/>
+    <s v="Nuevas cámaras de videovigilancia en La Loma, Pachuca; Jorge Reyes supervisa su funcionamiento"/>
     <x v="2"/>
     <s v="Ayuntamiento"/>
     <s v="Alcalde"/>
@@ -1638,7 +1640,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="6"/>
+    <x v="9"/>
     <s v="Todo listo para Pachuca Rock Fest en su nueva sede"/>
     <x v="0"/>
     <s v="Otros"/>
@@ -1650,7 +1652,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="6"/>
+    <x v="9"/>
     <s v="Talento hidalguense destaca en las Olimpiadas Mexicanas de Informática 2026"/>
     <x v="0"/>
     <s v="SEPH"/>
@@ -1662,7 +1664,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="6"/>
+    <x v="9"/>
     <s v="Hidlago vive un momento histórico con finanzas sólidas e inversión récord: Hacienda"/>
     <x v="0"/>
     <s v="Hacienda"/>
@@ -1674,7 +1676,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="6"/>
+    <x v="9"/>
     <s v="ariana Seoane y La Casetera hicieron bailar a la feria"/>
     <x v="0"/>
     <s v="Turismo"/>
@@ -1686,7 +1688,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="6"/>
+    <x v="9"/>
     <s v="61 niñas, niños y adolescentes encontraron un hogar a través de la adopción"/>
     <x v="5"/>
     <s v="DIFH"/>
@@ -1698,7 +1700,7 @@
   </r>
   <r>
     <d v="2026-10-14T00:00:00"/>
-    <x v="6"/>
+    <x v="9"/>
     <s v="Recuerda: La detección temprana salva vidas"/>
     <x v="0"/>
     <s v="Ayuntamiento"/>
@@ -1712,20 +1714,22 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DEEED8E4-C61E-4489-B373-2D4A90347DBF}" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A4:B39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DEEED8E4-C61E-4489-B373-2D4A90347DBF}" name="TablaDinámica1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A4:B45" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="9">
+      <items count="11">
         <item x="2"/>
         <item x="0"/>
         <item x="1"/>
         <item x="4"/>
-        <item x="7"/>
+        <item x="8"/>
         <item x="3"/>
         <item x="6"/>
         <item x="5"/>
+        <item x="7"/>
+        <item x="9"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1752,7 +1756,7 @@
     <field x="1"/>
     <field x="3"/>
   </rowFields>
-  <rowItems count="35">
+  <rowItems count="41">
     <i>
       <x/>
     </i>
@@ -1835,7 +1839,34 @@
       <x v="1"/>
     </i>
     <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i r="1">
       <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="9"/>
     </i>
     <i r="1">
       <x v="3"/>
@@ -1845,15 +1876,6 @@
     </i>
     <i r="1">
       <x v="5"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -2254,7 +2276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{987B67DB-D046-44C0-B978-386A50233412}">
-  <dimension ref="A4:B39"/>
+  <dimension ref="A4:B45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
@@ -2270,282 +2292,330 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="15">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="15">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="15">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="15">
         <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="15">
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="15">
         <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="15">
         <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="13">
-        <v>18</v>
+      <c r="B30" s="15">
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="13">
+      <c r="A32" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="15">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="13">
+      <c r="B35" s="15">
         <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" s="13">
-        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" s="13">
-        <v>4</v>
+        <v>13</v>
+      </c>
+      <c r="B36" s="15">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="13">
-        <v>3</v>
+      <c r="A37" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" s="15">
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="13">
+      <c r="A38" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B41" s="15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B45" s="15">
         <v>64</v>
       </c>
     </row>

--- a/MuestraPortadas.xlsx
+++ b/MuestraPortadas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\Reporteportadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81AB89A-7CC7-4064-ADAD-9D1CAB3C51CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C625CA-DDAB-4C51-80BD-59E6C3AE9BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{56C16FF2-DC5E-4EA2-A3CB-6D506676B8B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja3" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="186">
   <si>
     <t>Fecha</t>
   </si>
@@ -307,9 +307,6 @@
     <t>OEEH</t>
   </si>
   <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
     <t>Plan Nacional De Vivienda</t>
   </si>
   <si>
@@ -325,282 +322,15 @@
     <t>Editorial</t>
   </si>
   <si>
-    <t>Atención médica</t>
-  </si>
-  <si>
-    <t>Reunión con sindicato</t>
-  </si>
-  <si>
-    <t>61 niñas, niños y adolescentes encontraron un hogar a través de la adopción</t>
-  </si>
-  <si>
-    <t>Acumula Hidalgo 160 homicidios dolosos</t>
-  </si>
-  <si>
-    <t>Incidencia Delictiva</t>
-  </si>
-  <si>
-    <t>Estiman entrega de viviendas en diciembre</t>
-  </si>
-  <si>
-    <t>Infonavit</t>
-  </si>
-  <si>
-    <t>Se manifiestan en contra de ajuste salarial</t>
-  </si>
-  <si>
     <t>Protesta sindical</t>
   </si>
   <si>
-    <t>Aumenta 96% ingreso propio</t>
-  </si>
-  <si>
-    <t>Por viaje en tren, no pagarían más de $100</t>
-  </si>
-  <si>
-    <t>SICT</t>
-  </si>
-  <si>
-    <t>Tren AIFA</t>
-  </si>
-  <si>
-    <t>Delincuencia da nuevo uso al aceite comestible</t>
-  </si>
-  <si>
-    <t>Destacan estudiantes en Olimpiada de Informática</t>
-  </si>
-  <si>
-    <t>Olimpiada de informática</t>
-  </si>
-  <si>
-    <t>Crecen 96% recursos propios en la entidad</t>
-  </si>
-  <si>
-    <t>Homicidios dolosos bajan 52% en 2 años: Sheinbaum</t>
-  </si>
-  <si>
-    <t>Estiman ahorro de 238 mdp</t>
-  </si>
-  <si>
     <t>Reforma a contrataciones municipales</t>
   </si>
   <si>
-    <t>Reprueban en turismo a Real del Monte</t>
-  </si>
-  <si>
-    <t>Van 50 municipios en bloque vs reforma a cabildos</t>
-  </si>
-  <si>
     <t>Regidor</t>
   </si>
   <si>
-    <t>Desploman la esperanza</t>
-  </si>
-  <si>
-    <t>Los grandes marcan el paso en la Champions</t>
-  </si>
-  <si>
-    <t>Casas del Bienestar: Hidalgo donará a la Federación predios</t>
-  </si>
-  <si>
-    <t>Alma Carolina Viggiano acusa estrategia para desprestigiarla</t>
-  </si>
-  <si>
-    <t>Viggiano</t>
-  </si>
-  <si>
-    <t>Enriquecimiento ilícito</t>
-  </si>
-  <si>
-    <t>Siguen pendientes recursos para los afectados por la vaguada de 2025</t>
-  </si>
-  <si>
-    <t>Movilización del IMSS reúne a más de 1,500 trabajadores</t>
-  </si>
-  <si>
-    <t>Julio Soto levanta la mano: Buscará el ayuntamiento de Tulancingo en 2027</t>
-  </si>
-  <si>
-    <t>Despresurizan al Poder Judicial con 40% de asuntos a mediación</t>
-  </si>
-  <si>
-    <t>Procuración de Justicia</t>
-  </si>
-  <si>
-    <t>Stephen King cierra ciclo con Carrie en serie</t>
-  </si>
-  <si>
-    <t>Goza Hidalgo de estabilidad y finanzas sanas</t>
-  </si>
-  <si>
-    <t>Río de las Avenidas: Prevén que la ampliación costará $500 millones</t>
-  </si>
-  <si>
-    <t>Rehabilitación Vial</t>
-  </si>
-  <si>
-    <t>Instalan 556 nuevas cámaras para vigilar la ciudad</t>
-  </si>
-  <si>
-    <t>Videovigilancia</t>
-  </si>
-  <si>
-    <t>La FGR dobla recompensas por capos y proyectan seis nuevos penales en el país</t>
-  </si>
-  <si>
-    <t>FGR</t>
-  </si>
-  <si>
-    <t>Combate a la delincuencia</t>
-  </si>
-  <si>
-    <t>Infraestructura y vivienda: Espera Claudia inversión por 8.4 biilones de pesos</t>
-  </si>
-  <si>
-    <t>Proyectos Federales</t>
-  </si>
-  <si>
-    <t>Agrupaciones variopintas se unen a trabajadores del IMSS</t>
-  </si>
-  <si>
-    <t>Fideicomiso del Polo de desarrollo de Zapotlán para el mes de octubre</t>
-  </si>
-  <si>
-    <t>Polos del Bienestar</t>
-  </si>
-  <si>
-    <t>Asignan 800 mdp para obras que atiendan daños por la vaguada</t>
-  </si>
-  <si>
-    <t>Puntual, comparecencia de García Harfuch: Ochoa</t>
-  </si>
-  <si>
-    <t>Ochoa</t>
-  </si>
-  <si>
-    <t>NINDE MOLRE: La protesta  nunca debe ser leída de  forma aislada, todas sus  manifestaciones tienen un origen anterior,  en el que la mayoría de las veces las  autoridades han sido omisas o deficientes  frente a esa problemática mayor que nos  impacta a todas las personas”.</t>
-  </si>
-  <si>
-    <t>Omisión</t>
-  </si>
-  <si>
-    <t>Harfuch captura a más de 70 mil</t>
-  </si>
-  <si>
-    <t>Seguridad Ciudadana</t>
-  </si>
-  <si>
-    <t>Personal del IMSS sale a las calles por cuarta ocasión</t>
-  </si>
-  <si>
-    <t>Marchan en Pachuca más de mil trabajadores del IMSS contra aumento salarial de 2.9%</t>
-  </si>
-  <si>
-    <t>A un año de la vaguada, Hidalgo ejecuta el 82% de recursos estatales para reconstrucción</t>
-  </si>
-  <si>
-    <t>Hidalgo registra reducción del 30.1% en homicidios dolosos</t>
-  </si>
-  <si>
-    <t>Jorge Reyes supervisa funcionamiento de cámaras de videovigilancia en La Loma</t>
-  </si>
-  <si>
-    <t>Ingresos propios de Hidalgo crecieron 96 por ciento: Secretaría de Hacienda</t>
-  </si>
-  <si>
-    <t>En dos años, los homicidios dolosos en México disminuyeron un 52%</t>
-  </si>
-  <si>
-    <t>Es doloroso y vergonzoso  que los médicos tengan  que salir a las calles a pedir  medicamentos y  equipamiento y  peor que no sean  escuchados por la  federación…</t>
-  </si>
-  <si>
-    <t>Trabajadores del IMSS exigen mejores condiciones laborales</t>
-  </si>
-  <si>
-    <t>Primera condena por violencia vicaria en Hidalgo</t>
-  </si>
-  <si>
-    <t>Violencia Vicaria</t>
-  </si>
-  <si>
-    <t>Hidalgo, entre los 5 estados con mejor manejo de deuda pública</t>
-  </si>
-  <si>
-    <t>IMSS protagoniza tercera protesta en Pachuca</t>
-  </si>
-  <si>
-    <t>Andrés Velázquez reconoce interés electoral entre diputados</t>
-  </si>
-  <si>
-    <t>Junta de Gobierno</t>
-  </si>
-  <si>
-    <t>Real del Monte, el pueblo mágico peor calificado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Instalan nuevas cámaras de vigilancia en La Loma</t>
-  </si>
-  <si>
-    <t>Hidalgo reduce 30.1% los homicidios dolosos</t>
-  </si>
-  <si>
-    <t>2 lesionados tras accidentar 4 vehículos en la Jorobas-Tula</t>
-  </si>
-  <si>
-    <t>Accidente Carretero</t>
-  </si>
-  <si>
-    <t>Hidalgo vive un momento histórico: finanzas sólidas e inversión récord</t>
-  </si>
-  <si>
-    <t>El Vaticano confirma que el Papa León XIV padece cáncer de pulmón</t>
-  </si>
-  <si>
-    <t>Diálogo abierto y atención directa con la ciudadanía en la Mesa de Seguridad de Tenango de Doria</t>
-  </si>
-  <si>
-    <t>Mesas de acercamiento</t>
-  </si>
-  <si>
-    <t>Nuevas cámaras de videovigilancia en La Loma, Pachuca; Jorge Reyes supervisa su funcionamiento</t>
-  </si>
-  <si>
-    <t>Hidalgo fortalece la atención a la infancia desde sus primeros años de vida</t>
-  </si>
-  <si>
-    <t>titul</t>
-  </si>
-  <si>
-    <t>Desde Molango continúa la nueva historia del magisterio con encuentro de jubilados del SNTE</t>
-  </si>
-  <si>
-    <t>Marchan nuevamente trabajadores del IMSS en Pachuca; exigen destitución de líder sindical</t>
-  </si>
-  <si>
-    <t>25 años Pueblos Mágicos</t>
-  </si>
-  <si>
-    <t>Pueblos Mágicos</t>
-  </si>
-  <si>
-    <t>Todo listo para Pachuca Rock Fest en su nueva sede</t>
-  </si>
-  <si>
-    <t>Cartelera De Eventos</t>
-  </si>
-  <si>
-    <t>Talento hidalguense destaca en las Olimpiadas Mexicanas de Informática 2026</t>
-  </si>
-  <si>
-    <t>Hidlago vive un momento histórico con finanzas sólidas e inversión récord: Hacienda</t>
-  </si>
-  <si>
-    <t>ariana Seoane y La Casetera hicieron bailar a la feria</t>
-  </si>
-  <si>
-    <t>Recuerda: La detección temprana salva vidas</t>
-  </si>
-  <si>
     <t>Cuenta de Recurso editorial</t>
   </si>
   <si>
@@ -614,6 +344,261 @@
   </si>
   <si>
     <t>Pachuca Brilla</t>
+  </si>
+  <si>
+    <t>A la venta, artesanías de internos del Cereso</t>
+  </si>
+  <si>
+    <t>Sigue protesta contra casas del Fovissste</t>
+  </si>
+  <si>
+    <t>ISSSTE</t>
+  </si>
+  <si>
+    <t>Resalta Henkel más inversión en Hidalgo</t>
+  </si>
+  <si>
+    <t>Acumula 38 demandas La Escuela es Nuestra</t>
+  </si>
+  <si>
+    <t>La Escuela es Nuestra</t>
+  </si>
+  <si>
+    <t>Códice Xólotl narra pasado de Hidalgo</t>
+  </si>
+  <si>
+    <t>INAH</t>
+  </si>
+  <si>
+    <t>Recuperación Del Patrimonio</t>
+  </si>
+  <si>
+    <t>Empleados del IMSS acusan irregularidades</t>
+  </si>
+  <si>
+    <t>Familias piden respuestas ate la CBPEH</t>
+  </si>
+  <si>
+    <t>CBPEH</t>
+  </si>
+  <si>
+    <t>Exigen localización de persona</t>
+  </si>
+  <si>
+    <t>Contraloría indaga casos de nepotismo en Cultura</t>
+  </si>
+  <si>
+    <t>Nepotismo</t>
+  </si>
+  <si>
+    <t>Aceleran compras por Día de Muertos</t>
+  </si>
+  <si>
+    <t>Día De Muertos</t>
+  </si>
+  <si>
+    <t>Se consolidan en Hidalgo 130 proyectos de inversiones</t>
+  </si>
+  <si>
+    <t>Hallan fosa clandestina con cinco cuerpos</t>
+  </si>
+  <si>
+    <t>Fosa clandestina</t>
+  </si>
+  <si>
+    <t>Salud Casa por Casa registra avance de 87%</t>
+  </si>
+  <si>
+    <t>Salud</t>
+  </si>
+  <si>
+    <t>Salud universal</t>
+  </si>
+  <si>
+    <t>Crece rechazo de regidores a ley que liita a los cabildos</t>
+  </si>
+  <si>
+    <t>Noche de goles en la Champions</t>
+  </si>
+  <si>
+    <t>Madurez y persistencia de Abril</t>
+  </si>
+  <si>
+    <t>Exigen avances en indagatorias de las personas desaparecidas</t>
+  </si>
+  <si>
+    <t>Investigarán el presunto nepotismo en Cultura</t>
+  </si>
+  <si>
+    <t>Es Hidalgo 5° lugar por la informalidad laboral: CHE</t>
+  </si>
+  <si>
+    <t>Han sido halladas 22 fosas clandestinas en los últimos 20 años</t>
+  </si>
+  <si>
+    <t>Luis Osorio desea que a Pachuca ""le vaya bien""</t>
+  </si>
+  <si>
+    <t>Bardales: por la Estafa ""los perseguiremos... hasta el fin del mundo""</t>
+  </si>
+  <si>
+    <t>Revelan que son nueve órdenes de aprehensión por la Escuela es Nuestra</t>
+  </si>
+  <si>
+    <t>Prevé Hacienda alza al presupuesto del IEEH, pero no será cheque en blanco</t>
+  </si>
+  <si>
+    <t>Presupuesto IEEH</t>
+  </si>
+  <si>
+    <t>"Ruptura con AMLO, nunca con Claudia"</t>
+  </si>
+  <si>
+    <t>Pachuca: Inicia Tránsito curso para enseñar a conducir bien</t>
+  </si>
+  <si>
+    <t>Policía municipal</t>
+  </si>
+  <si>
+    <t>Curso de manejo</t>
+  </si>
+  <si>
+    <t>En los últimos cuatro años creció la actividad turística en la entidad más de 20%</t>
+  </si>
+  <si>
+    <t>Misión de astrobiólogos: buscan en las supertierras condiciones ""habitables""</t>
+  </si>
+  <si>
+    <t>Premio Carlos Fuentes: Toda autoridad progresista promueve la crítica: Villoro</t>
+  </si>
+  <si>
+    <t>Hallan fosa clandestina en Atotonilco de Tula</t>
+  </si>
+  <si>
+    <t>Control a redes, en 30 días; sanción por incumplimiento</t>
+  </si>
+  <si>
+    <t>Violencia digital</t>
+  </si>
+  <si>
+    <t>Papa celebra misa tras perder parte de un pulmón por cáncer</t>
+  </si>
+  <si>
+    <t>Con farmacéutica canadiense se combatirá desabasto: Henkel</t>
+  </si>
+  <si>
+    <t>Cobijado por diputados petistas en San Lázaro, (Damián Sosa) acusó persecución  política y la politización de la justicia, se dijo decepcionado del gobierno estatal  y autocalificó al Clan Sosa Castelán como la vía para que la transformación llegue  a Hidalgo (…) Los lapsus son padecimiento familiar”.</t>
+  </si>
+  <si>
+    <t>Persecución política</t>
+  </si>
+  <si>
+    <t>Madres buscadoras de Hidalgo exigen agilizar la localización de sus familiares</t>
+  </si>
+  <si>
+    <t>Empresa canadiense deberá construir empresa mexicana para concretar inversión en Zapotlán</t>
+  </si>
+  <si>
+    <t>Encuentran fosa clandestina con 5 cuerpos</t>
+  </si>
+  <si>
+    <t>Hidalgo suma 38 denuncias por manejo irregular de recursos de La Escuela es Nuestra</t>
+  </si>
+  <si>
+    <t>No tuve la intención de dañar al réferi: aclara ""El Hijo de Fishman""</t>
+  </si>
+  <si>
+    <t>Homicidios</t>
+  </si>
+  <si>
+    <t>Descubren fosa clandestina con al menos 5 cuerpos</t>
+  </si>
+  <si>
+    <t>Diputados avalan ley de Ingresos para 2027</t>
+  </si>
+  <si>
+    <t>Ley De Ingresos</t>
+  </si>
+  <si>
+    <t>Tras marchas, Sheinbaum promete solucionar la falta de medicamentos</t>
+  </si>
+  <si>
+    <t>Logra Hidalgo inversiones por más de 147 mil mdp</t>
+  </si>
+  <si>
+    <t>Hidalgo busca hasta 5% más de presupuesto federal para 2027</t>
+  </si>
+  <si>
+    <t>Presupuesto De Egresos</t>
+  </si>
+  <si>
+    <t>"Carlos, escucha, tumadre está en la lucha": Madres buscadoras marchan a la Comisión de Búsqueda de Hidalgo</t>
+  </si>
+  <si>
+    <t>Contraloría de Hidalgo reporta 97 denuncias penales</t>
+  </si>
+  <si>
+    <t>Hidalgo, quinto estado con mayor informalidad laboral: Henkel reconoce rezago histórico</t>
+  </si>
+  <si>
+    <t>Nueva consulta definirá instalación de parques solares en Nopala</t>
+  </si>
+  <si>
+    <t>Iniciará Sebiso segunda entrega de tarjetas a personas cuidadoras</t>
+  </si>
+  <si>
+    <t>Apoyo a personas cuidadoras</t>
+  </si>
+  <si>
+    <t>Localizan cinco cuerpos en fosa clandestina: Hallazgo, tras solicitud de familiares de desaparecidos: Comisión de Búsqueda</t>
+  </si>
+  <si>
+    <t>Menchaca Salazar acompaña a Clara Brugada en Segundo Informe de Actividades</t>
+  </si>
+  <si>
+    <t>Asistencia a informe</t>
+  </si>
+  <si>
+    <t>Gobierno de Hidalgo y agrupaciones religiosas suman esfuerzos por la paz</t>
+  </si>
+  <si>
+    <t>Asuntos religiosos</t>
+  </si>
+  <si>
+    <t>Jorge Reyes acompaña prácticas de conducción responsable para fortalecer la seguridad vial en Pachuca</t>
+  </si>
+  <si>
+    <t>Tezontepec de Aldama realiza primer taller de participación social para el ordenamiento ecológico</t>
+  </si>
+  <si>
+    <t>Ordenamiento ecológico</t>
+  </si>
+  <si>
+    <t>360 millones de pesos en apoyos para familias en situación de emergencia: Es por ti</t>
+  </si>
+  <si>
+    <t>Julión Álvarez arrasa en el Palenque; La Changa y los Jrs. llenaron de baile la feria</t>
+  </si>
+  <si>
+    <t>Destaca Carlos Henkel proyectos insignia y apoyos a la competitividad en Hidalgo</t>
+  </si>
+  <si>
+    <t>Complejo Hidalgo Honesto fortalece la vigilancia del dinero público: Contraloría</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón entregó nuevos espacios educativos en beneficio de estudiantes de Alfajayucan</t>
+  </si>
+  <si>
+    <t>Entrega de infraestructura escolar</t>
+  </si>
+  <si>
+    <t>Jorge Reyes acompaña prácticas de conducción responsable</t>
+  </si>
+  <si>
+    <t>Recuerda: la detección temprana salva vidas</t>
+  </si>
+  <si>
+    <t>318 familias con personas con discapacidad recibieron proyectos productivos: Es por ti</t>
   </si>
 </sst>
 </file>
@@ -746,7 +731,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -768,12 +753,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1714,7 +1705,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DEEED8E4-C61E-4489-B373-2D4A90347DBF}" name="TablaDinámica1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DEEED8E4-C61E-4489-B373-2D4A90347DBF}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:B45" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField numFmtId="164" showAll="0"/>
@@ -1900,21 +1891,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}" name="Tabla1" displayName="Tabla1" ref="A1:J65" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5">
-  <autoFilter ref="A1:J65" xr:uid="{5593606E-308D-4113-AE3C-6E714B763B6E}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Plaza Juárez"/>
-      </filt